--- a/roster.xlsx
+++ b/roster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Unificar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\OneDrive\Documentos\GitHub\Fantasy-unificado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1187" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98A9FAAB-79FD-4040-A383-BC3CF6F16627}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE13B110-0961-40E8-ADDD-DE9F999E2B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="1" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="519">
   <si>
     <t>player_id</t>
   </si>
@@ -1689,10 +1689,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17731,6 +17727,15 @@
       <c r="C28">
         <v>1</v>
       </c>
+      <c r="D28" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="L28" t="str">
         <f>VLOOKUP(B28,players!A:B,2)</f>
         <v>Cam Spencer</v>
@@ -17746,6 +17751,15 @@
       <c r="C29">
         <v>2</v>
       </c>
+      <c r="D29" s="2">
+        <v>23500000</v>
+      </c>
+      <c r="F29" s="2">
+        <v>23500000</v>
+      </c>
+      <c r="H29" s="2">
+        <v>23500000</v>
+      </c>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
         <v>Alperen Şengün</v>
@@ -17761,6 +17775,9 @@
       <c r="C30">
         <v>3</v>
       </c>
+      <c r="D30" s="2">
+        <v>15000000</v>
+      </c>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
         <v>Kevin Durant</v>
@@ -17776,6 +17793,9 @@
       <c r="C31">
         <v>4</v>
       </c>
+      <c r="D31" s="2">
+        <v>9000000</v>
+      </c>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
         <v>Brandon Miller</v>
@@ -17786,14 +17806,23 @@
         <v>2</v>
       </c>
       <c r="B32">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
+      <c r="D32" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="F32" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="H32" s="2">
+        <v>7000000</v>
+      </c>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Jalen Green</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -17806,6 +17835,12 @@
       <c r="C33">
         <v>6</v>
       </c>
+      <c r="D33" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F33" s="2">
+        <v>6000000</v>
+      </c>
       <c r="L33" t="str">
         <f>VLOOKUP(B33,players!A:B,2)</f>
         <v>Tyler Herro</v>
@@ -17821,6 +17856,15 @@
       <c r="C34">
         <v>7</v>
       </c>
+      <c r="D34" s="2">
+        <v>21500000</v>
+      </c>
+      <c r="F34" s="2">
+        <v>21500000</v>
+      </c>
+      <c r="H34" s="2">
+        <v>21500000</v>
+      </c>
       <c r="L34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
         <v>Trae Young</v>
@@ -17846,14 +17890,29 @@
         <v>2</v>
       </c>
       <c r="B36">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C36">
         <v>9</v>
       </c>
+      <c r="D36" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="F36" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H36" s="2">
+        <v>3700000</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="L36" t="str">
         <f>VLOOKUP(B36,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Derik Queen</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -17866,6 +17925,15 @@
       <c r="C37">
         <v>10</v>
       </c>
+      <c r="D37" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F37" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H37" s="2">
+        <v>3100000</v>
+      </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
         <v>Bobby Portis</v>
@@ -17881,6 +17949,15 @@
       <c r="C38">
         <v>11</v>
       </c>
+      <c r="D38" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F38" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
         <v>Zach Edey</v>
@@ -17895,6 +17972,18 @@
       </c>
       <c r="C39">
         <v>12</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H39" s="2">
+        <v>1000000</v>
       </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\OneDrive\Documentos\GitHub\Fantasy-unificado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE13B110-0961-40E8-ADDD-DE9F999E2B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E3F245-36E9-44BF-A98B-03C55C786C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="522">
   <si>
     <t>player_id</t>
   </si>
@@ -1608,6 +1608,15 @@
   </si>
   <si>
     <t>J7R2S2526</t>
+  </si>
+  <si>
+    <t>SF/PF</t>
+  </si>
+  <si>
+    <t>PF/C</t>
+  </si>
+  <si>
+    <t>Clint Capela</t>
   </si>
 </sst>
 </file>
@@ -1667,12 +1676,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2008,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDFA625-895D-46B5-9149-0741A5E1C2FB}">
-  <dimension ref="A1:M416"/>
+  <dimension ref="A1:M417"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -2260,7 +2272,7 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1">
         <v>20.399999999999999</v>
@@ -2486,7 +2498,7 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E15" s="1">
         <v>22.5</v>
@@ -2519,7 +2531,7 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E16" s="1">
         <v>21.8</v>
@@ -2585,7 +2597,7 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E18" s="1">
         <v>27.6</v>
@@ -2649,7 +2661,7 @@
         <v>44</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E20" s="1">
         <v>18.2</v>
@@ -2746,7 +2758,7 @@
         <v>47</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E23" s="1">
         <v>17.100000000000001</v>
@@ -15382,6 +15394,38 @@
         <v>0</v>
       </c>
       <c r="K416" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>416</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E417" s="1">
+        <v>0</v>
+      </c>
+      <c r="F417" s="1">
+        <v>0</v>
+      </c>
+      <c r="G417" s="1">
+        <v>0</v>
+      </c>
+      <c r="H417" s="1">
+        <v>0</v>
+      </c>
+      <c r="I417" s="1">
+        <v>0</v>
+      </c>
+      <c r="J417" s="1">
+        <v>0</v>
+      </c>
+      <c r="K417" s="1">
         <v>0</v>
       </c>
     </row>
@@ -17149,13 +17193,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003E67E5-331D-4CC3-B636-B44F8A41C81C}">
-  <dimension ref="A1:L164"/>
+  <dimension ref="A1:L171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" style="2" customWidth="1"/>
@@ -18000,6 +18044,12 @@
       <c r="C40">
         <v>1</v>
       </c>
+      <c r="D40" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="F40" s="2">
+        <v>8000000</v>
+      </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
         <v>Immanuel Quickley</v>
@@ -18045,6 +18095,9 @@
       <c r="C43">
         <v>4</v>
       </c>
+      <c r="D43" s="2">
+        <v>5000000</v>
+      </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
         <v>Cameron Johnson</v>
@@ -18105,6 +18158,15 @@
       <c r="C47">
         <v>8</v>
       </c>
+      <c r="D47" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F47" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H47" s="2">
+        <v>40000000</v>
+      </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
         <v>Luka Dončić</v>
@@ -18120,6 +18182,9 @@
       <c r="C48">
         <v>9</v>
       </c>
+      <c r="D48" s="2">
+        <v>6000000</v>
+      </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
         <v>Kawhi Leonard</v>
@@ -18135,6 +18200,12 @@
       <c r="C49">
         <v>10</v>
       </c>
+      <c r="D49" s="2">
+        <v>14000000</v>
+      </c>
+      <c r="F49" s="2">
+        <v>14000000</v>
+      </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
         <v>Jaren Jackson Jr.</v>
@@ -18150,6 +18221,15 @@
       <c r="C50">
         <v>11</v>
       </c>
+      <c r="D50" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="F50" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="H50" s="2">
+        <v>6500000</v>
+      </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
         <v>OG Anunoby</v>
@@ -18165,6 +18245,9 @@
       <c r="C51">
         <v>12</v>
       </c>
+      <c r="D51" s="2">
+        <v>5000000</v>
+      </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
         <v>Kyrie Irving</v>
@@ -18172,17 +18255,20 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52">
-        <v>379</v>
+        <v>295</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D52" s="2">
+        <v>8000000</v>
       </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -18190,14 +18276,29 @@
         <v>4</v>
       </c>
       <c r="B53">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F53" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H53" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -18205,14 +18306,23 @@
         <v>4</v>
       </c>
       <c r="B54">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D54" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F54" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -18220,14 +18330,14 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -18235,14 +18345,17 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2500000</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -18250,14 +18363,17 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D57" s="2">
+        <v>11000000</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -18265,14 +18381,20 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D58" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F58" s="2">
+        <v>5000000</v>
       </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -18280,14 +18402,20 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D59" s="2">
+        <v>17000000</v>
+      </c>
+      <c r="F59" s="2">
+        <v>17000000</v>
       </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -18295,14 +18423,17 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C60">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D60" s="2">
+        <v>22500000</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -18310,14 +18441,23 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D61" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F61" s="2">
+        <v>5500000</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -18325,14 +18465,23 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="D62" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="F62" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H62" s="2">
+        <v>15000000</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -18340,29 +18489,41 @@
         <v>4</v>
       </c>
       <c r="B63">
-        <v>287</v>
+        <v>157</v>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D63" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="F63" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="H63" s="2">
+        <v>19000000</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D64" s="2">
+        <v>10000000</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -18370,14 +18531,14 @@
         <v>5</v>
       </c>
       <c r="B65">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -18385,14 +18546,29 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D66" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="F66" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H66" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -18400,14 +18576,14 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>49</v>
+        <v>274</v>
       </c>
       <c r="C67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>Derik Queen</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -18415,14 +18591,20 @@
         <v>5</v>
       </c>
       <c r="B68">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D68" s="2">
+        <v>21000000</v>
+      </c>
+      <c r="F68" s="2">
+        <v>21000000</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -18430,14 +18612,14 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -18445,14 +18627,29 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D70" s="2">
+        <v>2800000</v>
+      </c>
+      <c r="F70" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H70" s="2">
+        <v>3300000</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>Collin Murray-Boyles</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -18460,14 +18657,20 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C71">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D71" s="2">
+        <v>17000000</v>
+      </c>
+      <c r="F71" s="2">
+        <v>17000000</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -18475,14 +18678,23 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="C72">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D72" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F72" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H72" s="2">
+        <v>40000000</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>VJ Edgecombe</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -18490,14 +18702,20 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>219</v>
+        <v>72</v>
       </c>
       <c r="C73">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D73" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F73" s="2">
+        <v>3100000</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Jalen Green</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -18505,14 +18723,14 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="C74">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -18520,44 +18738,44 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>238</v>
+        <v>48</v>
       </c>
       <c r="C75">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B76">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B77">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -18565,14 +18783,20 @@
         <v>6</v>
       </c>
       <c r="B78">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D78" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F78" s="2">
+        <v>6000000</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -18580,14 +18804,17 @@
         <v>6</v>
       </c>
       <c r="B79">
-        <v>122</v>
+        <v>338</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D79" s="2">
+        <v>1000000</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -18595,14 +18822,14 @@
         <v>6</v>
       </c>
       <c r="B80">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -18610,14 +18837,14 @@
         <v>6</v>
       </c>
       <c r="B81">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -18625,14 +18852,14 @@
         <v>6</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -18640,14 +18867,14 @@
         <v>6</v>
       </c>
       <c r="B83">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -18655,14 +18882,17 @@
         <v>6</v>
       </c>
       <c r="B84">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D84" s="2">
+        <v>20000000</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -18670,14 +18900,14 @@
         <v>6</v>
       </c>
       <c r="B85">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -18685,14 +18915,17 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C86">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="D86" s="2">
+        <v>7000000</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -18700,89 +18933,110 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="C87">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D87" s="2">
+        <v>35000000</v>
+      </c>
+      <c r="F87" s="2">
+        <v>35000000</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B88">
-        <v>242</v>
+        <v>56</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D88" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F88" s="2">
+        <v>3100000</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B89">
-        <v>154</v>
+        <v>211</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="D89" s="2">
+        <v>1000000</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B90">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B91">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C91">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="D91" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F91" s="2">
+        <v>6000000</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B92">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -18790,14 +19044,23 @@
         <v>8</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>242</v>
       </c>
       <c r="C93">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D93" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="F93" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -18805,14 +19068,14 @@
         <v>8</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -18820,14 +19083,29 @@
         <v>8</v>
       </c>
       <c r="B95">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="D95" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F95" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H95" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -18835,14 +19113,17 @@
         <v>8</v>
       </c>
       <c r="B96">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C96">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="D96" s="2">
+        <v>2000000</v>
       </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -18850,14 +19131,23 @@
         <v>8</v>
       </c>
       <c r="B97">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="C97">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D97" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F97" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H97" s="2">
+        <v>6000000</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -18865,14 +19155,23 @@
         <v>8</v>
       </c>
       <c r="B98">
-        <v>203</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="D98" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="F98" s="2">
+        <v>7500000</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -18880,119 +19179,152 @@
         <v>8</v>
       </c>
       <c r="B99">
-        <v>225</v>
+        <v>5</v>
       </c>
       <c r="C99">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="D99" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="F99" s="2">
+        <v>4000000</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B100">
-        <v>384</v>
+        <v>14</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D100" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="F100" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="H100" s="2">
+        <v>16000000</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
+        <v>8</v>
+      </c>
+      <c r="B101">
+        <v>83</v>
+      </c>
+      <c r="C101">
         <v>9</v>
       </c>
-      <c r="B101">
-        <v>240</v>
-      </c>
-      <c r="C101">
-        <v>2</v>
+      <c r="D101" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="F101" s="2">
+        <v>9000000</v>
       </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B102">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="C102">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="D102" s="2">
+        <v>16000000</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B103">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="C103">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="D103" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="F103" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="H103" s="2">
+        <v>19000000</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B104">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="C104">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B105">
-        <v>263</v>
+        <v>59</v>
       </c>
       <c r="C105">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Ousmane Dieng</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B106">
-        <v>15</v>
+        <v>336</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -19000,14 +19332,23 @@
         <v>9</v>
       </c>
       <c r="B107">
-        <v>26</v>
+        <v>384</v>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="D107" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F107" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H107" s="2">
+        <v>3100000</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -19015,14 +19356,14 @@
         <v>9</v>
       </c>
       <c r="B108">
-        <v>89</v>
+        <v>240</v>
       </c>
       <c r="C108">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -19030,14 +19371,17 @@
         <v>9</v>
       </c>
       <c r="B109">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C109">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="D109" s="2">
+        <v>4500000</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -19045,14 +19389,14 @@
         <v>9</v>
       </c>
       <c r="B110">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="C110">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -19060,209 +19404,257 @@
         <v>9</v>
       </c>
       <c r="B111">
-        <v>331</v>
+        <v>416</v>
       </c>
       <c r="C111">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B112">
-        <v>303</v>
+        <v>170</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D112" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F112" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H112" s="2">
+        <v>3100000</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Scoot Henderson</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B113">
-        <v>373</v>
+        <v>15</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="D113" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="F113" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="H113" s="2">
+        <v>32000000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B114">
-        <v>249</v>
+        <v>26</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="D114" s="2">
+        <v>12500000</v>
+      </c>
+      <c r="F114" s="2">
+        <v>12500000</v>
+      </c>
+      <c r="H114" s="2">
+        <v>12500000</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B115">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="C115">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="D115" s="2">
+        <v>11500000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116">
+        <v>9</v>
+      </c>
+      <c r="B116">
+        <v>167</v>
+      </c>
+      <c r="C116">
         <v>10</v>
       </c>
-      <c r="B116">
-        <v>34</v>
-      </c>
-      <c r="C116">
-        <v>5</v>
+      <c r="D116" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F116" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H116" s="2">
+        <v>3100000</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B117">
-        <v>168</v>
+        <v>217</v>
       </c>
       <c r="C117">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="D117" s="2">
+        <v>25000000</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B118">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D118" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="F118" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H118" s="2">
+        <v>12000000</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>11</v>
-      </c>
-      <c r="B119">
-        <v>213</v>
+        <v>10</v>
       </c>
       <c r="C119">
-        <v>2</v>
-      </c>
-      <c r="L119" t="str">
+        <v>1</v>
+      </c>
+      <c r="L119" t="e">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B120">
-        <v>111</v>
+        <v>373</v>
       </c>
       <c r="C120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B121">
-        <v>58</v>
+        <v>249</v>
       </c>
       <c r="C121">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B122">
-        <v>18</v>
+        <v>169</v>
       </c>
       <c r="C122">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B123">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C123">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B124">
+        <v>168</v>
+      </c>
+      <c r="C124">
         <v>6</v>
-      </c>
-      <c r="C124">
-        <v>7</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -19270,14 +19662,14 @@
         <v>11</v>
       </c>
       <c r="B125">
-        <v>177</v>
+        <v>327</v>
       </c>
       <c r="C125">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -19285,14 +19677,14 @@
         <v>11</v>
       </c>
       <c r="B126">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="C126">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -19300,14 +19692,14 @@
         <v>11</v>
       </c>
       <c r="B127">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="C127">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -19315,14 +19707,14 @@
         <v>11</v>
       </c>
       <c r="B128">
-        <v>248</v>
+        <v>58</v>
       </c>
       <c r="C128">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -19330,119 +19722,119 @@
         <v>11</v>
       </c>
       <c r="B129">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="C129">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B130">
-        <v>279</v>
+        <v>63</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Cody Williams</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B131">
-        <v>345</v>
+        <v>6</v>
       </c>
       <c r="C131">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B132">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="C132">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Yves Missi</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B133">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="C133">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B134">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="C134">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Goga Bitadze</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B135">
-        <v>132</v>
+        <v>248</v>
       </c>
       <c r="C135">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Micah Potter</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136">
+        <v>11</v>
+      </c>
+      <c r="B136">
+        <v>109</v>
+      </c>
+      <c r="C136">
         <v>12</v>
-      </c>
-      <c r="B136">
-        <v>22</v>
-      </c>
-      <c r="C136">
-        <v>7</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -19450,14 +19842,14 @@
         <v>12</v>
       </c>
       <c r="B137">
-        <v>54</v>
+        <v>279</v>
       </c>
       <c r="C137">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Cody Williams</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -19465,14 +19857,14 @@
         <v>12</v>
       </c>
       <c r="B138">
-        <v>194</v>
+        <v>345</v>
       </c>
       <c r="C138">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -19480,14 +19872,14 @@
         <v>12</v>
       </c>
       <c r="B139">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="C139">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Yves Missi</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -19495,119 +19887,119 @@
         <v>12</v>
       </c>
       <c r="B140">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C140">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B141">
-        <v>307</v>
+        <v>135</v>
       </c>
       <c r="C141">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Goga Bitadze</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B142">
-        <v>363</v>
+        <v>132</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Micah Potter</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B143">
-        <v>296</v>
+        <v>22</v>
       </c>
       <c r="C143">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B144">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="C144">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B145">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="C145">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B146">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="C146">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B147">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -19615,14 +20007,14 @@
         <v>13</v>
       </c>
       <c r="B148">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="C148">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -19630,14 +20022,14 @@
         <v>13</v>
       </c>
       <c r="B149">
-        <v>55</v>
+        <v>363</v>
       </c>
       <c r="C149">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -19645,14 +20037,14 @@
         <v>13</v>
       </c>
       <c r="B150">
-        <v>66</v>
+        <v>296</v>
       </c>
       <c r="C150">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -19660,14 +20052,14 @@
         <v>13</v>
       </c>
       <c r="B151">
-        <v>94</v>
+        <v>171</v>
       </c>
       <c r="C151">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Zach Collins</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -19675,119 +20067,119 @@
         <v>13</v>
       </c>
       <c r="B152">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="C152">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B153">
-        <v>317</v>
+        <v>46</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B154">
-        <v>241</v>
+        <v>4</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Dylan Harper</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B155">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="C155">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B156">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="C156">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B157">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C157">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B158">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C158">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Toumani Camara</v>
+        <v>Zach Collins</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B159">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="C159">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -19795,14 +20187,14 @@
         <v>14</v>
       </c>
       <c r="B160">
-        <v>73</v>
+        <v>317</v>
       </c>
       <c r="C160">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -19810,14 +20202,14 @@
         <v>14</v>
       </c>
       <c r="B161">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="C161">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>Dylan Harper</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -19825,14 +20217,14 @@
         <v>14</v>
       </c>
       <c r="B162">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="C162">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -19840,14 +20232,14 @@
         <v>14</v>
       </c>
       <c r="B163">
-        <v>220</v>
+        <v>93</v>
       </c>
       <c r="C163">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -19855,13 +20247,118 @@
         <v>14</v>
       </c>
       <c r="B164">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="C164">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
+        <v>Moussa Diabaté</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>14</v>
+      </c>
+      <c r="B165">
+        <v>121</v>
+      </c>
+      <c r="C165">
+        <v>6</v>
+      </c>
+      <c r="L165" t="str">
+        <f>VLOOKUP(B165,players!A:B,2)</f>
+        <v>Toumani Camara</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>14</v>
+      </c>
+      <c r="B166">
+        <v>19</v>
+      </c>
+      <c r="C166">
+        <v>7</v>
+      </c>
+      <c r="L166" t="str">
+        <f>VLOOKUP(B166,players!A:B,2)</f>
+        <v>Evan Mobley</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>14</v>
+      </c>
+      <c r="B167">
+        <v>73</v>
+      </c>
+      <c r="C167">
+        <v>8</v>
+      </c>
+      <c r="L167" t="str">
+        <f>VLOOKUP(B167,players!A:B,2)</f>
+        <v>LeBron James</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>14</v>
+      </c>
+      <c r="B168">
+        <v>61</v>
+      </c>
+      <c r="C168">
+        <v>9</v>
+      </c>
+      <c r="L168" t="str">
+        <f>VLOOKUP(B168,players!A:B,2)</f>
+        <v>Cooper Flagg</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>14</v>
+      </c>
+      <c r="B169">
+        <v>2</v>
+      </c>
+      <c r="C169">
+        <v>10</v>
+      </c>
+      <c r="L169" t="str">
+        <f>VLOOKUP(B169,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>14</v>
+      </c>
+      <c r="B170">
+        <v>220</v>
+      </c>
+      <c r="C170">
+        <v>11</v>
+      </c>
+      <c r="L170" t="str">
+        <f>VLOOKUP(B170,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>14</v>
+      </c>
+      <c r="B171">
+        <v>145</v>
+      </c>
+      <c r="C171">
+        <v>12</v>
+      </c>
+      <c r="L171" t="str">
+        <f>VLOOKUP(B171,players!A:B,2)</f>
         <v>LaMelo Ball</v>
       </c>
     </row>
@@ -19873,7 +20370,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B357A823-6505-4984-ACC9-40636E218B6C}">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L165"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
@@ -19881,6 +20378,7 @@
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -19917,6 +20415,9 @@
       <c r="K1" t="s">
         <v>460</v>
       </c>
+      <c r="L1" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -19942,7 +20443,10 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="L2" t="str">
+        <f>VLOOKUP(B2,players!A:B,2)</f>
+        <v>Rob Dillingham</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -19968,7 +20472,10 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="L3" t="str">
+        <f>VLOOKUP(B3,players!A:B,2)</f>
+        <v>Tristan Da Silva</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -19994,7 +20501,10 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="L4" t="str">
+        <f>VLOOKUP(B4,players!A:B,2)</f>
+        <v>Isaiah Collier</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -20024,7 +20534,10 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
+      <c r="L5" t="str">
+        <f>VLOOKUP(B5,players!A:B,2)</f>
+        <v>Ryan Kalkbrenner</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -20056,7 +20569,10 @@
       <c r="K6" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="L6" s="2"/>
+      <c r="L6" t="str">
+        <f>VLOOKUP(B6,players!A:B,2)</f>
+        <v>Jeremiah Fears</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -20078,7 +20594,10 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="L7" t="str">
+        <f>VLOOKUP(B7,players!A:B,2)</f>
+        <v>Gradey Dick</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -20108,7 +20627,10 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="L8" t="str">
+        <f>VLOOKUP(B8,players!A:B,2)</f>
+        <v>Walter Clayton</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -20134,7 +20656,10 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="L9" t="str">
+        <f>VLOOKUP(B9,players!A:B,2)</f>
+        <v>Johnny Furphy</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -20164,7 +20689,10 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="L10" t="str">
+        <f>VLOOKUP(B10,players!A:B,2)</f>
+        <v>Nikola Topić</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -20190,14 +20718,17 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="L11" t="str">
+        <f>VLOOKUP(B11,players!A:B,2)</f>
+        <v>Jase Richardson</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12">
-        <v>305</v>
+        <v>92</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -20220,14 +20751,17 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="L12" t="str">
+        <f>VLOOKUP(B12,players!A:B,2)</f>
+        <v>VJ Edgecombe</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>5</v>
       </c>
       <c r="B13">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -20250,14 +20784,17 @@
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="L13" t="str">
+        <f>VLOOKUP(B13,players!A:B,2)</f>
+        <v>Danny Wolf</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -20280,7 +20817,10 @@
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="L14" t="str">
+        <f>VLOOKUP(B14,players!A:B,2)</f>
+        <v>Nique Clifford</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -20310,7 +20850,10 @@
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="L15" t="str">
+        <f>VLOOKUP(B15,players!A:B,2)</f>
+        <v>Hansen Yang</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -20336,7 +20879,10 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="L16" t="str">
+        <f>VLOOKUP(B16,players!A:B,2)</f>
+        <v>Tidjane Salaün</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
@@ -20362,7 +20908,10 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="L17" t="str">
+        <f>VLOOKUP(B17,players!A:B,2)</f>
+        <v>Kyle Filipowski</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
@@ -20392,7 +20941,10 @@
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+      <c r="L18" t="str">
+        <f>VLOOKUP(B18,players!A:B,2)</f>
+        <v>Kon Knueppel</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
@@ -20418,7 +20970,10 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+      <c r="L19" t="str">
+        <f>VLOOKUP(B19,players!A:B,2)</f>
+        <v>Jaylon Tyson</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
@@ -20444,7 +20999,10 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
+      <c r="L20" t="str">
+        <f>VLOOKUP(B20,players!A:B,2)</f>
+        <v>Joan Beringer</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
@@ -20474,7 +21032,10 @@
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
+      <c r="L21" t="str">
+        <f>VLOOKUP(B21,players!A:B,2)</f>
+        <v>Tre Johnson</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
@@ -20498,7 +21059,10 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+      <c r="L22" t="str">
+        <f>VLOOKUP(B22,players!A:B,2)</f>
+        <v>Ja'Kobe Walter</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -20520,7 +21084,10 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
+      <c r="L23" t="str">
+        <f>VLOOKUP(B23,players!A:B,2)</f>
+        <v>Cam Whitmore</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -20550,7 +21117,10 @@
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="L24" t="str">
+        <f>VLOOKUP(B24,players!A:B,2)</f>
+        <v>Thomas Sorber</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -20576,7 +21146,10 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="L25" t="str">
+        <f>VLOOKUP(B25,players!A:B,2)</f>
+        <v>Carter Bryant</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
@@ -20598,7 +21171,10 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="L26" t="str">
+        <f>VLOOKUP(B26,players!A:B,2)</f>
+        <v>Dalton Knecht</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
@@ -20620,7 +21196,10 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="L27" t="str">
+        <f>VLOOKUP(B27,players!A:B,2)</f>
+        <v>Ron Holland</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -20646,7 +21225,10 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
+      <c r="L28" t="str">
+        <f>VLOOKUP(B28,players!A:B,2)</f>
+        <v>Devin Carter</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
@@ -20676,7 +21258,10 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
+      <c r="L29" t="str">
+        <f>VLOOKUP(B29,players!A:B,2)</f>
+        <v>Kaman Maluach</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
@@ -20706,7 +21291,10 @@
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
+      <c r="L30" t="str">
+        <f>VLOOKUP(B30,players!A:B,2)</f>
+        <v>Dylan Harper</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
@@ -20730,7 +21318,10 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
+      <c r="L31" t="str">
+        <f>VLOOKUP(B31,players!A:B,2)</f>
+        <v>Cason Wallace</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -20752,7 +21343,10 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
+      <c r="L32" t="str">
+        <f>VLOOKUP(B32,players!A:B,2)</f>
+        <v>Jaylen Wells</v>
+      </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
@@ -20782,7 +21376,802 @@
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
+      <c r="L33" t="str">
+        <f>VLOOKUP(B33,players!A:B,2)</f>
+        <v>Noah Essengue</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L34" t="e">
+        <f>VLOOKUP(B34,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L35" t="e">
+        <f>VLOOKUP(B35,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L36" t="e">
+        <f>VLOOKUP(B36,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L37" t="e">
+        <f>VLOOKUP(B37,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L38" t="e">
+        <f>VLOOKUP(B38,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L39" t="e">
+        <f>VLOOKUP(B39,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L40" t="e">
+        <f>VLOOKUP(B40,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L41" t="e">
+        <f>VLOOKUP(B41,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L42" t="e">
+        <f>VLOOKUP(B42,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L43" t="e">
+        <f>VLOOKUP(B43,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L44" t="e">
+        <f>VLOOKUP(B44,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L45" t="e">
+        <f>VLOOKUP(B45,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L46" t="e">
+        <f>VLOOKUP(B46,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L47" t="e">
+        <f>VLOOKUP(B47,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L48" t="e">
+        <f>VLOOKUP(B48,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="49" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L49" t="e">
+        <f>VLOOKUP(B49,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="50" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L50" t="e">
+        <f>VLOOKUP(B50,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="51" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L51" t="e">
+        <f>VLOOKUP(B51,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="52" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L52" t="e">
+        <f>VLOOKUP(B52,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="53" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L53" t="e">
+        <f>VLOOKUP(B53,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="54" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L54" t="e">
+        <f>VLOOKUP(B54,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="55" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L55" t="e">
+        <f>VLOOKUP(B55,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="56" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L56" t="e">
+        <f>VLOOKUP(B56,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="57" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L57" t="e">
+        <f>VLOOKUP(B57,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="58" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L58" t="e">
+        <f>VLOOKUP(B58,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="59" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L59" t="e">
+        <f>VLOOKUP(B59,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="60" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L60" t="e">
+        <f>VLOOKUP(B60,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="61" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L61" t="e">
+        <f>VLOOKUP(B61,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="62" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L62" t="e">
+        <f>VLOOKUP(B62,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="63" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L63" t="e">
+        <f>VLOOKUP(B63,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="64" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L64" t="e">
+        <f>VLOOKUP(B64,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="65" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L65" t="e">
+        <f>VLOOKUP(B65,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="66" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L66" t="e">
+        <f>VLOOKUP(B66,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="67" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L67" t="e">
+        <f>VLOOKUP(B67,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="68" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L68" t="e">
+        <f>VLOOKUP(B68,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="69" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L69" t="e">
+        <f>VLOOKUP(B69,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="70" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L70" t="e">
+        <f>VLOOKUP(B70,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="71" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L71" t="e">
+        <f>VLOOKUP(B71,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="72" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L72" t="e">
+        <f>VLOOKUP(B72,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="73" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L73" t="e">
+        <f>VLOOKUP(B73,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="74" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L74" t="e">
+        <f>VLOOKUP(B74,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="75" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L75" t="e">
+        <f>VLOOKUP(B75,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="76" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L76" t="e">
+        <f>VLOOKUP(B76,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="77" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L77" t="e">
+        <f>VLOOKUP(B77,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="78" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L78" t="e">
+        <f>VLOOKUP(B78,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="79" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L79" t="e">
+        <f>VLOOKUP(B79,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="80" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L80" t="e">
+        <f>VLOOKUP(B80,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="81" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L81" t="e">
+        <f>VLOOKUP(B81,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="82" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L82" t="e">
+        <f>VLOOKUP(B82,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L83" t="e">
+        <f>VLOOKUP(B83,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="84" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L84" t="e">
+        <f>VLOOKUP(B84,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="85" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L85" t="e">
+        <f>VLOOKUP(B85,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="86" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L86" t="e">
+        <f>VLOOKUP(B86,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="87" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L87" t="e">
+        <f>VLOOKUP(B87,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="88" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L88" t="e">
+        <f>VLOOKUP(B88,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="89" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L89" t="e">
+        <f>VLOOKUP(B89,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="90" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L90" t="e">
+        <f>VLOOKUP(B90,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="91" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L91" t="e">
+        <f>VLOOKUP(B91,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="92" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L92" t="e">
+        <f>VLOOKUP(B92,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="93" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L93" t="e">
+        <f>VLOOKUP(B93,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="94" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L94" t="e">
+        <f>VLOOKUP(B94,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="95" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L95" t="e">
+        <f>VLOOKUP(B95,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="96" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L96" t="e">
+        <f>VLOOKUP(B96,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="97" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L97" t="e">
+        <f>VLOOKUP(B97,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="98" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L98" t="e">
+        <f>VLOOKUP(B98,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="99" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L99" t="e">
+        <f>VLOOKUP(B99,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="100" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L100" t="e">
+        <f>VLOOKUP(B100,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="101" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L101" t="e">
+        <f>VLOOKUP(B101,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="102" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L102" t="e">
+        <f>VLOOKUP(B102,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="103" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L103" t="e">
+        <f>VLOOKUP(B103,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="104" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L104" t="e">
+        <f>VLOOKUP(B104,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="105" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L105" t="e">
+        <f>VLOOKUP(B105,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="106" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L106" t="e">
+        <f>VLOOKUP(B106,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="107" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L107" t="e">
+        <f>VLOOKUP(B107,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="108" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L108" t="e">
+        <f>VLOOKUP(B108,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="109" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L109" t="e">
+        <f>VLOOKUP(B109,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="110" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L110" t="e">
+        <f>VLOOKUP(B110,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="111" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L111" t="e">
+        <f>VLOOKUP(B111,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="112" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L112" t="e">
+        <f>VLOOKUP(B112,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="113" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L113" t="e">
+        <f>VLOOKUP(B113,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="114" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L114" t="e">
+        <f>VLOOKUP(B114,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="115" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L115" t="e">
+        <f>VLOOKUP(B115,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="116" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L116" t="e">
+        <f>VLOOKUP(B116,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="117" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L117" t="e">
+        <f>VLOOKUP(B117,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="118" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L118" t="e">
+        <f>VLOOKUP(B118,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="119" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L119" t="e">
+        <f>VLOOKUP(B119,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="120" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L120" t="e">
+        <f>VLOOKUP(B120,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="121" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L121" t="e">
+        <f>VLOOKUP(B121,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="122" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L122" t="e">
+        <f>VLOOKUP(B122,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="123" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L123" t="e">
+        <f>VLOOKUP(B123,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="124" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L124" t="e">
+        <f>VLOOKUP(B124,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="125" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L125" t="e">
+        <f>VLOOKUP(B125,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="126" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L126" t="e">
+        <f>VLOOKUP(B126,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="127" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L127" t="e">
+        <f>VLOOKUP(B127,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="128" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L128" t="e">
+        <f>VLOOKUP(B128,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="129" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L129" t="e">
+        <f>VLOOKUP(B129,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="130" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L130" t="e">
+        <f>VLOOKUP(B130,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="131" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L131" t="e">
+        <f>VLOOKUP(B131,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="132" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L132" t="e">
+        <f>VLOOKUP(B132,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="133" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L133" t="e">
+        <f>VLOOKUP(B133,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="134" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L134" t="e">
+        <f>VLOOKUP(B134,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="135" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L135" t="e">
+        <f>VLOOKUP(B135,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="136" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L136" t="e">
+        <f>VLOOKUP(B136,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="137" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L137" t="e">
+        <f>VLOOKUP(B137,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="138" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L138" t="e">
+        <f>VLOOKUP(B138,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="139" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L139" t="e">
+        <f>VLOOKUP(B139,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="140" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L140" t="e">
+        <f>VLOOKUP(B140,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="141" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L141" t="e">
+        <f>VLOOKUP(B141,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="142" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L142" t="e">
+        <f>VLOOKUP(B142,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="143" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L143" t="e">
+        <f>VLOOKUP(B143,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="144" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L144" t="e">
+        <f>VLOOKUP(B144,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="145" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L145" t="e">
+        <f>VLOOKUP(B145,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="146" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L146" t="e">
+        <f>VLOOKUP(B146,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="147" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L147" t="e">
+        <f>VLOOKUP(B147,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="148" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L148" t="e">
+        <f>VLOOKUP(B148,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="149" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L149" t="e">
+        <f>VLOOKUP(B149,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="150" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L150" t="e">
+        <f>VLOOKUP(B150,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="151" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L151" t="e">
+        <f>VLOOKUP(B151,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="152" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L152" t="e">
+        <f>VLOOKUP(B152,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="153" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L153" t="e">
+        <f>VLOOKUP(B153,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="154" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L154" t="e">
+        <f>VLOOKUP(B154,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="155" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L155" t="e">
+        <f>VLOOKUP(B155,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="156" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L156" t="e">
+        <f>VLOOKUP(B156,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="157" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L157" t="e">
+        <f>VLOOKUP(B157,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="158" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L158" t="e">
+        <f>VLOOKUP(B158,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="159" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L159" t="e">
+        <f>VLOOKUP(B159,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="160" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L160" t="e">
+        <f>VLOOKUP(B160,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="161" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L161" t="e">
+        <f>VLOOKUP(B161,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="162" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L162" t="e">
+        <f>VLOOKUP(B162,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="163" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L163" t="e">
+        <f>VLOOKUP(B163,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="164" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L164" t="e">
+        <f>VLOOKUP(B164,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="165" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L165" t="e">
+        <f>VLOOKUP(B165,players!A:B,2)</f>
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\OneDrive\Documentos\GitHub\Fantasy-unificado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E3F245-36E9-44BF-A98B-03C55C786C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="4" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="522">
   <si>
     <t>player_id</t>
   </si>
@@ -17193,7 +17193,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003E67E5-331D-4CC3-B636-B44F8A41C81C}">
-  <dimension ref="A1:L171"/>
+  <dimension ref="A1:L176"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -17203,7 +17203,7 @@
     <col min="5" max="5" width="7.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" style="2" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" style="2" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="14" style="2" hidden="1" customWidth="1"/>
@@ -19574,12 +19574,15 @@
       <c r="A119">
         <v>10</v>
       </c>
+      <c r="B119">
+        <v>9</v>
+      </c>
       <c r="C119">
         <v>1</v>
       </c>
-      <c r="L119" t="e">
+      <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>#N/A</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -19622,6 +19625,9 @@
       <c r="C122">
         <v>4</v>
       </c>
+      <c r="D122" s="2">
+        <v>4100000</v>
+      </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
         <v>Bilal Coulibaly</v>
@@ -19637,6 +19643,12 @@
       <c r="C123">
         <v>5</v>
       </c>
+      <c r="D123" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F123" s="2">
+        <v>6000000</v>
+      </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
         <v>Mark Williams</v>
@@ -19652,6 +19664,9 @@
       <c r="C124">
         <v>6</v>
       </c>
+      <c r="D124" s="2">
+        <v>1000000</v>
+      </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
         <v>GG Jackson II</v>
@@ -19659,92 +19674,128 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B125">
-        <v>327</v>
+        <v>28</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B126">
-        <v>213</v>
+        <v>44</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="D126" s="2">
+        <v>9250000</v>
+      </c>
+      <c r="F126" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B127">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="C127">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="D127" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="F127" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H127" s="2">
+        <v>15000000</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B128">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="C128">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="D128" s="2">
+        <v>11000000</v>
+      </c>
+      <c r="F128" s="2">
+        <v>11000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129">
+        <v>10</v>
+      </c>
+      <c r="B129">
+        <v>160</v>
+      </c>
+      <c r="C129">
         <v>11</v>
       </c>
-      <c r="B129">
-        <v>18</v>
-      </c>
-      <c r="C129">
-        <v>5</v>
+      <c r="D129" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="F129" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="H129" s="2">
+        <v>16000000</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B130">
-        <v>63</v>
+        <v>246</v>
       </c>
       <c r="C130">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="D130" s="2">
+        <v>24000000</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -19752,14 +19803,14 @@
         <v>11</v>
       </c>
       <c r="B131">
-        <v>6</v>
+        <v>327</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -19767,14 +19818,14 @@
         <v>11</v>
       </c>
       <c r="B132">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="C132">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -19782,14 +19833,17 @@
         <v>11</v>
       </c>
       <c r="B133">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="C133">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="D133" s="2">
+        <v>1000000</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -19797,14 +19851,14 @@
         <v>11</v>
       </c>
       <c r="B134">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="C134">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -19812,14 +19866,17 @@
         <v>11</v>
       </c>
       <c r="B135">
-        <v>248</v>
+        <v>18</v>
       </c>
       <c r="C135">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="D135" s="2">
+        <v>1000000</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -19827,134 +19884,155 @@
         <v>11</v>
       </c>
       <c r="B136">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="C136">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B137">
-        <v>279</v>
+        <v>6</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D137" s="2">
+        <v>26000000</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Cody Williams</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B138">
-        <v>345</v>
+        <v>177</v>
       </c>
       <c r="C138">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="D138" s="2">
+        <v>15000000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B139">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="C139">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="D139" s="2">
+        <v>7500000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Yves Missi</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B140">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="C140">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="D140" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="F140" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="H140" s="2">
+        <v>30000000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B141">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="C141">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="D141" s="2">
+        <v>1000000</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Goga Bitadze</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142">
+        <v>11</v>
+      </c>
+      <c r="B142">
+        <v>109</v>
+      </c>
+      <c r="C142">
         <v>12</v>
-      </c>
-      <c r="B142">
-        <v>132</v>
-      </c>
-      <c r="C142">
-        <v>6</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Micah Potter</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B143">
-        <v>22</v>
+        <v>266</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B144">
-        <v>54</v>
+        <v>195</v>
       </c>
       <c r="C144">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -19962,14 +20040,20 @@
         <v>12</v>
       </c>
       <c r="B145">
-        <v>194</v>
+        <v>403</v>
       </c>
       <c r="C145">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="D145" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F145" s="2">
+        <v>5000000</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -19977,14 +20061,20 @@
         <v>12</v>
       </c>
       <c r="B146">
-        <v>226</v>
+        <v>345</v>
       </c>
       <c r="C146">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="D146" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="F146" s="2">
+        <v>3500000</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -19992,89 +20082,113 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C147">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="D147" s="2">
+        <v>1000000</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B148">
-        <v>307</v>
+        <v>22</v>
       </c>
       <c r="C148">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B149">
-        <v>363</v>
+        <v>54</v>
       </c>
       <c r="C149">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D149" s="2">
+        <v>11000000</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B150">
-        <v>296</v>
+        <v>194</v>
       </c>
       <c r="C150">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D150" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="F150" s="2">
+        <v>20000000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B151">
-        <v>171</v>
+        <v>226</v>
       </c>
       <c r="C151">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D151" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="F151" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="H151" s="2">
+        <v>18000000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B152">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="C152">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D152" s="2">
+        <v>2500000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -20082,14 +20196,17 @@
         <v>13</v>
       </c>
       <c r="B153">
-        <v>46</v>
+        <v>307</v>
       </c>
       <c r="C153">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D153" s="2">
+        <v>1000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -20097,14 +20214,14 @@
         <v>13</v>
       </c>
       <c r="B154">
-        <v>4</v>
+        <v>363</v>
       </c>
       <c r="C154">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -20112,14 +20229,17 @@
         <v>13</v>
       </c>
       <c r="B155">
-        <v>32</v>
+        <v>296</v>
       </c>
       <c r="C155">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="D155" s="2">
+        <v>3000000</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -20127,14 +20247,17 @@
         <v>13</v>
       </c>
       <c r="B156">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="C156">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="D156" s="2">
+        <v>2000000</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -20142,14 +20265,14 @@
         <v>13</v>
       </c>
       <c r="B157">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="C157">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -20157,14 +20280,14 @@
         <v>13</v>
       </c>
       <c r="B158">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="C158">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Zach Collins</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -20172,89 +20295,125 @@
         <v>13</v>
       </c>
       <c r="B159">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="C159">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="D159" s="2">
+        <v>11500000</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B160">
-        <v>317</v>
+        <v>32</v>
       </c>
       <c r="C160">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D160" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="F160" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="H160" s="2">
+        <v>16000000</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B161">
-        <v>241</v>
+        <v>55</v>
       </c>
       <c r="C161">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="D161" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="F161" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H161" s="2">
+        <v>12000000</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Dylan Harper</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B162">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="C162">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="D162" s="2">
+        <v>19000000</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B163">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C163">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="D163" s="2">
+        <v>1000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Zach Collins</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B164">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="C164">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="D164" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F164" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H164" s="2">
+        <v>6000000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -20262,14 +20421,14 @@
         <v>14</v>
       </c>
       <c r="B165">
-        <v>121</v>
+        <v>317</v>
       </c>
       <c r="C165">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Toumani Camara</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -20277,14 +20436,14 @@
         <v>14</v>
       </c>
       <c r="B166">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="C166">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -20292,14 +20451,14 @@
         <v>14</v>
       </c>
       <c r="B167">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C167">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -20307,14 +20466,14 @@
         <v>14</v>
       </c>
       <c r="B168">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C168">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -20322,14 +20481,17 @@
         <v>14</v>
       </c>
       <c r="B169">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C169">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D169" s="2">
+        <v>1000000</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -20337,14 +20499,17 @@
         <v>14</v>
       </c>
       <c r="B170">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C170">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="D170" s="2">
+        <v>3000000</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -20352,13 +20517,124 @@
         <v>14</v>
       </c>
       <c r="B171">
-        <v>145</v>
+        <v>19</v>
       </c>
       <c r="C171">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="D171" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="F171" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="H171" s="2">
+        <v>20500000</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
+        <v>Evan Mobley</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>14</v>
+      </c>
+      <c r="B172">
+        <v>73</v>
+      </c>
+      <c r="C172">
+        <v>8</v>
+      </c>
+      <c r="D172" s="2">
+        <v>19500000</v>
+      </c>
+      <c r="L172" t="str">
+        <f>VLOOKUP(B172,players!A:B,2)</f>
+        <v>LeBron James</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>14</v>
+      </c>
+      <c r="B173">
+        <v>61</v>
+      </c>
+      <c r="C173">
+        <v>9</v>
+      </c>
+      <c r="D173" s="2">
+        <v>9500000</v>
+      </c>
+      <c r="F173" s="2">
+        <v>10500000</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H173" s="2">
+        <v>11500000</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="L173" t="str">
+        <f>VLOOKUP(B173,players!A:B,2)</f>
+        <v>Cooper Flagg</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>14</v>
+      </c>
+      <c r="B174">
+        <v>2</v>
+      </c>
+      <c r="C174">
+        <v>10</v>
+      </c>
+      <c r="L174" t="str">
+        <f>VLOOKUP(B174,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>14</v>
+      </c>
+      <c r="B175">
+        <v>220</v>
+      </c>
+      <c r="C175">
+        <v>11</v>
+      </c>
+      <c r="L175" t="str">
+        <f>VLOOKUP(B175,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>14</v>
+      </c>
+      <c r="B176">
+        <v>145</v>
+      </c>
+      <c r="C176">
+        <v>12</v>
+      </c>
+      <c r="D176" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="F176" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="H176" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="L176" t="str">
+        <f>VLOOKUP(B176,players!A:B,2)</f>
         <v>LaMelo Ball</v>
       </c>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\OneDrive\Documentos\GitHub\Fantasy-unificado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04678D08-5B42-4F00-8E6D-3EF77B218A77}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="4" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="1" activeTab="4" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -17193,7 +17193,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003E67E5-331D-4CC3-B636-B44F8A41C81C}">
-  <dimension ref="A1:L176"/>
+  <dimension ref="A1:L177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -17763,26 +17763,17 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28">
-        <v>320</v>
+        <v>187</v>
       </c>
       <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F28" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>472</v>
+        <v>13</v>
       </c>
       <c r="L28" t="str">
         <f>VLOOKUP(B28,players!A:B,2)</f>
-        <v>Cam Spencer</v>
+        <v>Jay Huff</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -17790,23 +17781,23 @@
         <v>2</v>
       </c>
       <c r="B29">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2">
-        <v>23500000</v>
+        <v>1000000</v>
       </c>
       <c r="F29" s="2">
-        <v>23500000</v>
-      </c>
-      <c r="H29" s="2">
-        <v>23500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
-        <v>Alperen Şengün</v>
+        <v>Cam Spencer</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -17814,17 +17805,23 @@
         <v>2</v>
       </c>
       <c r="B30">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2">
-        <v>15000000</v>
+        <v>23500000</v>
+      </c>
+      <c r="F30" s="2">
+        <v>23500000</v>
+      </c>
+      <c r="H30" s="2">
+        <v>23500000</v>
       </c>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Kevin Durant</v>
+        <v>Alperen Şengün</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -17832,17 +17829,17 @@
         <v>2</v>
       </c>
       <c r="B31">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2">
-        <v>9000000</v>
+        <v>15000000</v>
       </c>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Brandon Miller</v>
+        <v>Kevin Durant</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -17850,23 +17847,17 @@
         <v>2</v>
       </c>
       <c r="B32">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2">
-        <v>7000000</v>
-      </c>
-      <c r="F32" s="2">
-        <v>7000000</v>
-      </c>
-      <c r="H32" s="2">
-        <v>7000000</v>
+        <v>9000000</v>
       </c>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
-        <v>Jalen Green</v>
+        <v>Brandon Miller</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -17874,20 +17865,23 @@
         <v>2</v>
       </c>
       <c r="B33">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
       <c r="F33" s="2">
-        <v>6000000</v>
+        <v>7000000</v>
+      </c>
+      <c r="H33" s="2">
+        <v>7000000</v>
       </c>
       <c r="L33" t="str">
         <f>VLOOKUP(B33,players!A:B,2)</f>
-        <v>Tyler Herro</v>
+        <v>Jalen Green</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -17895,23 +17889,20 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>362</v>
+        <v>144</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" s="2">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="F34" s="2">
-        <v>21500000</v>
-      </c>
-      <c r="H34" s="2">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="L34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
-        <v>Trae Young</v>
+        <v>Tyler Herro</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -17919,14 +17910,23 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D35" s="2">
+        <v>21500000</v>
+      </c>
+      <c r="F35" s="2">
+        <v>21500000</v>
+      </c>
+      <c r="H35" s="2">
+        <v>21500000</v>
       </c>
       <c r="L35" t="str">
         <f>VLOOKUP(B35,players!A:B,2)</f>
-        <v>Russell Westbrook</v>
+        <v>Trae Young</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -17934,29 +17934,14 @@
         <v>2</v>
       </c>
       <c r="B36">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="C36">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2">
-        <v>3200000</v>
-      </c>
-      <c r="F36" s="2">
-        <v>3400000</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H36" s="2">
-        <v>3700000</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>472</v>
+        <v>8</v>
       </c>
       <c r="L36" t="str">
         <f>VLOOKUP(B36,players!A:B,2)</f>
-        <v>Derik Queen</v>
+        <v>Russell Westbrook</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -17964,23 +17949,29 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2">
-        <v>3100000</v>
+        <v>3200000</v>
       </c>
       <c r="F37" s="2">
-        <v>3100000</v>
+        <v>3400000</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="H37" s="2">
-        <v>3100000</v>
+        <v>3700000</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>Bobby Portis</v>
+        <v>Derik Queen</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -17988,23 +17979,23 @@
         <v>2</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2">
-        <v>6000000</v>
+        <v>3100000</v>
       </c>
       <c r="F38" s="2">
-        <v>6500000</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>472</v>
+        <v>3100000</v>
+      </c>
+      <c r="H38" s="2">
+        <v>3100000</v>
       </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>Zach Edey</v>
+        <v>Bobby Portis</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -18012,47 +18003,50 @@
         <v>2</v>
       </c>
       <c r="B39">
-        <v>290</v>
+        <v>8</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D39" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="F39" s="2">
-        <v>1000000</v>
+        <v>6500000</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H39" s="2">
-        <v>1000000</v>
-      </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Will Riley</v>
+        <v>Zach Edey</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D40" s="2">
-        <v>8000000</v>
+        <v>1000000</v>
       </c>
       <c r="F40" s="2">
-        <v>8000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H40" s="2">
+        <v>1000000</v>
       </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Immanuel Quickley</v>
+        <v>Will Riley</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -18060,14 +18054,20 @@
         <v>3</v>
       </c>
       <c r="B41">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="F41" s="2">
+        <v>8000000</v>
       </c>
       <c r="L41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Nickeil Alexander-Walker</v>
+        <v>Immanuel Quickley</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -18075,14 +18075,14 @@
         <v>3</v>
       </c>
       <c r="B42">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Kyshawn George</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -18090,17 +18090,14 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="C43">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2">
-        <v>5000000</v>
+        <v>3</v>
       </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>Cameron Johnson</v>
+        <v>Kyshawn George</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -18108,14 +18105,17 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D44" s="2">
+        <v>5000000</v>
       </c>
       <c r="L44" t="str">
         <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>Myles Turner</v>
+        <v>Cameron Johnson</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -18123,14 +18123,14 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L45" t="str">
         <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>Mitchell Robinson</v>
+        <v>Myles Turner</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -18138,14 +18138,14 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L46" t="str">
         <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>Jalen Duren</v>
+        <v>Mitchell Robinson</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -18153,23 +18153,14 @@
         <v>3</v>
       </c>
       <c r="B47">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C47">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2">
-        <v>40000000</v>
-      </c>
-      <c r="F47" s="2">
-        <v>40000000</v>
-      </c>
-      <c r="H47" s="2">
-        <v>40000000</v>
+        <v>7</v>
       </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>Luka Dončić</v>
+        <v>Jalen Duren</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -18177,17 +18168,23 @@
         <v>3</v>
       </c>
       <c r="B48">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C48">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" s="2">
-        <v>6000000</v>
+        <v>40000000</v>
+      </c>
+      <c r="F48" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H48" s="2">
+        <v>40000000</v>
       </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>Kawhi Leonard</v>
+        <v>Luka Dončić</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -18195,20 +18192,17 @@
         <v>3</v>
       </c>
       <c r="B49">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2">
-        <v>14000000</v>
-      </c>
-      <c r="F49" s="2">
-        <v>14000000</v>
+        <v>6000000</v>
       </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>Jaren Jackson Jr.</v>
+        <v>Kawhi Leonard</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -18216,23 +18210,20 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C50">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D50" s="2">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="F50" s="2">
-        <v>6500000</v>
-      </c>
-      <c r="H50" s="2">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>OG Anunoby</v>
+        <v>Jaren Jackson Jr.</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -18240,17 +18231,23 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D51" s="2">
-        <v>5000000</v>
+        <v>6500000</v>
+      </c>
+      <c r="F51" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="H51" s="2">
+        <v>6500000</v>
       </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>Kyrie Irving</v>
+        <v>OG Anunoby</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -18258,47 +18255,35 @@
         <v>3</v>
       </c>
       <c r="B52">
-        <v>295</v>
+        <v>142</v>
       </c>
       <c r="C52">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D52" s="2">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Zach LaVine</v>
+        <v>Kyrie Irving</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53">
-        <v>379</v>
+        <v>295</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D53" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F53" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H53" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>472</v>
+        <v>8000000</v>
       </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -18306,10 +18291,10 @@
         <v>4</v>
       </c>
       <c r="B54">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" s="2">
         <v>1000000</v>
@@ -18320,9 +18305,15 @@
       <c r="G54" s="2" t="s">
         <v>472</v>
       </c>
+      <c r="H54" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -18330,14 +18321,23 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F55" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -18345,17 +18345,14 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C56">
-        <v>4</v>
-      </c>
-      <c r="D56" s="2">
-        <v>2500000</v>
+        <v>3</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -18363,17 +18360,17 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" s="2">
-        <v>11000000</v>
+        <v>2500000</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -18381,20 +18378,17 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" s="2">
-        <v>5000000</v>
-      </c>
-      <c r="F58" s="2">
-        <v>5000000</v>
+        <v>11000000</v>
       </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -18402,20 +18396,20 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59" s="2">
-        <v>17000000</v>
+        <v>5000000</v>
       </c>
       <c r="F59" s="2">
-        <v>17000000</v>
+        <v>5000000</v>
       </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -18423,17 +18417,20 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D60" s="2">
-        <v>22500000</v>
+        <v>17000000</v>
+      </c>
+      <c r="F60" s="2">
+        <v>17000000</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -18441,23 +18438,17 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C61">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D61" s="2">
-        <v>5000000</v>
-      </c>
-      <c r="F61" s="2">
-        <v>5500000</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>472</v>
+        <v>22500000</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -18465,23 +18456,23 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2">
-        <v>15000000</v>
+        <v>5000000</v>
       </c>
       <c r="F62" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="H62" s="2">
-        <v>15000000</v>
+        <v>5500000</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -18489,23 +18480,23 @@
         <v>4</v>
       </c>
       <c r="B63">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D63" s="2">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="F63" s="2">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="H63" s="2">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -18513,32 +18504,41 @@
         <v>4</v>
       </c>
       <c r="B64">
-        <v>287</v>
+        <v>157</v>
       </c>
       <c r="C64">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D64" s="2">
-        <v>10000000</v>
+        <v>19000000</v>
+      </c>
+      <c r="F64" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="H64" s="2">
+        <v>19000000</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D65" s="2">
+        <v>10000000</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -18546,29 +18546,14 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="C66">
-        <v>2</v>
-      </c>
-      <c r="D66" s="2">
-        <v>3600000</v>
-      </c>
-      <c r="F66" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H66" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>472</v>
+        <v>1</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -18576,14 +18561,29 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D67" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="F67" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H67" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -18591,20 +18591,14 @@
         <v>5</v>
       </c>
       <c r="B68">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="C68">
-        <v>4</v>
-      </c>
-      <c r="D68" s="2">
-        <v>21000000</v>
-      </c>
-      <c r="F68" s="2">
-        <v>21000000</v>
+        <v>3</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -18612,14 +18606,20 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D69" s="2">
+        <v>21000000</v>
+      </c>
+      <c r="F69" s="2">
+        <v>21000000</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -18627,29 +18627,14 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C70">
-        <v>6</v>
-      </c>
-      <c r="D70" s="2">
-        <v>2800000</v>
-      </c>
-      <c r="F70" s="2">
-        <v>3000000</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H70" s="2">
-        <v>3300000</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>472</v>
+        <v>5</v>
       </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Collin Murray-Boyles</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -18657,20 +18642,29 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D71" s="2">
-        <v>17000000</v>
+        <v>2800000</v>
       </c>
       <c r="F71" s="2">
-        <v>17000000</v>
+        <v>3000000</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H71" s="2">
+        <v>3300000</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>Collin Murray-Boyles</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -18678,23 +18672,20 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C72">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D72" s="2">
-        <v>40000000</v>
+        <v>17000000</v>
       </c>
       <c r="F72" s="2">
-        <v>40000000</v>
-      </c>
-      <c r="H72" s="2">
-        <v>40000000</v>
+        <v>17000000</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -18702,20 +18693,23 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="C73">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D73" s="2">
-        <v>3100000</v>
+        <v>40000000</v>
       </c>
       <c r="F73" s="2">
-        <v>3100000</v>
+        <v>40000000</v>
+      </c>
+      <c r="H73" s="2">
+        <v>40000000</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -18723,14 +18717,20 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>227</v>
+        <v>72</v>
       </c>
       <c r="C74">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D74" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F74" s="2">
+        <v>3100000</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>Jerami Grant</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -18738,14 +18738,14 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="C75">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -18753,14 +18753,14 @@
         <v>5</v>
       </c>
       <c r="B76">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="C76">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Royce O'Neale</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -18768,35 +18768,29 @@
         <v>5</v>
       </c>
       <c r="B77">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C77">
         <v>12</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>Ryan Rollins</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B78">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F78" s="2">
-        <v>6000000</v>
+        <v>12</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -18804,17 +18798,20 @@
         <v>6</v>
       </c>
       <c r="B79">
-        <v>338</v>
+        <v>162</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="F79" s="2">
+        <v>6000000</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -18822,14 +18819,17 @@
         <v>6</v>
       </c>
       <c r="B80">
-        <v>45</v>
+        <v>338</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D80" s="2">
+        <v>1000000</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -18837,14 +18837,14 @@
         <v>6</v>
       </c>
       <c r="B81">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -18852,14 +18852,14 @@
         <v>6</v>
       </c>
       <c r="B82">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -18867,14 +18867,14 @@
         <v>6</v>
       </c>
       <c r="B83">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -18882,17 +18882,14 @@
         <v>6</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C84">
-        <v>7</v>
-      </c>
-      <c r="D84" s="2">
-        <v>20000000</v>
+        <v>6</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -18900,14 +18897,17 @@
         <v>6</v>
       </c>
       <c r="B85">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D85" s="2">
+        <v>20000000</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -18915,17 +18915,14 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C86">
-        <v>9</v>
-      </c>
-      <c r="D86" s="2">
-        <v>7000000</v>
+        <v>8</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -18933,20 +18930,17 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2">
-        <v>35000000</v>
-      </c>
-      <c r="F87" s="2">
-        <v>35000000</v>
+        <v>7000000</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -18954,20 +18948,20 @@
         <v>6</v>
       </c>
       <c r="B88">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="C88">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D88" s="2">
-        <v>3100000</v>
+        <v>35000000</v>
       </c>
       <c r="F88" s="2">
-        <v>3100000</v>
+        <v>35000000</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -18975,17 +18969,20 @@
         <v>6</v>
       </c>
       <c r="B89">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="C89">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D89" s="2">
-        <v>1000000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F89" s="2">
+        <v>3100000</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -18993,14 +18990,17 @@
         <v>6</v>
       </c>
       <c r="B90">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="C90">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="D90" s="2">
+        <v>1000000</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Damian Lillard</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -19008,20 +19008,14 @@
         <v>6</v>
       </c>
       <c r="B91">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="C91">
-        <v>14</v>
-      </c>
-      <c r="D91" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F91" s="2">
-        <v>6000000</v>
+        <v>13</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -19029,38 +19023,35 @@
         <v>6</v>
       </c>
       <c r="B92">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C92">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="D92" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F92" s="2">
+        <v>6000000</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Tari Eason</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B93">
-        <v>242</v>
+        <v>71</v>
       </c>
       <c r="C93">
-        <v>1</v>
-      </c>
-      <c r="D93" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="F93" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>472</v>
+        <v>15</v>
       </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -19068,14 +19059,23 @@
         <v>8</v>
       </c>
       <c r="B94">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D94" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="F94" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -19083,29 +19083,14 @@
         <v>8</v>
       </c>
       <c r="B95">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="C95">
-        <v>3</v>
-      </c>
-      <c r="D95" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F95" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H95" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>472</v>
+        <v>2</v>
       </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -19113,17 +19098,29 @@
         <v>8</v>
       </c>
       <c r="B96">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C96">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D96" s="2">
-        <v>2000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H96" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -19131,23 +19128,17 @@
         <v>8</v>
       </c>
       <c r="B97">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D97" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F97" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="H97" s="2">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -19155,23 +19146,23 @@
         <v>8</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="C98">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D98" s="2">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
       <c r="F98" s="2">
-        <v>7500000</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>472</v>
+        <v>6000000</v>
+      </c>
+      <c r="H98" s="2">
+        <v>6000000</v>
       </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -19179,20 +19170,23 @@
         <v>8</v>
       </c>
       <c r="B99">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D99" s="2">
-        <v>4000000</v>
+        <v>7000000</v>
       </c>
       <c r="F99" s="2">
-        <v>4000000</v>
+        <v>7500000</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -19200,23 +19194,20 @@
         <v>8</v>
       </c>
       <c r="B100">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D100" s="2">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="F100" s="2">
-        <v>16000000</v>
-      </c>
-      <c r="H100" s="2">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -19224,20 +19215,23 @@
         <v>8</v>
       </c>
       <c r="B101">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="C101">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D101" s="2">
-        <v>9000000</v>
+        <v>16000000</v>
       </c>
       <c r="F101" s="2">
-        <v>9000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="H101" s="2">
+        <v>16000000</v>
       </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -19245,17 +19239,20 @@
         <v>8</v>
       </c>
       <c r="B102">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C102">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2">
-        <v>16000000</v>
+        <v>9000000</v>
+      </c>
+      <c r="F102" s="2">
+        <v>9000000</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -19263,23 +19260,17 @@
         <v>8</v>
       </c>
       <c r="B103">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="C103">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D103" s="2">
-        <v>19000000</v>
-      </c>
-      <c r="F103" s="2">
-        <v>19000000</v>
-      </c>
-      <c r="H103" s="2">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -19287,14 +19278,23 @@
         <v>8</v>
       </c>
       <c r="B104">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C104">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D104" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="F104" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="H104" s="2">
+        <v>19000000</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -19302,14 +19302,14 @@
         <v>8</v>
       </c>
       <c r="B105">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="C105">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -19317,38 +19317,29 @@
         <v>8</v>
       </c>
       <c r="B106">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="C106">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B107">
-        <v>384</v>
+        <v>336</v>
       </c>
       <c r="C107">
-        <v>1</v>
-      </c>
-      <c r="D107" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F107" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H107" s="2">
-        <v>3100000</v>
+        <v>14</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -19356,14 +19347,23 @@
         <v>9</v>
       </c>
       <c r="B108">
-        <v>240</v>
+        <v>384</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D108" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F108" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H108" s="2">
+        <v>3100000</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -19371,17 +19371,14 @@
         <v>9</v>
       </c>
       <c r="B109">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="C109">
-        <v>3</v>
-      </c>
-      <c r="D109" s="2">
-        <v>4500000</v>
+        <v>2</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -19389,14 +19386,17 @@
         <v>9</v>
       </c>
       <c r="B110">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="C110">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D110" s="2">
+        <v>4500000</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -19404,14 +19404,14 @@
         <v>9</v>
       </c>
       <c r="B111">
-        <v>416</v>
+        <v>251</v>
       </c>
       <c r="C111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -19419,23 +19419,14 @@
         <v>9</v>
       </c>
       <c r="B112">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="C112">
-        <v>6</v>
-      </c>
-      <c r="D112" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F112" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H112" s="2">
-        <v>3100000</v>
+        <v>5</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -19443,23 +19434,23 @@
         <v>9</v>
       </c>
       <c r="B113">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D113" s="2">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="F113" s="2">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="H113" s="2">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -19467,23 +19458,23 @@
         <v>9</v>
       </c>
       <c r="B114">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D114" s="2">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="F114" s="2">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="H114" s="2">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -19491,17 +19482,23 @@
         <v>9</v>
       </c>
       <c r="B115">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="C115">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D115" s="2">
-        <v>11500000</v>
+        <v>12500000</v>
+      </c>
+      <c r="F115" s="2">
+        <v>12500000</v>
+      </c>
+      <c r="H115" s="2">
+        <v>12500000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -19509,23 +19506,17 @@
         <v>9</v>
       </c>
       <c r="B116">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F116" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H116" s="2">
-        <v>3100000</v>
+        <v>11500000</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -19533,17 +19524,23 @@
         <v>9</v>
       </c>
       <c r="B117">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="C117">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D117" s="2">
-        <v>25000000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F117" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H117" s="2">
+        <v>3100000</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -19551,38 +19548,41 @@
         <v>9</v>
       </c>
       <c r="B118">
-        <v>331</v>
+        <v>217</v>
       </c>
       <c r="C118">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D118" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="F118" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="H118" s="2">
-        <v>12000000</v>
+        <v>25000000</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B119">
-        <v>9</v>
+        <v>331</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D119" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="F119" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H119" s="2">
+        <v>12000000</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Walker Kessler</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -19590,14 +19590,14 @@
         <v>10</v>
       </c>
       <c r="B120">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -19605,14 +19605,14 @@
         <v>10</v>
       </c>
       <c r="B121">
-        <v>249</v>
+        <v>373</v>
       </c>
       <c r="C121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -19620,17 +19620,14 @@
         <v>10</v>
       </c>
       <c r="B122">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="C122">
-        <v>4</v>
-      </c>
-      <c r="D122" s="2">
-        <v>4100000</v>
+        <v>3</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -19638,20 +19635,17 @@
         <v>10</v>
       </c>
       <c r="B123">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="C123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D123" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F123" s="2">
-        <v>6000000</v>
+        <v>4100000</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -19659,17 +19653,20 @@
         <v>10</v>
       </c>
       <c r="B124">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="C124">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D124" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="F124" s="2">
+        <v>6000000</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -19677,14 +19674,17 @@
         <v>10</v>
       </c>
       <c r="B125">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D125" s="2">
+        <v>1000000</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -19692,23 +19692,14 @@
         <v>10</v>
       </c>
       <c r="B126">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C126">
-        <v>8</v>
-      </c>
-      <c r="D126" s="2">
-        <v>9250000</v>
-      </c>
-      <c r="F126" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>472</v>
+        <v>7</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -19716,23 +19707,23 @@
         <v>10</v>
       </c>
       <c r="B127">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C127">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D127" s="2">
-        <v>15000000</v>
+        <v>9250000</v>
       </c>
       <c r="F127" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="H127" s="2">
-        <v>15000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -19740,20 +19731,23 @@
         <v>10</v>
       </c>
       <c r="B128">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="C128">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D128" s="2">
-        <v>11000000</v>
+        <v>15000000</v>
       </c>
       <c r="F128" s="2">
-        <v>11000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="H128" s="2">
+        <v>15000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -19761,23 +19755,20 @@
         <v>10</v>
       </c>
       <c r="B129">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C129">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D129" s="2">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="F129" s="2">
-        <v>16000000</v>
-      </c>
-      <c r="H129" s="2">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -19785,32 +19776,41 @@
         <v>10</v>
       </c>
       <c r="B130">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="C130">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D130" s="2">
-        <v>24000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="F130" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="H130" s="2">
+        <v>16000000</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B131">
-        <v>327</v>
+        <v>246</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D131" s="2">
+        <v>24000000</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -19818,14 +19818,14 @@
         <v>11</v>
       </c>
       <c r="B132">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -19833,17 +19833,14 @@
         <v>11</v>
       </c>
       <c r="B133">
-        <v>111</v>
+        <v>213</v>
       </c>
       <c r="C133">
-        <v>3</v>
-      </c>
-      <c r="D133" s="2">
-        <v>1000000</v>
+        <v>2</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -19851,14 +19848,17 @@
         <v>11</v>
       </c>
       <c r="B134">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C134">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D134" s="2">
+        <v>1000000</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -19866,17 +19866,14 @@
         <v>11</v>
       </c>
       <c r="B135">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C135">
-        <v>5</v>
-      </c>
-      <c r="D135" s="2">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -19884,14 +19881,17 @@
         <v>11</v>
       </c>
       <c r="B136">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C136">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D136" s="2">
+        <v>1000000</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -19899,17 +19899,14 @@
         <v>11</v>
       </c>
       <c r="B137">
+        <v>63</v>
+      </c>
+      <c r="C137">
         <v>6</v>
-      </c>
-      <c r="C137">
-        <v>7</v>
-      </c>
-      <c r="D137" s="2">
-        <v>26000000</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -19917,17 +19914,17 @@
         <v>11</v>
       </c>
       <c r="B138">
-        <v>177</v>
+        <v>6</v>
       </c>
       <c r="C138">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D138" s="2">
-        <v>15000000</v>
+        <v>26000000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -19935,17 +19932,17 @@
         <v>11</v>
       </c>
       <c r="B139">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="C139">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D139" s="2">
-        <v>7500000</v>
+        <v>15000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -19953,23 +19950,17 @@
         <v>11</v>
       </c>
       <c r="B140">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="C140">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D140" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="F140" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="H140" s="2">
-        <v>30000000</v>
+        <v>7500000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -19977,17 +19968,23 @@
         <v>11</v>
       </c>
       <c r="B141">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="C141">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D141" s="2">
-        <v>1000000</v>
+        <v>30000000</v>
+      </c>
+      <c r="F141" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="H141" s="2">
+        <v>30000000</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -19995,14 +19992,17 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="C142">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D142" s="2">
+        <v>1000000</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -20010,14 +20010,14 @@
         <v>11</v>
       </c>
       <c r="B143">
-        <v>266</v>
+        <v>109</v>
       </c>
       <c r="C143">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -20025,35 +20025,29 @@
         <v>11</v>
       </c>
       <c r="B144">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="C144">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B145">
-        <v>403</v>
+        <v>195</v>
       </c>
       <c r="C145">
-        <v>1</v>
-      </c>
-      <c r="D145" s="2">
-        <v>5000000</v>
-      </c>
-      <c r="F145" s="2">
-        <v>5000000</v>
+        <v>14</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -20061,20 +20055,20 @@
         <v>12</v>
       </c>
       <c r="B146">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D146" s="2">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="F146" s="2">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -20082,17 +20076,20 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>120</v>
+        <v>345</v>
       </c>
       <c r="C147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D147" s="2">
-        <v>1000000</v>
+        <v>3500000</v>
+      </c>
+      <c r="F147" s="2">
+        <v>3500000</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -20100,14 +20097,17 @@
         <v>12</v>
       </c>
       <c r="B148">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="C148">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D148" s="2">
+        <v>1000000</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -20115,17 +20115,14 @@
         <v>12</v>
       </c>
       <c r="B149">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C149">
-        <v>5</v>
-      </c>
-      <c r="D149" s="2">
-        <v>11000000</v>
+        <v>4</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -20133,20 +20130,17 @@
         <v>12</v>
       </c>
       <c r="B150">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="C150">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D150" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="F150" s="2">
-        <v>20000000</v>
+        <v>11000000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -20154,23 +20148,20 @@
         <v>12</v>
       </c>
       <c r="B151">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="C151">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D151" s="2">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="F151" s="2">
-        <v>18000000</v>
-      </c>
-      <c r="H151" s="2">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -20178,35 +20169,41 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="C152">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D152" s="2">
-        <v>2500000</v>
+        <v>18000000</v>
+      </c>
+      <c r="F152" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="H152" s="2">
+        <v>18000000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B153">
-        <v>307</v>
+        <v>115</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D153" s="2">
-        <v>1000000</v>
+        <v>2500000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -20214,14 +20211,17 @@
         <v>13</v>
       </c>
       <c r="B154">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D154" s="2">
+        <v>1000000</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -20229,17 +20229,14 @@
         <v>13</v>
       </c>
       <c r="B155">
-        <v>296</v>
+        <v>363</v>
       </c>
       <c r="C155">
-        <v>3</v>
-      </c>
-      <c r="D155" s="2">
-        <v>3000000</v>
+        <v>2</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -20247,17 +20244,17 @@
         <v>13</v>
       </c>
       <c r="B156">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="C156">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D156" s="2">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -20265,14 +20262,17 @@
         <v>13</v>
       </c>
       <c r="B157">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="C157">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D157" s="2">
+        <v>2000000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -20280,14 +20280,14 @@
         <v>13</v>
       </c>
       <c r="B158">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -20295,17 +20295,14 @@
         <v>13</v>
       </c>
       <c r="B159">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C159">
-        <v>7</v>
-      </c>
-      <c r="D159" s="2">
-        <v>11500000</v>
+        <v>6</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -20313,23 +20310,17 @@
         <v>13</v>
       </c>
       <c r="B160">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C160">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D160" s="2">
-        <v>16000000</v>
-      </c>
-      <c r="F160" s="2">
-        <v>16000000</v>
-      </c>
-      <c r="H160" s="2">
-        <v>16000000</v>
+        <v>11500000</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -20337,23 +20328,23 @@
         <v>13</v>
       </c>
       <c r="B161">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C161">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D161" s="2">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="F161" s="2">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="H161" s="2">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -20361,17 +20352,23 @@
         <v>13</v>
       </c>
       <c r="B162">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C162">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D162" s="2">
-        <v>19000000</v>
+        <v>12000000</v>
+      </c>
+      <c r="F162" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H162" s="2">
+        <v>12000000</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -20379,17 +20376,17 @@
         <v>13</v>
       </c>
       <c r="B163">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="C163">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D163" s="2">
-        <v>1000000</v>
+        <v>19000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Zach Collins</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -20397,38 +20394,41 @@
         <v>13</v>
       </c>
       <c r="B164">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="C164">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D164" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F164" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="H164" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Zach Collins</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B165">
-        <v>317</v>
+        <v>150</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D165" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F165" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H165" s="2">
+        <v>6000000</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -20436,14 +20436,14 @@
         <v>14</v>
       </c>
       <c r="B166">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -20451,14 +20451,14 @@
         <v>14</v>
       </c>
       <c r="B167">
-        <v>129</v>
+        <v>299</v>
       </c>
       <c r="C167">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -20466,14 +20466,14 @@
         <v>14</v>
       </c>
       <c r="B168">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="C168">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -20481,17 +20481,14 @@
         <v>14</v>
       </c>
       <c r="B169">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="C169">
-        <v>5</v>
-      </c>
-      <c r="D169" s="2">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -20499,17 +20496,17 @@
         <v>14</v>
       </c>
       <c r="B170">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="C170">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D170" s="2">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -20517,23 +20514,17 @@
         <v>14</v>
       </c>
       <c r="B171">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="C171">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D171" s="2">
-        <v>20500000</v>
-      </c>
-      <c r="F171" s="2">
-        <v>20500000</v>
-      </c>
-      <c r="H171" s="2">
-        <v>20500000</v>
+        <v>3000000</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -20541,17 +20532,23 @@
         <v>14</v>
       </c>
       <c r="B172">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C172">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D172" s="2">
-        <v>19500000</v>
+        <v>20500000</v>
+      </c>
+      <c r="F172" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="H172" s="2">
+        <v>20500000</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -20559,29 +20556,17 @@
         <v>14</v>
       </c>
       <c r="B173">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C173">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D173" s="2">
-        <v>9500000</v>
-      </c>
-      <c r="F173" s="2">
-        <v>10500000</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H173" s="2">
-        <v>11500000</v>
-      </c>
-      <c r="I173" s="2" t="s">
-        <v>472</v>
+        <v>19500000</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -20589,14 +20574,29 @@
         <v>14</v>
       </c>
       <c r="B174">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C174">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D174" s="2">
+        <v>9500000</v>
+      </c>
+      <c r="F174" s="2">
+        <v>10500000</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H174" s="2">
+        <v>11500000</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -20604,14 +20604,14 @@
         <v>14</v>
       </c>
       <c r="B175">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="C175">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L175" t="str">
         <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -20619,22 +20619,37 @@
         <v>14</v>
       </c>
       <c r="B176">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C176">
-        <v>12</v>
-      </c>
-      <c r="D176" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="F176" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="H176" s="2">
-        <v>20000000</v>
+        <v>11</v>
       </c>
       <c r="L176" t="str">
         <f>VLOOKUP(B176,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>14</v>
+      </c>
+      <c r="B177">
+        <v>145</v>
+      </c>
+      <c r="C177">
+        <v>12</v>
+      </c>
+      <c r="D177" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="F177" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="H177" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="L177" t="str">
+        <f>VLOOKUP(B177,players!A:B,2)</f>
         <v>LaMelo Ball</v>
       </c>
     </row>
@@ -20826,43 +20841,30 @@
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <v>8250000</v>
+        <v>4500000</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2">
-        <v>4500000</v>
-      </c>
-      <c r="G6" s="2"/>
+        <v>5000000</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H6" s="2">
-        <v>5000000</v>
+        <v>5500000</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="J6" s="2">
-        <v>5500000</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
       <c r="L6" t="str">
         <f>VLOOKUP(B6,players!A:B,2)</f>
         <v>Jeremiah Fears</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>375</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3900000</v>
-      </c>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -20870,10 +20872,6 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" t="str">
-        <f>VLOOKUP(B7,players!A:B,2)</f>
-        <v>Gradey Dick</v>
-      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04678D08-5B42-4F00-8E6D-3EF77B218A77}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F2B8C6A-431A-4941-8572-4AD8A326A097}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="1" activeTab="4" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="9" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -1701,6 +1701,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20661,7 +20665,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B357A823-6505-4984-ACC9-40636E218B6C}">
-  <dimension ref="A1:L165"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
@@ -20864,24 +20868,47 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D7" s="2"/>
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>365</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1000000</v>
+      </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="F7" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
+      <c r="L7" t="str">
+        <f>VLOOKUP(B7,players!A:B,2)</f>
+        <v>Walter Clayton</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
       <c r="B8">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2">
         <v>1000000</v>
@@ -20893,28 +20920,24 @@
       <c r="G8" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H8" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" t="str">
         <f>VLOOKUP(B8,players!A:B,2)</f>
-        <v>Walter Clayton</v>
+        <v>Johnny Furphy</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2">
         <v>1000000</v>
@@ -20926,13 +20949,17 @@
       <c r="G9" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="H9" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" t="str">
         <f>VLOOKUP(B9,players!A:B,2)</f>
-        <v>Johnny Furphy</v>
+        <v>Nikola Topić</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -20940,61 +20967,61 @@
         <v>3</v>
       </c>
       <c r="B10">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>1000000</v>
+        <v>3400000</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2">
-        <v>1000000</v>
+        <v>3700000</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H10" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" t="str">
         <f>VLOOKUP(B10,players!A:B,2)</f>
-        <v>Nikola Topić</v>
+        <v>Jase Richardson</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B11">
-        <v>408</v>
+        <v>92</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>3400000</v>
+        <v>6500000</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2">
-        <v>3700000</v>
+        <v>7000000</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="H11" s="2">
+        <v>7500000</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" t="str">
         <f>VLOOKUP(B11,players!A:B,2)</f>
-        <v>Jase Richardson</v>
+        <v>VJ Edgecombe</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -21002,23 +21029,23 @@
         <v>5</v>
       </c>
       <c r="B12">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H12" s="2">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>472</v>
@@ -21027,7 +21054,7 @@
       <c r="K12" s="2"/>
       <c r="L12" t="str">
         <f>VLOOKUP(B12,players!A:B,2)</f>
-        <v>VJ Edgecombe</v>
+        <v>Danny Wolf</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -21035,10 +21062,10 @@
         <v>5</v>
       </c>
       <c r="B13">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
         <v>1000000</v>
@@ -21060,7 +21087,7 @@
       <c r="K13" s="2"/>
       <c r="L13" t="str">
         <f>VLOOKUP(B13,players!A:B,2)</f>
-        <v>Danny Wolf</v>
+        <v>Nique Clifford</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -21068,23 +21095,23 @@
         <v>5</v>
       </c>
       <c r="B14">
-        <v>209</v>
+        <v>409</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2">
-        <v>1000000</v>
+        <v>4200000</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H14" s="2">
-        <v>1000000</v>
+        <v>4500000</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>472</v>
@@ -21093,58 +21120,54 @@
       <c r="K14" s="2"/>
       <c r="L14" t="str">
         <f>VLOOKUP(B14,players!A:B,2)</f>
-        <v>Nique Clifford</v>
+        <v>Hansen Yang</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15">
-        <v>409</v>
+        <v>192</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>4000000</v>
+        <v>3200000</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2">
-        <v>4200000</v>
+        <v>3500000</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H15" s="2">
-        <v>4500000</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" t="str">
         <f>VLOOKUP(B15,players!A:B,2)</f>
-        <v>Hansen Yang</v>
+        <v>Tidjane Salaün</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B16">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>3200000</v>
+        <v>1000000</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2">
-        <v>3500000</v>
+        <v>1000000</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>472</v>
@@ -21155,36 +21178,40 @@
       <c r="K16" s="2"/>
       <c r="L16" t="str">
         <f>VLOOKUP(B16,players!A:B,2)</f>
-        <v>Tidjane Salaün</v>
+        <v>Kyle Filipowski</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2">
-        <v>1000000</v>
+        <v>5500000</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+      <c r="H17" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" t="str">
         <f>VLOOKUP(B17,players!A:B,2)</f>
-        <v>Kyle Filipowski</v>
+        <v>Kon Knueppel</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -21192,32 +21219,28 @@
         <v>9</v>
       </c>
       <c r="B18">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2">
-        <v>5500000</v>
+        <v>1000000</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H18" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" t="str">
         <f>VLOOKUP(B18,players!A:B,2)</f>
-        <v>Kon Knueppel</v>
+        <v>Jaylon Tyson</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -21225,10 +21248,10 @@
         <v>9</v>
       </c>
       <c r="B19">
-        <v>123</v>
+        <v>410</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2">
         <v>1000000</v>
@@ -21246,36 +21269,40 @@
       <c r="K19" s="2"/>
       <c r="L19" t="str">
         <f>VLOOKUP(B19,players!A:B,2)</f>
-        <v>Jaylon Tyson</v>
+        <v>Joan Beringer</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20">
-        <v>410</v>
+        <v>297</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>1000000</v>
+        <v>5500000</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+      <c r="H20" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" t="str">
         <f>VLOOKUP(B20,players!A:B,2)</f>
-        <v>Joan Beringer</v>
+        <v>Tre Johnson</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -21283,32 +21310,26 @@
         <v>10</v>
       </c>
       <c r="B21">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2">
-        <v>5500000</v>
+        <v>1000000</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H21" s="2">
-        <v>6500000</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>472</v>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" t="str">
         <f>VLOOKUP(B21,players!A:B,2)</f>
-        <v>Tre Johnson</v>
+        <v>Ja'Kobe Walter</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -21316,18 +21337,16 @@
         <v>10</v>
       </c>
       <c r="B22">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="2">
-        <v>1000000</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -21335,7 +21354,7 @@
       <c r="K22" s="2"/>
       <c r="L22" t="str">
         <f>VLOOKUP(B22,players!A:B,2)</f>
-        <v>Ja'Kobe Walter</v>
+        <v>Cam Whitmore</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -21343,57 +21362,61 @@
         <v>10</v>
       </c>
       <c r="B23">
-        <v>300</v>
+        <v>411</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="F23" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" t="str">
         <f>VLOOKUP(B23,players!A:B,2)</f>
-        <v>Cam Whitmore</v>
+        <v>Thomas Sorber</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2">
-        <v>1000000</v>
+        <v>3500000</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H24" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" t="str">
         <f>VLOOKUP(B24,players!A:B,2)</f>
-        <v>Thomas Sorber</v>
+        <v>Carter Bryant</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -21401,28 +21424,24 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2">
-        <v>3200000</v>
+        <v>3300000</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2">
-        <v>3500000</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" t="str">
         <f>VLOOKUP(B25,players!A:B,2)</f>
-        <v>Carter Bryant</v>
+        <v>Dalton Knecht</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -21430,13 +21449,13 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>413</v>
+        <v>189</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2">
-        <v>3300000</v>
+        <v>6000000</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -21447,32 +21466,36 @@
       <c r="K26" s="2"/>
       <c r="L26" t="str">
         <f>VLOOKUP(B26,players!A:B,2)</f>
-        <v>Dalton Knecht</v>
+        <v>Ron Holland</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B27">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="F27" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" t="str">
         <f>VLOOKUP(B27,players!A:B,2)</f>
-        <v>Ron Holland</v>
+        <v>Devin Carter</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -21480,28 +21503,32 @@
         <v>13</v>
       </c>
       <c r="B28">
-        <v>252</v>
+        <v>414</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2">
-        <v>1000000</v>
+        <v>3600000</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="H28" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" t="str">
         <f>VLOOKUP(B28,players!A:B,2)</f>
-        <v>Devin Carter</v>
+        <v>Kaman Maluach</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -21509,23 +21536,23 @@
         <v>13</v>
       </c>
       <c r="B29">
-        <v>414</v>
+        <v>241</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2">
-        <v>3600000</v>
+        <v>8500000</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2">
-        <v>3800000</v>
+        <v>9250000</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H29" s="2">
-        <v>4100000</v>
+        <v>10000000</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>472</v>
@@ -21534,40 +21561,34 @@
       <c r="K29" s="2"/>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
-        <v>Kaman Maluach</v>
+        <v>Dylan Harper</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B30">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2">
-        <v>8500000</v>
+        <v>3200000</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2">
-        <v>9250000</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H30" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>472</v>
-      </c>
+        <v>3500000</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Dylan Harper</v>
+        <v>Cason Wallace</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -21575,18 +21596,16 @@
         <v>14</v>
       </c>
       <c r="B31">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2">
-        <v>3200000</v>
+        <v>1000000</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="2">
-        <v>3500000</v>
-      </c>
+      <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -21594,7 +21613,7 @@
       <c r="K31" s="2"/>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>Jaylen Wells</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -21602,849 +21621,32 @@
         <v>14</v>
       </c>
       <c r="B32">
-        <v>259</v>
+        <v>415</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="F32" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4200000</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
-        <v>Jaylen Wells</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>14</v>
-      </c>
-      <c r="B33">
-        <v>415</v>
-      </c>
-      <c r="C33">
-        <v>3</v>
-      </c>
-      <c r="D33" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2">
-        <v>4000000</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H33" s="2">
-        <v>4200000</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" t="str">
-        <f>VLOOKUP(B33,players!A:B,2)</f>
         <v>Noah Essengue</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L34" t="e">
-        <f>VLOOKUP(B34,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L35" t="e">
-        <f>VLOOKUP(B35,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L36" t="e">
-        <f>VLOOKUP(B36,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L37" t="e">
-        <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L38" t="e">
-        <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L39" t="e">
-        <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L40" t="e">
-        <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L41" t="e">
-        <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L42" t="e">
-        <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L43" t="e">
-        <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L44" t="e">
-        <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L45" t="e">
-        <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L46" t="e">
-        <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L47" t="e">
-        <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L48" t="e">
-        <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="49" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L49" t="e">
-        <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="50" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L50" t="e">
-        <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="51" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L51" t="e">
-        <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="52" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L52" t="e">
-        <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="53" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L53" t="e">
-        <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="54" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L54" t="e">
-        <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="55" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L55" t="e">
-        <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="56" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L56" t="e">
-        <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="57" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L57" t="e">
-        <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="58" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L58" t="e">
-        <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="59" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L59" t="e">
-        <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="60" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L60" t="e">
-        <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="61" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L61" t="e">
-        <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="62" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L62" t="e">
-        <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="63" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L63" t="e">
-        <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="64" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L64" t="e">
-        <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="65" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L65" t="e">
-        <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="66" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L66" t="e">
-        <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="67" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L67" t="e">
-        <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="68" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L68" t="e">
-        <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="69" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L69" t="e">
-        <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="70" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L70" t="e">
-        <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="71" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L71" t="e">
-        <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="72" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L72" t="e">
-        <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="73" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L73" t="e">
-        <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="74" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L74" t="e">
-        <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="75" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L75" t="e">
-        <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="76" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L76" t="e">
-        <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="77" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L77" t="e">
-        <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="78" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L78" t="e">
-        <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="79" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L79" t="e">
-        <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="80" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L80" t="e">
-        <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="81" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L81" t="e">
-        <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="82" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L82" t="e">
-        <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="83" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L83" t="e">
-        <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="84" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L84" t="e">
-        <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="85" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L85" t="e">
-        <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="86" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L86" t="e">
-        <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="87" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L87" t="e">
-        <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="88" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L88" t="e">
-        <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="89" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L89" t="e">
-        <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="90" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L90" t="e">
-        <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="91" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L91" t="e">
-        <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="92" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L92" t="e">
-        <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="93" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L93" t="e">
-        <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="94" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L94" t="e">
-        <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="95" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L95" t="e">
-        <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="96" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L96" t="e">
-        <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="97" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L97" t="e">
-        <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="98" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L98" t="e">
-        <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="99" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L99" t="e">
-        <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="100" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L100" t="e">
-        <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="101" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L101" t="e">
-        <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="102" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L102" t="e">
-        <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="103" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L103" t="e">
-        <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="104" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L104" t="e">
-        <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="105" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L105" t="e">
-        <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="106" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L106" t="e">
-        <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="107" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L107" t="e">
-        <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="108" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L108" t="e">
-        <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="109" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L109" t="e">
-        <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="110" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L110" t="e">
-        <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="111" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L111" t="e">
-        <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="112" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L112" t="e">
-        <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="113" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L113" t="e">
-        <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="114" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L114" t="e">
-        <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="115" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L115" t="e">
-        <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="116" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L116" t="e">
-        <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="117" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L117" t="e">
-        <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="118" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L118" t="e">
-        <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="119" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L119" t="e">
-        <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="120" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L120" t="e">
-        <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="121" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L121" t="e">
-        <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="122" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L122" t="e">
-        <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="123" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L123" t="e">
-        <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="124" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L124" t="e">
-        <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="125" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L125" t="e">
-        <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="126" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L126" t="e">
-        <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="127" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L127" t="e">
-        <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="128" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L128" t="e">
-        <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="129" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L129" t="e">
-        <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="130" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L130" t="e">
-        <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="131" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L131" t="e">
-        <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="132" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L132" t="e">
-        <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="133" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L133" t="e">
-        <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="134" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L134" t="e">
-        <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="135" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L135" t="e">
-        <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="136" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L136" t="e">
-        <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="137" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L137" t="e">
-        <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="138" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L138" t="e">
-        <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="139" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L139" t="e">
-        <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="140" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L140" t="e">
-        <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="141" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L141" t="e">
-        <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="142" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L142" t="e">
-        <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="143" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L143" t="e">
-        <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="144" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L144" t="e">
-        <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="145" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L145" t="e">
-        <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="146" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L146" t="e">
-        <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="147" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L147" t="e">
-        <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="148" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L148" t="e">
-        <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="149" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L149" t="e">
-        <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="150" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L150" t="e">
-        <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="151" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L151" t="e">
-        <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="152" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L152" t="e">
-        <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="153" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L153" t="e">
-        <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="154" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L154" t="e">
-        <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="155" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L155" t="e">
-        <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="156" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L156" t="e">
-        <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="157" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L157" t="e">
-        <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="158" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L158" t="e">
-        <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="159" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L159" t="e">
-        <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="160" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L160" t="e">
-        <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="161" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L161" t="e">
-        <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="162" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L162" t="e">
-        <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="163" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L163" t="e">
-        <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="164" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L164" t="e">
-        <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="165" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L165" t="e">
-        <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>#N/A</v>
       </c>
     </row>
   </sheetData>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F2B8C6A-431A-4941-8572-4AD8A326A097}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05111786-FC54-47B2-86F5-452A860D58C3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="9" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="524">
   <si>
     <t>player_id</t>
   </si>
@@ -1617,6 +1617,12 @@
   </si>
   <si>
     <t>Clint Capela</t>
+  </si>
+  <si>
+    <t>PG/SG</t>
+  </si>
+  <si>
+    <t>SG/SF</t>
   </si>
 </sst>
 </file>
@@ -3085,7 +3091,7 @@
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E33" s="1">
         <v>17</v>
@@ -3181,7 +3187,7 @@
         <v>60</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>24</v>
+        <v>519</v>
       </c>
       <c r="E36" s="1">
         <v>18.3</v>
@@ -3214,7 +3220,7 @@
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E37" s="1">
         <v>33.5</v>
@@ -3343,7 +3349,7 @@
         <v>65</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E41" s="1">
         <v>18.100000000000001</v>
@@ -3503,7 +3509,7 @@
         <v>70</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E46" s="1">
         <v>12</v>
@@ -3535,7 +3541,7 @@
         <v>71</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>21</v>
+        <v>520</v>
       </c>
       <c r="E47" s="1">
         <v>11.8</v>
@@ -3600,7 +3606,7 @@
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E49" s="1">
         <v>24.2</v>
@@ -3664,7 +3670,7 @@
         <v>75</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E51" s="1">
         <v>14.2</v>
@@ -3761,7 +3767,7 @@
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E54" s="1">
         <v>28.7</v>
@@ -3793,7 +3799,7 @@
         <v>79</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E55" s="1">
         <v>26.7</v>
@@ -3826,7 +3832,7 @@
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E56" s="1">
         <v>24.2</v>
@@ -3954,7 +3960,7 @@
         <v>84</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E60" s="1">
         <v>11.9</v>
@@ -4018,7 +4024,7 @@
         <v>86</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E62" s="1">
         <v>21</v>
@@ -4178,7 +4184,7 @@
         <v>91</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E67" s="1">
         <v>24</v>
@@ -4243,7 +4249,7 @@
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E69" s="1">
         <v>27.9</v>
@@ -4275,7 +4281,7 @@
         <v>94</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E70" s="1">
         <v>13.7</v>
@@ -4339,7 +4345,7 @@
         <v>96</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E72" s="1">
         <v>10.5</v>
@@ -4404,7 +4410,7 @@
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E74" s="1">
         <v>20.9</v>
@@ -4436,7 +4442,7 @@
         <v>99</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E75" s="1">
         <v>10.5</v>
@@ -4500,7 +4506,7 @@
         <v>101</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E77" s="1">
         <v>13.6</v>
@@ -4533,7 +4539,7 @@
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E78" s="1">
         <v>17.100000000000001</v>
@@ -4726,7 +4732,7 @@
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E84" s="1">
         <v>21.5</v>
@@ -4792,7 +4798,7 @@
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1" t="s">
-        <v>21</v>
+        <v>520</v>
       </c>
       <c r="E86" s="1">
         <v>19.399999999999999</v>
@@ -4856,7 +4862,7 @@
         <v>112</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E88" s="1">
         <v>10.6</v>
@@ -4953,7 +4959,7 @@
         <v>115</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E91" s="1">
         <v>20</v>
@@ -5147,7 +5153,7 @@
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E97" s="1">
         <v>26</v>
@@ -5212,7 +5218,7 @@
         <v>123</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E99" s="1">
         <v>8.4</v>
@@ -5340,7 +5346,7 @@
         <v>127</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E103" s="1">
         <v>16.7</v>
@@ -5372,7 +5378,7 @@
         <v>128</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E104" s="1">
         <v>15.2</v>
@@ -5404,7 +5410,7 @@
         <v>129</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E105" s="1">
         <v>13.2</v>
@@ -5500,7 +5506,7 @@
         <v>132</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E108" s="1">
         <v>19.3</v>
@@ -5564,7 +5570,7 @@
         <v>134</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>22</v>
+        <v>523</v>
       </c>
       <c r="E110" s="1">
         <v>17.3</v>
@@ -5597,7 +5603,7 @@
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E111" s="1">
         <v>16.7</v>
@@ -5629,7 +5635,7 @@
         <v>136</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E112" s="1">
         <v>13.6</v>
@@ -5726,7 +5732,7 @@
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E115" s="1">
         <v>20.6</v>
@@ -5758,7 +5764,7 @@
         <v>140</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E116" s="1">
         <v>17.399999999999999</v>
@@ -5823,7 +5829,7 @@
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E118" s="1">
         <v>16.7</v>
@@ -5887,7 +5893,7 @@
         <v>144</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E120" s="1">
         <v>14.8</v>
@@ -5919,7 +5925,7 @@
         <v>145</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E121" s="1">
         <v>13.8</v>
@@ -5983,7 +5989,7 @@
         <v>147</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E123" s="1">
         <v>13.3</v>
@@ -6015,7 +6021,7 @@
         <v>148</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E124" s="1">
         <v>13.2</v>
@@ -6176,7 +6182,7 @@
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E129" s="1">
         <v>28.8</v>
@@ -6208,7 +6214,7 @@
         <v>154</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E130" s="1">
         <v>15.4</v>
@@ -6240,7 +6246,7 @@
         <v>155</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E131" s="1">
         <v>14.1</v>
@@ -6433,7 +6439,7 @@
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E137" s="1">
         <v>20.2</v>
@@ -6626,7 +6632,7 @@
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E143" s="1">
         <v>24.7</v>
@@ -6659,7 +6665,7 @@
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E144" s="1">
         <v>23.6</v>
@@ -6757,7 +6763,7 @@
         <v>171</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E147" s="1">
         <v>15.4</v>
@@ -6789,7 +6795,7 @@
         <v>172</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E148" s="1">
         <v>12</v>
@@ -6821,7 +6827,7 @@
         <v>173</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E149" s="1">
         <v>9.8000000000000007</v>
@@ -6886,7 +6892,7 @@
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E151" s="1">
         <v>23.3</v>
@@ -6982,7 +6988,7 @@
         <v>178</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>25</v>
+        <v>519</v>
       </c>
       <c r="E154" s="1">
         <v>17.100000000000001</v>
@@ -7111,7 +7117,7 @@
       </c>
       <c r="C158" s="1"/>
       <c r="D158" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E158" s="1">
         <v>27.9</v>
@@ -7143,7 +7149,7 @@
         <v>183</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E159" s="1">
         <v>13</v>
@@ -7207,7 +7213,7 @@
         <v>185</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E161" s="1">
         <v>25.4</v>
@@ -7271,7 +7277,7 @@
         <v>187</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E163" s="1">
         <v>16.5</v>
@@ -7399,7 +7405,7 @@
         <v>191</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E167" s="1">
         <v>31.1</v>
@@ -7432,7 +7438,7 @@
       </c>
       <c r="C168" s="1"/>
       <c r="D168" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E168" s="1">
         <v>20.8</v>
@@ -7464,7 +7470,7 @@
         <v>193</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E169" s="1">
         <v>12.5</v>
@@ -7496,7 +7502,7 @@
         <v>194</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E170" s="1">
         <v>11.7</v>
@@ -7528,7 +7534,7 @@
         <v>195</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E171" s="1">
         <v>14.8</v>
@@ -7560,7 +7566,7 @@
         <v>196</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E172" s="1">
         <v>13.8</v>
@@ -7721,7 +7727,7 @@
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E177" s="1">
         <v>28.3</v>
@@ -7753,7 +7759,7 @@
         <v>202</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E178" s="1">
         <v>20.100000000000001</v>
@@ -7785,7 +7791,7 @@
         <v>203</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E179" s="1">
         <v>13.7</v>
@@ -7881,7 +7887,7 @@
         <v>206</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E182" s="1">
         <v>12.2</v>
@@ -7977,7 +7983,7 @@
         <v>209</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E185" s="1">
         <v>16.399999999999999</v>
@@ -8041,7 +8047,7 @@
         <v>211</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E187" s="1">
         <v>13.9</v>
@@ -8298,7 +8304,7 @@
       </c>
       <c r="C195" s="1"/>
       <c r="D195" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E195" s="1">
         <v>26.1</v>
@@ -8330,7 +8336,7 @@
         <v>220</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E196" s="1">
         <v>17</v>
@@ -8362,7 +8368,7 @@
         <v>221</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E197" s="1">
         <v>13.8</v>
@@ -8618,7 +8624,7 @@
         <v>229</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E205" s="1">
         <v>15</v>
@@ -8650,7 +8656,7 @@
         <v>230</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E206" s="1">
         <v>14.4</v>
@@ -8682,7 +8688,7 @@
         <v>231</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E207" s="1">
         <v>12.2</v>
@@ -8843,7 +8849,7 @@
       </c>
       <c r="C212" s="1"/>
       <c r="D212" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E212" s="1">
         <v>23.6</v>
@@ -8907,7 +8913,7 @@
         <v>238</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E214" s="1">
         <v>10.199999999999999</v>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05111786-FC54-47B2-86F5-452A860D58C3}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55689F1F-13E8-420E-8314-EE38933CB507}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
@@ -9138,7 +9138,7 @@
         <v>245</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E221" s="1">
         <v>13.4</v>
@@ -9331,7 +9331,7 @@
         <v>251</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E227" s="1">
         <v>19</v>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="C228" s="1"/>
       <c r="D228" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E228" s="1">
         <v>18.600000000000001</v>
@@ -9684,7 +9684,7 @@
         <v>262</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E238" s="1">
         <v>20.8</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="C239" s="1"/>
       <c r="D239" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E239" s="1">
         <v>17.399999999999999</v>
@@ -9813,7 +9813,7 @@
         <v>266</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E242" s="1">
         <v>11.8</v>
@@ -10037,7 +10037,7 @@
         <v>273</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E249" s="1">
         <v>18.7</v>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="C288" s="1"/>
       <c r="D288" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E288" s="1">
         <v>18.399999999999999</v>
@@ -11318,7 +11318,7 @@
         <v>313</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E289" s="1">
         <v>13.5</v>
@@ -11542,7 +11542,7 @@
         <v>320</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E296" s="1">
         <v>19.2</v>
@@ -11638,7 +11638,7 @@
         <v>323</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E299" s="1">
         <v>9.9</v>
@@ -11702,7 +11702,7 @@
         <v>325</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E301" s="1">
         <v>9.1999999999999993</v>
@@ -12150,7 +12150,7 @@
         <v>339</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E315" s="1">
         <v>7.4</v>
@@ -12246,7 +12246,7 @@
         <v>342</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E318" s="1">
         <v>14.3</v>
@@ -12855,7 +12855,7 @@
         <v>361</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E337" s="1">
         <v>15.4</v>
@@ -12919,7 +12919,7 @@
         <v>363</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E339" s="1">
         <v>10.199999999999999</v>
@@ -13143,7 +13143,7 @@
         <v>370</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E346" s="1">
         <v>7.6</v>
@@ -13719,7 +13719,7 @@
         <v>388</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E364" s="1">
         <v>13.4</v>
@@ -13943,7 +13943,7 @@
         <v>395</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E371" s="1">
         <v>6.3</v>
@@ -14039,7 +14039,7 @@
         <v>398</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E374" s="1">
         <v>12.5</v>
@@ -14263,7 +14263,7 @@
         <v>405</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E381" s="1">
         <v>8.6</v>
@@ -14999,7 +14999,7 @@
         <v>428</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E404" s="1">
         <v>8.1999999999999993</v>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55689F1F-13E8-420E-8314-EE38933CB507}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62FFA30F-5A49-4041-9C0E-7735BFB4A2F2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -16000,10 +16000,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19E893F-F6CA-495F-B37D-0D5DEFFEED8B}">
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -16020,7 +16020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>7</v>
       </c>
@@ -16033,8 +16033,12 @@
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="str">
+        <f>VLOOKUP(B2,players!A:B,2)</f>
+        <v>Anthony Davis</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7</v>
       </c>
@@ -16047,8 +16051,12 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="str">
+        <f>VLOOKUP(B3,players!A:B,2)</f>
+        <v>Kel'el Ware</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>7</v>
       </c>
@@ -16061,8 +16069,12 @@
       <c r="D4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="str">
+        <f>VLOOKUP(B4,players!A:B,2)</f>
+        <v>Ausar Thompson</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
@@ -16075,8 +16087,12 @@
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="str">
+        <f>VLOOKUP(B5,players!A:B,2)</f>
+        <v>Ja Morant</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>7</v>
       </c>
@@ -16089,8 +16105,12 @@
       <c r="D6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="str">
+        <f>VLOOKUP(B6,players!A:B,2)</f>
+        <v>Scottie Barnes</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -16103,8 +16123,12 @@
       <c r="D7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="str">
+        <f>VLOOKUP(B7,players!A:B,2)</f>
+        <v>Dejounte Murray</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -16117,8 +16141,12 @@
       <c r="D8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="str">
+        <f>VLOOKUP(B8,players!A:B,2)</f>
+        <v>Onyeka Okongwu</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -16131,8 +16159,12 @@
       <c r="D9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="str">
+        <f>VLOOKUP(B9,players!A:B,2)</f>
+        <v>Matas Buzelis</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -16145,8 +16177,12 @@
       <c r="D10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="str">
+        <f>VLOOKUP(B10,players!A:B,2)</f>
+        <v>Anthony Edwards</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -16159,8 +16195,12 @@
       <c r="D11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="str">
+        <f>VLOOKUP(B11,players!A:B,2)</f>
+        <v>Tyrese Maxey</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
@@ -16173,8 +16213,12 @@
       <c r="D12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="str">
+        <f>VLOOKUP(B12,players!A:B,2)</f>
+        <v>Donte DiVincenzo</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
@@ -16187,8 +16231,12 @@
       <c r="D13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="str">
+        <f>VLOOKUP(B13,players!A:B,2)</f>
+        <v>Mikal Bridges</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -16201,8 +16249,12 @@
       <c r="D14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="str">
+        <f>VLOOKUP(B14,players!A:B,2)</f>
+        <v>Alperen Şengün</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -16215,8 +16267,12 @@
       <c r="D15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="str">
+        <f>VLOOKUP(B15,players!A:B,2)</f>
+        <v>Kevin Durant</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -16229,13 +16285,17 @@
       <c r="D16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F16" t="str">
+        <f>VLOOKUP(B16,players!A:B,2)</f>
+        <v>Brandon Miller</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>438</v>
@@ -16243,8 +16303,12 @@
       <c r="D17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F17" t="str">
+        <f>VLOOKUP(B17,players!A:B,2)</f>
+        <v>Jalen Green</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -16257,8 +16321,12 @@
       <c r="D18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F18" t="str">
+        <f>VLOOKUP(B18,players!A:B,2)</f>
+        <v>Tyler Herro</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2</v>
       </c>
@@ -16271,8 +16339,12 @@
       <c r="D19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F19" t="str">
+        <f>VLOOKUP(B19,players!A:B,2)</f>
+        <v>Trae Young</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3</v>
       </c>
@@ -16285,8 +16357,12 @@
       <c r="D20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F20" t="str">
+        <f>VLOOKUP(B20,players!A:B,2)</f>
+        <v>Jalen Duren</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3</v>
       </c>
@@ -16299,8 +16375,12 @@
       <c r="D21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F21" t="str">
+        <f>VLOOKUP(B21,players!A:B,2)</f>
+        <v>Luka Dončić</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3</v>
       </c>
@@ -16313,8 +16393,12 @@
       <c r="D22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F22" t="str">
+        <f>VLOOKUP(B22,players!A:B,2)</f>
+        <v>Kawhi Leonard</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3</v>
       </c>
@@ -16327,8 +16411,12 @@
       <c r="D23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F23" t="str">
+        <f>VLOOKUP(B23,players!A:B,2)</f>
+        <v>Jaren Jackson Jr.</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3</v>
       </c>
@@ -16341,8 +16429,12 @@
       <c r="D24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F24" t="str">
+        <f>VLOOKUP(B24,players!A:B,2)</f>
+        <v>OG Anunoby</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -16355,8 +16447,12 @@
       <c r="D25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F25" t="str">
+        <f>VLOOKUP(B25,players!A:B,2)</f>
+        <v>Kyrie Irving</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -16369,8 +16465,12 @@
       <c r="D26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F26" t="str">
+        <f>VLOOKUP(B26,players!A:B,2)</f>
+        <v>Bam Adebayo</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
@@ -16383,8 +16483,12 @@
       <c r="D27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F27" t="str">
+        <f>VLOOKUP(B27,players!A:B,2)</f>
+        <v>Jaylen Brown</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4</v>
       </c>
@@ -16397,8 +16501,12 @@
       <c r="D28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F28" t="str">
+        <f>VLOOKUP(B28,players!A:B,2)</f>
+        <v>Stephon Castle</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -16411,8 +16519,12 @@
       <c r="D29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F29" t="str">
+        <f>VLOOKUP(B29,players!A:B,2)</f>
+        <v>Franz Wagner</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4</v>
       </c>
@@ -16425,8 +16537,12 @@
       <c r="D30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F30" t="str">
+        <f>VLOOKUP(B30,players!A:B,2)</f>
+        <v>Donovan Mitchell</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4</v>
       </c>
@@ -16439,8 +16555,12 @@
       <c r="D31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F31" t="str">
+        <f>VLOOKUP(B31,players!A:B,2)</f>
+        <v>DeMar DeRozan</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -16453,8 +16573,12 @@
       <c r="D32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F32" t="str">
+        <f>VLOOKUP(B32,players!A:B,2)</f>
+        <v>Joel Embiid</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>5</v>
       </c>
@@ -16467,8 +16591,12 @@
       <c r="D33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F33" t="str">
+        <f>VLOOKUP(B33,players!A:B,2)</f>
+        <v>Giannis Antetokounmpo</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -16481,13 +16609,17 @@
       <c r="D34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F34" t="str">
+        <f>VLOOKUP(B34,players!A:B,2)</f>
+        <v>VJ Edgecombe</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35">
-        <v>219</v>
+        <v>143</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>25</v>
@@ -16495,8 +16627,12 @@
       <c r="D35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F35" t="str">
+        <f>VLOOKUP(B35,players!A:B,2)</f>
+        <v>James Harden</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -16509,13 +16645,17 @@
       <c r="D36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F36" t="str">
+        <f>VLOOKUP(B36,players!A:B,2)</f>
+        <v>Michael Porter Jr.</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>5</v>
       </c>
       <c r="B37">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>24</v>
@@ -16523,8 +16663,12 @@
       <c r="D37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F37" t="str">
+        <f>VLOOKUP(B37,players!A:B,2)</f>
+        <v>Naz Reid</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>6</v>
       </c>
@@ -16537,8 +16681,12 @@
       <c r="D38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F38" t="str">
+        <f>VLOOKUP(B38,players!A:B,2)</f>
+        <v>Nikola Jokić</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6</v>
       </c>
@@ -16551,8 +16699,12 @@
       <c r="D39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F39" t="str">
+        <f>VLOOKUP(B39,players!A:B,2)</f>
+        <v>Paolo Banchero</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>6</v>
       </c>
@@ -16565,8 +16717,12 @@
       <c r="D40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F40" t="str">
+        <f>VLOOKUP(B40,players!A:B,2)</f>
+        <v>Miles Bridges</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>6</v>
       </c>
@@ -16579,8 +16735,12 @@
       <c r="D41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F41" t="str">
+        <f>VLOOKUP(B41,players!A:B,2)</f>
+        <v>Cade Cunningham</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>6</v>
       </c>
@@ -16593,8 +16753,12 @@
       <c r="D42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F42" t="str">
+        <f>VLOOKUP(B42,players!A:B,2)</f>
+        <v>Derrick White</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>6</v>
       </c>
@@ -16607,13 +16771,17 @@
       <c r="D43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F43" t="str">
+        <f>VLOOKUP(B43,players!A:B,2)</f>
+        <v>Keyonte George</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>21</v>
@@ -16621,8 +16789,12 @@
       <c r="D44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F44" t="str">
+        <f>VLOOKUP(B44,players!A:B,2)</f>
+        <v>Donovan Clingan</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -16635,8 +16807,12 @@
       <c r="D45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F45" t="str">
+        <f>VLOOKUP(B45,players!A:B,2)</f>
+        <v>Jalen Johnson</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>8</v>
       </c>
@@ -16649,8 +16825,12 @@
       <c r="D46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F46" t="str">
+        <f>VLOOKUP(B46,players!A:B,2)</f>
+        <v>Trey Murphy III</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>8</v>
       </c>
@@ -16663,8 +16843,12 @@
       <c r="D47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F47" t="str">
+        <f>VLOOKUP(B47,players!A:B,2)</f>
+        <v>Zion Williamson</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>8</v>
       </c>
@@ -16677,8 +16861,12 @@
       <c r="D48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F48" t="str">
+        <f>VLOOKUP(B48,players!A:B,2)</f>
+        <v>De'Aaron Fox</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>8</v>
       </c>
@@ -16691,8 +16879,12 @@
       <c r="D49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F49" t="str">
+        <f>VLOOKUP(B49,players!A:B,2)</f>
+        <v>Norman Powell</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>9</v>
       </c>
@@ -16705,8 +16897,12 @@
       <c r="D50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F50" t="str">
+        <f>VLOOKUP(B50,players!A:B,2)</f>
+        <v>Jayson Tatum</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>9</v>
       </c>
@@ -16719,8 +16915,12 @@
       <c r="D51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F51" t="str">
+        <f>VLOOKUP(B51,players!A:B,2)</f>
+        <v>Jarrett Allen</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>9</v>
       </c>
@@ -16733,8 +16933,12 @@
       <c r="D52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F52" t="str">
+        <f>VLOOKUP(B52,players!A:B,2)</f>
+        <v>Brandon Ingram</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>9</v>
       </c>
@@ -16747,8 +16951,12 @@
       <c r="D53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F53" t="str">
+        <f>VLOOKUP(B53,players!A:B,2)</f>
+        <v>Shaedon Sharpe</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>9</v>
       </c>
@@ -16761,8 +16969,12 @@
       <c r="D54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F54" t="str">
+        <f>VLOOKUP(B54,players!A:B,2)</f>
+        <v>Stephen Curry</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9</v>
       </c>
@@ -16775,8 +16987,12 @@
       <c r="D55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F55" t="str">
+        <f>VLOOKUP(B55,players!A:B,2)</f>
+        <v>Darius Garland</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10</v>
       </c>
@@ -16789,8 +17005,12 @@
       <c r="D56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F56" t="str">
+        <f>VLOOKUP(B56,players!A:B,2)</f>
+        <v>Nikola Vučević</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>10</v>
       </c>
@@ -16803,8 +17023,12 @@
       <c r="D57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F57" t="str">
+        <f>VLOOKUP(B57,players!A:B,2)</f>
+        <v>Alex Sarr</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>10</v>
       </c>
@@ -16817,8 +17041,12 @@
       <c r="D58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F58" t="str">
+        <f>VLOOKUP(B58,players!A:B,2)</f>
+        <v>Julius Randle</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>10</v>
       </c>
@@ -16831,8 +17059,12 @@
       <c r="D59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F59" t="str">
+        <f>VLOOKUP(B59,players!A:B,2)</f>
+        <v>Jalen Williams</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>10</v>
       </c>
@@ -16845,8 +17077,12 @@
       <c r="D60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F60" t="str">
+        <f>VLOOKUP(B60,players!A:B,2)</f>
+        <v>Jamal Murray</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>10</v>
       </c>
@@ -16859,8 +17095,12 @@
       <c r="D61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F61" t="str">
+        <f>VLOOKUP(B61,players!A:B,2)</f>
+        <v>Jalen Brunson</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>11</v>
       </c>
@@ -16873,8 +17113,12 @@
       <c r="D62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F62" t="str">
+        <f>VLOOKUP(B62,players!A:B,2)</f>
+        <v>Domantas Sabonis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>11</v>
       </c>
@@ -16887,8 +17131,12 @@
       <c r="D63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F63" t="str">
+        <f>VLOOKUP(B63,players!A:B,2)</f>
+        <v>Desmond Bane</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>11</v>
       </c>
@@ -16901,8 +17149,12 @@
       <c r="D64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F64" t="str">
+        <f>VLOOKUP(B64,players!A:B,2)</f>
+        <v>Amen Thompson</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>11</v>
       </c>
@@ -16915,8 +17167,12 @@
       <c r="D65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F65" t="str">
+        <f>VLOOKUP(B65,players!A:B,2)</f>
+        <v>Shai Gilgeous-Alexander</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>11</v>
       </c>
@@ -16929,8 +17185,12 @@
       <c r="D66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F66" t="str">
+        <f>VLOOKUP(B66,players!A:B,2)</f>
+        <v>CJ McCollum</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>11</v>
       </c>
@@ -16943,8 +17203,12 @@
       <c r="D67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F67" t="str">
+        <f>VLOOKUP(B67,players!A:B,2)</f>
+        <v>Paul George</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>12</v>
       </c>
@@ -16957,8 +17221,12 @@
       <c r="D68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F68" t="str">
+        <f>VLOOKUP(B68,players!A:B,2)</f>
+        <v>Chet Holmgren</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>12</v>
       </c>
@@ -16971,8 +17239,12 @@
       <c r="D69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F69" t="str">
+        <f>VLOOKUP(B69,players!A:B,2)</f>
+        <v>Lauri Markkanen</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>12</v>
       </c>
@@ -16985,8 +17257,12 @@
       <c r="D70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F70" t="str">
+        <f>VLOOKUP(B70,players!A:B,2)</f>
+        <v>Devin Booker</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>12</v>
       </c>
@@ -16999,8 +17275,12 @@
       <c r="D71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F71" t="str">
+        <f>VLOOKUP(B71,players!A:B,2)</f>
+        <v>Tyrese Haliburton</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>12</v>
       </c>
@@ -17013,8 +17293,12 @@
       <c r="D72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F72" t="str">
+        <f>VLOOKUP(B72,players!A:B,2)</f>
+        <v>Brandin Podziemski</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>12</v>
       </c>
@@ -17027,8 +17311,12 @@
       <c r="D73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F73" t="str">
+        <f>VLOOKUP(B73,players!A:B,2)</f>
+        <v>Kevin Porter Jr.</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>13</v>
       </c>
@@ -17041,8 +17329,12 @@
       <c r="D74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F74" t="str">
+        <f>VLOOKUP(B74,players!A:B,2)</f>
+        <v>Victor Wembanyama</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>13</v>
       </c>
@@ -17055,8 +17347,12 @@
       <c r="D75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F75" t="str">
+        <f>VLOOKUP(B75,players!A:B,2)</f>
+        <v>Josh Giddey</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>13</v>
       </c>
@@ -17069,8 +17365,12 @@
       <c r="D76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F76" t="str">
+        <f>VLOOKUP(B76,players!A:B,2)</f>
+        <v>Deni Avdija</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>13</v>
       </c>
@@ -17083,8 +17383,12 @@
       <c r="D77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F77" t="str">
+        <f>VLOOKUP(B77,players!A:B,2)</f>
+        <v>Pascal Siakam</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>13</v>
       </c>
@@ -17097,8 +17401,12 @@
       <c r="D78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F78" t="str">
+        <f>VLOOKUP(B78,players!A:B,2)</f>
+        <v>Andrew Nembhard</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>13</v>
       </c>
@@ -17111,8 +17419,12 @@
       <c r="D79">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F79" t="str">
+        <f>VLOOKUP(B79,players!A:B,2)</f>
+        <v>Austin Reaves</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>14</v>
       </c>
@@ -17125,8 +17437,12 @@
       <c r="D80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F80" t="str">
+        <f>VLOOKUP(B80,players!A:B,2)</f>
+        <v>Evan Mobley</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>14</v>
       </c>
@@ -17139,8 +17455,12 @@
       <c r="D81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F81" t="str">
+        <f>VLOOKUP(B81,players!A:B,2)</f>
+        <v>LeBron James</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>14</v>
       </c>
@@ -17153,8 +17473,12 @@
       <c r="D82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F82" t="str">
+        <f>VLOOKUP(B82,players!A:B,2)</f>
+        <v>Cooper Flagg</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>14</v>
       </c>
@@ -17167,8 +17491,12 @@
       <c r="D83">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F83" t="str">
+        <f>VLOOKUP(B83,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>14</v>
       </c>
@@ -17181,8 +17509,12 @@
       <c r="D84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F84" t="str">
+        <f>VLOOKUP(B84,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>14</v>
       </c>
@@ -17194,6 +17526,10 @@
       </c>
       <c r="D85">
         <v>1</v>
+      </c>
+      <c r="F85" t="str">
+        <f>VLOOKUP(B85,players!A:B,2)</f>
+        <v>LaMelo Ball</v>
       </c>
     </row>
   </sheetData>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62FFA30F-5A49-4041-9C0E-7735BFB4A2F2}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6237B9C0-4D38-4F99-8D99-ECB2CB384BEE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -22045,8 +22045,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D71993F-8E81-4064-B756-2C14E71F7CC9}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -22067,6 +22073,158 @@
       <c r="F1" s="2" t="s">
         <v>478</v>
       </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1638000</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1050000</v>
+      </c>
+      <c r="C6" s="2">
+        <v>300000</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>750000</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>600000</v>
+      </c>
+      <c r="C15" s="2">
+        <v>600000</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6237B9C0-4D38-4F99-8D99-ECB2CB384BEE}"/>
+  <xr:revisionPtr revIDLastSave="575" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40F15487-114E-48DB-81F8-CF62C3BD08E8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="635">
   <si>
     <t>player_id</t>
   </si>
@@ -1623,6 +1623,339 @@
   </si>
   <si>
     <t>SG/SF</t>
+  </si>
+  <si>
+    <t>P2026_R1_T09</t>
+  </si>
+  <si>
+    <t>P2026_R2_T07</t>
+  </si>
+  <si>
+    <t>P2028_R1_T07</t>
+  </si>
+  <si>
+    <t>P2028_R2_T07</t>
+  </si>
+  <si>
+    <t>P2029_R1_T07</t>
+  </si>
+  <si>
+    <t>P2029_R2_T07</t>
+  </si>
+  <si>
+    <t>P2026_R1_T01</t>
+  </si>
+  <si>
+    <t>P2026_R1_T11</t>
+  </si>
+  <si>
+    <t>P2026_R1_T02</t>
+  </si>
+  <si>
+    <t>P2026_R2_T01</t>
+  </si>
+  <si>
+    <t>P2026_R2_T05</t>
+  </si>
+  <si>
+    <t>P2027_R1_T01</t>
+  </si>
+  <si>
+    <t>P2027_R2_T01</t>
+  </si>
+  <si>
+    <t>P2027_R2_T05</t>
+  </si>
+  <si>
+    <t>P2027_R2_T06</t>
+  </si>
+  <si>
+    <t>P2028_R1_T01</t>
+  </si>
+  <si>
+    <t>P2028_R2_T01</t>
+  </si>
+  <si>
+    <t>P2029_R1_T01</t>
+  </si>
+  <si>
+    <t>P2029_R2_T01</t>
+  </si>
+  <si>
+    <t>P2026_R1_T10</t>
+  </si>
+  <si>
+    <t>P2026_R2_T02</t>
+  </si>
+  <si>
+    <t>P2027_R1_T02</t>
+  </si>
+  <si>
+    <t>P2028_R1_T02</t>
+  </si>
+  <si>
+    <t>P2029_R1_T02</t>
+  </si>
+  <si>
+    <t>P2028_R2_T02</t>
+  </si>
+  <si>
+    <t>P2029_R2_T02</t>
+  </si>
+  <si>
+    <t>P2026_R1_T03</t>
+  </si>
+  <si>
+    <t>P2027_R1_T03</t>
+  </si>
+  <si>
+    <t>P2027_R2_T03</t>
+  </si>
+  <si>
+    <t>P2028_R1_T03</t>
+  </si>
+  <si>
+    <t>P2028_R2_T03</t>
+  </si>
+  <si>
+    <t>P2029_R1_T03</t>
+  </si>
+  <si>
+    <t>P2029_R2_T03</t>
+  </si>
+  <si>
+    <t>P2026_R2_T04</t>
+  </si>
+  <si>
+    <t>P2027_R2_T04</t>
+  </si>
+  <si>
+    <t>P2027_R1_T04</t>
+  </si>
+  <si>
+    <t>P2028_R1_T04</t>
+  </si>
+  <si>
+    <t>P2028_R2_T04</t>
+  </si>
+  <si>
+    <t>P2029_R1_T04</t>
+  </si>
+  <si>
+    <t>P2029_R2_T04</t>
+  </si>
+  <si>
+    <t>P2026_R1_T14</t>
+  </si>
+  <si>
+    <t>P2026_R1_T13</t>
+  </si>
+  <si>
+    <t>P2026_R2_T14</t>
+  </si>
+  <si>
+    <t>P2026_R2_T10</t>
+  </si>
+  <si>
+    <t>P2026_R1_T05</t>
+  </si>
+  <si>
+    <t>P2027_R1_T05</t>
+  </si>
+  <si>
+    <t>P2027_R2_T07</t>
+  </si>
+  <si>
+    <t>P2028_R2_T05</t>
+  </si>
+  <si>
+    <t>P2029_R1_T05</t>
+  </si>
+  <si>
+    <t>P2029_R2_T05</t>
+  </si>
+  <si>
+    <t>P2026_R1_T06</t>
+  </si>
+  <si>
+    <t>P2026_R2_T06</t>
+  </si>
+  <si>
+    <t>P2027_R1_T06</t>
+  </si>
+  <si>
+    <t>P2028_R1_T06</t>
+  </si>
+  <si>
+    <t>P2029_R1_T06</t>
+  </si>
+  <si>
+    <t>P2028_R1_T05</t>
+  </si>
+  <si>
+    <t>P2029_R2_T06</t>
+  </si>
+  <si>
+    <t>P2026_R1_T08</t>
+  </si>
+  <si>
+    <t>P2026_R2_T08</t>
+  </si>
+  <si>
+    <t>P2026_R2_T03</t>
+  </si>
+  <si>
+    <t>P2027_R1_T08</t>
+  </si>
+  <si>
+    <t>P2027_R2_T08</t>
+  </si>
+  <si>
+    <t>P2028_R1_T08</t>
+  </si>
+  <si>
+    <t>P2028_R2_T08</t>
+  </si>
+  <si>
+    <t>P2028_R2_T06</t>
+  </si>
+  <si>
+    <t>P2029_R1_T08</t>
+  </si>
+  <si>
+    <t>P2029_R2_T08</t>
+  </si>
+  <si>
+    <t>P2026_R2_T09</t>
+  </si>
+  <si>
+    <t>P2027_R1_T09</t>
+  </si>
+  <si>
+    <t>P2027_R2_T09</t>
+  </si>
+  <si>
+    <t>P2028_R1_T09</t>
+  </si>
+  <si>
+    <t>P2028_R2_T09</t>
+  </si>
+  <si>
+    <t>P2029_R1_T09</t>
+  </si>
+  <si>
+    <t>P2029_R2_T09</t>
+  </si>
+  <si>
+    <t>P2026_R2_T13</t>
+  </si>
+  <si>
+    <t>P2027_R1_T10</t>
+  </si>
+  <si>
+    <t>P2028_R1_T10</t>
+  </si>
+  <si>
+    <t>P2029_R1_T10</t>
+  </si>
+  <si>
+    <t>P2029_R2_T10</t>
+  </si>
+  <si>
+    <t>P2028_R2_T10</t>
+  </si>
+  <si>
+    <t>P2027_R1_T07</t>
+  </si>
+  <si>
+    <t>P2027_R2_T10</t>
+  </si>
+  <si>
+    <t>P2026_R2_T11</t>
+  </si>
+  <si>
+    <t>P2029_R2_T11</t>
+  </si>
+  <si>
+    <t>P2028_R2_T11</t>
+  </si>
+  <si>
+    <t>P2027_R2_T11</t>
+  </si>
+  <si>
+    <t>P2027_R1_T11</t>
+  </si>
+  <si>
+    <t>P2028_R1_T11</t>
+  </si>
+  <si>
+    <t>P2029_R1_T11</t>
+  </si>
+  <si>
+    <t>P2026_R1_T12</t>
+  </si>
+  <si>
+    <t>P2026_R2_T12</t>
+  </si>
+  <si>
+    <t>P2027_R1_T12</t>
+  </si>
+  <si>
+    <t>P2027_R2_T12</t>
+  </si>
+  <si>
+    <t>P2028_R1_T12</t>
+  </si>
+  <si>
+    <t>P2028_R2_T12</t>
+  </si>
+  <si>
+    <t>P2029_R1_T12</t>
+  </si>
+  <si>
+    <t>P2029_R2_T12</t>
+  </si>
+  <si>
+    <t>P2026_R1_T04</t>
+  </si>
+  <si>
+    <t>P2027_R1_T13</t>
+  </si>
+  <si>
+    <t>P2027_R2_T13</t>
+  </si>
+  <si>
+    <t>P2028_R1_T13</t>
+  </si>
+  <si>
+    <t>P2028_R2_T13</t>
+  </si>
+  <si>
+    <t>P2029_R1_T13</t>
+  </si>
+  <si>
+    <t>P2029_R2_T13</t>
+  </si>
+  <si>
+    <t>P2027_R1_T14</t>
+  </si>
+  <si>
+    <t>P2027_R2_T14</t>
+  </si>
+  <si>
+    <t>P2027_R2_T02</t>
+  </si>
+  <si>
+    <t>P2028_R1_T14</t>
+  </si>
+  <si>
+    <t>P2028_R2_T14</t>
+  </si>
+  <si>
+    <t>P2029_R1_T14</t>
+  </si>
+  <si>
+    <t>P2029_R2_T14</t>
   </si>
 </sst>
 </file>
@@ -21998,10 +22331,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD8F2BA-1077-4C4D-A103-CA2B53B5C282}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -22036,6 +22373,1893 @@
       </c>
       <c r="E2">
         <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2026</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2026</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>526</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2028</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2028</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>528</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>2029</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>529</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>2029</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>530</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>2026</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>531</v>
+      </c>
+      <c r="B10">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2026</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>532</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>2026</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>533</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>2026</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>534</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>2026</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>535</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>2027</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>536</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>2027</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>537</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>2027</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>538</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>2027</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>539</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>2028</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>540</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>2028</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>541</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>2029</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>542</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>2029</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>543</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>2026</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>544</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>2026</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>545</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>2027</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>546</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>2028</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>548</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>2028</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>547</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>2029</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>549</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>2029</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>550</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>2026</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>551</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>2027</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>552</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>2027</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>553</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>2028</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>554</v>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>2028</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>555</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>2029</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>556</v>
+      </c>
+      <c r="B35">
+        <v>3</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>2029</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>557</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>2026</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>559</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>2027</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>558</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>2027</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>560</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>2028</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>561</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>2028</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>562</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>2029</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>563</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>2029</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>564</v>
+      </c>
+      <c r="B43">
+        <v>14</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>2026</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>565</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>2026</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>566</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>2026</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>567</v>
+      </c>
+      <c r="B46">
+        <v>10</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>2026</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>569</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>2027</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>570</v>
+      </c>
+      <c r="B48">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>2027</v>
+      </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>571</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <v>2028</v>
+      </c>
+      <c r="E49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>572</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>2029</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>573</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
+        <v>2029</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>574</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>2026</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>568</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>2026</v>
+      </c>
+      <c r="E53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>575</v>
+      </c>
+      <c r="B54">
+        <v>6</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>2026</v>
+      </c>
+      <c r="E54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>576</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>2027</v>
+      </c>
+      <c r="E55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>577</v>
+      </c>
+      <c r="B56">
+        <v>6</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>2028</v>
+      </c>
+      <c r="E56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>579</v>
+      </c>
+      <c r="B57">
+        <v>5</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>2028</v>
+      </c>
+      <c r="E57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>578</v>
+      </c>
+      <c r="B58">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>2029</v>
+      </c>
+      <c r="E58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>580</v>
+      </c>
+      <c r="B59">
+        <v>6</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <v>2029</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>581</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>2026</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>582</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>2026</v>
+      </c>
+      <c r="E61">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>583</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>2026</v>
+      </c>
+      <c r="E62">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>584</v>
+      </c>
+      <c r="B63">
+        <v>8</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>2027</v>
+      </c>
+      <c r="E63">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>585</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>2027</v>
+      </c>
+      <c r="E64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>586</v>
+      </c>
+      <c r="B65">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>2028</v>
+      </c>
+      <c r="E65">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>587</v>
+      </c>
+      <c r="B66">
+        <v>8</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66">
+        <v>2028</v>
+      </c>
+      <c r="E66">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>588</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67">
+        <v>2028</v>
+      </c>
+      <c r="E67">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>589</v>
+      </c>
+      <c r="B68">
+        <v>8</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>2029</v>
+      </c>
+      <c r="E68">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>590</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="D69">
+        <v>2029</v>
+      </c>
+      <c r="E69">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>591</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="D70">
+        <v>2026</v>
+      </c>
+      <c r="E70">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>592</v>
+      </c>
+      <c r="B71">
+        <v>9</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>2027</v>
+      </c>
+      <c r="E71">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>593</v>
+      </c>
+      <c r="B72">
+        <v>9</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72">
+        <v>2027</v>
+      </c>
+      <c r="E72">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>594</v>
+      </c>
+      <c r="B73">
+        <v>9</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>2028</v>
+      </c>
+      <c r="E73">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>595</v>
+      </c>
+      <c r="B74">
+        <v>9</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74">
+        <v>2028</v>
+      </c>
+      <c r="E74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>596</v>
+      </c>
+      <c r="B75">
+        <v>9</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>2029</v>
+      </c>
+      <c r="E75">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>597</v>
+      </c>
+      <c r="B76">
+        <v>9</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>2029</v>
+      </c>
+      <c r="E76">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>598</v>
+      </c>
+      <c r="B77">
+        <v>13</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>2026</v>
+      </c>
+      <c r="E77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>604</v>
+      </c>
+      <c r="B78">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>2027</v>
+      </c>
+      <c r="E78">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>599</v>
+      </c>
+      <c r="B79">
+        <v>10</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79">
+        <v>2027</v>
+      </c>
+      <c r="E79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>605</v>
+      </c>
+      <c r="B80">
+        <v>10</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>2027</v>
+      </c>
+      <c r="E80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>600</v>
+      </c>
+      <c r="B81">
+        <v>10</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>2028</v>
+      </c>
+      <c r="E81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>603</v>
+      </c>
+      <c r="B82">
+        <v>10</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+      <c r="D82">
+        <v>2028</v>
+      </c>
+      <c r="E82">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>601</v>
+      </c>
+      <c r="B83">
+        <v>10</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>2029</v>
+      </c>
+      <c r="E83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>602</v>
+      </c>
+      <c r="B84">
+        <v>10</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84">
+        <v>2029</v>
+      </c>
+      <c r="E84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>606</v>
+      </c>
+      <c r="B85">
+        <v>11</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85">
+        <v>2026</v>
+      </c>
+      <c r="E85">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>610</v>
+      </c>
+      <c r="B86">
+        <v>11</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>2027</v>
+      </c>
+      <c r="E86">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>609</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87">
+        <v>2027</v>
+      </c>
+      <c r="E87">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>611</v>
+      </c>
+      <c r="B88">
+        <v>11</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>2028</v>
+      </c>
+      <c r="E88">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>608</v>
+      </c>
+      <c r="B89">
+        <v>11</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+      <c r="D89">
+        <v>2028</v>
+      </c>
+      <c r="E89">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>612</v>
+      </c>
+      <c r="B90">
+        <v>11</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>2029</v>
+      </c>
+      <c r="E90">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>607</v>
+      </c>
+      <c r="B91">
+        <v>11</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91">
+        <v>2029</v>
+      </c>
+      <c r="E91">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>613</v>
+      </c>
+      <c r="B92">
+        <v>12</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>2026</v>
+      </c>
+      <c r="E92">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>614</v>
+      </c>
+      <c r="B93">
+        <v>12</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <v>2026</v>
+      </c>
+      <c r="E93">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>615</v>
+      </c>
+      <c r="B94">
+        <v>12</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94">
+        <v>2027</v>
+      </c>
+      <c r="E94">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>616</v>
+      </c>
+      <c r="B95">
+        <v>12</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95">
+        <v>2027</v>
+      </c>
+      <c r="E95">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>617</v>
+      </c>
+      <c r="B96">
+        <v>12</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>2028</v>
+      </c>
+      <c r="E96">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>618</v>
+      </c>
+      <c r="B97">
+        <v>12</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+      <c r="D97">
+        <v>2028</v>
+      </c>
+      <c r="E97">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>619</v>
+      </c>
+      <c r="B98">
+        <v>12</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>2029</v>
+      </c>
+      <c r="E98">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>620</v>
+      </c>
+      <c r="B99">
+        <v>12</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99">
+        <v>2029</v>
+      </c>
+      <c r="E99">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>621</v>
+      </c>
+      <c r="B100">
+        <v>4</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
+        <v>2026</v>
+      </c>
+      <c r="E100">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>622</v>
+      </c>
+      <c r="B101">
+        <v>13</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>2027</v>
+      </c>
+      <c r="E101">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>623</v>
+      </c>
+      <c r="B102">
+        <v>13</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102">
+        <v>2027</v>
+      </c>
+      <c r="E102">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>624</v>
+      </c>
+      <c r="B103">
+        <v>13</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>2028</v>
+      </c>
+      <c r="E103">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>625</v>
+      </c>
+      <c r="B104">
+        <v>13</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="D104">
+        <v>2028</v>
+      </c>
+      <c r="E104">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>626</v>
+      </c>
+      <c r="B105">
+        <v>13</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>2029</v>
+      </c>
+      <c r="E105">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>627</v>
+      </c>
+      <c r="B106">
+        <v>13</v>
+      </c>
+      <c r="C106">
+        <v>2</v>
+      </c>
+      <c r="D106">
+        <v>2029</v>
+      </c>
+      <c r="E106">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>628</v>
+      </c>
+      <c r="B107">
+        <v>14</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107">
+        <v>2027</v>
+      </c>
+      <c r="E107">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>629</v>
+      </c>
+      <c r="B108">
+        <v>14</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108">
+        <v>2027</v>
+      </c>
+      <c r="E108">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>630</v>
+      </c>
+      <c r="B109">
+        <v>2</v>
+      </c>
+      <c r="C109">
+        <v>2</v>
+      </c>
+      <c r="D109">
+        <v>2027</v>
+      </c>
+      <c r="E109">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>631</v>
+      </c>
+      <c r="B110">
+        <v>14</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110">
+        <v>2028</v>
+      </c>
+      <c r="E110">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>632</v>
+      </c>
+      <c r="B111">
+        <v>14</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111">
+        <v>2028</v>
+      </c>
+      <c r="E111">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>633</v>
+      </c>
+      <c r="B112">
+        <v>14</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112">
+        <v>2029</v>
+      </c>
+      <c r="E112">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>634</v>
+      </c>
+      <c r="B113">
+        <v>14</v>
+      </c>
+      <c r="C113">
+        <v>2</v>
+      </c>
+      <c r="D113">
+        <v>2029</v>
+      </c>
+      <c r="E113">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="575" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40F15487-114E-48DB-81F8-CF62C3BD08E8}"/>
+  <xr:revisionPtr revIDLastSave="582" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B436B21-DC26-43B0-9411-4ABAAB6BABFB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -17872,7 +17872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003E67E5-331D-4CC3-B636-B44F8A41C81C}">
-  <dimension ref="A1:L177"/>
+  <dimension ref="A1:L176"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -21073,41 +21073,38 @@
         <v>13</v>
       </c>
       <c r="B164">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="C164">
         <v>11</v>
       </c>
       <c r="D164" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="F164" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H164" s="2">
+        <v>6000000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Zach Collins</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B165">
-        <v>150</v>
+        <v>317</v>
       </c>
       <c r="C165">
-        <v>12</v>
-      </c>
-      <c r="D165" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F165" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="H165" s="2">
-        <v>6000000</v>
+        <v>1</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -21115,14 +21112,14 @@
         <v>14</v>
       </c>
       <c r="B166">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -21130,14 +21127,14 @@
         <v>14</v>
       </c>
       <c r="B167">
-        <v>299</v>
+        <v>129</v>
       </c>
       <c r="C167">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -21145,14 +21142,14 @@
         <v>14</v>
       </c>
       <c r="B168">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="C168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -21160,14 +21157,17 @@
         <v>14</v>
       </c>
       <c r="B169">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="C169">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D169" s="2">
+        <v>1000000</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -21175,17 +21175,17 @@
         <v>14</v>
       </c>
       <c r="B170">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="C170">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D170" s="2">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -21193,17 +21193,23 @@
         <v>14</v>
       </c>
       <c r="B171">
-        <v>238</v>
+        <v>19</v>
       </c>
       <c r="C171">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D171" s="2">
-        <v>3000000</v>
+        <v>20500000</v>
+      </c>
+      <c r="F171" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="H171" s="2">
+        <v>20500000</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -21211,23 +21217,17 @@
         <v>14</v>
       </c>
       <c r="B172">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="C172">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D172" s="2">
-        <v>20500000</v>
-      </c>
-      <c r="F172" s="2">
-        <v>20500000</v>
-      </c>
-      <c r="H172" s="2">
-        <v>20500000</v>
+        <v>19500000</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -21235,17 +21235,29 @@
         <v>14</v>
       </c>
       <c r="B173">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C173">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D173" s="2">
-        <v>19500000</v>
+        <v>9500000</v>
+      </c>
+      <c r="F173" s="2">
+        <v>10500000</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H173" s="2">
+        <v>11500000</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -21253,29 +21265,14 @@
         <v>14</v>
       </c>
       <c r="B174">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C174">
-        <v>9</v>
-      </c>
-      <c r="D174" s="2">
-        <v>9500000</v>
-      </c>
-      <c r="F174" s="2">
-        <v>10500000</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H174" s="2">
-        <v>11500000</v>
-      </c>
-      <c r="I174" s="2" t="s">
-        <v>472</v>
+        <v>10</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -21283,14 +21280,14 @@
         <v>14</v>
       </c>
       <c r="B175">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="C175">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L175" t="str">
         <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Quentin Grimes</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -21298,37 +21295,22 @@
         <v>14</v>
       </c>
       <c r="B176">
-        <v>220</v>
+        <v>145</v>
       </c>
       <c r="C176">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D176" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="F176" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="H176" s="2">
+        <v>20000000</v>
       </c>
       <c r="L176" t="str">
         <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177">
-        <v>14</v>
-      </c>
-      <c r="B177">
-        <v>145</v>
-      </c>
-      <c r="C177">
-        <v>12</v>
-      </c>
-      <c r="D177" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="F177" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="H177" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="L177" t="str">
-        <f>VLOOKUP(B177,players!A:B,2)</f>
         <v>LaMelo Ball</v>
       </c>
     </row>
@@ -24345,10 +24327,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>1050000</v>
+        <f>1050000+150000</f>
+        <v>1200000</v>
       </c>
       <c r="C6" s="2">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -24430,7 +24413,9 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2">
+        <v>150000</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="582" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B436B21-DC26-43B0-9411-4ABAAB6BABFB}"/>
+  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DC4B71F-B4B3-4A03-B83A-31A45631BA14}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="635">
   <si>
     <t>player_id</t>
   </si>
@@ -21322,7 +21322,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B357A823-6505-4984-ACC9-40636E218B6C}">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
@@ -21719,23 +21719,23 @@
         <v>5</v>
       </c>
       <c r="B13">
-        <v>209</v>
+        <v>409</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
-        <v>1000000</v>
+        <v>4200000</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H13" s="2">
-        <v>1000000</v>
+        <v>4500000</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>472</v>
@@ -21744,58 +21744,54 @@
       <c r="K13" s="2"/>
       <c r="L13" t="str">
         <f>VLOOKUP(B13,players!A:B,2)</f>
-        <v>Nique Clifford</v>
+        <v>Hansen Yang</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14">
-        <v>409</v>
+        <v>192</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>4000000</v>
+        <v>3200000</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2">
-        <v>4200000</v>
+        <v>3500000</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H14" s="2">
-        <v>4500000</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" t="str">
         <f>VLOOKUP(B14,players!A:B,2)</f>
-        <v>Hansen Yang</v>
+        <v>Tidjane Salaün</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B15">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>3200000</v>
+        <v>1000000</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2">
-        <v>3500000</v>
+        <v>1000000</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>472</v>
@@ -21806,36 +21802,40 @@
       <c r="K15" s="2"/>
       <c r="L15" t="str">
         <f>VLOOKUP(B15,players!A:B,2)</f>
-        <v>Tidjane Salaün</v>
+        <v>Kyle Filipowski</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2">
-        <v>1000000</v>
+        <v>5500000</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+      <c r="H16" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" t="str">
         <f>VLOOKUP(B16,players!A:B,2)</f>
-        <v>Kyle Filipowski</v>
+        <v>Kon Knueppel</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -21843,32 +21843,28 @@
         <v>9</v>
       </c>
       <c r="B17">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2">
-        <v>5500000</v>
+        <v>1000000</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H17" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" t="str">
         <f>VLOOKUP(B17,players!A:B,2)</f>
-        <v>Kon Knueppel</v>
+        <v>Jaylon Tyson</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -21876,10 +21872,10 @@
         <v>9</v>
       </c>
       <c r="B18">
-        <v>123</v>
+        <v>410</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2">
         <v>1000000</v>
@@ -21897,36 +21893,40 @@
       <c r="K18" s="2"/>
       <c r="L18" t="str">
         <f>VLOOKUP(B18,players!A:B,2)</f>
-        <v>Jaylon Tyson</v>
+        <v>Joan Beringer</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19">
-        <v>410</v>
+        <v>297</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>1000000</v>
+        <v>5500000</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="H19" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" t="str">
         <f>VLOOKUP(B19,players!A:B,2)</f>
-        <v>Joan Beringer</v>
+        <v>Tre Johnson</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -21934,32 +21934,26 @@
         <v>10</v>
       </c>
       <c r="B20">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2">
-        <v>5500000</v>
+        <v>1000000</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H20" s="2">
-        <v>6500000</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>472</v>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" t="str">
         <f>VLOOKUP(B20,players!A:B,2)</f>
-        <v>Tre Johnson</v>
+        <v>Ja'Kobe Walter</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -21967,18 +21961,16 @@
         <v>10</v>
       </c>
       <c r="B21">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="2">
-        <v>1000000</v>
-      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -21986,7 +21978,7 @@
       <c r="K21" s="2"/>
       <c r="L21" t="str">
         <f>VLOOKUP(B21,players!A:B,2)</f>
-        <v>Ja'Kobe Walter</v>
+        <v>Cam Whitmore</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -21994,57 +21986,61 @@
         <v>10</v>
       </c>
       <c r="B22">
-        <v>300</v>
+        <v>411</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+      <c r="F22" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" t="str">
         <f>VLOOKUP(B22,players!A:B,2)</f>
-        <v>Cam Whitmore</v>
+        <v>Thomas Sorber</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2">
-        <v>1000000</v>
+        <v>3500000</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H23" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" t="str">
         <f>VLOOKUP(B23,players!A:B,2)</f>
-        <v>Thomas Sorber</v>
+        <v>Carter Bryant</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -22052,28 +22048,24 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2">
-        <v>3200000</v>
+        <v>3300000</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="2">
-        <v>3500000</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" t="str">
         <f>VLOOKUP(B24,players!A:B,2)</f>
-        <v>Carter Bryant</v>
+        <v>Dalton Knecht</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -22081,13 +22073,13 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>413</v>
+        <v>189</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>3300000</v>
+        <v>6000000</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -22098,32 +22090,36 @@
       <c r="K25" s="2"/>
       <c r="L25" t="str">
         <f>VLOOKUP(B25,players!A:B,2)</f>
-        <v>Dalton Knecht</v>
+        <v>Ron Holland</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B26">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="F26" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" t="str">
         <f>VLOOKUP(B26,players!A:B,2)</f>
-        <v>Ron Holland</v>
+        <v>Devin Carter</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -22131,28 +22127,32 @@
         <v>13</v>
       </c>
       <c r="B27">
-        <v>252</v>
+        <v>414</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2">
-        <v>1000000</v>
+        <v>3600000</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="H27" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" t="str">
         <f>VLOOKUP(B27,players!A:B,2)</f>
-        <v>Devin Carter</v>
+        <v>Kaman Maluach</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -22160,23 +22160,23 @@
         <v>13</v>
       </c>
       <c r="B28">
-        <v>414</v>
+        <v>241</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2">
-        <v>3600000</v>
+        <v>8500000</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2">
-        <v>3800000</v>
+        <v>9250000</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H28" s="2">
-        <v>4100000</v>
+        <v>10000000</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>472</v>
@@ -22185,40 +22185,34 @@
       <c r="K28" s="2"/>
       <c r="L28" t="str">
         <f>VLOOKUP(B28,players!A:B,2)</f>
-        <v>Kaman Maluach</v>
+        <v>Dylan Harper</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2">
-        <v>8500000</v>
+        <v>3200000</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2">
-        <v>9250000</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H29" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>472</v>
-      </c>
+        <v>3500000</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
-        <v>Dylan Harper</v>
+        <v>Cason Wallace</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -22226,18 +22220,16 @@
         <v>14</v>
       </c>
       <c r="B30">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2">
-        <v>3200000</v>
+        <v>1000000</v>
       </c>
       <c r="E30" s="2"/>
-      <c r="F30" s="2">
-        <v>3500000</v>
-      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -22245,7 +22237,7 @@
       <c r="K30" s="2"/>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>Jaylen Wells</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -22253,56 +22245,31 @@
         <v>14</v>
       </c>
       <c r="B31">
-        <v>259</v>
+        <v>415</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+      <c r="F31" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H31" s="2">
+        <v>4200000</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Jaylen Wells</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>14</v>
-      </c>
-      <c r="B32">
-        <v>415</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2">
-        <v>4000000</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H32" s="2">
-        <v>4200000</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" t="str">
-        <f>VLOOKUP(B32,players!A:B,2)</f>
         <v>Noah Essengue</v>
       </c>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DC4B71F-B4B3-4A03-B83A-31A45631BA14}"/>
+  <xr:revisionPtr revIDLastSave="602" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FCB96EE-9DD3-443F-9441-041433179731}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -17872,7 +17872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003E67E5-331D-4CC3-B636-B44F8A41C81C}">
-  <dimension ref="A1:L176"/>
+  <dimension ref="A1:L174"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -18628,104 +18628,74 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2">
-        <v>3200000</v>
+        <v>3100000</v>
       </c>
       <c r="F37" s="2">
-        <v>3400000</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>472</v>
+        <v>3100000</v>
       </c>
       <c r="H37" s="2">
-        <v>3700000</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>472</v>
+        <v>3100000</v>
       </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>Derik Queen</v>
+        <v>Bobby Portis</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38">
-        <v>69</v>
+        <v>184</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2">
-        <v>3100000</v>
+        <v>8000000</v>
       </c>
       <c r="F38" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H38" s="2">
-        <v>3100000</v>
+        <v>8000000</v>
       </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>Bobby Portis</v>
+        <v>Immanuel Quickley</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>237</v>
+      </c>
+      <c r="C39">
         <v>2</v>
-      </c>
-      <c r="B39">
-        <v>8</v>
-      </c>
-      <c r="C39">
-        <v>11</v>
-      </c>
-      <c r="D39" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F39" s="2">
-        <v>6500000</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Zach Edey</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B40">
-        <v>290</v>
+        <v>119</v>
       </c>
       <c r="C40">
-        <v>12</v>
-      </c>
-      <c r="D40" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H40" s="2">
-        <v>1000000</v>
+        <v>3</v>
       </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Will Riley</v>
+        <v>Kyshawn George</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -18733,20 +18703,17 @@
         <v>3</v>
       </c>
       <c r="B41">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41" s="2">
-        <v>8000000</v>
-      </c>
-      <c r="F41" s="2">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
       <c r="L41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Immanuel Quickley</v>
+        <v>Cameron Johnson</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -18754,14 +18721,14 @@
         <v>3</v>
       </c>
       <c r="B42">
-        <v>237</v>
+        <v>112</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Nickeil Alexander-Walker</v>
+        <v>Myles Turner</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -18769,14 +18736,14 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>Kyshawn George</v>
+        <v>Mitchell Robinson</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -18784,17 +18751,14 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>206</v>
+        <v>11</v>
       </c>
       <c r="C44">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2">
-        <v>5000000</v>
+        <v>7</v>
       </c>
       <c r="L44" t="str">
         <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>Cameron Johnson</v>
+        <v>Jalen Duren</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -18802,14 +18766,23 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D45" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F45" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H45" s="2">
+        <v>40000000</v>
       </c>
       <c r="L45" t="str">
         <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>Myles Turner</v>
+        <v>Luka Dončić</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -18817,14 +18790,17 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D46" s="2">
+        <v>6000000</v>
       </c>
       <c r="L46" t="str">
         <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>Mitchell Robinson</v>
+        <v>Kawhi Leonard</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -18832,14 +18808,20 @@
         <v>3</v>
       </c>
       <c r="B47">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="D47" s="2">
+        <v>14000000</v>
+      </c>
+      <c r="F47" s="2">
+        <v>14000000</v>
       </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>Jalen Duren</v>
+        <v>Jaren Jackson Jr.</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -18847,23 +18829,23 @@
         <v>3</v>
       </c>
       <c r="B48">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2">
-        <v>40000000</v>
+        <v>6500000</v>
       </c>
       <c r="F48" s="2">
-        <v>40000000</v>
+        <v>6500000</v>
       </c>
       <c r="H48" s="2">
-        <v>40000000</v>
+        <v>6500000</v>
       </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>Luka Dončić</v>
+        <v>OG Anunoby</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -18871,17 +18853,17 @@
         <v>3</v>
       </c>
       <c r="B49">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="C49">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D49" s="2">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>Kawhi Leonard</v>
+        <v>Kyrie Irving</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -18889,80 +18871,86 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>85</v>
+        <v>295</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D50" s="2">
-        <v>14000000</v>
-      </c>
-      <c r="F50" s="2">
-        <v>14000000</v>
+        <v>8000000</v>
       </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>Jaren Jackson Jr.</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B51">
-        <v>117</v>
+        <v>379</v>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="F51" s="2">
-        <v>6500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="H51" s="2">
-        <v>6500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>OG Anunoby</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B52">
-        <v>142</v>
+        <v>364</v>
       </c>
       <c r="C52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2">
-        <v>5000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Kyrie Irving</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>104</v>
+      </c>
+      <c r="C53">
         <v>3</v>
-      </c>
-      <c r="B53">
-        <v>295</v>
-      </c>
-      <c r="C53">
-        <v>13</v>
-      </c>
-      <c r="D53" s="2">
-        <v>8000000</v>
       </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>Zach LaVine</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -18970,29 +18958,17 @@
         <v>4</v>
       </c>
       <c r="B54">
-        <v>379</v>
+        <v>62</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F54" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H54" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>472</v>
+        <v>2500000</v>
       </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -19000,23 +18976,17 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>364</v>
+        <v>33</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F55" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>472</v>
+        <v>11000000</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -19024,14 +18994,20 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D56" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F56" s="2">
+        <v>5000000</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -19039,17 +19015,20 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D57" s="2">
-        <v>2500000</v>
+        <v>17000000</v>
+      </c>
+      <c r="F57" s="2">
+        <v>17000000</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -19057,17 +19036,17 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2">
-        <v>11000000</v>
+        <v>22500000</v>
       </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -19075,20 +19054,23 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2">
         <v>5000000</v>
       </c>
       <c r="F59" s="2">
-        <v>5000000</v>
+        <v>5500000</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -19096,20 +19078,23 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D60" s="2">
-        <v>17000000</v>
+        <v>15000000</v>
       </c>
       <c r="F60" s="2">
-        <v>17000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="H60" s="2">
+        <v>15000000</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -19117,17 +19102,23 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D61" s="2">
-        <v>22500000</v>
+        <v>19000000</v>
+      </c>
+      <c r="F61" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="H61" s="2">
+        <v>19000000</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -19135,89 +19126,77 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>110</v>
+        <v>287</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D62" s="2">
-        <v>5000000</v>
-      </c>
-      <c r="F62" s="2">
-        <v>5500000</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>472</v>
+        <v>10000000</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B63">
-        <v>114</v>
+        <v>305</v>
       </c>
       <c r="C63">
-        <v>10</v>
-      </c>
-      <c r="D63" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="F63" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="H63" s="2">
-        <v>15000000</v>
+        <v>1</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B64">
-        <v>157</v>
+        <v>262</v>
       </c>
       <c r="C64">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D64" s="2">
-        <v>19000000</v>
+        <v>3600000</v>
       </c>
       <c r="F64" s="2">
-        <v>19000000</v>
+        <v>3800000</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="H64" s="2">
-        <v>19000000</v>
+        <v>4100000</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B65">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C65">
-        <v>12</v>
-      </c>
-      <c r="D65" s="2">
-        <v>10000000</v>
+        <v>3</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -19225,14 +19204,20 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>305</v>
+        <v>143</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D66" s="2">
+        <v>21000000</v>
+      </c>
+      <c r="F66" s="2">
+        <v>21000000</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -19240,29 +19225,14 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>262</v>
+        <v>131</v>
       </c>
       <c r="C67">
-        <v>2</v>
-      </c>
-      <c r="D67" s="2">
-        <v>3600000</v>
-      </c>
-      <c r="F67" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H67" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>472</v>
+        <v>5</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -19270,14 +19240,29 @@
         <v>5</v>
       </c>
       <c r="B68">
-        <v>274</v>
+        <v>139</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D68" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F68" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H68" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Danny Wolf</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -19285,20 +19270,20 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D69" s="2">
-        <v>21000000</v>
+        <v>17000000</v>
       </c>
       <c r="F69" s="2">
-        <v>21000000</v>
+        <v>17000000</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -19306,14 +19291,23 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D70" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F70" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H70" s="2">
+        <v>40000000</v>
       </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -19321,29 +19315,20 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2">
-        <v>2800000</v>
+        <v>3100000</v>
       </c>
       <c r="F71" s="2">
-        <v>3000000</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H71" s="2">
-        <v>3300000</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>472</v>
+        <v>3100000</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Collin Murray-Boyles</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -19351,20 +19336,14 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>37</v>
+        <v>227</v>
       </c>
       <c r="C72">
-        <v>7</v>
-      </c>
-      <c r="D72" s="2">
-        <v>17000000</v>
-      </c>
-      <c r="F72" s="2">
-        <v>17000000</v>
+        <v>10</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -19372,23 +19351,14 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C73">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2">
-        <v>40000000</v>
-      </c>
-      <c r="F73" s="2">
-        <v>40000000</v>
-      </c>
-      <c r="H73" s="2">
-        <v>40000000</v>
+        <v>11</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -19396,20 +19366,14 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="C74">
-        <v>9</v>
-      </c>
-      <c r="D74" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F74" s="2">
-        <v>3100000</v>
+        <v>12</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -19417,59 +19381,68 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="C75">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Jerami Grant</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B76">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="C76">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="D76" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F76" s="2">
+        <v>6000000</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B77">
-        <v>148</v>
+        <v>338</v>
       </c>
       <c r="C77">
-        <v>12</v>
+        <v>2</v>
+      </c>
+      <c r="D77" s="2">
+        <v>1000000</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>Royce O'Neale</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B78">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="C78">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Ryan Rollins</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -19477,20 +19450,14 @@
         <v>6</v>
       </c>
       <c r="B79">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F79" s="2">
-        <v>6000000</v>
+        <v>4</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -19498,17 +19465,14 @@
         <v>6</v>
       </c>
       <c r="B80">
-        <v>338</v>
+        <v>98</v>
       </c>
       <c r="C80">
-        <v>2</v>
-      </c>
-      <c r="D80" s="2">
-        <v>1000000</v>
+        <v>5</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -19516,14 +19480,14 @@
         <v>6</v>
       </c>
       <c r="B81">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -19531,14 +19495,17 @@
         <v>6</v>
       </c>
       <c r="B82">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D82" s="2">
+        <v>20000000</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -19546,14 +19513,14 @@
         <v>6</v>
       </c>
       <c r="B83">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -19561,14 +19528,17 @@
         <v>6</v>
       </c>
       <c r="B84">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="C84">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D84" s="2">
+        <v>7000000</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -19576,17 +19546,20 @@
         <v>6</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D85" s="2">
-        <v>20000000</v>
+        <v>35000000</v>
+      </c>
+      <c r="F85" s="2">
+        <v>35000000</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -19594,14 +19567,20 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C86">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="D86" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F86" s="2">
+        <v>3100000</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -19609,17 +19588,17 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="C87">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D87" s="2">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -19627,20 +19606,14 @@
         <v>6</v>
       </c>
       <c r="B88">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="C88">
-        <v>10</v>
-      </c>
-      <c r="D88" s="2">
-        <v>35000000</v>
-      </c>
-      <c r="F88" s="2">
-        <v>35000000</v>
+        <v>13</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -19648,20 +19621,20 @@
         <v>6</v>
       </c>
       <c r="B89">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C89">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D89" s="2">
-        <v>3100000</v>
+        <v>6000000</v>
       </c>
       <c r="F89" s="2">
-        <v>3100000</v>
+        <v>6000000</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -19669,68 +19642,83 @@
         <v>6</v>
       </c>
       <c r="B90">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="C90">
-        <v>12</v>
-      </c>
-      <c r="D90" s="2">
-        <v>1000000</v>
+        <v>15</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B91">
-        <v>161</v>
+        <v>242</v>
       </c>
       <c r="C91">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="F91" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Damian Lillard</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B92">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="C92">
-        <v>14</v>
-      </c>
-      <c r="D92" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F92" s="2">
-        <v>6000000</v>
+        <v>2</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B93">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C93">
-        <v>15</v>
+        <v>3</v>
+      </c>
+      <c r="D93" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F93" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H93" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Tari Eason</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -19738,23 +19726,17 @@
         <v>8</v>
       </c>
       <c r="B94">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D94" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="F94" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>472</v>
+        <v>2000000</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -19762,14 +19744,23 @@
         <v>8</v>
       </c>
       <c r="B95">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D95" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F95" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H95" s="2">
+        <v>6000000</v>
       </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -19777,29 +19768,23 @@
         <v>8</v>
       </c>
       <c r="B96">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D96" s="2">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="F96" s="2">
-        <v>1000000</v>
+        <v>7500000</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H96" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>472</v>
-      </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -19807,17 +19792,20 @@
         <v>8</v>
       </c>
       <c r="B97">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D97" s="2">
-        <v>2000000</v>
+        <v>4000000</v>
+      </c>
+      <c r="F97" s="2">
+        <v>4000000</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -19825,23 +19813,23 @@
         <v>8</v>
       </c>
       <c r="B98">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="C98">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D98" s="2">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="F98" s="2">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="H98" s="2">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -19849,23 +19837,20 @@
         <v>8</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C99">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2">
-        <v>7000000</v>
+        <v>9000000</v>
       </c>
       <c r="F99" s="2">
-        <v>7500000</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>472</v>
+        <v>9000000</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -19873,20 +19858,17 @@
         <v>8</v>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D100" s="2">
-        <v>4000000</v>
-      </c>
-      <c r="F100" s="2">
-        <v>4000000</v>
+        <v>16000000</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -19894,23 +19876,23 @@
         <v>8</v>
       </c>
       <c r="B101">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="C101">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D101" s="2">
-        <v>16000000</v>
+        <v>19000000</v>
       </c>
       <c r="F101" s="2">
-        <v>16000000</v>
+        <v>19000000</v>
       </c>
       <c r="H101" s="2">
-        <v>16000000</v>
+        <v>19000000</v>
       </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -19918,20 +19900,14 @@
         <v>8</v>
       </c>
       <c r="B102">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="C102">
-        <v>9</v>
-      </c>
-      <c r="D102" s="2">
-        <v>9000000</v>
-      </c>
-      <c r="F102" s="2">
-        <v>9000000</v>
+        <v>12</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -19939,17 +19915,14 @@
         <v>8</v>
       </c>
       <c r="B103">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="C103">
-        <v>10</v>
-      </c>
-      <c r="D103" s="2">
-        <v>16000000</v>
+        <v>13</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -19957,68 +19930,71 @@
         <v>8</v>
       </c>
       <c r="B104">
-        <v>203</v>
+        <v>336</v>
       </c>
       <c r="C104">
-        <v>11</v>
-      </c>
-      <c r="D104" s="2">
-        <v>19000000</v>
-      </c>
-      <c r="F104" s="2">
-        <v>19000000</v>
-      </c>
-      <c r="H104" s="2">
-        <v>19000000</v>
+        <v>14</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B105">
-        <v>225</v>
+        <v>384</v>
       </c>
       <c r="C105">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="D105" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F105" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H105" s="2">
+        <v>3100000</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B106">
-        <v>59</v>
+        <v>240</v>
       </c>
       <c r="C106">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B107">
-        <v>336</v>
+        <v>186</v>
       </c>
       <c r="C107">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="D107" s="2">
+        <v>4500000</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -20026,23 +20002,14 @@
         <v>9</v>
       </c>
       <c r="B108">
-        <v>384</v>
+        <v>251</v>
       </c>
       <c r="C108">
-        <v>1</v>
-      </c>
-      <c r="D108" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F108" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H108" s="2">
-        <v>3100000</v>
+        <v>4</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -20050,14 +20017,14 @@
         <v>9</v>
       </c>
       <c r="B109">
-        <v>240</v>
+        <v>416</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -20065,17 +20032,23 @@
         <v>9</v>
       </c>
       <c r="B110">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D110" s="2">
-        <v>4500000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F110" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H110" s="2">
+        <v>3100000</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -20083,14 +20056,23 @@
         <v>9</v>
       </c>
       <c r="B111">
-        <v>251</v>
+        <v>15</v>
       </c>
       <c r="C111">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D111" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="F111" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="H111" s="2">
+        <v>32000000</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -20098,14 +20080,23 @@
         <v>9</v>
       </c>
       <c r="B112">
-        <v>416</v>
+        <v>26</v>
       </c>
       <c r="C112">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D112" s="2">
+        <v>12500000</v>
+      </c>
+      <c r="F112" s="2">
+        <v>12500000</v>
+      </c>
+      <c r="H112" s="2">
+        <v>12500000</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -20113,23 +20104,17 @@
         <v>9</v>
       </c>
       <c r="B113">
-        <v>170</v>
+        <v>89</v>
       </c>
       <c r="C113">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F113" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H113" s="2">
-        <v>3100000</v>
+        <v>11500000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -20137,23 +20122,23 @@
         <v>9</v>
       </c>
       <c r="B114">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D114" s="2">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="F114" s="2">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="H114" s="2">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -20161,23 +20146,17 @@
         <v>9</v>
       </c>
       <c r="B115">
-        <v>26</v>
+        <v>217</v>
       </c>
       <c r="C115">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D115" s="2">
-        <v>12500000</v>
-      </c>
-      <c r="F115" s="2">
-        <v>12500000</v>
-      </c>
-      <c r="H115" s="2">
-        <v>12500000</v>
+        <v>25000000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -20185,83 +20164,68 @@
         <v>9</v>
       </c>
       <c r="B116">
-        <v>89</v>
+        <v>331</v>
       </c>
       <c r="C116">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D116" s="2">
-        <v>11500000</v>
+        <v>12000000</v>
+      </c>
+      <c r="F116" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H116" s="2">
+        <v>12000000</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
+        <v>10</v>
+      </c>
+      <c r="B117">
         <v>9</v>
       </c>
-      <c r="B117">
-        <v>167</v>
-      </c>
       <c r="C117">
-        <v>10</v>
-      </c>
-      <c r="D117" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F117" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H117" s="2">
-        <v>3100000</v>
+        <v>1</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B118">
-        <v>217</v>
+        <v>373</v>
       </c>
       <c r="C118">
-        <v>11</v>
-      </c>
-      <c r="D118" s="2">
-        <v>25000000</v>
+        <v>2</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B119">
-        <v>331</v>
+        <v>249</v>
       </c>
       <c r="C119">
-        <v>12</v>
-      </c>
-      <c r="D119" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="F119" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="H119" s="2">
-        <v>12000000</v>
+        <v>3</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -20269,14 +20233,17 @@
         <v>10</v>
       </c>
       <c r="B120">
-        <v>9</v>
+        <v>169</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D120" s="2">
+        <v>4100000</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Walker Kessler</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -20284,14 +20251,20 @@
         <v>10</v>
       </c>
       <c r="B121">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D121" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F121" s="2">
+        <v>6000000</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -20299,14 +20272,17 @@
         <v>10</v>
       </c>
       <c r="B122">
-        <v>249</v>
+        <v>168</v>
       </c>
       <c r="C122">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D122" s="2">
+        <v>1000000</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -20314,17 +20290,14 @@
         <v>10</v>
       </c>
       <c r="B123">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="C123">
-        <v>4</v>
-      </c>
-      <c r="D123" s="2">
-        <v>4100000</v>
+        <v>7</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -20332,20 +20305,23 @@
         <v>10</v>
       </c>
       <c r="B124">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C124">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D124" s="2">
-        <v>6000000</v>
+        <v>9250000</v>
       </c>
       <c r="F124" s="2">
-        <v>6000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -20353,17 +20329,23 @@
         <v>10</v>
       </c>
       <c r="B125">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="C125">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2">
-        <v>1000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="F125" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H125" s="2">
+        <v>15000000</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -20371,14 +20353,20 @@
         <v>10</v>
       </c>
       <c r="B126">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="D126" s="2">
+        <v>11000000</v>
+      </c>
+      <c r="F126" s="2">
+        <v>11000000</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -20386,23 +20374,23 @@
         <v>10</v>
       </c>
       <c r="B127">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="C127">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D127" s="2">
-        <v>9250000</v>
+        <v>16000000</v>
       </c>
       <c r="F127" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>472</v>
+        <v>16000000</v>
+      </c>
+      <c r="H127" s="2">
+        <v>16000000</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -20410,86 +20398,65 @@
         <v>10</v>
       </c>
       <c r="B128">
-        <v>60</v>
+        <v>246</v>
       </c>
       <c r="C128">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D128" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="F128" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="H128" s="2">
-        <v>15000000</v>
+        <v>24000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B129">
-        <v>153</v>
+        <v>327</v>
       </c>
       <c r="C129">
-        <v>10</v>
-      </c>
-      <c r="D129" s="2">
-        <v>11000000</v>
-      </c>
-      <c r="F129" s="2">
-        <v>11000000</v>
+        <v>1</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B130">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="C130">
-        <v>11</v>
-      </c>
-      <c r="D130" s="2">
-        <v>16000000</v>
-      </c>
-      <c r="F130" s="2">
-        <v>16000000</v>
-      </c>
-      <c r="H130" s="2">
-        <v>16000000</v>
+        <v>2</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B131">
-        <v>246</v>
+        <v>111</v>
       </c>
       <c r="C131">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D131" s="2">
-        <v>24000000</v>
+        <v>1000000</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -20497,14 +20464,14 @@
         <v>11</v>
       </c>
       <c r="B132">
-        <v>327</v>
+        <v>58</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -20512,14 +20479,17 @@
         <v>11</v>
       </c>
       <c r="B133">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D133" s="2">
+        <v>1000000</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -20527,17 +20497,14 @@
         <v>11</v>
       </c>
       <c r="B134">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="C134">
-        <v>3</v>
-      </c>
-      <c r="D134" s="2">
-        <v>1000000</v>
+        <v>6</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -20545,14 +20512,17 @@
         <v>11</v>
       </c>
       <c r="B135">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="C135">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D135" s="2">
+        <v>26000000</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -20560,17 +20530,17 @@
         <v>11</v>
       </c>
       <c r="B136">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="C136">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D136" s="2">
-        <v>1000000</v>
+        <v>15000000</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -20578,14 +20548,17 @@
         <v>11</v>
       </c>
       <c r="B137">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C137">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D137" s="2">
+        <v>7500000</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -20593,17 +20566,23 @@
         <v>11</v>
       </c>
       <c r="B138">
-        <v>6</v>
+        <v>166</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D138" s="2">
-        <v>26000000</v>
+        <v>30000000</v>
+      </c>
+      <c r="F138" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="H138" s="2">
+        <v>30000000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -20611,17 +20590,17 @@
         <v>11</v>
       </c>
       <c r="B139">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="C139">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D139" s="2">
-        <v>15000000</v>
+        <v>1000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -20629,17 +20608,14 @@
         <v>11</v>
       </c>
       <c r="B140">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="C140">
-        <v>9</v>
-      </c>
-      <c r="D140" s="2">
-        <v>7500000</v>
+        <v>12</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -20647,23 +20623,14 @@
         <v>11</v>
       </c>
       <c r="B141">
-        <v>166</v>
+        <v>266</v>
       </c>
       <c r="C141">
-        <v>10</v>
-      </c>
-      <c r="D141" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="F141" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="H141" s="2">
-        <v>30000000</v>
+        <v>13</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -20671,62 +20638,74 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="C142">
-        <v>11</v>
-      </c>
-      <c r="D142" s="2">
-        <v>1000000</v>
+        <v>14</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B143">
-        <v>109</v>
+        <v>403</v>
       </c>
       <c r="C143">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F143" s="2">
+        <v>5000000</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B144">
-        <v>266</v>
+        <v>345</v>
       </c>
       <c r="C144">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="D144" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="F144" s="2">
+        <v>3500000</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B145">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="C145">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="D145" s="2">
+        <v>1000000</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -20734,20 +20713,14 @@
         <v>12</v>
       </c>
       <c r="B146">
-        <v>403</v>
+        <v>22</v>
       </c>
       <c r="C146">
-        <v>1</v>
-      </c>
-      <c r="D146" s="2">
-        <v>5000000</v>
-      </c>
-      <c r="F146" s="2">
-        <v>5000000</v>
+        <v>4</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -20755,20 +20728,17 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>345</v>
+        <v>54</v>
       </c>
       <c r="C147">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D147" s="2">
-        <v>3500000</v>
-      </c>
-      <c r="F147" s="2">
-        <v>3500000</v>
+        <v>11000000</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -20776,17 +20746,20 @@
         <v>12</v>
       </c>
       <c r="B148">
-        <v>120</v>
+        <v>194</v>
       </c>
       <c r="C148">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D148" s="2">
-        <v>1000000</v>
+        <v>20000000</v>
+      </c>
+      <c r="F148" s="2">
+        <v>20000000</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -20794,14 +20767,23 @@
         <v>12</v>
       </c>
       <c r="B149">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="C149">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D149" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="F149" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="H149" s="2">
+        <v>18000000</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -20809,80 +20791,68 @@
         <v>12</v>
       </c>
       <c r="B150">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="C150">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D150" s="2">
-        <v>11000000</v>
+        <v>2500000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B151">
-        <v>194</v>
+        <v>307</v>
       </c>
       <c r="C151">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D151" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="F151" s="2">
-        <v>20000000</v>
+        <v>1000000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B152">
-        <v>226</v>
+        <v>363</v>
       </c>
       <c r="C152">
-        <v>7</v>
-      </c>
-      <c r="D152" s="2">
-        <v>18000000</v>
-      </c>
-      <c r="F152" s="2">
-        <v>18000000</v>
-      </c>
-      <c r="H152" s="2">
-        <v>18000000</v>
+        <v>2</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B153">
-        <v>115</v>
+        <v>296</v>
       </c>
       <c r="C153">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D153" s="2">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -20890,17 +20860,17 @@
         <v>13</v>
       </c>
       <c r="B154">
-        <v>307</v>
+        <v>171</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D154" s="2">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -20908,14 +20878,14 @@
         <v>13</v>
       </c>
       <c r="B155">
-        <v>363</v>
+        <v>10</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -20923,17 +20893,14 @@
         <v>13</v>
       </c>
       <c r="B156">
-        <v>296</v>
+        <v>46</v>
       </c>
       <c r="C156">
-        <v>3</v>
-      </c>
-      <c r="D156" s="2">
-        <v>3000000</v>
+        <v>6</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -20941,17 +20908,17 @@
         <v>13</v>
       </c>
       <c r="B157">
-        <v>171</v>
+        <v>4</v>
       </c>
       <c r="C157">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D157" s="2">
-        <v>2000000</v>
+        <v>11500000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -20959,14 +20926,23 @@
         <v>13</v>
       </c>
       <c r="B158">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C158">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D158" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="F158" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="H158" s="2">
+        <v>16000000</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -20974,14 +20950,23 @@
         <v>13</v>
       </c>
       <c r="B159">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C159">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D159" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="F159" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H159" s="2">
+        <v>12000000</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -20989,17 +20974,17 @@
         <v>13</v>
       </c>
       <c r="B160">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C160">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D160" s="2">
-        <v>11500000</v>
+        <v>19000000</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -21007,89 +20992,68 @@
         <v>13</v>
       </c>
       <c r="B161">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="C161">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D161" s="2">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="F161" s="2">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="H161" s="2">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B162">
-        <v>55</v>
+        <v>317</v>
       </c>
       <c r="C162">
-        <v>9</v>
-      </c>
-      <c r="D162" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="F162" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="H162" s="2">
-        <v>12000000</v>
+        <v>1</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B163">
-        <v>66</v>
+        <v>299</v>
       </c>
       <c r="C163">
-        <v>10</v>
-      </c>
-      <c r="D163" s="2">
-        <v>19000000</v>
+        <v>2</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B164">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="C164">
-        <v>11</v>
-      </c>
-      <c r="D164" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F164" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="H164" s="2">
-        <v>6000000</v>
+        <v>3</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -21097,14 +21061,14 @@
         <v>14</v>
       </c>
       <c r="B165">
-        <v>317</v>
+        <v>90</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -21112,14 +21076,17 @@
         <v>14</v>
       </c>
       <c r="B166">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="C166">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D166" s="2">
+        <v>1000000</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -21127,14 +21094,17 @@
         <v>14</v>
       </c>
       <c r="B167">
-        <v>129</v>
+        <v>238</v>
       </c>
       <c r="C167">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D167" s="2">
+        <v>3000000</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -21142,14 +21112,23 @@
         <v>14</v>
       </c>
       <c r="B168">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="C168">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D168" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="F168" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="H168" s="2">
+        <v>20500000</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -21157,17 +21136,17 @@
         <v>14</v>
       </c>
       <c r="B169">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C169">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D169" s="2">
-        <v>1000000</v>
+        <v>19500000</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -21175,17 +21154,29 @@
         <v>14</v>
       </c>
       <c r="B170">
-        <v>238</v>
+        <v>61</v>
       </c>
       <c r="C170">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D170" s="2">
-        <v>3000000</v>
+        <v>9500000</v>
+      </c>
+      <c r="F170" s="2">
+        <v>10500000</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H170" s="2">
+        <v>11500000</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -21193,23 +21184,14 @@
         <v>14</v>
       </c>
       <c r="B171">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C171">
-        <v>7</v>
-      </c>
-      <c r="D171" s="2">
-        <v>20500000</v>
-      </c>
-      <c r="F171" s="2">
-        <v>20500000</v>
-      </c>
-      <c r="H171" s="2">
-        <v>20500000</v>
+        <v>10</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -21217,17 +21199,14 @@
         <v>14</v>
       </c>
       <c r="B172">
-        <v>73</v>
+        <v>220</v>
       </c>
       <c r="C172">
-        <v>8</v>
-      </c>
-      <c r="D172" s="2">
-        <v>19500000</v>
+        <v>11</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Quentin Grimes</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -21235,29 +21214,23 @@
         <v>14</v>
       </c>
       <c r="B173">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="C173">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D173" s="2">
-        <v>9500000</v>
+        <v>20000000</v>
       </c>
       <c r="F173" s="2">
-        <v>10500000</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>472</v>
+        <v>20000000</v>
       </c>
       <c r="H173" s="2">
-        <v>11500000</v>
-      </c>
-      <c r="I173" s="2" t="s">
-        <v>472</v>
+        <v>20000000</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>LaMelo Ball</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -21265,53 +21238,20 @@
         <v>14</v>
       </c>
       <c r="B174">
-        <v>2</v>
+        <v>273</v>
       </c>
       <c r="C174">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D174" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="F174" s="2">
+        <v>3500000</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175">
-        <v>14</v>
-      </c>
-      <c r="B175">
-        <v>220</v>
-      </c>
-      <c r="C175">
-        <v>11</v>
-      </c>
-      <c r="L175" t="str">
-        <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176">
-        <v>14</v>
-      </c>
-      <c r="B176">
-        <v>145</v>
-      </c>
-      <c r="C176">
-        <v>12</v>
-      </c>
-      <c r="D176" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="F176" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="H176" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="L176" t="str">
-        <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Cason Wallace</v>
       </c>
     </row>
   </sheetData>
@@ -21322,7 +21262,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B357A823-6505-4984-ACC9-40636E218B6C}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
@@ -21588,88 +21528,86 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>377</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2">
-        <v>1000000</v>
+        <v>6500000</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H9" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" t="str">
         <f>VLOOKUP(B9,players!A:B,2)</f>
-        <v>Nikola Topić</v>
+        <v>Zach Edey</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>408</v>
+        <v>290</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2">
-        <v>3400000</v>
+        <v>1000000</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2">
-        <v>3700000</v>
+        <v>1000000</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2">
+        <v>1000000</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" t="str">
         <f>VLOOKUP(B10,players!A:B,2)</f>
-        <v>Jase Richardson</v>
+        <v>Will Riley</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B11">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2">
-        <v>6500000</v>
+        <v>3200000</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2">
-        <v>7000000</v>
+        <v>3400000</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H11" s="2">
-        <v>7500000</v>
+        <v>3700000</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>472</v>
@@ -21678,18 +21616,18 @@
       <c r="K11" s="2"/>
       <c r="L11" t="str">
         <f>VLOOKUP(B11,players!A:B,2)</f>
-        <v>VJ Edgecombe</v>
+        <v>Derik Queen</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B12">
-        <v>139</v>
+        <v>377</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2">
         <v>1000000</v>
@@ -21711,122 +21649,126 @@
       <c r="K12" s="2"/>
       <c r="L12" t="str">
         <f>VLOOKUP(B12,players!A:B,2)</f>
-        <v>Danny Wolf</v>
+        <v>Nikola Topić</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>4000000</v>
+        <v>3400000</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
-        <v>4200000</v>
+        <v>3700000</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H13" s="2">
-        <v>4500000</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" t="str">
         <f>VLOOKUP(B13,players!A:B,2)</f>
-        <v>Hansen Yang</v>
+        <v>Jase Richardson</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>3200000</v>
+        <v>6500000</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2">
-        <v>3500000</v>
+        <v>7000000</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="H14" s="2">
+        <v>7500000</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" t="str">
         <f>VLOOKUP(B14,players!A:B,2)</f>
-        <v>Tidjane Salaün</v>
+        <v>VJ Edgecombe</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B15">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D15" s="2">
-        <v>1000000</v>
+        <v>2800000</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="H15" s="2">
+        <v>3300000</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" t="str">
         <f>VLOOKUP(B15,players!A:B,2)</f>
-        <v>Kyle Filipowski</v>
+        <v>Collin Murray-Boyles</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B16">
-        <v>108</v>
+        <v>409</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2">
-        <v>5500000</v>
+        <v>4200000</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H16" s="2">
-        <v>6000000</v>
+        <v>4500000</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>472</v>
@@ -21835,25 +21777,25 @@
       <c r="K16" s="2"/>
       <c r="L16" t="str">
         <f>VLOOKUP(B16,players!A:B,2)</f>
-        <v>Kon Knueppel</v>
+        <v>Hansen Yang</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B17">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2">
-        <v>1000000</v>
+        <v>3500000</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>472</v>
@@ -21864,18 +21806,18 @@
       <c r="K17" s="2"/>
       <c r="L17" t="str">
         <f>VLOOKUP(B17,players!A:B,2)</f>
-        <v>Jaylon Tyson</v>
+        <v>Tidjane Salaün</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18">
-        <v>410</v>
+        <v>47</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2">
         <v>1000000</v>
@@ -21893,31 +21835,31 @@
       <c r="K18" s="2"/>
       <c r="L18" t="str">
         <f>VLOOKUP(B18,players!A:B,2)</f>
-        <v>Joan Beringer</v>
+        <v>Kyle Filipowski</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19">
-        <v>297</v>
+        <v>108</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>5500000</v>
+        <v>5000000</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2">
-        <v>6000000</v>
+        <v>5500000</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H19" s="2">
-        <v>6500000</v>
+        <v>6000000</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>472</v>
@@ -21926,15 +21868,15 @@
       <c r="K19" s="2"/>
       <c r="L19" t="str">
         <f>VLOOKUP(B19,players!A:B,2)</f>
-        <v>Tre Johnson</v>
+        <v>Kon Knueppel</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20">
-        <v>313</v>
+        <v>123</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -21946,39 +21888,45 @@
       <c r="F20" s="2">
         <v>1000000</v>
       </c>
-      <c r="G20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" t="str">
         <f>VLOOKUP(B20,players!A:B,2)</f>
-        <v>Ja'Kobe Walter</v>
+        <v>Jaylon Tyson</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21">
-        <v>300</v>
+        <v>410</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="F21" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" t="str">
         <f>VLOOKUP(B21,players!A:B,2)</f>
-        <v>Cam Whitmore</v>
+        <v>Joan Beringer</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -21986,23 +21934,23 @@
         <v>10</v>
       </c>
       <c r="B22">
-        <v>411</v>
+        <v>297</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>1000000</v>
+        <v>5500000</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H22" s="2">
-        <v>1000000</v>
+        <v>6500000</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>472</v>
@@ -22011,50 +21959,48 @@
       <c r="K22" s="2"/>
       <c r="L22" t="str">
         <f>VLOOKUP(B22,players!A:B,2)</f>
-        <v>Thomas Sorber</v>
+        <v>Tre Johnson</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23">
-        <v>412</v>
+        <v>313</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
-        <v>3200000</v>
+        <v>1000000</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2">
-        <v>3500000</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>472</v>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" t="str">
         <f>VLOOKUP(B23,players!A:B,2)</f>
-        <v>Carter Bryant</v>
+        <v>Ja'Kobe Walter</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24">
-        <v>413</v>
+        <v>300</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>3300000</v>
+        <v>6000000</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -22065,50 +22011,58 @@
       <c r="K24" s="2"/>
       <c r="L24" t="str">
         <f>VLOOKUP(B24,players!A:B,2)</f>
-        <v>Dalton Knecht</v>
+        <v>Cam Whitmore</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25">
-        <v>189</v>
+        <v>411</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="F25" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" t="str">
         <f>VLOOKUP(B25,players!A:B,2)</f>
-        <v>Ron Holland</v>
+        <v>Thomas Sorber</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B26">
-        <v>252</v>
+        <v>412</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2">
-        <v>1000000</v>
+        <v>3500000</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>472</v>
@@ -22119,149 +22073,143 @@
       <c r="K26" s="2"/>
       <c r="L26" t="str">
         <f>VLOOKUP(B26,players!A:B,2)</f>
-        <v>Devin Carter</v>
+        <v>Carter Bryant</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B27">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" s="2">
-        <v>3600000</v>
+        <v>3300000</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H27" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" t="str">
         <f>VLOOKUP(B27,players!A:B,2)</f>
-        <v>Kaman Maluach</v>
+        <v>Dalton Knecht</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B28">
-        <v>241</v>
+        <v>189</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28" s="2">
-        <v>8500000</v>
+        <v>6000000</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="2">
-        <v>9250000</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H28" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" t="str">
         <f>VLOOKUP(B28,players!A:B,2)</f>
-        <v>Dylan Harper</v>
+        <v>Ron Holland</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" s="2">
-        <v>3200000</v>
+        <v>1000000</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2">
-        <v>3500000</v>
-      </c>
-      <c r="G29" s="2"/>
+        <v>1000000</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>Devin Carter</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30">
-        <v>259</v>
+        <v>414</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30" s="2">
-        <v>1000000</v>
+        <v>3600000</v>
       </c>
       <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="F30" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H30" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Jaylen Wells</v>
+        <v>Kaman Maluach</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B31">
-        <v>415</v>
+        <v>241</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" s="2">
-        <v>3800000</v>
+        <v>8500000</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2">
-        <v>4000000</v>
+        <v>9250000</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H31" s="2">
-        <v>4200000</v>
+        <v>10000000</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>472</v>
@@ -22270,6 +22218,64 @@
       <c r="K31" s="2"/>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
+        <v>Dylan Harper</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>14</v>
+      </c>
+      <c r="B32">
+        <v>259</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" t="str">
+        <f>VLOOKUP(B32,players!A:B,2)</f>
+        <v>Jaylen Wells</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>14</v>
+      </c>
+      <c r="B33">
+        <v>415</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H33" s="2">
+        <v>4200000</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" t="str">
+        <f>VLOOKUP(B33,players!A:B,2)</f>
         <v>Noah Essengue</v>
       </c>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="602" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FCB96EE-9DD3-443F-9441-041433179731}"/>
+  <xr:revisionPtr revIDLastSave="700" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3CE607F-5F33-4891-85F6-D984135E260A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView minimized="1" xWindow="32925" yWindow="2265" windowWidth="21600" windowHeight="11835" firstSheet="1" activeTab="8" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="fines" sheetId="11" r:id="rId7"/>
     <sheet name="transactions" sheetId="12" r:id="rId8"/>
     <sheet name="transaction_items" sheetId="13" r:id="rId9"/>
-    <sheet name="games" sheetId="14" r:id="rId10"/>
+    <sheet name="transactions_leg" sheetId="15" r:id="rId10"/>
+    <sheet name="games" sheetId="14" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">players!$A$1:$K$407</definedName>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="653">
   <si>
     <t>player_id</t>
   </si>
@@ -1956,6 +1957,60 @@
   </si>
   <si>
     <t>P2029_R2_T14</t>
+  </si>
+  <si>
+    <t>2627T01</t>
+  </si>
+  <si>
+    <t>Trade</t>
+  </si>
+  <si>
+    <t>Pick Swap</t>
+  </si>
+  <si>
+    <t>DEV_PROMOTION</t>
+  </si>
+  <si>
+    <t>CUT</t>
+  </si>
+  <si>
+    <t>SIGN</t>
+  </si>
+  <si>
+    <t>DEV_DEMOTION</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>PLAYER</t>
+  </si>
+  <si>
+    <t>PICK</t>
+  </si>
+  <si>
+    <t>P2026R1T07</t>
+  </si>
+  <si>
+    <t>MAIN</t>
+  </si>
+  <si>
+    <t>DEV</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Gema</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>pick</t>
+  </si>
+  <si>
+    <t>2026-27</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +2070,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2024,6 +2079,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2040,10 +2096,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15783,6 +15835,157 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA00E26-9ACA-4654-8EDE-4273989987AE}">
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E1" t="s">
+        <v>483</v>
+      </c>
+      <c r="F1" t="s">
+        <v>484</v>
+      </c>
+      <c r="G1" t="s">
+        <v>485</v>
+      </c>
+      <c r="H1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>636</v>
+      </c>
+      <c r="G2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>479</v>
+      </c>
+      <c r="B10" t="s">
+        <v>486</v>
+      </c>
+      <c r="C10" t="s">
+        <v>487</v>
+      </c>
+      <c r="D10" t="s">
+        <v>488</v>
+      </c>
+      <c r="E10" t="s">
+        <v>483</v>
+      </c>
+      <c r="F10" t="s">
+        <v>484</v>
+      </c>
+      <c r="G10" t="s">
+        <v>489</v>
+      </c>
+      <c r="H10" t="s">
+        <v>490</v>
+      </c>
+      <c r="I10" t="s">
+        <v>491</v>
+      </c>
+      <c r="J10" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>643</v>
+      </c>
+      <c r="D11">
+        <v>247</v>
+      </c>
+      <c r="G11" t="s">
+        <v>646</v>
+      </c>
+      <c r="H11" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>644</v>
+      </c>
+      <c r="D12" t="s">
+        <v>645</v>
+      </c>
+      <c r="G12" t="s">
+        <v>647</v>
+      </c>
+      <c r="H12" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>648</v>
+      </c>
+      <c r="H13" t="s">
+        <v>648</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C74861F-411E-43E0-91B2-C73D752B81C9}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24415,8 +24618,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC749459-A282-4BAD-8215-D4598FFF67A1}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -24445,6 +24659,32 @@
       </c>
       <c r="I1" t="s">
         <v>478</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C2" s="4">
+        <v>46166</v>
+      </c>
+      <c r="D2" t="s">
+        <v>652</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>649</v>
+      </c>
+      <c r="H2" t="s">
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -24454,10 +24694,18 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF1C31C-AE58-4E4E-8CDE-8E9DE04175C9}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -24492,6 +24740,93 @@
         <v>492</v>
       </c>
     </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>648</v>
+      </c>
+      <c r="H2" t="s">
+        <v>648</v>
+      </c>
+      <c r="I2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>635</v>
+      </c>
+      <c r="B3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D3" t="s">
+        <v>621</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>648</v>
+      </c>
+      <c r="H3" t="s">
+        <v>648</v>
+      </c>
+      <c r="I3" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>635</v>
+      </c>
+      <c r="B4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C4" t="s">
+        <v>651</v>
+      </c>
+      <c r="D4" t="s">
+        <v>531</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>648</v>
+      </c>
+      <c r="H4" t="s">
+        <v>648</v>
+      </c>
+      <c r="I4" t="s">
+        <v>652</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="700" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3CE607F-5F33-4891-85F6-D984135E260A}"/>
+  <xr:revisionPtr revIDLastSave="1139" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75E7B87B-C430-49C6-A5F7-ABD3FA1B8EEF}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="32925" yWindow="2265" windowWidth="21600" windowHeight="11835" firstSheet="1" activeTab="8" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="683">
   <si>
     <t>player_id</t>
   </si>
@@ -2011,6 +2011,96 @@
   </si>
   <si>
     <t>2026-27</t>
+  </si>
+  <si>
+    <t>2627T02</t>
+  </si>
+  <si>
+    <t>player</t>
+  </si>
+  <si>
+    <t>2627T03</t>
+  </si>
+  <si>
+    <t>2627T04</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>2627T05</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>P2026_R1_T5</t>
+  </si>
+  <si>
+    <t>2627T06</t>
+  </si>
+  <si>
+    <t>Peleia</t>
+  </si>
+  <si>
+    <t>2627T07</t>
+  </si>
+  <si>
+    <t>Pharynx</t>
+  </si>
+  <si>
+    <t>2627T08</t>
+  </si>
+  <si>
+    <t>Barons</t>
+  </si>
+  <si>
+    <t>2627T09</t>
+  </si>
+  <si>
+    <t>2627T10</t>
+  </si>
+  <si>
+    <t>2627T11</t>
+  </si>
+  <si>
+    <t>2627T12</t>
+  </si>
+  <si>
+    <t>2627T13</t>
+  </si>
+  <si>
+    <t>2627T14</t>
+  </si>
+  <si>
+    <t>dev</t>
+  </si>
+  <si>
+    <t>2627T15</t>
+  </si>
+  <si>
+    <t>BlackMamba</t>
+  </si>
+  <si>
+    <t>2627T16</t>
+  </si>
+  <si>
+    <t>2627T17</t>
+  </si>
+  <si>
+    <t>Celtics</t>
+  </si>
+  <si>
+    <t>2627T18</t>
+  </si>
+  <si>
+    <t>2627T19</t>
+  </si>
+  <si>
+    <t>Multa 150.000 em 1 ano</t>
+  </si>
+  <si>
+    <t>Multa 150.000 em 3 anos</t>
   </si>
 </sst>
 </file>
@@ -2096,6 +2186,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24618,7 +24712,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC749459-A282-4BAD-8215-D4598FFF67A1}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -24687,14 +24781,483 @@
         <v>650</v>
       </c>
     </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>653</v>
+      </c>
+      <c r="B3" t="s">
+        <v>636</v>
+      </c>
+      <c r="C3" s="4">
+        <v>46166</v>
+      </c>
+      <c r="D3" t="s">
+        <v>652</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>649</v>
+      </c>
+      <c r="H3" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>655</v>
+      </c>
+      <c r="B4" t="s">
+        <v>636</v>
+      </c>
+      <c r="C4" s="4">
+        <v>46172</v>
+      </c>
+      <c r="D4" t="s">
+        <v>652</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>649</v>
+      </c>
+      <c r="H4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>656</v>
+      </c>
+      <c r="B5" t="s">
+        <v>636</v>
+      </c>
+      <c r="C5" s="4">
+        <v>46173</v>
+      </c>
+      <c r="D5" t="s">
+        <v>652</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>657</v>
+      </c>
+      <c r="H5" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>658</v>
+      </c>
+      <c r="B6" t="s">
+        <v>636</v>
+      </c>
+      <c r="C6" s="4">
+        <v>46173</v>
+      </c>
+      <c r="D6" t="s">
+        <v>652</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>649</v>
+      </c>
+      <c r="H6" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>661</v>
+      </c>
+      <c r="B7" t="s">
+        <v>636</v>
+      </c>
+      <c r="C7" s="4">
+        <v>46174</v>
+      </c>
+      <c r="D7" t="s">
+        <v>652</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>662</v>
+      </c>
+      <c r="H7" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>663</v>
+      </c>
+      <c r="B8" t="s">
+        <v>636</v>
+      </c>
+      <c r="C8" s="4">
+        <v>46174</v>
+      </c>
+      <c r="D8" t="s">
+        <v>652</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>664</v>
+      </c>
+      <c r="H8" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>665</v>
+      </c>
+      <c r="B9" t="s">
+        <v>636</v>
+      </c>
+      <c r="C9" s="4">
+        <v>46175</v>
+      </c>
+      <c r="D9" t="s">
+        <v>652</v>
+      </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>666</v>
+      </c>
+      <c r="H9" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>667</v>
+      </c>
+      <c r="B10" t="s">
+        <v>636</v>
+      </c>
+      <c r="C10" s="4">
+        <v>46175</v>
+      </c>
+      <c r="D10" t="s">
+        <v>652</v>
+      </c>
+      <c r="E10">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>649</v>
+      </c>
+      <c r="H10" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>668</v>
+      </c>
+      <c r="B11" t="s">
+        <v>636</v>
+      </c>
+      <c r="C11" s="4">
+        <v>46178</v>
+      </c>
+      <c r="D11" t="s">
+        <v>652</v>
+      </c>
+      <c r="E11">
+        <v>14</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>649</v>
+      </c>
+      <c r="H11" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>669</v>
+      </c>
+      <c r="B12" t="s">
+        <v>636</v>
+      </c>
+      <c r="C12" s="4">
+        <v>46179</v>
+      </c>
+      <c r="D12" t="s">
+        <v>652</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12" t="s">
+        <v>649</v>
+      </c>
+      <c r="H12" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>670</v>
+      </c>
+      <c r="B13" t="s">
+        <v>641</v>
+      </c>
+      <c r="C13" s="4">
+        <v>46175</v>
+      </c>
+      <c r="D13" t="s">
+        <v>652</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>649</v>
+      </c>
+      <c r="H13" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>671</v>
+      </c>
+      <c r="B14" t="s">
+        <v>641</v>
+      </c>
+      <c r="C14" s="4">
+        <v>46178</v>
+      </c>
+      <c r="D14" t="s">
+        <v>652</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>675</v>
+      </c>
+      <c r="H14" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>672</v>
+      </c>
+      <c r="B15" t="s">
+        <v>641</v>
+      </c>
+      <c r="C15" s="4">
+        <v>46178</v>
+      </c>
+      <c r="D15" t="s">
+        <v>652</v>
+      </c>
+      <c r="E15">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>662</v>
+      </c>
+      <c r="H15" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>674</v>
+      </c>
+      <c r="B16" t="s">
+        <v>641</v>
+      </c>
+      <c r="C16" s="4">
+        <v>46178</v>
+      </c>
+      <c r="D16" t="s">
+        <v>652</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>649</v>
+      </c>
+      <c r="H16" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>676</v>
+      </c>
+      <c r="B17" t="s">
+        <v>638</v>
+      </c>
+      <c r="C17" s="4">
+        <v>46188</v>
+      </c>
+      <c r="D17" t="s">
+        <v>652</v>
+      </c>
+      <c r="E17">
+        <v>14</v>
+      </c>
+      <c r="F17">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>662</v>
+      </c>
+      <c r="H17" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>677</v>
+      </c>
+      <c r="B18" t="s">
+        <v>641</v>
+      </c>
+      <c r="C18" s="4">
+        <v>46195</v>
+      </c>
+      <c r="D18" t="s">
+        <v>652</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>678</v>
+      </c>
+      <c r="H18" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>679</v>
+      </c>
+      <c r="B19" t="s">
+        <v>639</v>
+      </c>
+      <c r="C19" s="4">
+        <v>46181</v>
+      </c>
+      <c r="D19" t="s">
+        <v>652</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>648</v>
+      </c>
+      <c r="G19" t="s">
+        <v>649</v>
+      </c>
+      <c r="H19" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>680</v>
+      </c>
+      <c r="B20" t="s">
+        <v>639</v>
+      </c>
+      <c r="C20" s="4">
+        <v>46199</v>
+      </c>
+      <c r="D20" t="s">
+        <v>652</v>
+      </c>
+      <c r="E20">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>648</v>
+      </c>
+      <c r="G20" t="s">
+        <v>675</v>
+      </c>
+      <c r="H20" t="s">
+        <v>650</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF1C31C-AE58-4E4E-8CDE-8E9DE04175C9}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -24803,13 +25366,13 @@
         <v>635</v>
       </c>
       <c r="B4" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C4" t="s">
         <v>651</v>
       </c>
       <c r="D4" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -24827,7 +25390,1406 @@
         <v>652</v>
       </c>
     </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C5" t="s">
+        <v>651</v>
+      </c>
+      <c r="D5" t="s">
+        <v>567</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>648</v>
+      </c>
+      <c r="H5" t="s">
+        <v>648</v>
+      </c>
+      <c r="I5" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>654</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>659</v>
+      </c>
+      <c r="H6" t="s">
+        <v>659</v>
+      </c>
+      <c r="I6" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B7">
+        <v>219</v>
+      </c>
+      <c r="C7" t="s">
+        <v>654</v>
+      </c>
+      <c r="D7">
+        <v>219</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>659</v>
+      </c>
+      <c r="H7" t="s">
+        <v>659</v>
+      </c>
+      <c r="I7" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>655</v>
+      </c>
+      <c r="B8">
+        <v>220</v>
+      </c>
+      <c r="C8" t="s">
+        <v>654</v>
+      </c>
+      <c r="D8">
+        <v>220</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>659</v>
+      </c>
+      <c r="H8" t="s">
+        <v>659</v>
+      </c>
+      <c r="I8" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B9">
+        <v>194</v>
+      </c>
+      <c r="C9" t="s">
+        <v>654</v>
+      </c>
+      <c r="D9">
+        <v>194</v>
+      </c>
+      <c r="E9">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>659</v>
+      </c>
+      <c r="H9" t="s">
+        <v>659</v>
+      </c>
+      <c r="I9" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>656</v>
+      </c>
+      <c r="B10">
+        <v>158</v>
+      </c>
+      <c r="C10" t="s">
+        <v>654</v>
+      </c>
+      <c r="D10">
+        <v>158</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>659</v>
+      </c>
+      <c r="H10" t="s">
+        <v>659</v>
+      </c>
+      <c r="I10" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>656</v>
+      </c>
+      <c r="B11">
+        <v>247</v>
+      </c>
+      <c r="C11" t="s">
+        <v>654</v>
+      </c>
+      <c r="D11">
+        <v>247</v>
+      </c>
+      <c r="E11">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>659</v>
+      </c>
+      <c r="H11" t="s">
+        <v>659</v>
+      </c>
+      <c r="I11" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>656</v>
+      </c>
+      <c r="B12">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>654</v>
+      </c>
+      <c r="D12">
+        <v>88</v>
+      </c>
+      <c r="E12">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12" t="s">
+        <v>659</v>
+      </c>
+      <c r="H12" t="s">
+        <v>659</v>
+      </c>
+      <c r="I12" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>658</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>654</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>659</v>
+      </c>
+      <c r="H13" t="s">
+        <v>659</v>
+      </c>
+      <c r="I13" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>658</v>
+      </c>
+      <c r="B14">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
+        <v>654</v>
+      </c>
+      <c r="D14">
+        <v>152</v>
+      </c>
+      <c r="E14">
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>659</v>
+      </c>
+      <c r="H14" t="s">
+        <v>659</v>
+      </c>
+      <c r="I14" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>658</v>
+      </c>
+      <c r="B15" t="s">
+        <v>564</v>
+      </c>
+      <c r="C15" t="s">
+        <v>651</v>
+      </c>
+      <c r="D15" t="s">
+        <v>564</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>648</v>
+      </c>
+      <c r="H15" t="s">
+        <v>648</v>
+      </c>
+      <c r="I15" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>658</v>
+      </c>
+      <c r="B16" t="s">
+        <v>660</v>
+      </c>
+      <c r="C16" t="s">
+        <v>651</v>
+      </c>
+      <c r="D16" t="s">
+        <v>660</v>
+      </c>
+      <c r="E16">
+        <v>14</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>648</v>
+      </c>
+      <c r="H16" t="s">
+        <v>648</v>
+      </c>
+      <c r="I16" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>661</v>
+      </c>
+      <c r="B17" t="s">
+        <v>565</v>
+      </c>
+      <c r="C17" t="s">
+        <v>651</v>
+      </c>
+      <c r="D17" t="s">
+        <v>565</v>
+      </c>
+      <c r="E17">
+        <v>14</v>
+      </c>
+      <c r="F17">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>648</v>
+      </c>
+      <c r="H17" t="s">
+        <v>648</v>
+      </c>
+      <c r="I17" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>661</v>
+      </c>
+      <c r="B18" t="s">
+        <v>566</v>
+      </c>
+      <c r="C18" t="s">
+        <v>651</v>
+      </c>
+      <c r="D18" t="s">
+        <v>566</v>
+      </c>
+      <c r="E18">
+        <v>14</v>
+      </c>
+      <c r="F18">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>648</v>
+      </c>
+      <c r="H18" t="s">
+        <v>648</v>
+      </c>
+      <c r="I18" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>661</v>
+      </c>
+      <c r="B19">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>654</v>
+      </c>
+      <c r="D19">
+        <v>73</v>
+      </c>
+      <c r="E19">
+        <v>13</v>
+      </c>
+      <c r="F19">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>659</v>
+      </c>
+      <c r="H19" t="s">
+        <v>659</v>
+      </c>
+      <c r="I19" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>661</v>
+      </c>
+      <c r="B20">
+        <v>241</v>
+      </c>
+      <c r="C20" t="s">
+        <v>654</v>
+      </c>
+      <c r="D20">
+        <v>241</v>
+      </c>
+      <c r="E20">
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>659</v>
+      </c>
+      <c r="H20" t="s">
+        <v>659</v>
+      </c>
+      <c r="I20" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>661</v>
+      </c>
+      <c r="B21">
+        <v>121</v>
+      </c>
+      <c r="C21" t="s">
+        <v>654</v>
+      </c>
+      <c r="D21">
+        <v>121</v>
+      </c>
+      <c r="E21">
+        <v>14</v>
+      </c>
+      <c r="F21">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>659</v>
+      </c>
+      <c r="H21" t="s">
+        <v>659</v>
+      </c>
+      <c r="I21" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>663</v>
+      </c>
+      <c r="B22">
+        <v>177</v>
+      </c>
+      <c r="C22" t="s">
+        <v>654</v>
+      </c>
+      <c r="D22">
+        <v>177</v>
+      </c>
+      <c r="E22">
+        <v>14</v>
+      </c>
+      <c r="F22">
+        <v>11</v>
+      </c>
+      <c r="G22" t="s">
+        <v>659</v>
+      </c>
+      <c r="H22" t="s">
+        <v>659</v>
+      </c>
+      <c r="I22" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>663</v>
+      </c>
+      <c r="B23">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>654</v>
+      </c>
+      <c r="D23">
+        <v>66</v>
+      </c>
+      <c r="E23">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>659</v>
+      </c>
+      <c r="H23" t="s">
+        <v>659</v>
+      </c>
+      <c r="I23" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>665</v>
+      </c>
+      <c r="B24">
+        <v>145</v>
+      </c>
+      <c r="C24" t="s">
+        <v>654</v>
+      </c>
+      <c r="D24">
+        <v>145</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>659</v>
+      </c>
+      <c r="H24" t="s">
+        <v>659</v>
+      </c>
+      <c r="I24" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>665</v>
+      </c>
+      <c r="B25">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
+        <v>654</v>
+      </c>
+      <c r="D25">
+        <v>56</v>
+      </c>
+      <c r="E25">
+        <v>14</v>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+      <c r="G25" t="s">
+        <v>659</v>
+      </c>
+      <c r="H25" t="s">
+        <v>659</v>
+      </c>
+      <c r="I25" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>665</v>
+      </c>
+      <c r="B26">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
+        <v>654</v>
+      </c>
+      <c r="D26">
+        <v>93</v>
+      </c>
+      <c r="E26">
+        <v>14</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
+      </c>
+      <c r="G26" t="s">
+        <v>659</v>
+      </c>
+      <c r="H26" t="s">
+        <v>659</v>
+      </c>
+      <c r="I26" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>665</v>
+      </c>
+      <c r="B27">
+        <v>161</v>
+      </c>
+      <c r="C27" t="s">
+        <v>654</v>
+      </c>
+      <c r="D27">
+        <v>161</v>
+      </c>
+      <c r="E27">
+        <v>14</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27" t="s">
+        <v>659</v>
+      </c>
+      <c r="H27" t="s">
+        <v>659</v>
+      </c>
+      <c r="I27" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>665</v>
+      </c>
+      <c r="B28" t="s">
+        <v>660</v>
+      </c>
+      <c r="C28" t="s">
+        <v>651</v>
+      </c>
+      <c r="D28" t="s">
+        <v>660</v>
+      </c>
+      <c r="E28">
+        <v>14</v>
+      </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+      <c r="G28" t="s">
+        <v>648</v>
+      </c>
+      <c r="H28" t="s">
+        <v>648</v>
+      </c>
+      <c r="I28" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>667</v>
+      </c>
+      <c r="B29" t="s">
+        <v>565</v>
+      </c>
+      <c r="C29" t="s">
+        <v>651</v>
+      </c>
+      <c r="D29" t="s">
+        <v>565</v>
+      </c>
+      <c r="E29">
+        <v>13</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29" t="s">
+        <v>648</v>
+      </c>
+      <c r="H29" t="s">
+        <v>648</v>
+      </c>
+      <c r="I29" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>667</v>
+      </c>
+      <c r="B30" t="s">
+        <v>566</v>
+      </c>
+      <c r="C30" t="s">
+        <v>651</v>
+      </c>
+      <c r="D30" t="s">
+        <v>566</v>
+      </c>
+      <c r="E30">
+        <v>13</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" t="s">
+        <v>648</v>
+      </c>
+      <c r="H30" t="s">
+        <v>648</v>
+      </c>
+      <c r="I30" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>667</v>
+      </c>
+      <c r="B31" t="s">
+        <v>621</v>
+      </c>
+      <c r="C31" t="s">
+        <v>651</v>
+      </c>
+      <c r="D31" t="s">
+        <v>621</v>
+      </c>
+      <c r="E31">
+        <v>5</v>
+      </c>
+      <c r="F31">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s">
+        <v>648</v>
+      </c>
+      <c r="H31" t="s">
+        <v>648</v>
+      </c>
+      <c r="I31" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>667</v>
+      </c>
+      <c r="B32">
+        <v>409</v>
+      </c>
+      <c r="C32" t="s">
+        <v>654</v>
+      </c>
+      <c r="D32">
+        <v>409</v>
+      </c>
+      <c r="E32">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32" t="s">
+        <v>659</v>
+      </c>
+      <c r="H32" t="s">
+        <v>659</v>
+      </c>
+      <c r="I32" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>667</v>
+      </c>
+      <c r="B33">
+        <v>48</v>
+      </c>
+      <c r="C33" t="s">
+        <v>654</v>
+      </c>
+      <c r="D33">
+        <v>48</v>
+      </c>
+      <c r="E33">
+        <v>13</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33" t="s">
+        <v>659</v>
+      </c>
+      <c r="H33" t="s">
+        <v>659</v>
+      </c>
+      <c r="I33" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>667</v>
+      </c>
+      <c r="B34">
+        <v>414</v>
+      </c>
+      <c r="C34" t="s">
+        <v>654</v>
+      </c>
+      <c r="D34">
+        <v>414</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s">
+        <v>659</v>
+      </c>
+      <c r="H34" t="s">
+        <v>659</v>
+      </c>
+      <c r="I34" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>668</v>
+      </c>
+      <c r="B35">
+        <v>238</v>
+      </c>
+      <c r="C35" t="s">
+        <v>654</v>
+      </c>
+      <c r="D35">
+        <v>238</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+      <c r="F35">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>659</v>
+      </c>
+      <c r="H35" t="s">
+        <v>659</v>
+      </c>
+      <c r="I35" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>668</v>
+      </c>
+      <c r="B36">
+        <v>133</v>
+      </c>
+      <c r="C36" t="s">
+        <v>654</v>
+      </c>
+      <c r="D36">
+        <v>133</v>
+      </c>
+      <c r="E36">
+        <v>14</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>659</v>
+      </c>
+      <c r="H36" t="s">
+        <v>659</v>
+      </c>
+      <c r="I36" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>669</v>
+      </c>
+      <c r="B37">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s">
+        <v>654</v>
+      </c>
+      <c r="D37">
+        <v>143</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37" t="s">
+        <v>659</v>
+      </c>
+      <c r="H37" t="s">
+        <v>659</v>
+      </c>
+      <c r="I37" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>669</v>
+      </c>
+      <c r="B38">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>654</v>
+      </c>
+      <c r="D38">
+        <v>72</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38" t="s">
+        <v>659</v>
+      </c>
+      <c r="H38" t="s">
+        <v>659</v>
+      </c>
+      <c r="I38" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>669</v>
+      </c>
+      <c r="B39">
+        <v>219</v>
+      </c>
+      <c r="C39" t="s">
+        <v>654</v>
+      </c>
+      <c r="D39">
+        <v>219</v>
+      </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39" t="s">
+        <v>659</v>
+      </c>
+      <c r="H39" t="s">
+        <v>659</v>
+      </c>
+      <c r="I39" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>669</v>
+      </c>
+      <c r="B40">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>654</v>
+      </c>
+      <c r="D40">
+        <v>49</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40" t="s">
+        <v>659</v>
+      </c>
+      <c r="H40" t="s">
+        <v>659</v>
+      </c>
+      <c r="I40" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>669</v>
+      </c>
+      <c r="B41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C41" t="s">
+        <v>651</v>
+      </c>
+      <c r="D41" t="s">
+        <v>543</v>
+      </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="s">
+        <v>648</v>
+      </c>
+      <c r="H41" t="s">
+        <v>648</v>
+      </c>
+      <c r="I41" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>670</v>
+      </c>
+      <c r="B42">
+        <v>92</v>
+      </c>
+      <c r="C42" t="s">
+        <v>654</v>
+      </c>
+      <c r="D42">
+        <v>92</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42" t="s">
+        <v>659</v>
+      </c>
+      <c r="H42" t="s">
+        <v>673</v>
+      </c>
+      <c r="I42" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>671</v>
+      </c>
+      <c r="B43">
+        <v>241</v>
+      </c>
+      <c r="C43" t="s">
+        <v>654</v>
+      </c>
+      <c r="D43">
+        <v>241</v>
+      </c>
+      <c r="E43">
+        <v>13</v>
+      </c>
+      <c r="F43">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s">
+        <v>659</v>
+      </c>
+      <c r="H43" t="s">
+        <v>673</v>
+      </c>
+      <c r="I43" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>672</v>
+      </c>
+      <c r="B44">
+        <v>259</v>
+      </c>
+      <c r="C44" t="s">
+        <v>654</v>
+      </c>
+      <c r="D44">
+        <v>259</v>
+      </c>
+      <c r="E44">
+        <v>14</v>
+      </c>
+      <c r="F44">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>659</v>
+      </c>
+      <c r="H44" t="s">
+        <v>673</v>
+      </c>
+      <c r="I44" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>674</v>
+      </c>
+      <c r="B45">
+        <v>133</v>
+      </c>
+      <c r="C45" t="s">
+        <v>654</v>
+      </c>
+      <c r="D45">
+        <v>133</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45" t="s">
+        <v>659</v>
+      </c>
+      <c r="H45" t="s">
+        <v>673</v>
+      </c>
+      <c r="I45" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>674</v>
+      </c>
+      <c r="B46">
+        <v>139</v>
+      </c>
+      <c r="C46" t="s">
+        <v>654</v>
+      </c>
+      <c r="D46">
+        <v>139</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46" t="s">
+        <v>673</v>
+      </c>
+      <c r="H46" t="s">
+        <v>659</v>
+      </c>
+      <c r="I46" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>676</v>
+      </c>
+      <c r="B47">
+        <v>273</v>
+      </c>
+      <c r="C47" t="s">
+        <v>654</v>
+      </c>
+      <c r="D47">
+        <v>273</v>
+      </c>
+      <c r="E47">
+        <v>14</v>
+      </c>
+      <c r="F47">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>673</v>
+      </c>
+      <c r="H47" t="s">
+        <v>659</v>
+      </c>
+      <c r="I47" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>677</v>
+      </c>
+      <c r="B48">
+        <v>49</v>
+      </c>
+      <c r="C48" t="s">
+        <v>654</v>
+      </c>
+      <c r="D48">
+        <v>49</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48" t="s">
+        <v>659</v>
+      </c>
+      <c r="H48" t="s">
+        <v>673</v>
+      </c>
+      <c r="I48" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>677</v>
+      </c>
+      <c r="B49">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>654</v>
+      </c>
+      <c r="D49">
+        <v>8</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49" t="s">
+        <v>659</v>
+      </c>
+      <c r="H49" t="s">
+        <v>673</v>
+      </c>
+      <c r="I49" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>677</v>
+      </c>
+      <c r="B50">
+        <v>290</v>
+      </c>
+      <c r="C50" t="s">
+        <v>654</v>
+      </c>
+      <c r="D50">
+        <v>290</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50" t="s">
+        <v>659</v>
+      </c>
+      <c r="H50" t="s">
+        <v>673</v>
+      </c>
+      <c r="I50" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>679</v>
+      </c>
+      <c r="B51">
+        <v>209</v>
+      </c>
+      <c r="C51" t="s">
+        <v>654</v>
+      </c>
+      <c r="D51">
+        <v>209</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+      <c r="F51" t="s">
+        <v>648</v>
+      </c>
+      <c r="G51" t="s">
+        <v>659</v>
+      </c>
+      <c r="H51" t="s">
+        <v>648</v>
+      </c>
+      <c r="I51" t="s">
+        <v>652</v>
+      </c>
+      <c r="J51" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>680</v>
+      </c>
+      <c r="B52">
+        <v>94</v>
+      </c>
+      <c r="C52" t="s">
+        <v>654</v>
+      </c>
+      <c r="D52">
+        <v>94</v>
+      </c>
+      <c r="E52">
+        <v>13</v>
+      </c>
+      <c r="F52" t="s">
+        <v>648</v>
+      </c>
+      <c r="G52" t="s">
+        <v>659</v>
+      </c>
+      <c r="H52" t="s">
+        <v>648</v>
+      </c>
+      <c r="I52" t="s">
+        <v>652</v>
+      </c>
+      <c r="J52" t="s">
+        <v>681</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/roster.xlsx
+++ b/roster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sefazpegovbr-my.sharepoint.com/personal/filipe_lima_sefaz_pe_gov_br/Documents/Documents/GitHub/Fantasy-unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12B2ECF9-4285-493A-84ED-1AAF22E23E88}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43BCC050-E6D4-4141-93B1-3DA592554448}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="702">
   <si>
     <t>player</t>
   </si>
@@ -2143,6 +2143,15 @@
   </si>
   <si>
     <t>initiatedby</t>
+  </si>
+  <si>
+    <t>A.J. Dybantsa</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>Cameron Boozer</t>
   </si>
 </sst>
 </file>
@@ -2229,10 +2238,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2552,7 +2557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M417"/>
+  <dimension ref="A1:M420"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -15958,6 +15963,102 @@
         <v>0</v>
       </c>
       <c r="K417" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>417</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E418" s="1">
+        <v>0</v>
+      </c>
+      <c r="F418" s="1">
+        <v>0</v>
+      </c>
+      <c r="G418" s="1">
+        <v>0</v>
+      </c>
+      <c r="H418" s="1">
+        <v>0</v>
+      </c>
+      <c r="I418" s="1">
+        <v>0</v>
+      </c>
+      <c r="J418" s="1">
+        <v>0</v>
+      </c>
+      <c r="K418" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>418</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E419" s="1">
+        <v>0</v>
+      </c>
+      <c r="F419" s="1">
+        <v>0</v>
+      </c>
+      <c r="G419" s="1">
+        <v>0</v>
+      </c>
+      <c r="H419" s="1">
+        <v>0</v>
+      </c>
+      <c r="I419" s="1">
+        <v>0</v>
+      </c>
+      <c r="J419" s="1">
+        <v>0</v>
+      </c>
+      <c r="K419" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>419</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E420" s="1">
+        <v>0</v>
+      </c>
+      <c r="F420" s="1">
+        <v>0</v>
+      </c>
+      <c r="G420" s="1">
+        <v>0</v>
+      </c>
+      <c r="H420" s="1">
+        <v>0</v>
+      </c>
+      <c r="I420" s="1">
+        <v>0</v>
+      </c>
+      <c r="J420" s="1">
+        <v>0</v>
+      </c>
+      <c r="K420" s="1">
         <v>0</v>
       </c>
     </row>
@@ -23611,7 +23712,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:L177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24182,26 +24283,35 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29">
-        <v>320</v>
+        <v>419</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D29">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="F29">
-        <v>1000000</v>
-      </c>
-      <c r="G29" t="s">
+        <v>7500000</v>
+      </c>
+      <c r="H29">
+        <v>8250000</v>
+      </c>
+      <c r="I29" t="s">
+        <v>571</v>
+      </c>
+      <c r="J29">
+        <v>9000000</v>
+      </c>
+      <c r="K29" t="s">
         <v>571</v>
       </c>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
-        <v>Cam Spencer</v>
+        <v>Cameron Boozer</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -24209,23 +24319,23 @@
         <v>2</v>
       </c>
       <c r="B30">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>23500000</v>
+        <v>1000000</v>
       </c>
       <c r="F30">
-        <v>23500000</v>
-      </c>
-      <c r="H30">
-        <v>23500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G30" t="s">
+        <v>571</v>
       </c>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Alperen Şengün</v>
+        <v>Cam Spencer</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -24233,17 +24343,23 @@
         <v>2</v>
       </c>
       <c r="B31">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>15000000</v>
+        <v>23500000</v>
+      </c>
+      <c r="F31">
+        <v>23500000</v>
+      </c>
+      <c r="H31">
+        <v>23500000</v>
       </c>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Kevin Durant</v>
+        <v>Alperen Şengün</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -24251,17 +24367,17 @@
         <v>2</v>
       </c>
       <c r="B32">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>9000000</v>
+        <v>15000000</v>
       </c>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
-        <v>Brandon Miller</v>
+        <v>Kevin Durant</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -24269,23 +24385,17 @@
         <v>2</v>
       </c>
       <c r="B33">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>7000000</v>
-      </c>
-      <c r="F33">
-        <v>7000000</v>
-      </c>
-      <c r="H33">
-        <v>7000000</v>
+        <v>9000000</v>
       </c>
       <c r="L33" t="str">
         <f>VLOOKUP(B33,players!A:B,2)</f>
-        <v>Jalen Green</v>
+        <v>Brandon Miller</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -24293,20 +24403,23 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
       <c r="F34">
-        <v>6000000</v>
+        <v>7000000</v>
+      </c>
+      <c r="H34">
+        <v>7000000</v>
       </c>
       <c r="L34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
-        <v>Tyler Herro</v>
+        <v>Jalen Green</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -24314,23 +24427,20 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>362</v>
+        <v>144</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="F35">
-        <v>21500000</v>
-      </c>
-      <c r="H35">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="L35" t="str">
         <f>VLOOKUP(B35,players!A:B,2)</f>
-        <v>Trae Young</v>
+        <v>Tyler Herro</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -24338,14 +24448,23 @@
         <v>2</v>
       </c>
       <c r="B36">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D36">
+        <v>21500000</v>
+      </c>
+      <c r="F36">
+        <v>21500000</v>
+      </c>
+      <c r="H36">
+        <v>21500000</v>
       </c>
       <c r="L36" t="str">
         <f>VLOOKUP(B36,players!A:B,2)</f>
-        <v>Russell Westbrook</v>
+        <v>Trae Young</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -24353,44 +24472,38 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C37">
-        <v>10</v>
-      </c>
-      <c r="D37">
-        <v>3100000</v>
-      </c>
-      <c r="F37">
-        <v>3100000</v>
-      </c>
-      <c r="H37">
-        <v>3100000</v>
+        <v>8</v>
       </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>Bobby Portis</v>
+        <v>Russell Westbrook</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D38">
-        <v>8000000</v>
+        <v>3100000</v>
       </c>
       <c r="F38">
-        <v>8000000</v>
+        <v>3100000</v>
+      </c>
+      <c r="H38">
+        <v>3100000</v>
       </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>Immanuel Quickley</v>
+        <v>Bobby Portis</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -24398,14 +24511,20 @@
         <v>3</v>
       </c>
       <c r="B39">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>8000000</v>
+      </c>
+      <c r="F39">
+        <v>8000000</v>
       </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Nickeil Alexander-Walker</v>
+        <v>Immanuel Quickley</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -24413,14 +24532,14 @@
         <v>3</v>
       </c>
       <c r="B40">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Kyshawn George</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -24428,17 +24547,14 @@
         <v>3</v>
       </c>
       <c r="B41">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="C41">
-        <v>4</v>
-      </c>
-      <c r="D41">
-        <v>5000000</v>
+        <v>3</v>
       </c>
       <c r="L41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Cameron Johnson</v>
+        <v>Kyshawn George</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -24446,14 +24562,17 @@
         <v>3</v>
       </c>
       <c r="B42">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D42">
+        <v>5000000</v>
       </c>
       <c r="L42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Myles Turner</v>
+        <v>Cameron Johnson</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -24461,14 +24580,14 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>Mitchell Robinson</v>
+        <v>Myles Turner</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -24476,14 +24595,14 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L44" t="str">
         <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>Jalen Duren</v>
+        <v>Mitchell Robinson</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -24491,23 +24610,14 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C45">
-        <v>8</v>
-      </c>
-      <c r="D45">
-        <v>40000000</v>
-      </c>
-      <c r="F45">
-        <v>40000000</v>
-      </c>
-      <c r="H45">
-        <v>40000000</v>
+        <v>7</v>
       </c>
       <c r="L45" t="str">
         <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>Luka Dončić</v>
+        <v>Jalen Duren</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -24515,17 +24625,23 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46">
-        <v>6000000</v>
+        <v>40000000</v>
+      </c>
+      <c r="F46">
+        <v>40000000</v>
+      </c>
+      <c r="H46">
+        <v>40000000</v>
       </c>
       <c r="L46" t="str">
         <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>Kawhi Leonard</v>
+        <v>Luka Dončić</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -24533,20 +24649,17 @@
         <v>3</v>
       </c>
       <c r="B47">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D47">
-        <v>14000000</v>
-      </c>
-      <c r="F47">
-        <v>14000000</v>
+        <v>6000000</v>
       </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>Jaren Jackson Jr.</v>
+        <v>Kawhi Leonard</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -24554,23 +24667,20 @@
         <v>3</v>
       </c>
       <c r="B48">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C48">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="F48">
-        <v>6500000</v>
-      </c>
-      <c r="H48">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>OG Anunoby</v>
+        <v>Jaren Jackson Jr.</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -24578,17 +24688,23 @@
         <v>3</v>
       </c>
       <c r="B49">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C49">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49">
-        <v>5000000</v>
+        <v>6500000</v>
+      </c>
+      <c r="F49">
+        <v>6500000</v>
+      </c>
+      <c r="H49">
+        <v>6500000</v>
       </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>Kyrie Irving</v>
+        <v>OG Anunoby</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -24596,47 +24712,35 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>295</v>
+        <v>142</v>
       </c>
       <c r="C50">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D50">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>Zach LaVine</v>
+        <v>Kyrie Irving</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B51">
-        <v>379</v>
+        <v>295</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D51">
-        <v>1000000</v>
-      </c>
-      <c r="F51">
-        <v>1000000</v>
-      </c>
-      <c r="G51" t="s">
-        <v>571</v>
-      </c>
-      <c r="H51">
-        <v>1000000</v>
-      </c>
-      <c r="I51" t="s">
-        <v>571</v>
+        <v>8000000</v>
       </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -24644,10 +24748,10 @@
         <v>4</v>
       </c>
       <c r="B52">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>1000000</v>
@@ -24658,9 +24762,15 @@
       <c r="G52" t="s">
         <v>571</v>
       </c>
+      <c r="H52">
+        <v>1000000</v>
+      </c>
+      <c r="I52" t="s">
+        <v>571</v>
+      </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -24668,14 +24778,23 @@
         <v>4</v>
       </c>
       <c r="B53">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>1000000</v>
+      </c>
+      <c r="F53">
+        <v>1000000</v>
+      </c>
+      <c r="G53" t="s">
+        <v>571</v>
       </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -24683,17 +24802,14 @@
         <v>4</v>
       </c>
       <c r="B54">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C54">
-        <v>4</v>
-      </c>
-      <c r="D54">
-        <v>2500000</v>
+        <v>3</v>
       </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -24701,17 +24817,17 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D55">
-        <v>11000000</v>
+        <v>2500000</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -24719,20 +24835,17 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56">
-        <v>5000000</v>
-      </c>
-      <c r="F56">
-        <v>5000000</v>
+        <v>11000000</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -24740,20 +24853,20 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57">
-        <v>17000000</v>
+        <v>5000000</v>
       </c>
       <c r="F57">
-        <v>17000000</v>
+        <v>5000000</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -24761,17 +24874,20 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C58">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58">
-        <v>22500000</v>
+        <v>17000000</v>
+      </c>
+      <c r="F58">
+        <v>17000000</v>
       </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -24779,23 +24895,17 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C59">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59">
-        <v>5000000</v>
-      </c>
-      <c r="F59">
-        <v>5500000</v>
-      </c>
-      <c r="G59" t="s">
-        <v>571</v>
+        <v>22500000</v>
       </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -24803,23 +24913,23 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D60">
-        <v>15000000</v>
+        <v>5000000</v>
       </c>
       <c r="F60">
-        <v>15000000</v>
-      </c>
-      <c r="H60">
-        <v>15000000</v>
+        <v>5500000</v>
+      </c>
+      <c r="G60" t="s">
+        <v>571</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -24827,23 +24937,23 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="C61">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D61">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="F61">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="H61">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -24851,32 +24961,41 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>287</v>
+        <v>157</v>
       </c>
       <c r="C62">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D62">
-        <v>10000000</v>
+        <v>19000000</v>
+      </c>
+      <c r="F62">
+        <v>19000000</v>
+      </c>
+      <c r="H62">
+        <v>19000000</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B63">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D63">
+        <v>10000000</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -24884,29 +25003,14 @@
         <v>5</v>
       </c>
       <c r="B64">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="C64">
-        <v>2</v>
-      </c>
-      <c r="D64">
-        <v>3600000</v>
-      </c>
-      <c r="F64">
-        <v>3800000</v>
-      </c>
-      <c r="G64" t="s">
-        <v>571</v>
-      </c>
-      <c r="H64">
-        <v>4100000</v>
-      </c>
-      <c r="I64" t="s">
-        <v>571</v>
+        <v>1</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -24914,14 +25018,29 @@
         <v>5</v>
       </c>
       <c r="B65">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D65">
+        <v>3600000</v>
+      </c>
+      <c r="F65">
+        <v>3800000</v>
+      </c>
+      <c r="G65" t="s">
+        <v>571</v>
+      </c>
+      <c r="H65">
+        <v>4100000</v>
+      </c>
+      <c r="I65" t="s">
+        <v>571</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -24929,20 +25048,14 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="C66">
-        <v>4</v>
-      </c>
-      <c r="D66">
-        <v>21000000</v>
-      </c>
-      <c r="F66">
-        <v>21000000</v>
+        <v>3</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -24950,14 +25063,20 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C67">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D67">
+        <v>21000000</v>
+      </c>
+      <c r="F67">
+        <v>21000000</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -24965,29 +25084,14 @@
         <v>5</v>
       </c>
       <c r="B68">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C68">
-        <v>6</v>
-      </c>
-      <c r="D68">
-        <v>1000000</v>
-      </c>
-      <c r="F68">
-        <v>1000000</v>
-      </c>
-      <c r="G68" t="s">
-        <v>571</v>
-      </c>
-      <c r="H68">
-        <v>1000000</v>
-      </c>
-      <c r="I68" t="s">
-        <v>571</v>
+        <v>5</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>Danny Wolf</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -24995,20 +25099,29 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69">
-        <v>17000000</v>
+        <v>1000000</v>
       </c>
       <c r="F69">
-        <v>17000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G69" t="s">
+        <v>571</v>
+      </c>
+      <c r="H69">
+        <v>1000000</v>
+      </c>
+      <c r="I69" t="s">
+        <v>571</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>Danny Wolf</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -25016,23 +25129,20 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C70">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D70">
-        <v>40000000</v>
+        <v>17000000</v>
       </c>
       <c r="F70">
-        <v>40000000</v>
-      </c>
-      <c r="H70">
-        <v>40000000</v>
+        <v>17000000</v>
       </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -25040,20 +25150,23 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="C71">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D71">
-        <v>3100000</v>
+        <v>40000000</v>
       </c>
       <c r="F71">
-        <v>3100000</v>
+        <v>40000000</v>
+      </c>
+      <c r="H71">
+        <v>40000000</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -25061,14 +25174,20 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>227</v>
+        <v>72</v>
       </c>
       <c r="C72">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D72">
+        <v>3100000</v>
+      </c>
+      <c r="F72">
+        <v>3100000</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>Jerami Grant</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -25076,14 +25195,14 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="C73">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -25091,14 +25210,14 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="C74">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>Royce O'Neale</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -25106,53 +25225,62 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C75">
         <v>12</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Ryan Rollins</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B76">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76">
-        <v>6000000</v>
-      </c>
-      <c r="F76">
-        <v>6000000</v>
+        <v>12</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B77">
-        <v>338</v>
+        <v>418</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D77">
-        <v>1000000</v>
+        <v>8000000</v>
+      </c>
+      <c r="F77">
+        <v>8500000</v>
+      </c>
+      <c r="H77">
+        <v>9250000</v>
+      </c>
+      <c r="I77" t="s">
+        <v>571</v>
+      </c>
+      <c r="J77">
+        <v>10000000</v>
+      </c>
+      <c r="K77" t="s">
+        <v>571</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Caleb Wilson</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -25160,14 +25288,20 @@
         <v>6</v>
       </c>
       <c r="B78">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>6000000</v>
+      </c>
+      <c r="F78">
+        <v>6000000</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -25175,14 +25309,17 @@
         <v>6</v>
       </c>
       <c r="B79">
-        <v>122</v>
+        <v>338</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>1000000</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -25190,14 +25327,14 @@
         <v>6</v>
       </c>
       <c r="B80">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -25205,14 +25342,14 @@
         <v>6</v>
       </c>
       <c r="B81">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -25220,17 +25357,14 @@
         <v>6</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C82">
-        <v>7</v>
-      </c>
-      <c r="D82">
-        <v>20000000</v>
+        <v>5</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -25238,14 +25372,14 @@
         <v>6</v>
       </c>
       <c r="B83">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -25253,17 +25387,17 @@
         <v>6</v>
       </c>
       <c r="B84">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D84">
-        <v>7000000</v>
+        <v>20000000</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -25271,20 +25405,14 @@
         <v>6</v>
       </c>
       <c r="B85">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C85">
-        <v>10</v>
-      </c>
-      <c r="D85">
-        <v>35000000</v>
-      </c>
-      <c r="F85">
-        <v>35000000</v>
+        <v>8</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -25292,20 +25420,17 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C86">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D86">
-        <v>3100000</v>
-      </c>
-      <c r="F86">
-        <v>3100000</v>
+        <v>7000000</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -25313,17 +25438,20 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="C87">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D87">
-        <v>1000000</v>
+        <v>35000000</v>
+      </c>
+      <c r="F87">
+        <v>35000000</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -25331,14 +25459,20 @@
         <v>6</v>
       </c>
       <c r="B88">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="C88">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="D88">
+        <v>3100000</v>
+      </c>
+      <c r="F88">
+        <v>3100000</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Damian Lillard</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -25346,20 +25480,17 @@
         <v>6</v>
       </c>
       <c r="B89">
-        <v>93</v>
+        <v>211</v>
       </c>
       <c r="C89">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D89">
-        <v>6000000</v>
-      </c>
-      <c r="F89">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -25367,53 +25498,50 @@
         <v>6</v>
       </c>
       <c r="B90">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="C90">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Tari Eason</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B91">
-        <v>242</v>
+        <v>93</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D91">
-        <v>3800000</v>
+        <v>6000000</v>
       </c>
       <c r="F91">
-        <v>4100000</v>
-      </c>
-      <c r="G91" t="s">
-        <v>571</v>
+        <v>6000000</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B92">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -25421,29 +25549,23 @@
         <v>8</v>
       </c>
       <c r="B93">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="C93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D93">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="F93">
-        <v>1000000</v>
+        <v>4100000</v>
       </c>
       <c r="G93" t="s">
         <v>571</v>
       </c>
-      <c r="H93">
-        <v>1000000</v>
-      </c>
-      <c r="I93" t="s">
-        <v>571</v>
-      </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -25451,17 +25573,14 @@
         <v>8</v>
       </c>
       <c r="B94">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="C94">
-        <v>4</v>
-      </c>
-      <c r="D94">
-        <v>2000000</v>
+        <v>2</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -25469,23 +25588,29 @@
         <v>8</v>
       </c>
       <c r="B95">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C95">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D95">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="F95">
-        <v>6000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G95" t="s">
+        <v>571</v>
       </c>
       <c r="H95">
-        <v>6000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="I95" t="s">
+        <v>571</v>
       </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -25493,23 +25618,17 @@
         <v>8</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="C96">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D96">
-        <v>7000000</v>
-      </c>
-      <c r="F96">
-        <v>7500000</v>
-      </c>
-      <c r="G96" t="s">
-        <v>571</v>
+        <v>2000000</v>
       </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -25517,20 +25636,23 @@
         <v>8</v>
       </c>
       <c r="B97">
+        <v>116</v>
+      </c>
+      <c r="C97">
         <v>5</v>
       </c>
-      <c r="C97">
-        <v>7</v>
-      </c>
       <c r="D97">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="F97">
-        <v>4000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="H97">
+        <v>6000000</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -25538,23 +25660,23 @@
         <v>8</v>
       </c>
       <c r="B98">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D98">
-        <v>16000000</v>
+        <v>7000000</v>
       </c>
       <c r="F98">
-        <v>16000000</v>
-      </c>
-      <c r="H98">
-        <v>16000000</v>
+        <v>7500000</v>
+      </c>
+      <c r="G98" t="s">
+        <v>571</v>
       </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -25562,20 +25684,20 @@
         <v>8</v>
       </c>
       <c r="B99">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="C99">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D99">
-        <v>9000000</v>
+        <v>4000000</v>
       </c>
       <c r="F99">
-        <v>9000000</v>
+        <v>4000000</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -25583,17 +25705,23 @@
         <v>8</v>
       </c>
       <c r="B100">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="C100">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D100">
         <v>16000000</v>
       </c>
+      <c r="F100">
+        <v>16000000</v>
+      </c>
+      <c r="H100">
+        <v>16000000</v>
+      </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -25601,23 +25729,20 @@
         <v>8</v>
       </c>
       <c r="B101">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="C101">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D101">
-        <v>19000000</v>
+        <v>9000000</v>
       </c>
       <c r="F101">
-        <v>19000000</v>
-      </c>
-      <c r="H101">
-        <v>19000000</v>
+        <v>9000000</v>
       </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -25625,14 +25750,17 @@
         <v>8</v>
       </c>
       <c r="B102">
-        <v>225</v>
+        <v>84</v>
       </c>
       <c r="C102">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D102">
+        <v>16000000</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -25640,14 +25768,23 @@
         <v>8</v>
       </c>
       <c r="B103">
-        <v>59</v>
+        <v>203</v>
       </c>
       <c r="C103">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="D103">
+        <v>19000000</v>
+      </c>
+      <c r="F103">
+        <v>19000000</v>
+      </c>
+      <c r="H103">
+        <v>19000000</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -25655,53 +25792,44 @@
         <v>8</v>
       </c>
       <c r="B104">
-        <v>336</v>
+        <v>225</v>
       </c>
       <c r="C104">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B105">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="C105">
-        <v>1</v>
-      </c>
-      <c r="D105">
-        <v>3100000</v>
-      </c>
-      <c r="F105">
-        <v>3100000</v>
-      </c>
-      <c r="H105">
-        <v>3100000</v>
+        <v>13</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B106">
-        <v>240</v>
+        <v>336</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -25709,17 +25837,23 @@
         <v>9</v>
       </c>
       <c r="B107">
-        <v>186</v>
+        <v>384</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D107">
-        <v>4500000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F107">
+        <v>3100000</v>
+      </c>
+      <c r="H107">
+        <v>3100000</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -25727,14 +25861,14 @@
         <v>9</v>
       </c>
       <c r="B108">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -25742,14 +25876,17 @@
         <v>9</v>
       </c>
       <c r="B109">
-        <v>416</v>
+        <v>186</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="D109">
+        <v>4500000</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -25757,23 +25894,14 @@
         <v>9</v>
       </c>
       <c r="B110">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="C110">
-        <v>6</v>
-      </c>
-      <c r="D110">
-        <v>3100000</v>
-      </c>
-      <c r="F110">
-        <v>3100000</v>
-      </c>
-      <c r="H110">
-        <v>3100000</v>
+        <v>4</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -25781,23 +25909,14 @@
         <v>9</v>
       </c>
       <c r="B111">
-        <v>15</v>
+        <v>416</v>
       </c>
       <c r="C111">
-        <v>7</v>
-      </c>
-      <c r="D111">
-        <v>32000000</v>
-      </c>
-      <c r="F111">
-        <v>32000000</v>
-      </c>
-      <c r="H111">
-        <v>32000000</v>
+        <v>5</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -25805,23 +25924,23 @@
         <v>9</v>
       </c>
       <c r="B112">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="C112">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D112">
-        <v>12500000</v>
+        <v>3100000</v>
       </c>
       <c r="F112">
-        <v>12500000</v>
+        <v>3100000</v>
       </c>
       <c r="H112">
-        <v>12500000</v>
+        <v>3100000</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -25829,17 +25948,23 @@
         <v>9</v>
       </c>
       <c r="B113">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C113">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D113">
-        <v>11500000</v>
+        <v>32000000</v>
+      </c>
+      <c r="F113">
+        <v>32000000</v>
+      </c>
+      <c r="H113">
+        <v>32000000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -25847,23 +25972,23 @@
         <v>9</v>
       </c>
       <c r="B114">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="C114">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D114">
-        <v>3100000</v>
+        <v>12500000</v>
       </c>
       <c r="F114">
-        <v>3100000</v>
+        <v>12500000</v>
       </c>
       <c r="H114">
-        <v>3100000</v>
+        <v>12500000</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -25871,17 +25996,17 @@
         <v>9</v>
       </c>
       <c r="B115">
-        <v>217</v>
+        <v>89</v>
       </c>
       <c r="C115">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D115">
-        <v>25000000</v>
+        <v>11500000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -25889,53 +26014,65 @@
         <v>9</v>
       </c>
       <c r="B116">
-        <v>331</v>
+        <v>167</v>
       </c>
       <c r="C116">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D116">
-        <v>12000000</v>
+        <v>3100000</v>
       </c>
       <c r="F116">
-        <v>12000000</v>
+        <v>3100000</v>
       </c>
       <c r="H116">
-        <v>12000000</v>
+        <v>3100000</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B117">
-        <v>9</v>
+        <v>217</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D117">
+        <v>25000000</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Walker Kessler</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B118">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="D118">
+        <v>12000000</v>
+      </c>
+      <c r="F118">
+        <v>12000000</v>
+      </c>
+      <c r="H118">
+        <v>12000000</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -25943,14 +26080,14 @@
         <v>10</v>
       </c>
       <c r="B119">
-        <v>249</v>
+        <v>9</v>
       </c>
       <c r="C119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -25958,17 +26095,14 @@
         <v>10</v>
       </c>
       <c r="B120">
-        <v>169</v>
+        <v>373</v>
       </c>
       <c r="C120">
-        <v>4</v>
-      </c>
-      <c r="D120">
-        <v>4100000</v>
+        <v>2</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -25976,20 +26110,14 @@
         <v>10</v>
       </c>
       <c r="B121">
-        <v>34</v>
+        <v>249</v>
       </c>
       <c r="C121">
-        <v>5</v>
-      </c>
-      <c r="D121">
-        <v>6000000</v>
-      </c>
-      <c r="F121">
-        <v>6000000</v>
+        <v>3</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -25997,17 +26125,17 @@
         <v>10</v>
       </c>
       <c r="B122">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C122">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D122">
-        <v>1000000</v>
+        <v>4100000</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -26015,14 +26143,20 @@
         <v>10</v>
       </c>
       <c r="B123">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="D123">
+        <v>6000000</v>
+      </c>
+      <c r="F123">
+        <v>6000000</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -26030,23 +26164,17 @@
         <v>10</v>
       </c>
       <c r="B124">
-        <v>44</v>
+        <v>168</v>
       </c>
       <c r="C124">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D124">
-        <v>9250000</v>
-      </c>
-      <c r="F124">
-        <v>10000000</v>
-      </c>
-      <c r="G124" t="s">
-        <v>571</v>
+        <v>1000000</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -26054,23 +26182,14 @@
         <v>10</v>
       </c>
       <c r="B125">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C125">
-        <v>9</v>
-      </c>
-      <c r="D125">
-        <v>15000000</v>
-      </c>
-      <c r="F125">
-        <v>15000000</v>
-      </c>
-      <c r="H125">
-        <v>15000000</v>
+        <v>7</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -26078,20 +26197,23 @@
         <v>10</v>
       </c>
       <c r="B126">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="C126">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D126">
-        <v>11000000</v>
+        <v>9250000</v>
       </c>
       <c r="F126">
-        <v>11000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G126" t="s">
+        <v>571</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -26099,23 +26221,23 @@
         <v>10</v>
       </c>
       <c r="B127">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="C127">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D127">
-        <v>16000000</v>
+        <v>15000000</v>
       </c>
       <c r="F127">
-        <v>16000000</v>
+        <v>15000000</v>
       </c>
       <c r="H127">
-        <v>16000000</v>
+        <v>15000000</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -26123,47 +26245,62 @@
         <v>10</v>
       </c>
       <c r="B128">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="C128">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D128">
-        <v>24000000</v>
+        <v>11000000</v>
+      </c>
+      <c r="F128">
+        <v>11000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129">
+        <v>10</v>
+      </c>
+      <c r="B129">
+        <v>160</v>
+      </c>
+      <c r="C129">
         <v>11</v>
       </c>
-      <c r="B129">
-        <v>327</v>
-      </c>
-      <c r="C129">
-        <v>1</v>
+      <c r="D129">
+        <v>16000000</v>
+      </c>
+      <c r="F129">
+        <v>16000000</v>
+      </c>
+      <c r="H129">
+        <v>16000000</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B130">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="D130">
+        <v>24000000</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -26171,17 +26308,14 @@
         <v>11</v>
       </c>
       <c r="B131">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="C131">
-        <v>3</v>
-      </c>
-      <c r="D131">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -26189,14 +26323,14 @@
         <v>11</v>
       </c>
       <c r="B132">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="C132">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -26204,17 +26338,17 @@
         <v>11</v>
       </c>
       <c r="B133">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="C133">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D133">
         <v>1000000</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -26222,14 +26356,14 @@
         <v>11</v>
       </c>
       <c r="B134">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C134">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -26237,17 +26371,17 @@
         <v>11</v>
       </c>
       <c r="B135">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D135">
-        <v>26000000</v>
+        <v>1000000</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -26255,17 +26389,14 @@
         <v>11</v>
       </c>
       <c r="B136">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="C136">
-        <v>8</v>
-      </c>
-      <c r="D136">
-        <v>15000000</v>
+        <v>6</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -26273,17 +26404,17 @@
         <v>11</v>
       </c>
       <c r="B137">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C137">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D137">
-        <v>7500000</v>
+        <v>26000000</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -26291,23 +26422,17 @@
         <v>11</v>
       </c>
       <c r="B138">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C138">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D138">
-        <v>30000000</v>
-      </c>
-      <c r="F138">
-        <v>30000000</v>
-      </c>
-      <c r="H138">
-        <v>30000000</v>
+        <v>15000000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -26315,17 +26440,17 @@
         <v>11</v>
       </c>
       <c r="B139">
-        <v>248</v>
+        <v>35</v>
       </c>
       <c r="C139">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D139">
-        <v>1000000</v>
+        <v>7500000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -26333,14 +26458,23 @@
         <v>11</v>
       </c>
       <c r="B140">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="C140">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D140">
+        <v>30000000</v>
+      </c>
+      <c r="F140">
+        <v>30000000</v>
+      </c>
+      <c r="H140">
+        <v>30000000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -26348,14 +26482,17 @@
         <v>11</v>
       </c>
       <c r="B141">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="C141">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="D141">
+        <v>1000000</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -26363,56 +26500,44 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="C142">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B143">
-        <v>403</v>
+        <v>266</v>
       </c>
       <c r="C143">
-        <v>1</v>
-      </c>
-      <c r="D143">
-        <v>5000000</v>
-      </c>
-      <c r="F143">
-        <v>5000000</v>
+        <v>13</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B144">
-        <v>345</v>
+        <v>195</v>
       </c>
       <c r="C144">
-        <v>2</v>
-      </c>
-      <c r="D144">
-        <v>3500000</v>
-      </c>
-      <c r="F144">
-        <v>3500000</v>
+        <v>14</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -26420,17 +26545,20 @@
         <v>12</v>
       </c>
       <c r="B145">
-        <v>120</v>
+        <v>403</v>
       </c>
       <c r="C145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145">
-        <v>1000000</v>
+        <v>5000000</v>
+      </c>
+      <c r="F145">
+        <v>5000000</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -26438,14 +26566,20 @@
         <v>12</v>
       </c>
       <c r="B146">
-        <v>22</v>
+        <v>345</v>
       </c>
       <c r="C146">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D146">
+        <v>3500000</v>
+      </c>
+      <c r="F146">
+        <v>3500000</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -26453,17 +26587,17 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="C147">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D147">
-        <v>11000000</v>
+        <v>1000000</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -26471,20 +26605,14 @@
         <v>12</v>
       </c>
       <c r="B148">
-        <v>194</v>
+        <v>22</v>
       </c>
       <c r="C148">
-        <v>6</v>
-      </c>
-      <c r="D148">
-        <v>20000000</v>
-      </c>
-      <c r="F148">
-        <v>20000000</v>
+        <v>4</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -26492,23 +26620,17 @@
         <v>12</v>
       </c>
       <c r="B149">
-        <v>226</v>
+        <v>54</v>
       </c>
       <c r="C149">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D149">
-        <v>18000000</v>
-      </c>
-      <c r="F149">
-        <v>18000000</v>
-      </c>
-      <c r="H149">
-        <v>18000000</v>
+        <v>11000000</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -26516,68 +26638,92 @@
         <v>12</v>
       </c>
       <c r="B150">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="C150">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D150">
-        <v>2500000</v>
+        <v>20000000</v>
+      </c>
+      <c r="F150">
+        <v>20000000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B151">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D151">
-        <v>1000000</v>
+        <v>18000000</v>
+      </c>
+      <c r="F151">
+        <v>18000000</v>
+      </c>
+      <c r="H151">
+        <v>18000000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B152">
-        <v>363</v>
+        <v>115</v>
       </c>
       <c r="C152">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="D152">
+        <v>2500000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B153">
-        <v>296</v>
+        <v>417</v>
       </c>
       <c r="C153">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D153">
-        <v>3000000</v>
+        <v>9000000</v>
+      </c>
+      <c r="F153">
+        <v>9500000</v>
+      </c>
+      <c r="H153">
+        <v>10500000</v>
+      </c>
+      <c r="I153" t="s">
+        <v>571</v>
+      </c>
+      <c r="J153">
+        <v>11500000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>A.J. Dybantsa</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -26585,17 +26731,17 @@
         <v>13</v>
       </c>
       <c r="B154">
-        <v>171</v>
+        <v>307</v>
       </c>
       <c r="C154">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D154">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -26603,14 +26749,14 @@
         <v>13</v>
       </c>
       <c r="B155">
-        <v>10</v>
+        <v>363</v>
       </c>
       <c r="C155">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -26618,14 +26764,17 @@
         <v>13</v>
       </c>
       <c r="B156">
-        <v>46</v>
+        <v>296</v>
       </c>
       <c r="C156">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="D156">
+        <v>3000000</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -26633,17 +26782,17 @@
         <v>13</v>
       </c>
       <c r="B157">
+        <v>171</v>
+      </c>
+      <c r="C157">
         <v>4</v>
       </c>
-      <c r="C157">
-        <v>7</v>
-      </c>
       <c r="D157">
-        <v>11500000</v>
+        <v>2000000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -26651,23 +26800,14 @@
         <v>13</v>
       </c>
       <c r="B158">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C158">
-        <v>8</v>
-      </c>
-      <c r="D158">
-        <v>16000000</v>
-      </c>
-      <c r="F158">
-        <v>16000000</v>
-      </c>
-      <c r="H158">
-        <v>16000000</v>
+        <v>5</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -26675,23 +26815,14 @@
         <v>13</v>
       </c>
       <c r="B159">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C159">
-        <v>9</v>
-      </c>
-      <c r="D159">
-        <v>12000000</v>
-      </c>
-      <c r="F159">
-        <v>12000000</v>
-      </c>
-      <c r="H159">
-        <v>12000000</v>
+        <v>6</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -26699,17 +26830,17 @@
         <v>13</v>
       </c>
       <c r="B160">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="C160">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D160">
-        <v>19000000</v>
+        <v>11500000</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -26717,68 +26848,89 @@
         <v>13</v>
       </c>
       <c r="B161">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="C161">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D161">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="F161">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="H161">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B162">
-        <v>317</v>
+        <v>55</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="D162">
+        <v>12000000</v>
+      </c>
+      <c r="F162">
+        <v>12000000</v>
+      </c>
+      <c r="H162">
+        <v>12000000</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B163">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="D163">
+        <v>19000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B164">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C164">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D164">
+        <v>6000000</v>
+      </c>
+      <c r="F164">
+        <v>6000000</v>
+      </c>
+      <c r="H164">
+        <v>6000000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -26786,14 +26938,14 @@
         <v>14</v>
       </c>
       <c r="B165">
-        <v>90</v>
+        <v>317</v>
       </c>
       <c r="C165">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -26801,17 +26953,14 @@
         <v>14</v>
       </c>
       <c r="B166">
-        <v>24</v>
+        <v>299</v>
       </c>
       <c r="C166">
-        <v>5</v>
-      </c>
-      <c r="D166">
-        <v>1000000</v>
+        <v>2</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -26819,17 +26968,14 @@
         <v>14</v>
       </c>
       <c r="B167">
-        <v>238</v>
+        <v>129</v>
       </c>
       <c r="C167">
-        <v>6</v>
-      </c>
-      <c r="D167">
-        <v>3000000</v>
+        <v>3</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -26837,23 +26983,14 @@
         <v>14</v>
       </c>
       <c r="B168">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C168">
-        <v>7</v>
-      </c>
-      <c r="D168">
-        <v>20500000</v>
-      </c>
-      <c r="F168">
-        <v>20500000</v>
-      </c>
-      <c r="H168">
-        <v>20500000</v>
+        <v>4</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -26861,17 +26998,17 @@
         <v>14</v>
       </c>
       <c r="B169">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="C169">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D169">
-        <v>19500000</v>
+        <v>1000000</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -26879,29 +27016,17 @@
         <v>14</v>
       </c>
       <c r="B170">
-        <v>61</v>
+        <v>238</v>
       </c>
       <c r="C170">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D170">
-        <v>9500000</v>
-      </c>
-      <c r="F170">
-        <v>10500000</v>
-      </c>
-      <c r="G170" t="s">
-        <v>571</v>
-      </c>
-      <c r="H170">
-        <v>11500000</v>
-      </c>
-      <c r="I170" t="s">
-        <v>571</v>
+        <v>3000000</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -26909,14 +27034,23 @@
         <v>14</v>
       </c>
       <c r="B171">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C171">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D171">
+        <v>20500000</v>
+      </c>
+      <c r="F171">
+        <v>20500000</v>
+      </c>
+      <c r="H171">
+        <v>20500000</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -26924,14 +27058,17 @@
         <v>14</v>
       </c>
       <c r="B172">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="C172">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="D172">
+        <v>19500000</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -26939,23 +27076,29 @@
         <v>14</v>
       </c>
       <c r="B173">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="C173">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D173">
-        <v>20000000</v>
+        <v>9500000</v>
       </c>
       <c r="F173">
-        <v>20000000</v>
+        <v>10500000</v>
+      </c>
+      <c r="G173" t="s">
+        <v>571</v>
       </c>
       <c r="H173">
-        <v>20000000</v>
+        <v>11500000</v>
+      </c>
+      <c r="I173" t="s">
+        <v>571</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -26963,19 +27106,73 @@
         <v>14</v>
       </c>
       <c r="B174">
-        <v>273</v>
+        <v>2</v>
       </c>
       <c r="C174">
-        <v>13</v>
-      </c>
-      <c r="D174">
-        <v>3200000</v>
-      </c>
-      <c r="F174">
-        <v>3500000</v>
+        <v>10</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>14</v>
+      </c>
+      <c r="B175">
+        <v>220</v>
+      </c>
+      <c r="C175">
+        <v>11</v>
+      </c>
+      <c r="L175" t="str">
+        <f>VLOOKUP(B175,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>14</v>
+      </c>
+      <c r="B176">
+        <v>145</v>
+      </c>
+      <c r="C176">
+        <v>12</v>
+      </c>
+      <c r="D176">
+        <v>20000000</v>
+      </c>
+      <c r="F176">
+        <v>20000000</v>
+      </c>
+      <c r="H176">
+        <v>20000000</v>
+      </c>
+      <c r="L176" t="str">
+        <f>VLOOKUP(B176,players!A:B,2)</f>
+        <v>LaMelo Ball</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>14</v>
+      </c>
+      <c r="B177">
+        <v>273</v>
+      </c>
+      <c r="C177">
+        <v>13</v>
+      </c>
+      <c r="D177">
+        <v>3200000</v>
+      </c>
+      <c r="F177">
+        <v>3500000</v>
+      </c>
+      <c r="L177" t="str">
+        <f>VLOOKUP(B177,players!A:B,2)</f>
         <v>Cason Wallace</v>
       </c>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sefazpegovbr-my.sharepoint.com/personal/filipe_lima_sefaz_pe_gov_br/Documents/Documents/GitHub/Fantasy-unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43BCC050-E6D4-4141-93B1-3DA592554448}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21447A72-2EBF-4D52-83D7-8697F6774188}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="704">
   <si>
     <t>player</t>
   </si>
@@ -2152,6 +2152,12 @@
   </si>
   <si>
     <t>Cameron Boozer</t>
+  </si>
+  <si>
+    <t>Darryn Peterson</t>
+  </si>
+  <si>
+    <t>Darius Acuff</t>
   </si>
 </sst>
 </file>
@@ -2557,7 +2563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M420"/>
+  <dimension ref="A1:M422"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -16059,6 +16065,70 @@
         <v>0</v>
       </c>
       <c r="K420" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>420</v>
+      </c>
+      <c r="B421" t="s">
+        <v>702</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E421" s="1">
+        <v>0</v>
+      </c>
+      <c r="F421" s="1">
+        <v>0</v>
+      </c>
+      <c r="G421" s="1">
+        <v>0</v>
+      </c>
+      <c r="H421" s="1">
+        <v>0</v>
+      </c>
+      <c r="I421" s="1">
+        <v>0</v>
+      </c>
+      <c r="J421" s="1">
+        <v>0</v>
+      </c>
+      <c r="K421" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>421</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E422" s="1">
+        <v>0</v>
+      </c>
+      <c r="F422" s="1">
+        <v>0</v>
+      </c>
+      <c r="G422" s="1">
+        <v>0</v>
+      </c>
+      <c r="H422" s="1">
+        <v>0</v>
+      </c>
+      <c r="I422" s="1">
+        <v>0</v>
+      </c>
+      <c r="J422" s="1">
+        <v>0</v>
+      </c>
+      <c r="K422" s="1">
         <v>0</v>
       </c>
     </row>
@@ -23712,7 +23782,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:L177"/>
+  <dimension ref="A1:L179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24016,41 +24086,59 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B16">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D16">
-        <v>3100000</v>
+        <v>5000000</v>
       </c>
       <c r="F16">
-        <v>3100000</v>
+        <v>5500000</v>
       </c>
       <c r="H16">
-        <v>3100000</v>
+        <v>6000000</v>
+      </c>
+      <c r="I16" t="s">
+        <v>571</v>
+      </c>
+      <c r="J16">
+        <v>6500000</v>
+      </c>
+      <c r="K16" t="s">
+        <v>571</v>
       </c>
       <c r="L16" t="str">
         <f>VLOOKUP(B16,players!A:B,2)</f>
-        <v>Jaden Ivey</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>Darius Acuff</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>3100000</v>
+      </c>
+      <c r="F17">
+        <v>3100000</v>
+      </c>
+      <c r="H17">
+        <v>3100000</v>
       </c>
       <c r="L17" t="str">
         <f>VLOOKUP(B17,players!A:B,2)</f>
-        <v>Bogdan Bogdanović</v>
+        <v>Jaden Ivey</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -24058,29 +24146,14 @@
         <v>1</v>
       </c>
       <c r="B18">
-        <v>172</v>
+        <v>314</v>
       </c>
       <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>7500000</v>
-      </c>
-      <c r="F18">
-        <v>8500000</v>
-      </c>
-      <c r="G18" t="s">
-        <v>571</v>
-      </c>
-      <c r="H18">
-        <v>9000000</v>
-      </c>
-      <c r="I18" t="s">
-        <v>571</v>
+        <v>2</v>
       </c>
       <c r="L18" t="str">
         <f>VLOOKUP(B18,players!A:B,2)</f>
-        <v>Ace Bailey</v>
+        <v>Bogdan Bogdanović</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -24088,14 +24161,29 @@
         <v>1</v>
       </c>
       <c r="B19">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>7500000</v>
+      </c>
+      <c r="F19">
+        <v>8500000</v>
+      </c>
+      <c r="G19" t="s">
+        <v>571</v>
+      </c>
+      <c r="H19">
+        <v>9000000</v>
+      </c>
+      <c r="I19" t="s">
+        <v>571</v>
       </c>
       <c r="L19" t="str">
         <f>VLOOKUP(B19,players!A:B,2)</f>
-        <v>Andrew Wiggins</v>
+        <v>Ace Bailey</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -24103,14 +24191,14 @@
         <v>1</v>
       </c>
       <c r="B20">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L20" t="str">
         <f>VLOOKUP(B20,players!A:B,2)</f>
-        <v>Noah Clowney</v>
+        <v>Andrew Wiggins</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -24118,29 +24206,14 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>355</v>
+        <v>180</v>
       </c>
       <c r="C21">
-        <v>6</v>
-      </c>
-      <c r="D21">
-        <v>1000000</v>
-      </c>
-      <c r="F21">
-        <v>1000000</v>
-      </c>
-      <c r="G21" t="s">
-        <v>571</v>
-      </c>
-      <c r="H21">
-        <v>1000000</v>
-      </c>
-      <c r="I21" t="s">
-        <v>571</v>
+        <v>5</v>
       </c>
       <c r="L21" t="str">
         <f>VLOOKUP(B21,players!A:B,2)</f>
-        <v>Asa Newell</v>
+        <v>Noah Clowney</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -24148,14 +24221,29 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>39</v>
+        <v>355</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>1000000</v>
+      </c>
+      <c r="F22">
+        <v>1000000</v>
+      </c>
+      <c r="G22" t="s">
+        <v>571</v>
+      </c>
+      <c r="H22">
+        <v>1000000</v>
+      </c>
+      <c r="I22" t="s">
+        <v>571</v>
       </c>
       <c r="L22" t="str">
         <f>VLOOKUP(B22,players!A:B,2)</f>
-        <v>Onyeka Okongwu</v>
+        <v>Asa Newell</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -24163,23 +24251,14 @@
         <v>1</v>
       </c>
       <c r="B23">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="C23">
-        <v>8</v>
-      </c>
-      <c r="D23">
-        <v>4200000</v>
-      </c>
-      <c r="F23">
-        <v>4500000</v>
-      </c>
-      <c r="G23" t="s">
-        <v>571</v>
+        <v>7</v>
       </c>
       <c r="L23" t="str">
         <f>VLOOKUP(B23,players!A:B,2)</f>
-        <v>Matas Buzelis</v>
+        <v>Onyeka Okongwu</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -24187,23 +24266,23 @@
         <v>1</v>
       </c>
       <c r="B24">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>40000000</v>
+        <v>4200000</v>
       </c>
       <c r="F24">
-        <v>40000000</v>
-      </c>
-      <c r="H24">
-        <v>40000000</v>
+        <v>4500000</v>
+      </c>
+      <c r="G24" t="s">
+        <v>571</v>
       </c>
       <c r="L24" t="str">
         <f>VLOOKUP(B24,players!A:B,2)</f>
-        <v>Anthony Edwards</v>
+        <v>Matas Buzelis</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -24211,23 +24290,23 @@
         <v>1</v>
       </c>
       <c r="B25">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25">
-        <v>30500000</v>
+        <v>40000000</v>
       </c>
       <c r="F25">
-        <v>30500000</v>
+        <v>40000000</v>
       </c>
       <c r="H25">
-        <v>30500000</v>
+        <v>40000000</v>
       </c>
       <c r="L25" t="str">
         <f>VLOOKUP(B25,players!A:B,2)</f>
-        <v>Tyrese Maxey</v>
+        <v>Anthony Edwards</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -24235,17 +24314,23 @@
         <v>1</v>
       </c>
       <c r="B26">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>1000000</v>
+        <v>30500000</v>
+      </c>
+      <c r="F26">
+        <v>30500000</v>
+      </c>
+      <c r="H26">
+        <v>30500000</v>
       </c>
       <c r="L26" t="str">
         <f>VLOOKUP(B26,players!A:B,2)</f>
-        <v>Donte DiVincenzo</v>
+        <v>Tyrese Maxey</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -24253,17 +24338,17 @@
         <v>1</v>
       </c>
       <c r="B27">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="L27" t="str">
         <f>VLOOKUP(B27,players!A:B,2)</f>
-        <v>Mikal Bridges</v>
+        <v>Donte DiVincenzo</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -24271,14 +24356,17 @@
         <v>1</v>
       </c>
       <c r="B28">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="C28">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="D28">
+        <v>7000000</v>
       </c>
       <c r="L28" t="str">
         <f>VLOOKUP(B28,players!A:B,2)</f>
-        <v>Jay Huff</v>
+        <v>Mikal Bridges</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -24286,56 +24374,47 @@
         <v>1</v>
       </c>
       <c r="B29">
-        <v>419</v>
+        <v>187</v>
       </c>
       <c r="C29">
-        <v>14</v>
-      </c>
-      <c r="D29">
-        <v>7000000</v>
-      </c>
-      <c r="F29">
-        <v>7500000</v>
-      </c>
-      <c r="H29">
-        <v>8250000</v>
-      </c>
-      <c r="I29" t="s">
-        <v>571</v>
-      </c>
-      <c r="J29">
-        <v>9000000</v>
-      </c>
-      <c r="K29" t="s">
-        <v>571</v>
+        <v>13</v>
       </c>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
-        <v>Cameron Boozer</v>
+        <v>Jay Huff</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30">
-        <v>320</v>
+        <v>419</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D30">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="F30">
-        <v>1000000</v>
-      </c>
-      <c r="G30" t="s">
+        <v>7500000</v>
+      </c>
+      <c r="H30">
+        <v>8250000</v>
+      </c>
+      <c r="I30" t="s">
+        <v>571</v>
+      </c>
+      <c r="J30">
+        <v>9000000</v>
+      </c>
+      <c r="K30" t="s">
         <v>571</v>
       </c>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Cam Spencer</v>
+        <v>Cameron Boozer</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -24343,23 +24422,23 @@
         <v>2</v>
       </c>
       <c r="B31">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>23500000</v>
+        <v>1000000</v>
       </c>
       <c r="F31">
-        <v>23500000</v>
-      </c>
-      <c r="H31">
-        <v>23500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G31" t="s">
+        <v>571</v>
       </c>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Alperen Şengün</v>
+        <v>Cam Spencer</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -24367,17 +24446,23 @@
         <v>2</v>
       </c>
       <c r="B32">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>15000000</v>
+        <v>23500000</v>
+      </c>
+      <c r="F32">
+        <v>23500000</v>
+      </c>
+      <c r="H32">
+        <v>23500000</v>
       </c>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
-        <v>Kevin Durant</v>
+        <v>Alperen Şengün</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -24385,17 +24470,17 @@
         <v>2</v>
       </c>
       <c r="B33">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>9000000</v>
+        <v>15000000</v>
       </c>
       <c r="L33" t="str">
         <f>VLOOKUP(B33,players!A:B,2)</f>
-        <v>Brandon Miller</v>
+        <v>Kevin Durant</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -24403,23 +24488,17 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>7000000</v>
-      </c>
-      <c r="F34">
-        <v>7000000</v>
-      </c>
-      <c r="H34">
-        <v>7000000</v>
+        <v>9000000</v>
       </c>
       <c r="L34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
-        <v>Jalen Green</v>
+        <v>Brandon Miller</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -24427,20 +24506,23 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
       <c r="F35">
-        <v>6000000</v>
+        <v>7000000</v>
+      </c>
+      <c r="H35">
+        <v>7000000</v>
       </c>
       <c r="L35" t="str">
         <f>VLOOKUP(B35,players!A:B,2)</f>
-        <v>Tyler Herro</v>
+        <v>Jalen Green</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -24448,23 +24530,20 @@
         <v>2</v>
       </c>
       <c r="B36">
-        <v>362</v>
+        <v>144</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="F36">
-        <v>21500000</v>
-      </c>
-      <c r="H36">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="L36" t="str">
         <f>VLOOKUP(B36,players!A:B,2)</f>
-        <v>Trae Young</v>
+        <v>Tyler Herro</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -24472,14 +24551,23 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D37">
+        <v>21500000</v>
+      </c>
+      <c r="F37">
+        <v>21500000</v>
+      </c>
+      <c r="H37">
+        <v>21500000</v>
       </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>Russell Westbrook</v>
+        <v>Trae Young</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -24487,44 +24575,38 @@
         <v>2</v>
       </c>
       <c r="B38">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C38">
-        <v>10</v>
-      </c>
-      <c r="D38">
-        <v>3100000</v>
-      </c>
-      <c r="F38">
-        <v>3100000</v>
-      </c>
-      <c r="H38">
-        <v>3100000</v>
+        <v>8</v>
       </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>Bobby Portis</v>
+        <v>Russell Westbrook</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D39">
-        <v>8000000</v>
+        <v>3100000</v>
       </c>
       <c r="F39">
-        <v>8000000</v>
+        <v>3100000</v>
+      </c>
+      <c r="H39">
+        <v>3100000</v>
       </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Immanuel Quickley</v>
+        <v>Bobby Portis</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -24532,14 +24614,20 @@
         <v>3</v>
       </c>
       <c r="B40">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>8000000</v>
+      </c>
+      <c r="F40">
+        <v>8000000</v>
       </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Nickeil Alexander-Walker</v>
+        <v>Immanuel Quickley</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -24547,14 +24635,14 @@
         <v>3</v>
       </c>
       <c r="B41">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Kyshawn George</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -24562,17 +24650,14 @@
         <v>3</v>
       </c>
       <c r="B42">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="C42">
-        <v>4</v>
-      </c>
-      <c r="D42">
-        <v>5000000</v>
+        <v>3</v>
       </c>
       <c r="L42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Cameron Johnson</v>
+        <v>Kyshawn George</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -24580,14 +24665,17 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D43">
+        <v>5000000</v>
       </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>Myles Turner</v>
+        <v>Cameron Johnson</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -24595,14 +24683,14 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L44" t="str">
         <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>Mitchell Robinson</v>
+        <v>Myles Turner</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -24610,14 +24698,14 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L45" t="str">
         <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>Jalen Duren</v>
+        <v>Mitchell Robinson</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -24625,23 +24713,14 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C46">
-        <v>8</v>
-      </c>
-      <c r="D46">
-        <v>40000000</v>
-      </c>
-      <c r="F46">
-        <v>40000000</v>
-      </c>
-      <c r="H46">
-        <v>40000000</v>
+        <v>7</v>
       </c>
       <c r="L46" t="str">
         <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>Luka Dončić</v>
+        <v>Jalen Duren</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -24649,17 +24728,23 @@
         <v>3</v>
       </c>
       <c r="B47">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47">
-        <v>6000000</v>
+        <v>40000000</v>
+      </c>
+      <c r="F47">
+        <v>40000000</v>
+      </c>
+      <c r="H47">
+        <v>40000000</v>
       </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>Kawhi Leonard</v>
+        <v>Luka Dončić</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -24667,20 +24752,17 @@
         <v>3</v>
       </c>
       <c r="B48">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D48">
-        <v>14000000</v>
-      </c>
-      <c r="F48">
-        <v>14000000</v>
+        <v>6000000</v>
       </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>Jaren Jackson Jr.</v>
+        <v>Kawhi Leonard</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -24688,23 +24770,20 @@
         <v>3</v>
       </c>
       <c r="B49">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C49">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D49">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="F49">
-        <v>6500000</v>
-      </c>
-      <c r="H49">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>OG Anunoby</v>
+        <v>Jaren Jackson Jr.</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -24712,17 +24791,23 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D50">
-        <v>5000000</v>
+        <v>6500000</v>
+      </c>
+      <c r="F50">
+        <v>6500000</v>
+      </c>
+      <c r="H50">
+        <v>6500000</v>
       </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>Kyrie Irving</v>
+        <v>OG Anunoby</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -24730,47 +24815,35 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>295</v>
+        <v>142</v>
       </c>
       <c r="C51">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D51">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>Zach LaVine</v>
+        <v>Kyrie Irving</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52">
-        <v>379</v>
+        <v>295</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D52">
-        <v>1000000</v>
-      </c>
-      <c r="F52">
-        <v>1000000</v>
-      </c>
-      <c r="G52" t="s">
-        <v>571</v>
-      </c>
-      <c r="H52">
-        <v>1000000</v>
-      </c>
-      <c r="I52" t="s">
-        <v>571</v>
+        <v>8000000</v>
       </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -24778,10 +24851,10 @@
         <v>4</v>
       </c>
       <c r="B53">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>1000000</v>
@@ -24792,9 +24865,15 @@
       <c r="G53" t="s">
         <v>571</v>
       </c>
+      <c r="H53">
+        <v>1000000</v>
+      </c>
+      <c r="I53" t="s">
+        <v>571</v>
+      </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -24802,14 +24881,23 @@
         <v>4</v>
       </c>
       <c r="B54">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>1000000</v>
+      </c>
+      <c r="F54">
+        <v>1000000</v>
+      </c>
+      <c r="G54" t="s">
+        <v>571</v>
       </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -24817,17 +24905,14 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C55">
-        <v>4</v>
-      </c>
-      <c r="D55">
-        <v>2500000</v>
+        <v>3</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -24835,17 +24920,17 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56">
-        <v>11000000</v>
+        <v>2500000</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -24853,20 +24938,17 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57">
-        <v>5000000</v>
-      </c>
-      <c r="F57">
-        <v>5000000</v>
+        <v>11000000</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -24874,20 +24956,20 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D58">
-        <v>17000000</v>
+        <v>5000000</v>
       </c>
       <c r="F58">
-        <v>17000000</v>
+        <v>5000000</v>
       </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -24895,17 +24977,20 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59">
-        <v>22500000</v>
+        <v>17000000</v>
+      </c>
+      <c r="F59">
+        <v>17000000</v>
       </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -24913,23 +24998,17 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D60">
-        <v>5000000</v>
-      </c>
-      <c r="F60">
-        <v>5500000</v>
-      </c>
-      <c r="G60" t="s">
-        <v>571</v>
+        <v>22500000</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -24937,23 +25016,23 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D61">
-        <v>15000000</v>
+        <v>5000000</v>
       </c>
       <c r="F61">
-        <v>15000000</v>
-      </c>
-      <c r="H61">
-        <v>15000000</v>
+        <v>5500000</v>
+      </c>
+      <c r="G61" t="s">
+        <v>571</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -24961,23 +25040,23 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D62">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="F62">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="H62">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -24985,62 +25064,74 @@
         <v>4</v>
       </c>
       <c r="B63">
-        <v>287</v>
+        <v>157</v>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D63">
-        <v>10000000</v>
+        <v>19000000</v>
+      </c>
+      <c r="F63">
+        <v>19000000</v>
+      </c>
+      <c r="H63">
+        <v>19000000</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D64">
+        <v>10000000</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65">
-        <v>262</v>
+        <v>420</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D65">
-        <v>3600000</v>
+        <v>6000000</v>
       </c>
       <c r="F65">
-        <v>3800000</v>
-      </c>
-      <c r="G65" t="s">
-        <v>571</v>
+        <v>6500000</v>
       </c>
       <c r="H65">
-        <v>4100000</v>
+        <v>7000000</v>
       </c>
       <c r="I65" t="s">
         <v>571</v>
       </c>
+      <c r="J65">
+        <v>7500000</v>
+      </c>
+      <c r="K65" t="s">
+        <v>571</v>
+      </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>Darryn Peterson</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -25048,14 +25139,14 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -25063,20 +25154,29 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>143</v>
+        <v>262</v>
       </c>
       <c r="C67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>21000000</v>
+        <v>3600000</v>
       </c>
       <c r="F67">
-        <v>21000000</v>
+        <v>3800000</v>
+      </c>
+      <c r="G67" t="s">
+        <v>571</v>
+      </c>
+      <c r="H67">
+        <v>4100000</v>
+      </c>
+      <c r="I67" t="s">
+        <v>571</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -25084,14 +25184,14 @@
         <v>5</v>
       </c>
       <c r="B68">
-        <v>131</v>
+        <v>274</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -25099,29 +25199,20 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D69">
-        <v>1000000</v>
+        <v>21000000</v>
       </c>
       <c r="F69">
-        <v>1000000</v>
-      </c>
-      <c r="G69" t="s">
-        <v>571</v>
-      </c>
-      <c r="H69">
-        <v>1000000</v>
-      </c>
-      <c r="I69" t="s">
-        <v>571</v>
+        <v>21000000</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>Danny Wolf</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -25129,20 +25220,14 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="C70">
-        <v>7</v>
-      </c>
-      <c r="D70">
-        <v>17000000</v>
-      </c>
-      <c r="F70">
-        <v>17000000</v>
+        <v>5</v>
       </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -25150,23 +25235,29 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C71">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D71">
-        <v>40000000</v>
+        <v>1000000</v>
       </c>
       <c r="F71">
-        <v>40000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G71" t="s">
+        <v>571</v>
       </c>
       <c r="H71">
-        <v>40000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="I71" t="s">
+        <v>571</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Danny Wolf</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -25174,20 +25265,20 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="C72">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D72">
-        <v>3100000</v>
+        <v>17000000</v>
       </c>
       <c r="F72">
-        <v>3100000</v>
+        <v>17000000</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -25195,14 +25286,23 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>227</v>
+        <v>17</v>
       </c>
       <c r="C73">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D73">
+        <v>40000000</v>
+      </c>
+      <c r="F73">
+        <v>40000000</v>
+      </c>
+      <c r="H73">
+        <v>40000000</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Jerami Grant</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -25210,14 +25310,20 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C74">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="D74">
+        <v>3100000</v>
+      </c>
+      <c r="F74">
+        <v>3100000</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -25225,14 +25331,14 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="C75">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Royce O'Neale</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -25240,14 +25346,14 @@
         <v>5</v>
       </c>
       <c r="B76">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="C76">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Ryan Rollins</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -25255,71 +25361,62 @@
         <v>5</v>
       </c>
       <c r="B77">
-        <v>418</v>
+        <v>148</v>
       </c>
       <c r="C77">
-        <v>13</v>
-      </c>
-      <c r="D77">
-        <v>8000000</v>
-      </c>
-      <c r="F77">
-        <v>8500000</v>
-      </c>
-      <c r="H77">
-        <v>9250000</v>
-      </c>
-      <c r="I77" t="s">
-        <v>571</v>
-      </c>
-      <c r="J77">
-        <v>10000000</v>
-      </c>
-      <c r="K77" t="s">
-        <v>571</v>
+        <v>12</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>Caleb Wilson</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B78">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78">
-        <v>6000000</v>
-      </c>
-      <c r="F78">
-        <v>6000000</v>
+        <v>12</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B79">
-        <v>338</v>
+        <v>418</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D79">
-        <v>1000000</v>
+        <v>8000000</v>
+      </c>
+      <c r="F79">
+        <v>8500000</v>
+      </c>
+      <c r="H79">
+        <v>9250000</v>
+      </c>
+      <c r="I79" t="s">
+        <v>571</v>
+      </c>
+      <c r="J79">
+        <v>10000000</v>
+      </c>
+      <c r="K79" t="s">
+        <v>571</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Caleb Wilson</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -25327,14 +25424,20 @@
         <v>6</v>
       </c>
       <c r="B80">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>6000000</v>
+      </c>
+      <c r="F80">
+        <v>6000000</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -25342,14 +25445,17 @@
         <v>6</v>
       </c>
       <c r="B81">
-        <v>122</v>
+        <v>338</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D81">
+        <v>1000000</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -25357,14 +25463,14 @@
         <v>6</v>
       </c>
       <c r="B82">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -25372,14 +25478,14 @@
         <v>6</v>
       </c>
       <c r="B83">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -25387,17 +25493,14 @@
         <v>6</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C84">
-        <v>7</v>
-      </c>
-      <c r="D84">
-        <v>20000000</v>
+        <v>5</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -25405,14 +25508,14 @@
         <v>6</v>
       </c>
       <c r="B85">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C85">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -25420,17 +25523,17 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D86">
-        <v>7000000</v>
+        <v>20000000</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -25438,20 +25541,14 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C87">
-        <v>10</v>
-      </c>
-      <c r="D87">
-        <v>35000000</v>
-      </c>
-      <c r="F87">
-        <v>35000000</v>
+        <v>8</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -25459,20 +25556,17 @@
         <v>6</v>
       </c>
       <c r="B88">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C88">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D88">
-        <v>3100000</v>
-      </c>
-      <c r="F88">
-        <v>3100000</v>
+        <v>7000000</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -25480,17 +25574,20 @@
         <v>6</v>
       </c>
       <c r="B89">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="C89">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D89">
-        <v>1000000</v>
+        <v>35000000</v>
+      </c>
+      <c r="F89">
+        <v>35000000</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -25498,14 +25595,20 @@
         <v>6</v>
       </c>
       <c r="B90">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="C90">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="D90">
+        <v>3100000</v>
+      </c>
+      <c r="F90">
+        <v>3100000</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Damian Lillard</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -25513,20 +25616,17 @@
         <v>6</v>
       </c>
       <c r="B91">
-        <v>93</v>
+        <v>211</v>
       </c>
       <c r="C91">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D91">
-        <v>6000000</v>
-      </c>
-      <c r="F91">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -25534,53 +25634,50 @@
         <v>6</v>
       </c>
       <c r="B92">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="C92">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Tari Eason</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B93">
-        <v>242</v>
+        <v>93</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D93">
-        <v>3800000</v>
+        <v>6000000</v>
       </c>
       <c r="F93">
-        <v>4100000</v>
-      </c>
-      <c r="G93" t="s">
-        <v>571</v>
+        <v>6000000</v>
       </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B94">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -25588,29 +25685,23 @@
         <v>8</v>
       </c>
       <c r="B95">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="F95">
-        <v>1000000</v>
+        <v>4100000</v>
       </c>
       <c r="G95" t="s">
         <v>571</v>
       </c>
-      <c r="H95">
-        <v>1000000</v>
-      </c>
-      <c r="I95" t="s">
-        <v>571</v>
-      </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -25618,17 +25709,14 @@
         <v>8</v>
       </c>
       <c r="B96">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="C96">
-        <v>4</v>
-      </c>
-      <c r="D96">
-        <v>2000000</v>
+        <v>2</v>
       </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -25636,23 +25724,29 @@
         <v>8</v>
       </c>
       <c r="B97">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D97">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="F97">
-        <v>6000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G97" t="s">
+        <v>571</v>
       </c>
       <c r="H97">
-        <v>6000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="I97" t="s">
+        <v>571</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -25660,23 +25754,17 @@
         <v>8</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="C98">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D98">
-        <v>7000000</v>
-      </c>
-      <c r="F98">
-        <v>7500000</v>
-      </c>
-      <c r="G98" t="s">
-        <v>571</v>
+        <v>2000000</v>
       </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -25684,20 +25772,23 @@
         <v>8</v>
       </c>
       <c r="B99">
+        <v>116</v>
+      </c>
+      <c r="C99">
         <v>5</v>
       </c>
-      <c r="C99">
-        <v>7</v>
-      </c>
       <c r="D99">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="F99">
-        <v>4000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="H99">
+        <v>6000000</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -25705,23 +25796,23 @@
         <v>8</v>
       </c>
       <c r="B100">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D100">
-        <v>16000000</v>
+        <v>7000000</v>
       </c>
       <c r="F100">
-        <v>16000000</v>
-      </c>
-      <c r="H100">
-        <v>16000000</v>
+        <v>7500000</v>
+      </c>
+      <c r="G100" t="s">
+        <v>571</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -25729,20 +25820,20 @@
         <v>8</v>
       </c>
       <c r="B101">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="C101">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D101">
-        <v>9000000</v>
+        <v>4000000</v>
       </c>
       <c r="F101">
-        <v>9000000</v>
+        <v>4000000</v>
       </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -25750,17 +25841,23 @@
         <v>8</v>
       </c>
       <c r="B102">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="C102">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D102">
         <v>16000000</v>
       </c>
+      <c r="F102">
+        <v>16000000</v>
+      </c>
+      <c r="H102">
+        <v>16000000</v>
+      </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -25768,23 +25865,20 @@
         <v>8</v>
       </c>
       <c r="B103">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="C103">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D103">
-        <v>19000000</v>
+        <v>9000000</v>
       </c>
       <c r="F103">
-        <v>19000000</v>
-      </c>
-      <c r="H103">
-        <v>19000000</v>
+        <v>9000000</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -25792,14 +25886,17 @@
         <v>8</v>
       </c>
       <c r="B104">
-        <v>225</v>
+        <v>84</v>
       </c>
       <c r="C104">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D104">
+        <v>16000000</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -25807,14 +25904,23 @@
         <v>8</v>
       </c>
       <c r="B105">
-        <v>59</v>
+        <v>203</v>
       </c>
       <c r="C105">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="D105">
+        <v>19000000</v>
+      </c>
+      <c r="F105">
+        <v>19000000</v>
+      </c>
+      <c r="H105">
+        <v>19000000</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -25822,53 +25928,44 @@
         <v>8</v>
       </c>
       <c r="B106">
-        <v>336</v>
+        <v>225</v>
       </c>
       <c r="C106">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B107">
-        <v>384</v>
+        <v>59</v>
       </c>
       <c r="C107">
-        <v>1</v>
-      </c>
-      <c r="D107">
-        <v>3100000</v>
-      </c>
-      <c r="F107">
-        <v>3100000</v>
-      </c>
-      <c r="H107">
-        <v>3100000</v>
+        <v>13</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B108">
-        <v>240</v>
+        <v>336</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -25876,17 +25973,23 @@
         <v>9</v>
       </c>
       <c r="B109">
-        <v>186</v>
+        <v>384</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109">
-        <v>4500000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F109">
+        <v>3100000</v>
+      </c>
+      <c r="H109">
+        <v>3100000</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -25894,14 +25997,14 @@
         <v>9</v>
       </c>
       <c r="B110">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -25909,14 +26012,17 @@
         <v>9</v>
       </c>
       <c r="B111">
-        <v>416</v>
+        <v>186</v>
       </c>
       <c r="C111">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="D111">
+        <v>4500000</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -25924,23 +26030,14 @@
         <v>9</v>
       </c>
       <c r="B112">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="C112">
-        <v>6</v>
-      </c>
-      <c r="D112">
-        <v>3100000</v>
-      </c>
-      <c r="F112">
-        <v>3100000</v>
-      </c>
-      <c r="H112">
-        <v>3100000</v>
+        <v>4</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -25948,23 +26045,14 @@
         <v>9</v>
       </c>
       <c r="B113">
-        <v>15</v>
+        <v>416</v>
       </c>
       <c r="C113">
-        <v>7</v>
-      </c>
-      <c r="D113">
-        <v>32000000</v>
-      </c>
-      <c r="F113">
-        <v>32000000</v>
-      </c>
-      <c r="H113">
-        <v>32000000</v>
+        <v>5</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -25972,23 +26060,23 @@
         <v>9</v>
       </c>
       <c r="B114">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D114">
-        <v>12500000</v>
+        <v>3100000</v>
       </c>
       <c r="F114">
-        <v>12500000</v>
+        <v>3100000</v>
       </c>
       <c r="H114">
-        <v>12500000</v>
+        <v>3100000</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -25996,17 +26084,23 @@
         <v>9</v>
       </c>
       <c r="B115">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C115">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D115">
-        <v>11500000</v>
+        <v>32000000</v>
+      </c>
+      <c r="F115">
+        <v>32000000</v>
+      </c>
+      <c r="H115">
+        <v>32000000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -26014,23 +26108,23 @@
         <v>9</v>
       </c>
       <c r="B116">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D116">
-        <v>3100000</v>
+        <v>12500000</v>
       </c>
       <c r="F116">
-        <v>3100000</v>
+        <v>12500000</v>
       </c>
       <c r="H116">
-        <v>3100000</v>
+        <v>12500000</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -26038,17 +26132,17 @@
         <v>9</v>
       </c>
       <c r="B117">
-        <v>217</v>
+        <v>89</v>
       </c>
       <c r="C117">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D117">
-        <v>25000000</v>
+        <v>11500000</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -26056,53 +26150,65 @@
         <v>9</v>
       </c>
       <c r="B118">
-        <v>331</v>
+        <v>167</v>
       </c>
       <c r="C118">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D118">
-        <v>12000000</v>
+        <v>3100000</v>
       </c>
       <c r="F118">
-        <v>12000000</v>
+        <v>3100000</v>
       </c>
       <c r="H118">
-        <v>12000000</v>
+        <v>3100000</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B119">
-        <v>9</v>
+        <v>217</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D119">
+        <v>25000000</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Walker Kessler</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B120">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="D120">
+        <v>12000000</v>
+      </c>
+      <c r="F120">
+        <v>12000000</v>
+      </c>
+      <c r="H120">
+        <v>12000000</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -26110,14 +26216,14 @@
         <v>10</v>
       </c>
       <c r="B121">
-        <v>249</v>
+        <v>9</v>
       </c>
       <c r="C121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -26125,17 +26231,14 @@
         <v>10</v>
       </c>
       <c r="B122">
-        <v>169</v>
+        <v>373</v>
       </c>
       <c r="C122">
-        <v>4</v>
-      </c>
-      <c r="D122">
-        <v>4100000</v>
+        <v>2</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -26143,20 +26246,14 @@
         <v>10</v>
       </c>
       <c r="B123">
-        <v>34</v>
+        <v>249</v>
       </c>
       <c r="C123">
-        <v>5</v>
-      </c>
-      <c r="D123">
-        <v>6000000</v>
-      </c>
-      <c r="F123">
-        <v>6000000</v>
+        <v>3</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -26164,17 +26261,17 @@
         <v>10</v>
       </c>
       <c r="B124">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C124">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D124">
-        <v>1000000</v>
+        <v>4100000</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -26182,14 +26279,20 @@
         <v>10</v>
       </c>
       <c r="B125">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="D125">
+        <v>6000000</v>
+      </c>
+      <c r="F125">
+        <v>6000000</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -26197,23 +26300,17 @@
         <v>10</v>
       </c>
       <c r="B126">
-        <v>44</v>
+        <v>168</v>
       </c>
       <c r="C126">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D126">
-        <v>9250000</v>
-      </c>
-      <c r="F126">
-        <v>10000000</v>
-      </c>
-      <c r="G126" t="s">
-        <v>571</v>
+        <v>1000000</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -26221,23 +26318,14 @@
         <v>10</v>
       </c>
       <c r="B127">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C127">
-        <v>9</v>
-      </c>
-      <c r="D127">
-        <v>15000000</v>
-      </c>
-      <c r="F127">
-        <v>15000000</v>
-      </c>
-      <c r="H127">
-        <v>15000000</v>
+        <v>7</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -26245,20 +26333,23 @@
         <v>10</v>
       </c>
       <c r="B128">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="C128">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D128">
-        <v>11000000</v>
+        <v>9250000</v>
       </c>
       <c r="F128">
-        <v>11000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G128" t="s">
+        <v>571</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -26266,23 +26357,23 @@
         <v>10</v>
       </c>
       <c r="B129">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="C129">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D129">
-        <v>16000000</v>
+        <v>15000000</v>
       </c>
       <c r="F129">
-        <v>16000000</v>
+        <v>15000000</v>
       </c>
       <c r="H129">
-        <v>16000000</v>
+        <v>15000000</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -26290,47 +26381,62 @@
         <v>10</v>
       </c>
       <c r="B130">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="C130">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D130">
-        <v>24000000</v>
+        <v>11000000</v>
+      </c>
+      <c r="F130">
+        <v>11000000</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131">
+        <v>10</v>
+      </c>
+      <c r="B131">
+        <v>160</v>
+      </c>
+      <c r="C131">
         <v>11</v>
       </c>
-      <c r="B131">
-        <v>327</v>
-      </c>
-      <c r="C131">
-        <v>1</v>
+      <c r="D131">
+        <v>16000000</v>
+      </c>
+      <c r="F131">
+        <v>16000000</v>
+      </c>
+      <c r="H131">
+        <v>16000000</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B132">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="D132">
+        <v>24000000</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -26338,17 +26444,14 @@
         <v>11</v>
       </c>
       <c r="B133">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="C133">
-        <v>3</v>
-      </c>
-      <c r="D133">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -26356,14 +26459,14 @@
         <v>11</v>
       </c>
       <c r="B134">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="C134">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -26371,17 +26474,17 @@
         <v>11</v>
       </c>
       <c r="B135">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="C135">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D135">
         <v>1000000</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -26389,14 +26492,14 @@
         <v>11</v>
       </c>
       <c r="B136">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C136">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -26404,17 +26507,17 @@
         <v>11</v>
       </c>
       <c r="B137">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D137">
-        <v>26000000</v>
+        <v>1000000</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -26422,17 +26525,14 @@
         <v>11</v>
       </c>
       <c r="B138">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="C138">
-        <v>8</v>
-      </c>
-      <c r="D138">
-        <v>15000000</v>
+        <v>6</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -26440,17 +26540,17 @@
         <v>11</v>
       </c>
       <c r="B139">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C139">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D139">
-        <v>7500000</v>
+        <v>26000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -26458,23 +26558,17 @@
         <v>11</v>
       </c>
       <c r="B140">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C140">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D140">
-        <v>30000000</v>
-      </c>
-      <c r="F140">
-        <v>30000000</v>
-      </c>
-      <c r="H140">
-        <v>30000000</v>
+        <v>15000000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -26482,17 +26576,17 @@
         <v>11</v>
       </c>
       <c r="B141">
-        <v>248</v>
+        <v>35</v>
       </c>
       <c r="C141">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D141">
-        <v>1000000</v>
+        <v>7500000</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -26500,14 +26594,23 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="C142">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D142">
+        <v>30000000</v>
+      </c>
+      <c r="F142">
+        <v>30000000</v>
+      </c>
+      <c r="H142">
+        <v>30000000</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -26515,14 +26618,17 @@
         <v>11</v>
       </c>
       <c r="B143">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="C143">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="D143">
+        <v>1000000</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -26530,56 +26636,44 @@
         <v>11</v>
       </c>
       <c r="B144">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="C144">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B145">
-        <v>403</v>
+        <v>266</v>
       </c>
       <c r="C145">
-        <v>1</v>
-      </c>
-      <c r="D145">
-        <v>5000000</v>
-      </c>
-      <c r="F145">
-        <v>5000000</v>
+        <v>13</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B146">
-        <v>345</v>
+        <v>195</v>
       </c>
       <c r="C146">
-        <v>2</v>
-      </c>
-      <c r="D146">
-        <v>3500000</v>
-      </c>
-      <c r="F146">
-        <v>3500000</v>
+        <v>14</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -26587,17 +26681,20 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>120</v>
+        <v>403</v>
       </c>
       <c r="C147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D147">
-        <v>1000000</v>
+        <v>5000000</v>
+      </c>
+      <c r="F147">
+        <v>5000000</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -26605,14 +26702,20 @@
         <v>12</v>
       </c>
       <c r="B148">
-        <v>22</v>
+        <v>345</v>
       </c>
       <c r="C148">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D148">
+        <v>3500000</v>
+      </c>
+      <c r="F148">
+        <v>3500000</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -26620,17 +26723,17 @@
         <v>12</v>
       </c>
       <c r="B149">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="C149">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D149">
-        <v>11000000</v>
+        <v>1000000</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -26638,20 +26741,14 @@
         <v>12</v>
       </c>
       <c r="B150">
-        <v>194</v>
+        <v>22</v>
       </c>
       <c r="C150">
-        <v>6</v>
-      </c>
-      <c r="D150">
-        <v>20000000</v>
-      </c>
-      <c r="F150">
-        <v>20000000</v>
+        <v>4</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -26659,23 +26756,17 @@
         <v>12</v>
       </c>
       <c r="B151">
-        <v>226</v>
+        <v>54</v>
       </c>
       <c r="C151">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D151">
-        <v>18000000</v>
-      </c>
-      <c r="F151">
-        <v>18000000</v>
-      </c>
-      <c r="H151">
-        <v>18000000</v>
+        <v>11000000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -26683,17 +26774,20 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="C152">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D152">
-        <v>2500000</v>
+        <v>20000000</v>
+      </c>
+      <c r="F152">
+        <v>20000000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -26701,62 +26795,71 @@
         <v>12</v>
       </c>
       <c r="B153">
-        <v>417</v>
+        <v>226</v>
       </c>
       <c r="C153">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D153">
-        <v>9000000</v>
+        <v>18000000</v>
       </c>
       <c r="F153">
-        <v>9500000</v>
+        <v>18000000</v>
       </c>
       <c r="H153">
-        <v>10500000</v>
-      </c>
-      <c r="I153" t="s">
-        <v>571</v>
-      </c>
-      <c r="J153">
-        <v>11500000</v>
+        <v>18000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>A.J. Dybantsa</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B154">
-        <v>307</v>
+        <v>115</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D154">
-        <v>1000000</v>
+        <v>2500000</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B155">
-        <v>363</v>
+        <v>417</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="D155">
+        <v>9000000</v>
+      </c>
+      <c r="F155">
+        <v>9500000</v>
+      </c>
+      <c r="H155">
+        <v>10500000</v>
+      </c>
+      <c r="I155" t="s">
+        <v>571</v>
+      </c>
+      <c r="J155">
+        <v>11500000</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>A.J. Dybantsa</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -26764,17 +26867,17 @@
         <v>13</v>
       </c>
       <c r="B156">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="C156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D156">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -26782,17 +26885,14 @@
         <v>13</v>
       </c>
       <c r="B157">
-        <v>171</v>
+        <v>363</v>
       </c>
       <c r="C157">
-        <v>4</v>
-      </c>
-      <c r="D157">
-        <v>2000000</v>
+        <v>2</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -26800,14 +26900,17 @@
         <v>13</v>
       </c>
       <c r="B158">
-        <v>10</v>
+        <v>296</v>
       </c>
       <c r="C158">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="D158">
+        <v>3000000</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -26815,14 +26918,17 @@
         <v>13</v>
       </c>
       <c r="B159">
-        <v>46</v>
+        <v>171</v>
       </c>
       <c r="C159">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D159">
+        <v>2000000</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -26830,17 +26936,14 @@
         <v>13</v>
       </c>
       <c r="B160">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C160">
-        <v>7</v>
-      </c>
-      <c r="D160">
-        <v>11500000</v>
+        <v>5</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -26848,23 +26951,14 @@
         <v>13</v>
       </c>
       <c r="B161">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C161">
-        <v>8</v>
-      </c>
-      <c r="D161">
-        <v>16000000</v>
-      </c>
-      <c r="F161">
-        <v>16000000</v>
-      </c>
-      <c r="H161">
-        <v>16000000</v>
+        <v>6</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -26872,23 +26966,17 @@
         <v>13</v>
       </c>
       <c r="B162">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C162">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D162">
-        <v>12000000</v>
-      </c>
-      <c r="F162">
-        <v>12000000</v>
-      </c>
-      <c r="H162">
-        <v>12000000</v>
+        <v>11500000</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -26896,17 +26984,23 @@
         <v>13</v>
       </c>
       <c r="B163">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="C163">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D163">
-        <v>19000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="F163">
+        <v>16000000</v>
+      </c>
+      <c r="H163">
+        <v>16000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -26914,53 +27008,65 @@
         <v>13</v>
       </c>
       <c r="B164">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="C164">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D164">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
       <c r="F164">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
       <c r="H164">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B165">
-        <v>317</v>
+        <v>66</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D165">
+        <v>19000000</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B166">
-        <v>299</v>
+        <v>150</v>
       </c>
       <c r="C166">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="D166">
+        <v>6000000</v>
+      </c>
+      <c r="F166">
+        <v>6000000</v>
+      </c>
+      <c r="H166">
+        <v>6000000</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -26968,14 +27074,14 @@
         <v>14</v>
       </c>
       <c r="B167">
-        <v>129</v>
+        <v>317</v>
       </c>
       <c r="C167">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -26983,14 +27089,14 @@
         <v>14</v>
       </c>
       <c r="B168">
-        <v>90</v>
+        <v>299</v>
       </c>
       <c r="C168">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -26998,17 +27104,14 @@
         <v>14</v>
       </c>
       <c r="B169">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="C169">
-        <v>5</v>
-      </c>
-      <c r="D169">
-        <v>1000000</v>
+        <v>3</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -27016,17 +27119,14 @@
         <v>14</v>
       </c>
       <c r="B170">
-        <v>238</v>
+        <v>90</v>
       </c>
       <c r="C170">
-        <v>6</v>
-      </c>
-      <c r="D170">
-        <v>3000000</v>
+        <v>4</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -27034,23 +27134,17 @@
         <v>14</v>
       </c>
       <c r="B171">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C171">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D171">
-        <v>20500000</v>
-      </c>
-      <c r="F171">
-        <v>20500000</v>
-      </c>
-      <c r="H171">
-        <v>20500000</v>
+        <v>1000000</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -27058,17 +27152,17 @@
         <v>14</v>
       </c>
       <c r="B172">
-        <v>73</v>
+        <v>238</v>
       </c>
       <c r="C172">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D172">
-        <v>19500000</v>
+        <v>3000000</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -27076,29 +27170,23 @@
         <v>14</v>
       </c>
       <c r="B173">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="C173">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D173">
-        <v>9500000</v>
+        <v>20500000</v>
       </c>
       <c r="F173">
-        <v>10500000</v>
-      </c>
-      <c r="G173" t="s">
-        <v>571</v>
+        <v>20500000</v>
       </c>
       <c r="H173">
-        <v>11500000</v>
-      </c>
-      <c r="I173" t="s">
-        <v>571</v>
+        <v>20500000</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -27106,14 +27194,17 @@
         <v>14</v>
       </c>
       <c r="B174">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="C174">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D174">
+        <v>19500000</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -27121,14 +27212,29 @@
         <v>14</v>
       </c>
       <c r="B175">
-        <v>220</v>
+        <v>61</v>
       </c>
       <c r="C175">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="D175">
+        <v>9500000</v>
+      </c>
+      <c r="F175">
+        <v>10500000</v>
+      </c>
+      <c r="G175" t="s">
+        <v>571</v>
+      </c>
+      <c r="H175">
+        <v>11500000</v>
+      </c>
+      <c r="I175" t="s">
+        <v>571</v>
       </c>
       <c r="L175" t="str">
         <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -27136,23 +27242,14 @@
         <v>14</v>
       </c>
       <c r="B176">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="C176">
-        <v>12</v>
-      </c>
-      <c r="D176">
-        <v>20000000</v>
-      </c>
-      <c r="F176">
-        <v>20000000</v>
-      </c>
-      <c r="H176">
-        <v>20000000</v>
+        <v>10</v>
       </c>
       <c r="L176" t="str">
         <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -27160,19 +27257,58 @@
         <v>14</v>
       </c>
       <c r="B177">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="C177">
-        <v>13</v>
-      </c>
-      <c r="D177">
-        <v>3200000</v>
-      </c>
-      <c r="F177">
-        <v>3500000</v>
+        <v>11</v>
       </c>
       <c r="L177" t="str">
         <f>VLOOKUP(B177,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>14</v>
+      </c>
+      <c r="B178">
+        <v>145</v>
+      </c>
+      <c r="C178">
+        <v>12</v>
+      </c>
+      <c r="D178">
+        <v>20000000</v>
+      </c>
+      <c r="F178">
+        <v>20000000</v>
+      </c>
+      <c r="H178">
+        <v>20000000</v>
+      </c>
+      <c r="L178" t="str">
+        <f>VLOOKUP(B178,players!A:B,2)</f>
+        <v>LaMelo Ball</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>14</v>
+      </c>
+      <c r="B179">
+        <v>273</v>
+      </c>
+      <c r="C179">
+        <v>13</v>
+      </c>
+      <c r="D179">
+        <v>3200000</v>
+      </c>
+      <c r="F179">
+        <v>3500000</v>
+      </c>
+      <c r="L179" t="str">
+        <f>VLOOKUP(B179,players!A:B,2)</f>
         <v>Cason Wallace</v>
       </c>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sefazpegovbr-my.sharepoint.com/personal/filipe_lima_sefaz_pe_gov_br/Documents/Documents/GitHub/Fantasy-unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21447A72-2EBF-4D52-83D7-8697F6774188}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A19F7E1A-F7D1-4927-9AA9-19B9AA091A21}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="705">
   <si>
     <t>player</t>
   </si>
@@ -2158,6 +2158,9 @@
   </si>
   <si>
     <t>Darius Acuff</t>
+  </si>
+  <si>
+    <t>Kingston Flemings</t>
   </si>
 </sst>
 </file>
@@ -2563,7 +2566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M422"/>
+  <dimension ref="A1:M423"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -16129,6 +16132,38 @@
         <v>0</v>
       </c>
       <c r="K422" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>422</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E423" s="1">
+        <v>0</v>
+      </c>
+      <c r="F423" s="1">
+        <v>0</v>
+      </c>
+      <c r="G423" s="1">
+        <v>0</v>
+      </c>
+      <c r="H423" s="1">
+        <v>0</v>
+      </c>
+      <c r="I423" s="1">
+        <v>0</v>
+      </c>
+      <c r="J423" s="1">
+        <v>0</v>
+      </c>
+      <c r="K423" s="1">
         <v>0</v>
       </c>
     </row>
@@ -23782,7 +23817,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:L179"/>
+  <dimension ref="A1:L180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -25106,32 +25141,32 @@
         <v>4</v>
       </c>
       <c r="B65">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C65">
         <v>13</v>
       </c>
       <c r="D65">
-        <v>6000000</v>
+        <v>4500000</v>
       </c>
       <c r="F65">
-        <v>6500000</v>
+        <v>5000000</v>
       </c>
       <c r="H65">
-        <v>7000000</v>
+        <v>5500000</v>
       </c>
       <c r="I65" t="s">
         <v>571</v>
       </c>
       <c r="J65">
-        <v>7500000</v>
+        <v>6000000</v>
       </c>
       <c r="K65" t="s">
         <v>571</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>Darryn Peterson</v>
+        <v>Kingston Flemings</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -25682,26 +25717,35 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B95">
-        <v>242</v>
+        <v>420</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D95">
-        <v>3800000</v>
+        <v>6000000</v>
       </c>
       <c r="F95">
-        <v>4100000</v>
-      </c>
-      <c r="G95" t="s">
+        <v>6500000</v>
+      </c>
+      <c r="H95">
+        <v>7000000</v>
+      </c>
+      <c r="I95" t="s">
+        <v>571</v>
+      </c>
+      <c r="J95">
+        <v>7500000</v>
+      </c>
+      <c r="K95" t="s">
         <v>571</v>
       </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Darryn Peterson</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -25709,14 +25753,23 @@
         <v>8</v>
       </c>
       <c r="B96">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>3800000</v>
+      </c>
+      <c r="F96">
+        <v>4100000</v>
+      </c>
+      <c r="G96" t="s">
+        <v>571</v>
       </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -25724,29 +25777,14 @@
         <v>8</v>
       </c>
       <c r="B97">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="C97">
-        <v>3</v>
-      </c>
-      <c r="D97">
-        <v>1000000</v>
-      </c>
-      <c r="F97">
-        <v>1000000</v>
-      </c>
-      <c r="G97" t="s">
-        <v>571</v>
-      </c>
-      <c r="H97">
-        <v>1000000</v>
-      </c>
-      <c r="I97" t="s">
-        <v>571</v>
+        <v>2</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -25754,17 +25792,29 @@
         <v>8</v>
       </c>
       <c r="B98">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D98">
-        <v>2000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F98">
+        <v>1000000</v>
+      </c>
+      <c r="G98" t="s">
+        <v>571</v>
+      </c>
+      <c r="H98">
+        <v>1000000</v>
+      </c>
+      <c r="I98" t="s">
+        <v>571</v>
       </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -25772,23 +25822,17 @@
         <v>8</v>
       </c>
       <c r="B99">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="C99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D99">
-        <v>6000000</v>
-      </c>
-      <c r="F99">
-        <v>6000000</v>
-      </c>
-      <c r="H99">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -25796,23 +25840,23 @@
         <v>8</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="C100">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D100">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
       <c r="F100">
-        <v>7500000</v>
-      </c>
-      <c r="G100" t="s">
-        <v>571</v>
+        <v>6000000</v>
+      </c>
+      <c r="H100">
+        <v>6000000</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -25820,20 +25864,23 @@
         <v>8</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D101">
-        <v>4000000</v>
+        <v>7000000</v>
       </c>
       <c r="F101">
-        <v>4000000</v>
+        <v>7500000</v>
+      </c>
+      <c r="G101" t="s">
+        <v>571</v>
       </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -25841,23 +25888,20 @@
         <v>8</v>
       </c>
       <c r="B102">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C102">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D102">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="F102">
-        <v>16000000</v>
-      </c>
-      <c r="H102">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -25865,20 +25909,23 @@
         <v>8</v>
       </c>
       <c r="B103">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="C103">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D103">
-        <v>9000000</v>
+        <v>16000000</v>
       </c>
       <c r="F103">
-        <v>9000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="H103">
+        <v>16000000</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -25886,17 +25933,20 @@
         <v>8</v>
       </c>
       <c r="B104">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C104">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D104">
-        <v>16000000</v>
+        <v>9000000</v>
+      </c>
+      <c r="F104">
+        <v>9000000</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -25904,23 +25954,17 @@
         <v>8</v>
       </c>
       <c r="B105">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="C105">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D105">
-        <v>19000000</v>
-      </c>
-      <c r="F105">
-        <v>19000000</v>
-      </c>
-      <c r="H105">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -25928,14 +25972,23 @@
         <v>8</v>
       </c>
       <c r="B106">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C106">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D106">
+        <v>19000000</v>
+      </c>
+      <c r="F106">
+        <v>19000000</v>
+      </c>
+      <c r="H106">
+        <v>19000000</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -25943,14 +25996,14 @@
         <v>8</v>
       </c>
       <c r="B107">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="C107">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -25958,38 +26011,29 @@
         <v>8</v>
       </c>
       <c r="B108">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="C108">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B109">
-        <v>384</v>
+        <v>336</v>
       </c>
       <c r="C109">
-        <v>1</v>
-      </c>
-      <c r="D109">
-        <v>3100000</v>
-      </c>
-      <c r="F109">
-        <v>3100000</v>
-      </c>
-      <c r="H109">
-        <v>3100000</v>
+        <v>14</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -25997,14 +26041,23 @@
         <v>9</v>
       </c>
       <c r="B110">
-        <v>240</v>
+        <v>384</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D110">
+        <v>3100000</v>
+      </c>
+      <c r="F110">
+        <v>3100000</v>
+      </c>
+      <c r="H110">
+        <v>3100000</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -26012,17 +26065,14 @@
         <v>9</v>
       </c>
       <c r="B111">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="C111">
-        <v>3</v>
-      </c>
-      <c r="D111">
-        <v>4500000</v>
+        <v>2</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -26030,14 +26080,17 @@
         <v>9</v>
       </c>
       <c r="B112">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="C112">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D112">
+        <v>4500000</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -26045,14 +26098,14 @@
         <v>9</v>
       </c>
       <c r="B113">
-        <v>416</v>
+        <v>251</v>
       </c>
       <c r="C113">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -26060,23 +26113,14 @@
         <v>9</v>
       </c>
       <c r="B114">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="C114">
-        <v>6</v>
-      </c>
-      <c r="D114">
-        <v>3100000</v>
-      </c>
-      <c r="F114">
-        <v>3100000</v>
-      </c>
-      <c r="H114">
-        <v>3100000</v>
+        <v>5</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -26084,23 +26128,23 @@
         <v>9</v>
       </c>
       <c r="B115">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D115">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="F115">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="H115">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -26108,23 +26152,23 @@
         <v>9</v>
       </c>
       <c r="B116">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C116">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D116">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="F116">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="H116">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -26132,17 +26176,23 @@
         <v>9</v>
       </c>
       <c r="B117">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="C117">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D117">
-        <v>11500000</v>
+        <v>12500000</v>
+      </c>
+      <c r="F117">
+        <v>12500000</v>
+      </c>
+      <c r="H117">
+        <v>12500000</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -26150,23 +26200,17 @@
         <v>9</v>
       </c>
       <c r="B118">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="C118">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D118">
-        <v>3100000</v>
-      </c>
-      <c r="F118">
-        <v>3100000</v>
-      </c>
-      <c r="H118">
-        <v>3100000</v>
+        <v>11500000</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -26174,17 +26218,23 @@
         <v>9</v>
       </c>
       <c r="B119">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="C119">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D119">
-        <v>25000000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F119">
+        <v>3100000</v>
+      </c>
+      <c r="H119">
+        <v>3100000</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -26192,38 +26242,41 @@
         <v>9</v>
       </c>
       <c r="B120">
-        <v>331</v>
+        <v>217</v>
       </c>
       <c r="C120">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D120">
-        <v>12000000</v>
-      </c>
-      <c r="F120">
-        <v>12000000</v>
-      </c>
-      <c r="H120">
-        <v>12000000</v>
+        <v>25000000</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B121">
-        <v>9</v>
+        <v>331</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D121">
+        <v>12000000</v>
+      </c>
+      <c r="F121">
+        <v>12000000</v>
+      </c>
+      <c r="H121">
+        <v>12000000</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Walker Kessler</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -26231,14 +26284,14 @@
         <v>10</v>
       </c>
       <c r="B122">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -26246,14 +26299,14 @@
         <v>10</v>
       </c>
       <c r="B123">
-        <v>249</v>
+        <v>373</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -26261,17 +26314,14 @@
         <v>10</v>
       </c>
       <c r="B124">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="C124">
-        <v>4</v>
-      </c>
-      <c r="D124">
-        <v>4100000</v>
+        <v>3</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -26279,20 +26329,17 @@
         <v>10</v>
       </c>
       <c r="B125">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D125">
-        <v>6000000</v>
-      </c>
-      <c r="F125">
-        <v>6000000</v>
+        <v>4100000</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -26300,17 +26347,20 @@
         <v>10</v>
       </c>
       <c r="B126">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="C126">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D126">
-        <v>1000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="F126">
+        <v>6000000</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -26318,14 +26368,17 @@
         <v>10</v>
       </c>
       <c r="B127">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D127">
+        <v>1000000</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -26333,23 +26386,14 @@
         <v>10</v>
       </c>
       <c r="B128">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C128">
-        <v>8</v>
-      </c>
-      <c r="D128">
-        <v>9250000</v>
-      </c>
-      <c r="F128">
-        <v>10000000</v>
-      </c>
-      <c r="G128" t="s">
-        <v>571</v>
+        <v>7</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -26357,23 +26401,23 @@
         <v>10</v>
       </c>
       <c r="B129">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C129">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D129">
-        <v>15000000</v>
+        <v>9250000</v>
       </c>
       <c r="F129">
-        <v>15000000</v>
-      </c>
-      <c r="H129">
-        <v>15000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G129" t="s">
+        <v>571</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -26381,20 +26425,23 @@
         <v>10</v>
       </c>
       <c r="B130">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="C130">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D130">
-        <v>11000000</v>
+        <v>15000000</v>
       </c>
       <c r="F130">
-        <v>11000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="H130">
+        <v>15000000</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -26402,23 +26449,20 @@
         <v>10</v>
       </c>
       <c r="B131">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C131">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D131">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="F131">
-        <v>16000000</v>
-      </c>
-      <c r="H131">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -26426,32 +26470,41 @@
         <v>10</v>
       </c>
       <c r="B132">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="C132">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D132">
-        <v>24000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="F132">
+        <v>16000000</v>
+      </c>
+      <c r="H132">
+        <v>16000000</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B133">
-        <v>327</v>
+        <v>246</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D133">
+        <v>24000000</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -26459,14 +26512,14 @@
         <v>11</v>
       </c>
       <c r="B134">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -26474,17 +26527,14 @@
         <v>11</v>
       </c>
       <c r="B135">
-        <v>111</v>
+        <v>213</v>
       </c>
       <c r="C135">
-        <v>3</v>
-      </c>
-      <c r="D135">
-        <v>1000000</v>
+        <v>2</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -26492,14 +26542,17 @@
         <v>11</v>
       </c>
       <c r="B136">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C136">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D136">
+        <v>1000000</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -26507,17 +26560,14 @@
         <v>11</v>
       </c>
       <c r="B137">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C137">
-        <v>5</v>
-      </c>
-      <c r="D137">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -26525,14 +26575,17 @@
         <v>11</v>
       </c>
       <c r="B138">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C138">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D138">
+        <v>1000000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -26540,17 +26593,14 @@
         <v>11</v>
       </c>
       <c r="B139">
+        <v>63</v>
+      </c>
+      <c r="C139">
         <v>6</v>
-      </c>
-      <c r="C139">
-        <v>7</v>
-      </c>
-      <c r="D139">
-        <v>26000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -26558,17 +26608,17 @@
         <v>11</v>
       </c>
       <c r="B140">
-        <v>177</v>
+        <v>6</v>
       </c>
       <c r="C140">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D140">
-        <v>15000000</v>
+        <v>26000000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -26576,17 +26626,17 @@
         <v>11</v>
       </c>
       <c r="B141">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="C141">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D141">
-        <v>7500000</v>
+        <v>15000000</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -26594,23 +26644,17 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="C142">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D142">
-        <v>30000000</v>
-      </c>
-      <c r="F142">
-        <v>30000000</v>
-      </c>
-      <c r="H142">
-        <v>30000000</v>
+        <v>7500000</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -26618,17 +26662,23 @@
         <v>11</v>
       </c>
       <c r="B143">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="C143">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D143">
-        <v>1000000</v>
+        <v>30000000</v>
+      </c>
+      <c r="F143">
+        <v>30000000</v>
+      </c>
+      <c r="H143">
+        <v>30000000</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -26636,14 +26686,17 @@
         <v>11</v>
       </c>
       <c r="B144">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="C144">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D144">
+        <v>1000000</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -26651,14 +26704,14 @@
         <v>11</v>
       </c>
       <c r="B145">
-        <v>266</v>
+        <v>109</v>
       </c>
       <c r="C145">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -26666,35 +26719,29 @@
         <v>11</v>
       </c>
       <c r="B146">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="C146">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B147">
-        <v>403</v>
+        <v>195</v>
       </c>
       <c r="C147">
-        <v>1</v>
-      </c>
-      <c r="D147">
-        <v>5000000</v>
-      </c>
-      <c r="F147">
-        <v>5000000</v>
+        <v>14</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -26702,20 +26749,20 @@
         <v>12</v>
       </c>
       <c r="B148">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="F148">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -26723,17 +26770,20 @@
         <v>12</v>
       </c>
       <c r="B149">
-        <v>120</v>
+        <v>345</v>
       </c>
       <c r="C149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D149">
-        <v>1000000</v>
+        <v>3500000</v>
+      </c>
+      <c r="F149">
+        <v>3500000</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -26741,14 +26791,17 @@
         <v>12</v>
       </c>
       <c r="B150">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="C150">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D150">
+        <v>1000000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -26756,17 +26809,14 @@
         <v>12</v>
       </c>
       <c r="B151">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C151">
-        <v>5</v>
-      </c>
-      <c r="D151">
-        <v>11000000</v>
+        <v>4</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -26774,20 +26824,17 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="C152">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D152">
-        <v>20000000</v>
-      </c>
-      <c r="F152">
-        <v>20000000</v>
+        <v>11000000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -26795,23 +26842,20 @@
         <v>12</v>
       </c>
       <c r="B153">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="C153">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D153">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="F153">
-        <v>18000000</v>
-      </c>
-      <c r="H153">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -26819,17 +26863,23 @@
         <v>12</v>
       </c>
       <c r="B154">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="C154">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D154">
-        <v>2500000</v>
+        <v>18000000</v>
+      </c>
+      <c r="F154">
+        <v>18000000</v>
+      </c>
+      <c r="H154">
+        <v>18000000</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -26837,47 +26887,47 @@
         <v>12</v>
       </c>
       <c r="B155">
-        <v>417</v>
+        <v>115</v>
       </c>
       <c r="C155">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D155">
-        <v>9000000</v>
-      </c>
-      <c r="F155">
-        <v>9500000</v>
-      </c>
-      <c r="H155">
-        <v>10500000</v>
-      </c>
-      <c r="I155" t="s">
-        <v>571</v>
-      </c>
-      <c r="J155">
-        <v>11500000</v>
+        <v>2500000</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>A.J. Dybantsa</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B156">
-        <v>307</v>
+        <v>417</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D156">
-        <v>1000000</v>
+        <v>9000000</v>
+      </c>
+      <c r="F156">
+        <v>9500000</v>
+      </c>
+      <c r="H156">
+        <v>10500000</v>
+      </c>
+      <c r="I156" t="s">
+        <v>571</v>
+      </c>
+      <c r="J156">
+        <v>11500000</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>A.J. Dybantsa</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -26885,14 +26935,17 @@
         <v>13</v>
       </c>
       <c r="B157">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c r="C157">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D157">
+        <v>1000000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -26900,17 +26953,14 @@
         <v>13</v>
       </c>
       <c r="B158">
-        <v>296</v>
+        <v>363</v>
       </c>
       <c r="C158">
-        <v>3</v>
-      </c>
-      <c r="D158">
-        <v>3000000</v>
+        <v>2</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -26918,17 +26968,17 @@
         <v>13</v>
       </c>
       <c r="B159">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="C159">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D159">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -26936,14 +26986,17 @@
         <v>13</v>
       </c>
       <c r="B160">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="C160">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D160">
+        <v>2000000</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -26951,14 +27004,14 @@
         <v>13</v>
       </c>
       <c r="B161">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C161">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -26966,17 +27019,14 @@
         <v>13</v>
       </c>
       <c r="B162">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C162">
-        <v>7</v>
-      </c>
-      <c r="D162">
-        <v>11500000</v>
+        <v>6</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -26984,23 +27034,17 @@
         <v>13</v>
       </c>
       <c r="B163">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C163">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D163">
-        <v>16000000</v>
-      </c>
-      <c r="F163">
-        <v>16000000</v>
-      </c>
-      <c r="H163">
-        <v>16000000</v>
+        <v>11500000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -27008,23 +27052,23 @@
         <v>13</v>
       </c>
       <c r="B164">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C164">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D164">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="F164">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="H164">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -27032,17 +27076,23 @@
         <v>13</v>
       </c>
       <c r="B165">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C165">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D165">
-        <v>19000000</v>
+        <v>12000000</v>
+      </c>
+      <c r="F165">
+        <v>12000000</v>
+      </c>
+      <c r="H165">
+        <v>12000000</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -27050,38 +27100,41 @@
         <v>13</v>
       </c>
       <c r="B166">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="C166">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D166">
-        <v>6000000</v>
-      </c>
-      <c r="F166">
-        <v>6000000</v>
-      </c>
-      <c r="H166">
-        <v>6000000</v>
+        <v>19000000</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B167">
-        <v>317</v>
+        <v>150</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D167">
+        <v>6000000</v>
+      </c>
+      <c r="F167">
+        <v>6000000</v>
+      </c>
+      <c r="H167">
+        <v>6000000</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -27089,14 +27142,14 @@
         <v>14</v>
       </c>
       <c r="B168">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -27104,14 +27157,14 @@
         <v>14</v>
       </c>
       <c r="B169">
-        <v>129</v>
+        <v>299</v>
       </c>
       <c r="C169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -27119,14 +27172,14 @@
         <v>14</v>
       </c>
       <c r="B170">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="C170">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -27134,17 +27187,14 @@
         <v>14</v>
       </c>
       <c r="B171">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="C171">
-        <v>5</v>
-      </c>
-      <c r="D171">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -27152,17 +27202,17 @@
         <v>14</v>
       </c>
       <c r="B172">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="C172">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D172">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -27170,23 +27220,17 @@
         <v>14</v>
       </c>
       <c r="B173">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="C173">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D173">
-        <v>20500000</v>
-      </c>
-      <c r="F173">
-        <v>20500000</v>
-      </c>
-      <c r="H173">
-        <v>20500000</v>
+        <v>3000000</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -27194,17 +27238,23 @@
         <v>14</v>
       </c>
       <c r="B174">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C174">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D174">
-        <v>19500000</v>
+        <v>20500000</v>
+      </c>
+      <c r="F174">
+        <v>20500000</v>
+      </c>
+      <c r="H174">
+        <v>20500000</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -27212,29 +27262,17 @@
         <v>14</v>
       </c>
       <c r="B175">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C175">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D175">
-        <v>9500000</v>
-      </c>
-      <c r="F175">
-        <v>10500000</v>
-      </c>
-      <c r="G175" t="s">
-        <v>571</v>
-      </c>
-      <c r="H175">
-        <v>11500000</v>
-      </c>
-      <c r="I175" t="s">
-        <v>571</v>
+        <v>19500000</v>
       </c>
       <c r="L175" t="str">
         <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -27242,14 +27280,29 @@
         <v>14</v>
       </c>
       <c r="B176">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C176">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D176">
+        <v>9500000</v>
+      </c>
+      <c r="F176">
+        <v>10500000</v>
+      </c>
+      <c r="G176" t="s">
+        <v>571</v>
+      </c>
+      <c r="H176">
+        <v>11500000</v>
+      </c>
+      <c r="I176" t="s">
+        <v>571</v>
       </c>
       <c r="L176" t="str">
         <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -27257,14 +27310,14 @@
         <v>14</v>
       </c>
       <c r="B177">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="C177">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L177" t="str">
         <f>VLOOKUP(B177,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -27272,23 +27325,14 @@
         <v>14</v>
       </c>
       <c r="B178">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C178">
-        <v>12</v>
-      </c>
-      <c r="D178">
-        <v>20000000</v>
-      </c>
-      <c r="F178">
-        <v>20000000</v>
-      </c>
-      <c r="H178">
-        <v>20000000</v>
+        <v>11</v>
       </c>
       <c r="L178" t="str">
         <f>VLOOKUP(B178,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Quentin Grimes</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -27296,19 +27340,43 @@
         <v>14</v>
       </c>
       <c r="B179">
-        <v>273</v>
+        <v>145</v>
       </c>
       <c r="C179">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D179">
-        <v>3200000</v>
+        <v>20000000</v>
       </c>
       <c r="F179">
-        <v>3500000</v>
+        <v>20000000</v>
+      </c>
+      <c r="H179">
+        <v>20000000</v>
       </c>
       <c r="L179" t="str">
         <f>VLOOKUP(B179,players!A:B,2)</f>
+        <v>LaMelo Ball</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>14</v>
+      </c>
+      <c r="B180">
+        <v>273</v>
+      </c>
+      <c r="C180">
+        <v>13</v>
+      </c>
+      <c r="D180">
+        <v>3200000</v>
+      </c>
+      <c r="F180">
+        <v>3500000</v>
+      </c>
+      <c r="L180" t="str">
+        <f>VLOOKUP(B180,players!A:B,2)</f>
         <v>Cason Wallace</v>
       </c>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sefazpegovbr-my.sharepoint.com/personal/filipe_lima_sefaz_pe_gov_br/Documents/Documents/GitHub/Fantasy-unificado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A19F7E1A-F7D1-4927-9AA9-19B9AA091A21}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22031B28-66C0-42EE-8A7D-E7EA8CBADCB5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -25717,7 +25717,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B95">
         <v>420</v>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22031B28-66C0-42EE-8A7D-E7EA8CBADCB5}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="11_791FA96ECBD6B4BC3EA43B8EE66197E7E776D260" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D28F3C0-2A21-4D74-B38A-7D891F26C61D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="709">
   <si>
     <t>player</t>
   </si>
@@ -2161,6 +2161,18 @@
   </si>
   <si>
     <t>Kingston Flemings</t>
+  </si>
+  <si>
+    <t>Mikel Brown Jr.</t>
+  </si>
+  <si>
+    <t>Hannes Steinbach</t>
+  </si>
+  <si>
+    <t>Keaton Wagler</t>
+  </si>
+  <si>
+    <t>Morez Johnson Jr.</t>
   </si>
 </sst>
 </file>
@@ -2247,6 +2259,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2566,7 +2582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M423"/>
+  <dimension ref="A1:M427"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -16164,6 +16180,134 @@
         <v>0</v>
       </c>
       <c r="K423" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>423</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E424" s="1">
+        <v>0</v>
+      </c>
+      <c r="F424" s="1">
+        <v>0</v>
+      </c>
+      <c r="G424" s="1">
+        <v>0</v>
+      </c>
+      <c r="H424" s="1">
+        <v>0</v>
+      </c>
+      <c r="I424" s="1">
+        <v>0</v>
+      </c>
+      <c r="J424" s="1">
+        <v>0</v>
+      </c>
+      <c r="K424" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>424</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E425" s="1">
+        <v>0</v>
+      </c>
+      <c r="F425" s="1">
+        <v>0</v>
+      </c>
+      <c r="G425" s="1">
+        <v>0</v>
+      </c>
+      <c r="H425" s="1">
+        <v>0</v>
+      </c>
+      <c r="I425" s="1">
+        <v>0</v>
+      </c>
+      <c r="J425" s="1">
+        <v>0</v>
+      </c>
+      <c r="K425" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>425</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E426" s="1">
+        <v>0</v>
+      </c>
+      <c r="F426" s="1">
+        <v>0</v>
+      </c>
+      <c r="G426" s="1">
+        <v>0</v>
+      </c>
+      <c r="H426" s="1">
+        <v>0</v>
+      </c>
+      <c r="I426" s="1">
+        <v>0</v>
+      </c>
+      <c r="J426" s="1">
+        <v>0</v>
+      </c>
+      <c r="K426" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>426</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E427" s="1">
+        <v>0</v>
+      </c>
+      <c r="F427" s="1">
+        <v>0</v>
+      </c>
+      <c r="G427" s="1">
+        <v>0</v>
+      </c>
+      <c r="H427" s="1">
+        <v>0</v>
+      </c>
+      <c r="I427" s="1">
+        <v>0</v>
+      </c>
+      <c r="J427" s="1">
+        <v>0</v>
+      </c>
+      <c r="K427" s="1">
         <v>0</v>
       </c>
     </row>
@@ -23817,7 +23961,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:L184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24454,50 +24598,68 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31">
-        <v>320</v>
+        <v>424</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D31">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="F31">
-        <v>1000000</v>
-      </c>
-      <c r="G31" t="s">
+        <v>4000000</v>
+      </c>
+      <c r="H31">
+        <v>4200000</v>
+      </c>
+      <c r="I31" t="s">
+        <v>571</v>
+      </c>
+      <c r="J31">
+        <v>4500000</v>
+      </c>
+      <c r="K31" t="s">
         <v>571</v>
       </c>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Cam Spencer</v>
+        <v>Hannes Steinbach</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D32">
-        <v>23500000</v>
+        <v>3600000</v>
       </c>
       <c r="F32">
-        <v>23500000</v>
+        <v>3800000</v>
       </c>
       <c r="H32">
-        <v>23500000</v>
+        <v>4000000</v>
+      </c>
+      <c r="I32" t="s">
+        <v>571</v>
+      </c>
+      <c r="J32">
+        <v>4300000</v>
+      </c>
+      <c r="K32" t="s">
+        <v>571</v>
       </c>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
-        <v>Alperen Şengün</v>
+        <v>Keaton Wagler</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -24505,17 +24667,23 @@
         <v>2</v>
       </c>
       <c r="B33">
-        <v>96</v>
+        <v>320</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>15000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F33">
+        <v>1000000</v>
+      </c>
+      <c r="G33" t="s">
+        <v>571</v>
       </c>
       <c r="L33" t="str">
         <f>VLOOKUP(B33,players!A:B,2)</f>
-        <v>Kevin Durant</v>
+        <v>Cam Spencer</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -24523,17 +24691,23 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>9000000</v>
+        <v>23500000</v>
+      </c>
+      <c r="F34">
+        <v>23500000</v>
+      </c>
+      <c r="H34">
+        <v>23500000</v>
       </c>
       <c r="L34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
-        <v>Brandon Miller</v>
+        <v>Alperen Şengün</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -24541,23 +24715,17 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>7000000</v>
-      </c>
-      <c r="F35">
-        <v>7000000</v>
-      </c>
-      <c r="H35">
-        <v>7000000</v>
+        <v>15000000</v>
       </c>
       <c r="L35" t="str">
         <f>VLOOKUP(B35,players!A:B,2)</f>
-        <v>Jalen Green</v>
+        <v>Kevin Durant</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -24565,20 +24733,17 @@
         <v>2</v>
       </c>
       <c r="B36">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>6000000</v>
-      </c>
-      <c r="F36">
-        <v>6000000</v>
+        <v>9000000</v>
       </c>
       <c r="L36" t="str">
         <f>VLOOKUP(B36,players!A:B,2)</f>
-        <v>Tyler Herro</v>
+        <v>Brandon Miller</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -24586,23 +24751,23 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>362</v>
+        <v>219</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>21500000</v>
+        <v>7000000</v>
       </c>
       <c r="F37">
-        <v>21500000</v>
+        <v>7000000</v>
       </c>
       <c r="H37">
-        <v>21500000</v>
+        <v>7000000</v>
       </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>Trae Young</v>
+        <v>Jalen Green</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -24610,14 +24775,20 @@
         <v>2</v>
       </c>
       <c r="B38">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D38">
+        <v>6000000</v>
+      </c>
+      <c r="F38">
+        <v>6000000</v>
       </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>Russell Westbrook</v>
+        <v>Tyler Herro</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -24625,74 +24796,95 @@
         <v>2</v>
       </c>
       <c r="B39">
-        <v>69</v>
+        <v>362</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>3100000</v>
+        <v>21500000</v>
       </c>
       <c r="F39">
-        <v>3100000</v>
+        <v>21500000</v>
       </c>
       <c r="H39">
-        <v>3100000</v>
+        <v>21500000</v>
       </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Bobby Portis</v>
+        <v>Trae Young</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>8000000</v>
-      </c>
-      <c r="F40">
-        <v>8000000</v>
+        <v>8</v>
       </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Immanuel Quickley</v>
+        <v>Russell Westbrook</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41">
-        <v>237</v>
+        <v>69</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="D41">
+        <v>3100000</v>
+      </c>
+      <c r="F41">
+        <v>3100000</v>
+      </c>
+      <c r="H41">
+        <v>3100000</v>
       </c>
       <c r="L41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Nickeil Alexander-Walker</v>
+        <v>Bobby Portis</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42">
-        <v>119</v>
+        <v>423</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D42">
+        <v>4000000</v>
+      </c>
+      <c r="F42">
+        <v>4500000</v>
+      </c>
+      <c r="H42">
+        <v>5000000</v>
+      </c>
+      <c r="I42" t="s">
+        <v>571</v>
+      </c>
+      <c r="J42">
+        <v>5500000</v>
+      </c>
+      <c r="K42" t="s">
+        <v>571</v>
       </c>
       <c r="L42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Kyshawn George</v>
+        <v>Mikel Brown Jr.</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -24700,17 +24892,20 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>5000000</v>
+        <v>8000000</v>
+      </c>
+      <c r="F43">
+        <v>8000000</v>
       </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>Cameron Johnson</v>
+        <v>Immanuel Quickley</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -24718,14 +24913,14 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L44" t="str">
         <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>Myles Turner</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -24733,14 +24928,14 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L45" t="str">
         <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>Mitchell Robinson</v>
+        <v>Kyshawn George</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -24748,14 +24943,17 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>11</v>
+        <v>206</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="D46">
+        <v>5000000</v>
       </c>
       <c r="L46" t="str">
         <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>Jalen Duren</v>
+        <v>Cameron Johnson</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -24763,23 +24961,14 @@
         <v>3</v>
       </c>
       <c r="B47">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="C47">
-        <v>8</v>
-      </c>
-      <c r="D47">
-        <v>40000000</v>
-      </c>
-      <c r="F47">
-        <v>40000000</v>
-      </c>
-      <c r="H47">
-        <v>40000000</v>
+        <v>5</v>
       </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>Luka Dončić</v>
+        <v>Myles Turner</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -24787,17 +24976,14 @@
         <v>3</v>
       </c>
       <c r="B48">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C48">
-        <v>9</v>
-      </c>
-      <c r="D48">
-        <v>6000000</v>
+        <v>6</v>
       </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>Kawhi Leonard</v>
+        <v>Mitchell Robinson</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -24805,20 +24991,14 @@
         <v>3</v>
       </c>
       <c r="B49">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C49">
-        <v>10</v>
-      </c>
-      <c r="D49">
-        <v>14000000</v>
-      </c>
-      <c r="F49">
-        <v>14000000</v>
+        <v>7</v>
       </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>Jaren Jackson Jr.</v>
+        <v>Jalen Duren</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -24826,23 +25006,23 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="C50">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D50">
-        <v>6500000</v>
+        <v>40000000</v>
       </c>
       <c r="F50">
-        <v>6500000</v>
+        <v>40000000</v>
       </c>
       <c r="H50">
-        <v>6500000</v>
+        <v>40000000</v>
       </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>OG Anunoby</v>
+        <v>Luka Dončić</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -24850,17 +25030,17 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>142</v>
+        <v>68</v>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D51">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>Kyrie Irving</v>
+        <v>Kawhi Leonard</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -24868,86 +25048,80 @@
         <v>3</v>
       </c>
       <c r="B52">
-        <v>295</v>
+        <v>85</v>
       </c>
       <c r="C52">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D52">
-        <v>8000000</v>
+        <v>14000000</v>
+      </c>
+      <c r="F52">
+        <v>14000000</v>
       </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Zach LaVine</v>
+        <v>Jaren Jackson Jr.</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53">
-        <v>379</v>
+        <v>117</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D53">
-        <v>1000000</v>
+        <v>6500000</v>
       </c>
       <c r="F53">
-        <v>1000000</v>
-      </c>
-      <c r="G53" t="s">
-        <v>571</v>
+        <v>6500000</v>
       </c>
       <c r="H53">
-        <v>1000000</v>
-      </c>
-      <c r="I53" t="s">
-        <v>571</v>
+        <v>6500000</v>
       </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>OG Anunoby</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54">
-        <v>364</v>
+        <v>142</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D54">
-        <v>1000000</v>
-      </c>
-      <c r="F54">
-        <v>1000000</v>
-      </c>
-      <c r="G54" t="s">
-        <v>571</v>
+        <v>5000000</v>
       </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Kyrie Irving</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B55">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="D55">
+        <v>8000000</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -24955,17 +25129,29 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>62</v>
+        <v>379</v>
       </c>
       <c r="C56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>2500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F56">
+        <v>1000000</v>
+      </c>
+      <c r="G56" t="s">
+        <v>571</v>
+      </c>
+      <c r="H56">
+        <v>1000000</v>
+      </c>
+      <c r="I56" t="s">
+        <v>571</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -24973,17 +25159,23 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>33</v>
+        <v>364</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D57">
-        <v>11000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F57">
+        <v>1000000</v>
+      </c>
+      <c r="G57" t="s">
+        <v>571</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -24991,20 +25183,14 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="C58">
-        <v>6</v>
-      </c>
-      <c r="D58">
-        <v>5000000</v>
-      </c>
-      <c r="F58">
-        <v>5000000</v>
+        <v>3</v>
       </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -25012,20 +25198,17 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D59">
-        <v>17000000</v>
-      </c>
-      <c r="F59">
-        <v>17000000</v>
+        <v>2500000</v>
       </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -25033,17 +25216,17 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D60">
-        <v>22500000</v>
+        <v>11000000</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -25051,23 +25234,20 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C61">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D61">
         <v>5000000</v>
       </c>
       <c r="F61">
-        <v>5500000</v>
-      </c>
-      <c r="G61" t="s">
-        <v>571</v>
+        <v>5000000</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -25075,23 +25255,20 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D62">
-        <v>15000000</v>
+        <v>17000000</v>
       </c>
       <c r="F62">
-        <v>15000000</v>
-      </c>
-      <c r="H62">
-        <v>15000000</v>
+        <v>17000000</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -25099,23 +25276,17 @@
         <v>4</v>
       </c>
       <c r="B63">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D63">
-        <v>19000000</v>
-      </c>
-      <c r="F63">
-        <v>19000000</v>
-      </c>
-      <c r="H63">
-        <v>19000000</v>
+        <v>22500000</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -25123,17 +25294,23 @@
         <v>4</v>
       </c>
       <c r="B64">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="C64">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D64">
-        <v>10000000</v>
+        <v>5000000</v>
+      </c>
+      <c r="F64">
+        <v>5500000</v>
+      </c>
+      <c r="G64" t="s">
+        <v>571</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -25141,92 +25318,98 @@
         <v>4</v>
       </c>
       <c r="B65">
-        <v>422</v>
+        <v>114</v>
       </c>
       <c r="C65">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D65">
-        <v>4500000</v>
+        <v>15000000</v>
       </c>
       <c r="F65">
-        <v>5000000</v>
+        <v>15000000</v>
       </c>
       <c r="H65">
-        <v>5500000</v>
-      </c>
-      <c r="I65" t="s">
-        <v>571</v>
-      </c>
-      <c r="J65">
-        <v>6000000</v>
-      </c>
-      <c r="K65" t="s">
-        <v>571</v>
+        <v>15000000</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>Kingston Flemings</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B66">
-        <v>305</v>
+        <v>157</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D66">
+        <v>19000000</v>
+      </c>
+      <c r="F66">
+        <v>19000000</v>
+      </c>
+      <c r="H66">
+        <v>19000000</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D67">
-        <v>3600000</v>
-      </c>
-      <c r="F67">
-        <v>3800000</v>
-      </c>
-      <c r="G67" t="s">
-        <v>571</v>
-      </c>
-      <c r="H67">
-        <v>4100000</v>
-      </c>
-      <c r="I67" t="s">
-        <v>571</v>
+        <v>10000000</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B68">
-        <v>274</v>
+        <v>422</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="D68">
+        <v>4500000</v>
+      </c>
+      <c r="F68">
+        <v>5000000</v>
+      </c>
+      <c r="H68">
+        <v>5500000</v>
+      </c>
+      <c r="I68" t="s">
+        <v>571</v>
+      </c>
+      <c r="J68">
+        <v>6000000</v>
+      </c>
+      <c r="K68" t="s">
+        <v>571</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Kingston Flemings</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -25234,20 +25417,14 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>143</v>
+        <v>305</v>
       </c>
       <c r="C69">
-        <v>4</v>
-      </c>
-      <c r="D69">
-        <v>21000000</v>
-      </c>
-      <c r="F69">
-        <v>21000000</v>
+        <v>1</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -25255,14 +25432,29 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="D70">
+        <v>3600000</v>
+      </c>
+      <c r="F70">
+        <v>3800000</v>
+      </c>
+      <c r="G70" t="s">
+        <v>571</v>
+      </c>
+      <c r="H70">
+        <v>4100000</v>
+      </c>
+      <c r="I70" t="s">
+        <v>571</v>
       </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -25270,29 +25462,14 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>139</v>
+        <v>274</v>
       </c>
       <c r="C71">
-        <v>6</v>
-      </c>
-      <c r="D71">
-        <v>1000000</v>
-      </c>
-      <c r="F71">
-        <v>1000000</v>
-      </c>
-      <c r="G71" t="s">
-        <v>571</v>
-      </c>
-      <c r="H71">
-        <v>1000000</v>
-      </c>
-      <c r="I71" t="s">
-        <v>571</v>
+        <v>3</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Danny Wolf</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -25300,20 +25477,20 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D72">
-        <v>17000000</v>
+        <v>21000000</v>
       </c>
       <c r="F72">
-        <v>17000000</v>
+        <v>21000000</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -25321,23 +25498,14 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="C73">
-        <v>8</v>
-      </c>
-      <c r="D73">
-        <v>40000000</v>
-      </c>
-      <c r="F73">
-        <v>40000000</v>
-      </c>
-      <c r="H73">
-        <v>40000000</v>
+        <v>5</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -25345,20 +25513,29 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="C74">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D74">
-        <v>3100000</v>
+        <v>1000000</v>
       </c>
       <c r="F74">
-        <v>3100000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G74" t="s">
+        <v>571</v>
+      </c>
+      <c r="H74">
+        <v>1000000</v>
+      </c>
+      <c r="I74" t="s">
+        <v>571</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Danny Wolf</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -25366,14 +25543,20 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>227</v>
+        <v>37</v>
       </c>
       <c r="C75">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D75">
+        <v>17000000</v>
+      </c>
+      <c r="F75">
+        <v>17000000</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Jerami Grant</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -25381,14 +25564,23 @@
         <v>5</v>
       </c>
       <c r="B76">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="C76">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="D76">
+        <v>40000000</v>
+      </c>
+      <c r="F76">
+        <v>40000000</v>
+      </c>
+      <c r="H76">
+        <v>40000000</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -25396,14 +25588,20 @@
         <v>5</v>
       </c>
       <c r="B77">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="C77">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="D77">
+        <v>3100000</v>
+      </c>
+      <c r="F77">
+        <v>3100000</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>Royce O'Neale</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -25411,14 +25609,14 @@
         <v>5</v>
       </c>
       <c r="B78">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="C78">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Ryan Rollins</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -25426,86 +25624,77 @@
         <v>5</v>
       </c>
       <c r="B79">
-        <v>418</v>
+        <v>48</v>
       </c>
       <c r="C79">
-        <v>13</v>
-      </c>
-      <c r="D79">
-        <v>8000000</v>
-      </c>
-      <c r="F79">
-        <v>8500000</v>
-      </c>
-      <c r="H79">
-        <v>9250000</v>
-      </c>
-      <c r="I79" t="s">
-        <v>571</v>
-      </c>
-      <c r="J79">
-        <v>10000000</v>
-      </c>
-      <c r="K79" t="s">
-        <v>571</v>
+        <v>11</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>Caleb Wilson</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B80">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80">
-        <v>6000000</v>
-      </c>
-      <c r="F80">
-        <v>6000000</v>
+        <v>12</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B81">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="C81">
-        <v>2</v>
-      </c>
-      <c r="D81">
-        <v>1000000</v>
+        <v>12</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B82">
-        <v>45</v>
+        <v>418</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="D82">
+        <v>8000000</v>
+      </c>
+      <c r="F82">
+        <v>8500000</v>
+      </c>
+      <c r="H82">
+        <v>9250000</v>
+      </c>
+      <c r="I82" t="s">
+        <v>571</v>
+      </c>
+      <c r="J82">
+        <v>10000000</v>
+      </c>
+      <c r="K82" t="s">
+        <v>571</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>Caleb Wilson</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -25513,14 +25702,20 @@
         <v>6</v>
       </c>
       <c r="B83">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>6000000</v>
+      </c>
+      <c r="F83">
+        <v>6000000</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -25528,14 +25723,17 @@
         <v>6</v>
       </c>
       <c r="B84">
-        <v>98</v>
+        <v>338</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="D84">
+        <v>1000000</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -25543,14 +25741,14 @@
         <v>6</v>
       </c>
       <c r="B85">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C85">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -25558,17 +25756,14 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="C86">
-        <v>7</v>
-      </c>
-      <c r="D86">
-        <v>20000000</v>
+        <v>4</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -25576,14 +25771,14 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="C87">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -25591,17 +25786,14 @@
         <v>6</v>
       </c>
       <c r="B88">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C88">
-        <v>9</v>
-      </c>
-      <c r="D88">
-        <v>7000000</v>
+        <v>6</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -25609,20 +25801,17 @@
         <v>6</v>
       </c>
       <c r="B89">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D89">
-        <v>35000000</v>
-      </c>
-      <c r="F89">
-        <v>35000000</v>
+        <v>20000000</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -25630,20 +25819,14 @@
         <v>6</v>
       </c>
       <c r="B90">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C90">
-        <v>11</v>
-      </c>
-      <c r="D90">
-        <v>3100000</v>
-      </c>
-      <c r="F90">
-        <v>3100000</v>
+        <v>8</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -25651,17 +25834,17 @@
         <v>6</v>
       </c>
       <c r="B91">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="C91">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D91">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -25669,14 +25852,20 @@
         <v>6</v>
       </c>
       <c r="B92">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="C92">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D92">
+        <v>35000000</v>
+      </c>
+      <c r="F92">
+        <v>35000000</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Damian Lillard</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -25684,20 +25873,20 @@
         <v>6</v>
       </c>
       <c r="B93">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="C93">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D93">
-        <v>6000000</v>
+        <v>3100000</v>
       </c>
       <c r="F93">
-        <v>6000000</v>
+        <v>3100000</v>
       </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -25705,14 +25894,17 @@
         <v>6</v>
       </c>
       <c r="B94">
-        <v>71</v>
+        <v>211</v>
       </c>
       <c r="C94">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="D94">
+        <v>1000000</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Tari Eason</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -25720,101 +25912,83 @@
         <v>6</v>
       </c>
       <c r="B95">
-        <v>420</v>
+        <v>161</v>
       </c>
       <c r="C95">
         <v>13</v>
       </c>
-      <c r="D95">
-        <v>6000000</v>
-      </c>
-      <c r="F95">
-        <v>6500000</v>
-      </c>
-      <c r="H95">
-        <v>7000000</v>
-      </c>
-      <c r="I95" t="s">
-        <v>571</v>
-      </c>
-      <c r="J95">
-        <v>7500000</v>
-      </c>
-      <c r="K95" t="s">
-        <v>571</v>
-      </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Darryn Peterson</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B96">
-        <v>242</v>
+        <v>93</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D96">
-        <v>3800000</v>
+        <v>6000000</v>
       </c>
       <c r="F96">
-        <v>4100000</v>
-      </c>
-      <c r="G96" t="s">
-        <v>571</v>
+        <v>6000000</v>
       </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B97">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B98">
-        <v>76</v>
+        <v>420</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D98">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="F98">
-        <v>1000000</v>
-      </c>
-      <c r="G98" t="s">
-        <v>571</v>
+        <v>6500000</v>
       </c>
       <c r="H98">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="I98" t="s">
         <v>571</v>
       </c>
+      <c r="J98">
+        <v>7500000</v>
+      </c>
+      <c r="K98" t="s">
+        <v>571</v>
+      </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Darryn Peterson</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -25822,17 +25996,23 @@
         <v>8</v>
       </c>
       <c r="B99">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="C99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D99">
-        <v>2000000</v>
+        <v>3800000</v>
+      </c>
+      <c r="F99">
+        <v>4100000</v>
+      </c>
+      <c r="G99" t="s">
+        <v>571</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -25840,23 +26020,14 @@
         <v>8</v>
       </c>
       <c r="B100">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C100">
-        <v>5</v>
-      </c>
-      <c r="D100">
-        <v>6000000</v>
-      </c>
-      <c r="F100">
-        <v>6000000</v>
-      </c>
-      <c r="H100">
-        <v>6000000</v>
+        <v>2</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -25864,23 +26035,29 @@
         <v>8</v>
       </c>
       <c r="B101">
+        <v>76</v>
+      </c>
+      <c r="C101">
         <v>3</v>
       </c>
-      <c r="C101">
-        <v>6</v>
-      </c>
       <c r="D101">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="F101">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="G101" t="s">
         <v>571</v>
       </c>
+      <c r="H101">
+        <v>1000000</v>
+      </c>
+      <c r="I101" t="s">
+        <v>571</v>
+      </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -25888,20 +26065,17 @@
         <v>8</v>
       </c>
       <c r="B102">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D102">
-        <v>4000000</v>
-      </c>
-      <c r="F102">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -25909,23 +26083,23 @@
         <v>8</v>
       </c>
       <c r="B103">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="C103">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D103">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="F103">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="H103">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -25933,20 +26107,23 @@
         <v>8</v>
       </c>
       <c r="B104">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="C104">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D104">
-        <v>9000000</v>
+        <v>7000000</v>
       </c>
       <c r="F104">
-        <v>9000000</v>
+        <v>7500000</v>
+      </c>
+      <c r="G104" t="s">
+        <v>571</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -25954,17 +26131,20 @@
         <v>8</v>
       </c>
       <c r="B105">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D105">
-        <v>16000000</v>
+        <v>4000000</v>
+      </c>
+      <c r="F105">
+        <v>4000000</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -25972,23 +26152,23 @@
         <v>8</v>
       </c>
       <c r="B106">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="C106">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D106">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="F106">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="H106">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -25996,14 +26176,20 @@
         <v>8</v>
       </c>
       <c r="B107">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="C107">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="D107">
+        <v>9000000</v>
+      </c>
+      <c r="F107">
+        <v>9000000</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -26011,14 +26197,17 @@
         <v>8</v>
       </c>
       <c r="B108">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C108">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D108">
+        <v>16000000</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -26026,71 +26215,68 @@
         <v>8</v>
       </c>
       <c r="B109">
-        <v>336</v>
+        <v>203</v>
       </c>
       <c r="C109">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="D109">
+        <v>19000000</v>
+      </c>
+      <c r="F109">
+        <v>19000000</v>
+      </c>
+      <c r="H109">
+        <v>19000000</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B110">
-        <v>384</v>
+        <v>225</v>
       </c>
       <c r="C110">
-        <v>1</v>
-      </c>
-      <c r="D110">
-        <v>3100000</v>
-      </c>
-      <c r="F110">
-        <v>3100000</v>
-      </c>
-      <c r="H110">
-        <v>3100000</v>
+        <v>12</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B111">
-        <v>240</v>
+        <v>59</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B112">
-        <v>186</v>
+        <v>336</v>
       </c>
       <c r="C112">
-        <v>3</v>
-      </c>
-      <c r="D112">
-        <v>4500000</v>
+        <v>14</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -26098,14 +26284,23 @@
         <v>9</v>
       </c>
       <c r="B113">
-        <v>251</v>
+        <v>384</v>
       </c>
       <c r="C113">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D113">
+        <v>3100000</v>
+      </c>
+      <c r="F113">
+        <v>3100000</v>
+      </c>
+      <c r="H113">
+        <v>3100000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -26113,14 +26308,14 @@
         <v>9</v>
       </c>
       <c r="B114">
-        <v>416</v>
+        <v>240</v>
       </c>
       <c r="C114">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -26128,23 +26323,17 @@
         <v>9</v>
       </c>
       <c r="B115">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="C115">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D115">
-        <v>3100000</v>
-      </c>
-      <c r="F115">
-        <v>3100000</v>
-      </c>
-      <c r="H115">
-        <v>3100000</v>
+        <v>4500000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -26152,23 +26341,14 @@
         <v>9</v>
       </c>
       <c r="B116">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="C116">
-        <v>7</v>
-      </c>
-      <c r="D116">
-        <v>32000000</v>
-      </c>
-      <c r="F116">
-        <v>32000000</v>
-      </c>
-      <c r="H116">
-        <v>32000000</v>
+        <v>4</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -26176,23 +26356,14 @@
         <v>9</v>
       </c>
       <c r="B117">
-        <v>26</v>
+        <v>416</v>
       </c>
       <c r="C117">
-        <v>8</v>
-      </c>
-      <c r="D117">
-        <v>12500000</v>
-      </c>
-      <c r="F117">
-        <v>12500000</v>
-      </c>
-      <c r="H117">
-        <v>12500000</v>
+        <v>5</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -26200,17 +26371,23 @@
         <v>9</v>
       </c>
       <c r="B118">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="C118">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D118">
-        <v>11500000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F118">
+        <v>3100000</v>
+      </c>
+      <c r="H118">
+        <v>3100000</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -26218,23 +26395,23 @@
         <v>9</v>
       </c>
       <c r="B119">
-        <v>167</v>
+        <v>15</v>
       </c>
       <c r="C119">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D119">
-        <v>3100000</v>
+        <v>32000000</v>
       </c>
       <c r="F119">
-        <v>3100000</v>
+        <v>32000000</v>
       </c>
       <c r="H119">
-        <v>3100000</v>
+        <v>32000000</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -26242,17 +26419,23 @@
         <v>9</v>
       </c>
       <c r="B120">
-        <v>217</v>
+        <v>26</v>
       </c>
       <c r="C120">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D120">
-        <v>25000000</v>
+        <v>12500000</v>
+      </c>
+      <c r="F120">
+        <v>12500000</v>
+      </c>
+      <c r="H120">
+        <v>12500000</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -26260,68 +26443,83 @@
         <v>9</v>
       </c>
       <c r="B121">
-        <v>331</v>
+        <v>89</v>
       </c>
       <c r="C121">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D121">
-        <v>12000000</v>
-      </c>
-      <c r="F121">
-        <v>12000000</v>
-      </c>
-      <c r="H121">
-        <v>12000000</v>
+        <v>11500000</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122">
+        <v>9</v>
+      </c>
+      <c r="B122">
+        <v>167</v>
+      </c>
+      <c r="C122">
         <v>10</v>
       </c>
-      <c r="B122">
-        <v>9</v>
-      </c>
-      <c r="C122">
-        <v>1</v>
+      <c r="D122">
+        <v>3100000</v>
+      </c>
+      <c r="F122">
+        <v>3100000</v>
+      </c>
+      <c r="H122">
+        <v>3100000</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Walker Kessler</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B123">
-        <v>373</v>
+        <v>217</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="D123">
+        <v>25000000</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B124">
-        <v>249</v>
+        <v>331</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="D124">
+        <v>12000000</v>
+      </c>
+      <c r="F124">
+        <v>12000000</v>
+      </c>
+      <c r="H124">
+        <v>12000000</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -26329,17 +26527,14 @@
         <v>10</v>
       </c>
       <c r="B125">
-        <v>169</v>
+        <v>9</v>
       </c>
       <c r="C125">
-        <v>4</v>
-      </c>
-      <c r="D125">
-        <v>4100000</v>
+        <v>1</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -26347,20 +26542,14 @@
         <v>10</v>
       </c>
       <c r="B126">
-        <v>34</v>
+        <v>373</v>
       </c>
       <c r="C126">
-        <v>5</v>
-      </c>
-      <c r="D126">
-        <v>6000000</v>
-      </c>
-      <c r="F126">
-        <v>6000000</v>
+        <v>2</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -26368,17 +26557,14 @@
         <v>10</v>
       </c>
       <c r="B127">
-        <v>168</v>
+        <v>249</v>
       </c>
       <c r="C127">
-        <v>6</v>
-      </c>
-      <c r="D127">
-        <v>1000000</v>
+        <v>3</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -26386,14 +26572,17 @@
         <v>10</v>
       </c>
       <c r="B128">
-        <v>28</v>
+        <v>169</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="D128">
+        <v>4100000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -26401,23 +26590,20 @@
         <v>10</v>
       </c>
       <c r="B129">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C129">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D129">
-        <v>9250000</v>
+        <v>6000000</v>
       </c>
       <c r="F129">
-        <v>10000000</v>
-      </c>
-      <c r="G129" t="s">
-        <v>571</v>
+        <v>6000000</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -26425,23 +26611,17 @@
         <v>10</v>
       </c>
       <c r="B130">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="C130">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D130">
-        <v>15000000</v>
-      </c>
-      <c r="F130">
-        <v>15000000</v>
-      </c>
-      <c r="H130">
-        <v>15000000</v>
+        <v>1000000</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -26449,20 +26629,14 @@
         <v>10</v>
       </c>
       <c r="B131">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="C131">
-        <v>10</v>
-      </c>
-      <c r="D131">
-        <v>11000000</v>
-      </c>
-      <c r="F131">
-        <v>11000000</v>
+        <v>7</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -26470,23 +26644,23 @@
         <v>10</v>
       </c>
       <c r="B132">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="C132">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D132">
-        <v>16000000</v>
+        <v>9250000</v>
       </c>
       <c r="F132">
-        <v>16000000</v>
-      </c>
-      <c r="H132">
-        <v>16000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G132" t="s">
+        <v>571</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -26494,65 +26668,86 @@
         <v>10</v>
       </c>
       <c r="B133">
-        <v>246</v>
+        <v>60</v>
       </c>
       <c r="C133">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D133">
-        <v>24000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="F133">
+        <v>15000000</v>
+      </c>
+      <c r="H133">
+        <v>15000000</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B134">
-        <v>327</v>
+        <v>153</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D134">
+        <v>11000000</v>
+      </c>
+      <c r="F134">
+        <v>11000000</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135">
+        <v>10</v>
+      </c>
+      <c r="B135">
+        <v>160</v>
+      </c>
+      <c r="C135">
         <v>11</v>
       </c>
-      <c r="B135">
-        <v>213</v>
-      </c>
-      <c r="C135">
-        <v>2</v>
+      <c r="D135">
+        <v>16000000</v>
+      </c>
+      <c r="F135">
+        <v>16000000</v>
+      </c>
+      <c r="H135">
+        <v>16000000</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B136">
-        <v>111</v>
+        <v>246</v>
       </c>
       <c r="C136">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D136">
-        <v>1000000</v>
+        <v>24000000</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -26560,14 +26755,14 @@
         <v>11</v>
       </c>
       <c r="B137">
-        <v>58</v>
+        <v>327</v>
       </c>
       <c r="C137">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -26575,17 +26770,14 @@
         <v>11</v>
       </c>
       <c r="B138">
-        <v>18</v>
+        <v>213</v>
       </c>
       <c r="C138">
-        <v>5</v>
-      </c>
-      <c r="D138">
-        <v>1000000</v>
+        <v>2</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -26593,14 +26785,17 @@
         <v>11</v>
       </c>
       <c r="B139">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="C139">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="D139">
+        <v>1000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -26608,17 +26803,14 @@
         <v>11</v>
       </c>
       <c r="B140">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="C140">
-        <v>7</v>
-      </c>
-      <c r="D140">
-        <v>26000000</v>
+        <v>4</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -26626,17 +26818,17 @@
         <v>11</v>
       </c>
       <c r="B141">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="C141">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D141">
-        <v>15000000</v>
+        <v>1000000</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -26644,17 +26836,14 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C142">
-        <v>9</v>
-      </c>
-      <c r="D142">
-        <v>7500000</v>
+        <v>6</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -26662,23 +26851,17 @@
         <v>11</v>
       </c>
       <c r="B143">
-        <v>166</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D143">
-        <v>30000000</v>
-      </c>
-      <c r="F143">
-        <v>30000000</v>
-      </c>
-      <c r="H143">
-        <v>30000000</v>
+        <v>26000000</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -26686,17 +26869,17 @@
         <v>11</v>
       </c>
       <c r="B144">
-        <v>248</v>
+        <v>177</v>
       </c>
       <c r="C144">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D144">
-        <v>1000000</v>
+        <v>15000000</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -26704,14 +26887,17 @@
         <v>11</v>
       </c>
       <c r="B145">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="C145">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="D145">
+        <v>7500000</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -26719,14 +26905,23 @@
         <v>11</v>
       </c>
       <c r="B146">
-        <v>266</v>
+        <v>166</v>
       </c>
       <c r="C146">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D146">
+        <v>30000000</v>
+      </c>
+      <c r="F146">
+        <v>30000000</v>
+      </c>
+      <c r="H146">
+        <v>30000000</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -26734,74 +26929,62 @@
         <v>11</v>
       </c>
       <c r="B147">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="C147">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="D147">
+        <v>1000000</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148">
+        <v>11</v>
+      </c>
+      <c r="B148">
+        <v>109</v>
+      </c>
+      <c r="C148">
         <v>12</v>
-      </c>
-      <c r="B148">
-        <v>403</v>
-      </c>
-      <c r="C148">
-        <v>1</v>
-      </c>
-      <c r="D148">
-        <v>5000000</v>
-      </c>
-      <c r="F148">
-        <v>5000000</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B149">
-        <v>345</v>
+        <v>266</v>
       </c>
       <c r="C149">
-        <v>2</v>
-      </c>
-      <c r="D149">
-        <v>3500000</v>
-      </c>
-      <c r="F149">
-        <v>3500000</v>
+        <v>13</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B150">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="C150">
-        <v>3</v>
-      </c>
-      <c r="D150">
-        <v>1000000</v>
+        <v>14</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -26809,14 +26992,20 @@
         <v>12</v>
       </c>
       <c r="B151">
-        <v>22</v>
+        <v>403</v>
       </c>
       <c r="C151">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D151">
+        <v>5000000</v>
+      </c>
+      <c r="F151">
+        <v>5000000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -26824,17 +27013,20 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>54</v>
+        <v>345</v>
       </c>
       <c r="C152">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D152">
-        <v>11000000</v>
+        <v>3500000</v>
+      </c>
+      <c r="F152">
+        <v>3500000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -26842,20 +27034,17 @@
         <v>12</v>
       </c>
       <c r="B153">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="C153">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D153">
-        <v>20000000</v>
-      </c>
-      <c r="F153">
-        <v>20000000</v>
+        <v>1000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -26863,23 +27052,14 @@
         <v>12</v>
       </c>
       <c r="B154">
-        <v>226</v>
+        <v>22</v>
       </c>
       <c r="C154">
-        <v>7</v>
-      </c>
-      <c r="D154">
-        <v>18000000</v>
-      </c>
-      <c r="F154">
-        <v>18000000</v>
-      </c>
-      <c r="H154">
-        <v>18000000</v>
+        <v>4</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -26887,17 +27067,17 @@
         <v>12</v>
       </c>
       <c r="B155">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="C155">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D155">
-        <v>2500000</v>
+        <v>11000000</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -26905,80 +27085,92 @@
         <v>12</v>
       </c>
       <c r="B156">
-        <v>417</v>
+        <v>194</v>
       </c>
       <c r="C156">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D156">
-        <v>9000000</v>
+        <v>20000000</v>
       </c>
       <c r="F156">
-        <v>9500000</v>
-      </c>
-      <c r="H156">
-        <v>10500000</v>
-      </c>
-      <c r="I156" t="s">
-        <v>571</v>
-      </c>
-      <c r="J156">
-        <v>11500000</v>
+        <v>20000000</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>A.J. Dybantsa</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B157">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D157">
-        <v>1000000</v>
+        <v>18000000</v>
+      </c>
+      <c r="F157">
+        <v>18000000</v>
+      </c>
+      <c r="H157">
+        <v>18000000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B158">
-        <v>363</v>
+        <v>115</v>
       </c>
       <c r="C158">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="D158">
+        <v>2500000</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B159">
-        <v>296</v>
+        <v>417</v>
       </c>
       <c r="C159">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D159">
-        <v>3000000</v>
+        <v>9000000</v>
+      </c>
+      <c r="F159">
+        <v>9500000</v>
+      </c>
+      <c r="H159">
+        <v>10500000</v>
+      </c>
+      <c r="I159" t="s">
+        <v>571</v>
+      </c>
+      <c r="J159">
+        <v>11500000</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>A.J. Dybantsa</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -26986,17 +27178,17 @@
         <v>13</v>
       </c>
       <c r="B160">
-        <v>171</v>
+        <v>307</v>
       </c>
       <c r="C160">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D160">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -27004,14 +27196,14 @@
         <v>13</v>
       </c>
       <c r="B161">
-        <v>10</v>
+        <v>363</v>
       </c>
       <c r="C161">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -27019,14 +27211,17 @@
         <v>13</v>
       </c>
       <c r="B162">
-        <v>46</v>
+        <v>296</v>
       </c>
       <c r="C162">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="D162">
+        <v>3000000</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -27034,17 +27229,17 @@
         <v>13</v>
       </c>
       <c r="B163">
+        <v>171</v>
+      </c>
+      <c r="C163">
         <v>4</v>
       </c>
-      <c r="C163">
-        <v>7</v>
-      </c>
       <c r="D163">
-        <v>11500000</v>
+        <v>2000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -27052,23 +27247,14 @@
         <v>13</v>
       </c>
       <c r="B164">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C164">
-        <v>8</v>
-      </c>
-      <c r="D164">
-        <v>16000000</v>
-      </c>
-      <c r="F164">
-        <v>16000000</v>
-      </c>
-      <c r="H164">
-        <v>16000000</v>
+        <v>5</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -27076,23 +27262,14 @@
         <v>13</v>
       </c>
       <c r="B165">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C165">
-        <v>9</v>
-      </c>
-      <c r="D165">
-        <v>12000000</v>
-      </c>
-      <c r="F165">
-        <v>12000000</v>
-      </c>
-      <c r="H165">
-        <v>12000000</v>
+        <v>6</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -27100,17 +27277,17 @@
         <v>13</v>
       </c>
       <c r="B166">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="C166">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D166">
-        <v>19000000</v>
+        <v>11500000</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -27118,68 +27295,89 @@
         <v>13</v>
       </c>
       <c r="B167">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="C167">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D167">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="F167">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="H167">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B168">
-        <v>317</v>
+        <v>55</v>
       </c>
       <c r="C168">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="D168">
+        <v>12000000</v>
+      </c>
+      <c r="F168">
+        <v>12000000</v>
+      </c>
+      <c r="H168">
+        <v>12000000</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B169">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="C169">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="D169">
+        <v>19000000</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B170">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C170">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D170">
+        <v>6000000</v>
+      </c>
+      <c r="F170">
+        <v>6000000</v>
+      </c>
+      <c r="H170">
+        <v>6000000</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -27187,14 +27385,14 @@
         <v>14</v>
       </c>
       <c r="B171">
-        <v>90</v>
+        <v>317</v>
       </c>
       <c r="C171">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -27202,17 +27400,14 @@
         <v>14</v>
       </c>
       <c r="B172">
-        <v>24</v>
+        <v>299</v>
       </c>
       <c r="C172">
-        <v>5</v>
-      </c>
-      <c r="D172">
-        <v>1000000</v>
+        <v>2</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -27220,17 +27415,14 @@
         <v>14</v>
       </c>
       <c r="B173">
-        <v>238</v>
+        <v>129</v>
       </c>
       <c r="C173">
-        <v>6</v>
-      </c>
-      <c r="D173">
-        <v>3000000</v>
+        <v>3</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -27238,23 +27430,14 @@
         <v>14</v>
       </c>
       <c r="B174">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C174">
-        <v>7</v>
-      </c>
-      <c r="D174">
-        <v>20500000</v>
-      </c>
-      <c r="F174">
-        <v>20500000</v>
-      </c>
-      <c r="H174">
-        <v>20500000</v>
+        <v>4</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -27262,17 +27445,17 @@
         <v>14</v>
       </c>
       <c r="B175">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="C175">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D175">
-        <v>19500000</v>
+        <v>1000000</v>
       </c>
       <c r="L175" t="str">
         <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -27280,29 +27463,17 @@
         <v>14</v>
       </c>
       <c r="B176">
-        <v>61</v>
+        <v>238</v>
       </c>
       <c r="C176">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D176">
-        <v>9500000</v>
-      </c>
-      <c r="F176">
-        <v>10500000</v>
-      </c>
-      <c r="G176" t="s">
-        <v>571</v>
-      </c>
-      <c r="H176">
-        <v>11500000</v>
-      </c>
-      <c r="I176" t="s">
-        <v>571</v>
+        <v>3000000</v>
       </c>
       <c r="L176" t="str">
         <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -27310,14 +27481,23 @@
         <v>14</v>
       </c>
       <c r="B177">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C177">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D177">
+        <v>20500000</v>
+      </c>
+      <c r="F177">
+        <v>20500000</v>
+      </c>
+      <c r="H177">
+        <v>20500000</v>
       </c>
       <c r="L177" t="str">
         <f>VLOOKUP(B177,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -27325,14 +27505,17 @@
         <v>14</v>
       </c>
       <c r="B178">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="C178">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="D178">
+        <v>19500000</v>
       </c>
       <c r="L178" t="str">
         <f>VLOOKUP(B178,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -27340,23 +27523,29 @@
         <v>14</v>
       </c>
       <c r="B179">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="C179">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D179">
-        <v>20000000</v>
+        <v>9500000</v>
       </c>
       <c r="F179">
-        <v>20000000</v>
+        <v>10500000</v>
+      </c>
+      <c r="G179" t="s">
+        <v>571</v>
       </c>
       <c r="H179">
-        <v>20000000</v>
+        <v>11500000</v>
+      </c>
+      <c r="I179" t="s">
+        <v>571</v>
       </c>
       <c r="L179" t="str">
         <f>VLOOKUP(B179,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -27364,20 +27553,107 @@
         <v>14</v>
       </c>
       <c r="B180">
-        <v>273</v>
+        <v>2</v>
       </c>
       <c r="C180">
-        <v>13</v>
-      </c>
-      <c r="D180">
-        <v>3200000</v>
-      </c>
-      <c r="F180">
-        <v>3500000</v>
+        <v>10</v>
       </c>
       <c r="L180" t="str">
         <f>VLOOKUP(B180,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>14</v>
+      </c>
+      <c r="B181">
+        <v>220</v>
+      </c>
+      <c r="C181">
+        <v>11</v>
+      </c>
+      <c r="L181" t="str">
+        <f>VLOOKUP(B181,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>14</v>
+      </c>
+      <c r="B182">
+        <v>145</v>
+      </c>
+      <c r="C182">
+        <v>12</v>
+      </c>
+      <c r="D182">
+        <v>20000000</v>
+      </c>
+      <c r="F182">
+        <v>20000000</v>
+      </c>
+      <c r="H182">
+        <v>20000000</v>
+      </c>
+      <c r="L182" t="str">
+        <f>VLOOKUP(B182,players!A:B,2)</f>
+        <v>LaMelo Ball</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>14</v>
+      </c>
+      <c r="B183">
+        <v>273</v>
+      </c>
+      <c r="C183">
+        <v>13</v>
+      </c>
+      <c r="D183">
+        <v>3200000</v>
+      </c>
+      <c r="F183">
+        <v>3500000</v>
+      </c>
+      <c r="L183" t="str">
+        <f>VLOOKUP(B183,players!A:B,2)</f>
         <v>Cason Wallace</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>14</v>
+      </c>
+      <c r="B184">
+        <v>426</v>
+      </c>
+      <c r="C184">
+        <v>14</v>
+      </c>
+      <c r="D184">
+        <v>3400000</v>
+      </c>
+      <c r="F184">
+        <v>3600000</v>
+      </c>
+      <c r="H184">
+        <v>3800000</v>
+      </c>
+      <c r="I184" t="s">
+        <v>571</v>
+      </c>
+      <c r="J184">
+        <v>4100000</v>
+      </c>
+      <c r="K184" t="s">
+        <v>571</v>
+      </c>
+      <c r="L184" t="str">
+        <f>VLOOKUP(B184,players!A:B,2)</f>
+        <v>Morez Johnson Jr.</v>
       </c>
     </row>
   </sheetData>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="11_1C3098EE5E7872337143A0BEC13924F4E4C08868" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD5950F-F7EF-43C9-858B-CF72F6F39398}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="11_1C3098EE5E7872337143A0BEC13924F4E4C08868" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7122C541-0865-4B33-9D99-4CAEE4D1A75B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -2855,7 +2855,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E7" s="1">
         <v>15.8</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E15" s="1">
         <v>22.5</v>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E56" s="1">
         <v>24.2</v>
@@ -4662,7 +4662,7 @@
         <v>93</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E63" s="1">
         <v>14</v>
@@ -4694,7 +4694,7 @@
         <v>94</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E64" s="1">
         <v>10.199999999999999</v>
@@ -4983,7 +4983,7 @@
         <v>104</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E73" s="1">
         <v>13.6</v>
@@ -6531,7 +6531,7 @@
         <v>153</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E121" s="1">
         <v>13.8</v>
@@ -8942,7 +8942,7 @@
         <v>228</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="E196" s="1">
         <v>17</v>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="C212" s="1"/>
       <c r="D212" s="1" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="E212" s="1">
         <v>23.6</v>
@@ -10675,7 +10675,7 @@
         <v>282</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E250" s="1">
         <v>13.6</v>
@@ -12532,7 +12532,7 @@
         <v>340</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="E308" s="1">
         <v>9.3000000000000007</v>
@@ -12916,7 +12916,7 @@
         <v>352</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="E320" s="1">
         <v>11.7</v>
@@ -14997,7 +14997,7 @@
         <v>417</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="E385" s="1">
         <v>13.5</v>
@@ -24908,7 +24908,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:L192"/>
+  <dimension ref="A1:L193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -25245,26 +25245,17 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B17">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>3100000</v>
-      </c>
-      <c r="F17">
-        <v>3100000</v>
-      </c>
-      <c r="H17">
-        <v>3100000</v>
+        <v>16</v>
       </c>
       <c r="L17" t="str">
         <f>VLOOKUP(B17,players!A:B,2)</f>
-        <v>Jaden Ivey</v>
+        <v>RJ Barrett</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -25272,14 +25263,23 @@
         <v>1</v>
       </c>
       <c r="B18">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>3100000</v>
+      </c>
+      <c r="F18">
+        <v>3100000</v>
+      </c>
+      <c r="H18">
+        <v>3100000</v>
       </c>
       <c r="L18" t="str">
         <f>VLOOKUP(B18,players!A:B,2)</f>
-        <v>Bogdan Bogdanović</v>
+        <v>Jaden Ivey</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -25287,29 +25287,14 @@
         <v>1</v>
       </c>
       <c r="B19">
-        <v>172</v>
+        <v>314</v>
       </c>
       <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19">
-        <v>7500000</v>
-      </c>
-      <c r="F19">
-        <v>8500000</v>
-      </c>
-      <c r="G19" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19">
-        <v>9000000</v>
-      </c>
-      <c r="I19" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L19" t="str">
         <f>VLOOKUP(B19,players!A:B,2)</f>
-        <v>Ace Bailey</v>
+        <v>Bogdan Bogdanović</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -25317,14 +25302,29 @@
         <v>1</v>
       </c>
       <c r="B20">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>7500000</v>
+      </c>
+      <c r="F20">
+        <v>8500000</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>9000000</v>
+      </c>
+      <c r="I20" t="s">
+        <v>12</v>
       </c>
       <c r="L20" t="str">
         <f>VLOOKUP(B20,players!A:B,2)</f>
-        <v>Andrew Wiggins</v>
+        <v>Ace Bailey</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -25332,14 +25332,14 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21" t="str">
         <f>VLOOKUP(B21,players!A:B,2)</f>
-        <v>Noah Clowney</v>
+        <v>Andrew Wiggins</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -25347,29 +25347,14 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>355</v>
+        <v>180</v>
       </c>
       <c r="C22">
-        <v>6</v>
-      </c>
-      <c r="D22">
-        <v>1000000</v>
-      </c>
-      <c r="F22">
-        <v>1000000</v>
-      </c>
-      <c r="G22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22">
-        <v>1000000</v>
-      </c>
-      <c r="I22" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L22" t="str">
         <f>VLOOKUP(B22,players!A:B,2)</f>
-        <v>Asa Newell</v>
+        <v>Noah Clowney</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -25377,14 +25362,29 @@
         <v>1</v>
       </c>
       <c r="B23">
-        <v>39</v>
+        <v>355</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>1000000</v>
+      </c>
+      <c r="F23">
+        <v>1000000</v>
+      </c>
+      <c r="G23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23">
+        <v>1000000</v>
+      </c>
+      <c r="I23" t="s">
+        <v>12</v>
       </c>
       <c r="L23" t="str">
         <f>VLOOKUP(B23,players!A:B,2)</f>
-        <v>Onyeka Okongwu</v>
+        <v>Asa Newell</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -25392,23 +25392,14 @@
         <v>1</v>
       </c>
       <c r="B24">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="C24">
-        <v>8</v>
-      </c>
-      <c r="D24">
-        <v>4200000</v>
-      </c>
-      <c r="F24">
-        <v>4500000</v>
-      </c>
-      <c r="G24" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L24" t="str">
         <f>VLOOKUP(B24,players!A:B,2)</f>
-        <v>Matas Buzelis</v>
+        <v>Onyeka Okongwu</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -25416,23 +25407,23 @@
         <v>1</v>
       </c>
       <c r="B25">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25">
-        <v>40000000</v>
+        <v>4200000</v>
       </c>
       <c r="F25">
-        <v>40000000</v>
-      </c>
-      <c r="H25">
-        <v>40000000</v>
+        <v>4500000</v>
+      </c>
+      <c r="G25" t="s">
+        <v>12</v>
       </c>
       <c r="L25" t="str">
         <f>VLOOKUP(B25,players!A:B,2)</f>
-        <v>Anthony Edwards</v>
+        <v>Matas Buzelis</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -25440,23 +25431,23 @@
         <v>1</v>
       </c>
       <c r="B26">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26">
-        <v>30500000</v>
+        <v>40000000</v>
       </c>
       <c r="F26">
-        <v>30500000</v>
+        <v>40000000</v>
       </c>
       <c r="H26">
-        <v>30500000</v>
+        <v>40000000</v>
       </c>
       <c r="L26" t="str">
         <f>VLOOKUP(B26,players!A:B,2)</f>
-        <v>Tyrese Maxey</v>
+        <v>Anthony Edwards</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -25464,17 +25455,23 @@
         <v>1</v>
       </c>
       <c r="B27">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>1000000</v>
+        <v>30500000</v>
+      </c>
+      <c r="F27">
+        <v>30500000</v>
+      </c>
+      <c r="H27">
+        <v>30500000</v>
       </c>
       <c r="L27" t="str">
         <f>VLOOKUP(B27,players!A:B,2)</f>
-        <v>Donte DiVincenzo</v>
+        <v>Tyrese Maxey</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -25482,17 +25479,17 @@
         <v>1</v>
       </c>
       <c r="B28">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="L28" t="str">
         <f>VLOOKUP(B28,players!A:B,2)</f>
-        <v>Mikal Bridges</v>
+        <v>Donte DiVincenzo</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -25500,14 +25497,17 @@
         <v>1</v>
       </c>
       <c r="B29">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="D29">
+        <v>7000000</v>
       </c>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
-        <v>Jay Huff</v>
+        <v>Mikal Bridges</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -25515,98 +25515,80 @@
         <v>1</v>
       </c>
       <c r="B30">
-        <v>432</v>
+        <v>187</v>
       </c>
       <c r="C30">
-        <v>14</v>
-      </c>
-      <c r="D30">
-        <v>1000000</v>
-      </c>
-      <c r="F30">
-        <v>1000000</v>
-      </c>
-      <c r="H30">
-        <v>1000000</v>
-      </c>
-      <c r="I30" t="s">
-        <v>12</v>
-      </c>
-      <c r="J30">
-        <v>1000000</v>
-      </c>
-      <c r="K30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Dailyn Swain</v>
+        <v>Jay Huff</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B31">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="C31">
         <v>14</v>
       </c>
       <c r="D31">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="F31">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="H31">
-        <v>8250000</v>
+        <v>1000000</v>
       </c>
       <c r="I31" t="s">
         <v>12</v>
       </c>
       <c r="J31">
-        <v>9000000</v>
+        <v>1000000</v>
       </c>
       <c r="K31" t="s">
         <v>12</v>
       </c>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Cameron Boozer</v>
+        <v>Dailyn Swain</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B32">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D32">
-        <v>3800000</v>
+        <v>7000000</v>
       </c>
       <c r="F32">
-        <v>4000000</v>
+        <v>7500000</v>
       </c>
       <c r="H32">
-        <v>4200000</v>
+        <v>8250000</v>
       </c>
       <c r="I32" t="s">
         <v>12</v>
       </c>
       <c r="J32">
-        <v>4500000</v>
+        <v>9000000</v>
       </c>
       <c r="K32" t="s">
         <v>12</v>
       </c>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
-        <v>Hannes Steinbach</v>
+        <v>Cameron Boozer</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -25614,56 +25596,65 @@
         <v>1</v>
       </c>
       <c r="B33">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C33">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33">
-        <v>3600000</v>
+        <v>3800000</v>
       </c>
       <c r="F33">
-        <v>3800000</v>
+        <v>4000000</v>
       </c>
       <c r="H33">
-        <v>4000000</v>
+        <v>4200000</v>
       </c>
       <c r="I33" t="s">
         <v>12</v>
       </c>
       <c r="J33">
-        <v>4300000</v>
+        <v>4500000</v>
       </c>
       <c r="K33" t="s">
         <v>12</v>
       </c>
       <c r="L33" t="str">
         <f>VLOOKUP(B33,players!A:B,2)</f>
-        <v>Keaton Wagler</v>
+        <v>Hannes Steinbach</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34">
-        <v>320</v>
+        <v>425</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D34">
-        <v>1000000</v>
+        <v>3600000</v>
       </c>
       <c r="F34">
-        <v>1000000</v>
-      </c>
-      <c r="G34" t="s">
+        <v>3800000</v>
+      </c>
+      <c r="H34">
+        <v>4000000</v>
+      </c>
+      <c r="I34" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34">
+        <v>4300000</v>
+      </c>
+      <c r="K34" t="s">
         <v>12</v>
       </c>
       <c r="L34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
-        <v>Cam Spencer</v>
+        <v>Keaton Wagler</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -25671,23 +25662,23 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>23500000</v>
+        <v>1000000</v>
       </c>
       <c r="F35">
-        <v>23500000</v>
-      </c>
-      <c r="H35">
-        <v>23500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G35" t="s">
+        <v>12</v>
       </c>
       <c r="L35" t="str">
         <f>VLOOKUP(B35,players!A:B,2)</f>
-        <v>Alperen Şengün</v>
+        <v>Cam Spencer</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -25695,17 +25686,23 @@
         <v>2</v>
       </c>
       <c r="B36">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>15000000</v>
+        <v>23500000</v>
+      </c>
+      <c r="F36">
+        <v>23500000</v>
+      </c>
+      <c r="H36">
+        <v>23500000</v>
       </c>
       <c r="L36" t="str">
         <f>VLOOKUP(B36,players!A:B,2)</f>
-        <v>Kevin Durant</v>
+        <v>Alperen Şengün</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -25713,17 +25710,17 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>9000000</v>
+        <v>15000000</v>
       </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>Brandon Miller</v>
+        <v>Kevin Durant</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -25731,23 +25728,17 @@
         <v>2</v>
       </c>
       <c r="B38">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>7000000</v>
-      </c>
-      <c r="F38">
-        <v>7000000</v>
-      </c>
-      <c r="H38">
-        <v>7000000</v>
+        <v>9000000</v>
       </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>Jalen Green</v>
+        <v>Brandon Miller</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -25755,20 +25746,23 @@
         <v>2</v>
       </c>
       <c r="B39">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
       <c r="F39">
-        <v>6000000</v>
+        <v>7000000</v>
+      </c>
+      <c r="H39">
+        <v>7000000</v>
       </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Tyler Herro</v>
+        <v>Jalen Green</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -25776,23 +25770,20 @@
         <v>2</v>
       </c>
       <c r="B40">
-        <v>362</v>
+        <v>144</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="F40">
-        <v>21500000</v>
-      </c>
-      <c r="H40">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Trae Young</v>
+        <v>Tyler Herro</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -25800,14 +25791,23 @@
         <v>2</v>
       </c>
       <c r="B41">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D41">
+        <v>21500000</v>
+      </c>
+      <c r="F41">
+        <v>21500000</v>
+      </c>
+      <c r="H41">
+        <v>21500000</v>
       </c>
       <c r="L41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Russell Westbrook</v>
+        <v>Trae Young</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -25815,23 +25815,14 @@
         <v>2</v>
       </c>
       <c r="B42">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C42">
-        <v>10</v>
-      </c>
-      <c r="D42">
-        <v>3100000</v>
-      </c>
-      <c r="F42">
-        <v>3100000</v>
-      </c>
-      <c r="H42">
-        <v>3100000</v>
+        <v>8</v>
       </c>
       <c r="L42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Bobby Portis</v>
+        <v>Russell Westbrook</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -25839,50 +25830,53 @@
         <v>2</v>
       </c>
       <c r="B43">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D43">
-        <v>3200000</v>
+        <v>3100000</v>
       </c>
       <c r="F43">
-        <v>3400000</v>
-      </c>
-      <c r="G43" t="s">
-        <v>12</v>
+        <v>3100000</v>
       </c>
       <c r="H43">
-        <v>3700000</v>
-      </c>
-      <c r="I43" t="s">
-        <v>12</v>
+        <v>3100000</v>
       </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>Derik Queen</v>
+        <v>Bobby Portis</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D44">
-        <v>8000000</v>
+        <v>3200000</v>
       </c>
       <c r="F44">
-        <v>8000000</v>
+        <v>3400000</v>
+      </c>
+      <c r="G44" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44">
+        <v>3700000</v>
+      </c>
+      <c r="I44" t="s">
+        <v>12</v>
       </c>
       <c r="L44" t="str">
         <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>Immanuel Quickley</v>
+        <v>Derik Queen</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -25890,14 +25884,20 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>8000000</v>
+      </c>
+      <c r="F45">
+        <v>8000000</v>
       </c>
       <c r="L45" t="str">
         <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>Nickeil Alexander-Walker</v>
+        <v>Immanuel Quickley</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -25905,14 +25905,14 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L46" t="str">
         <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>Kyshawn George</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -25920,17 +25920,14 @@
         <v>3</v>
       </c>
       <c r="B47">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="C47">
-        <v>4</v>
-      </c>
-      <c r="D47">
-        <v>5000000</v>
+        <v>3</v>
       </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>Cameron Johnson</v>
+        <v>Kyshawn George</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -25938,14 +25935,17 @@
         <v>3</v>
       </c>
       <c r="B48">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>5000000</v>
       </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>Myles Turner</v>
+        <v>Cameron Johnson</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -25953,14 +25953,14 @@
         <v>3</v>
       </c>
       <c r="B49">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>Mitchell Robinson</v>
+        <v>Myles Turner</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -25968,14 +25968,14 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>Jalen Duren</v>
+        <v>Mitchell Robinson</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -25983,23 +25983,14 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C51">
-        <v>8</v>
-      </c>
-      <c r="D51">
-        <v>40000000</v>
-      </c>
-      <c r="F51">
-        <v>40000000</v>
-      </c>
-      <c r="H51">
-        <v>40000000</v>
+        <v>7</v>
       </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>Luka Dončić</v>
+        <v>Jalen Duren</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -26007,17 +25998,23 @@
         <v>3</v>
       </c>
       <c r="B52">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C52">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52">
-        <v>6000000</v>
+        <v>40000000</v>
+      </c>
+      <c r="F52">
+        <v>40000000</v>
+      </c>
+      <c r="H52">
+        <v>40000000</v>
       </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Kawhi Leonard</v>
+        <v>Luka Dončić</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -26025,20 +26022,17 @@
         <v>3</v>
       </c>
       <c r="B53">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D53">
-        <v>14000000</v>
-      </c>
-      <c r="F53">
-        <v>14000000</v>
+        <v>6000000</v>
       </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>Jaren Jackson Jr.</v>
+        <v>Kawhi Leonard</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -26046,23 +26040,20 @@
         <v>3</v>
       </c>
       <c r="B54">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C54">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D54">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="F54">
-        <v>6500000</v>
-      </c>
-      <c r="H54">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>OG Anunoby</v>
+        <v>Jaren Jackson Jr.</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -26070,17 +26061,23 @@
         <v>3</v>
       </c>
       <c r="B55">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C55">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D55">
-        <v>5000000</v>
+        <v>6500000</v>
+      </c>
+      <c r="F55">
+        <v>6500000</v>
+      </c>
+      <c r="H55">
+        <v>6500000</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Kyrie Irving</v>
+        <v>OG Anunoby</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -26088,17 +26085,17 @@
         <v>3</v>
       </c>
       <c r="B56">
-        <v>295</v>
+        <v>142</v>
       </c>
       <c r="C56">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D56">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Zach LaVine</v>
+        <v>Kyrie Irving</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -26106,62 +26103,50 @@
         <v>3</v>
       </c>
       <c r="B57">
-        <v>427</v>
+        <v>295</v>
       </c>
       <c r="C57">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D57">
-        <v>3200000</v>
-      </c>
-      <c r="F57">
-        <v>3400000</v>
-      </c>
-      <c r="H57">
-        <v>3600000</v>
-      </c>
-      <c r="I57" t="s">
-        <v>12</v>
-      </c>
-      <c r="J57">
-        <v>3900000</v>
-      </c>
-      <c r="K57" t="s">
-        <v>12</v>
+        <v>8000000</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Brayden Burries</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B58">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D58">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="F58">
-        <v>1000000</v>
-      </c>
-      <c r="G58" t="s">
-        <v>12</v>
+        <v>3400000</v>
       </c>
       <c r="H58">
-        <v>1000000</v>
+        <v>3600000</v>
       </c>
       <c r="I58" t="s">
         <v>12</v>
       </c>
+      <c r="J58">
+        <v>3900000</v>
+      </c>
+      <c r="K58" t="s">
+        <v>12</v>
+      </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>Brayden Burries</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -26169,10 +26154,10 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59">
         <v>1000000</v>
@@ -26183,9 +26168,15 @@
       <c r="G59" t="s">
         <v>12</v>
       </c>
+      <c r="H59">
+        <v>1000000</v>
+      </c>
+      <c r="I59" t="s">
+        <v>12</v>
+      </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -26193,14 +26184,23 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="C60">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>1000000</v>
+      </c>
+      <c r="F60">
+        <v>1000000</v>
+      </c>
+      <c r="G60" t="s">
+        <v>12</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -26208,17 +26208,14 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C61">
-        <v>4</v>
-      </c>
-      <c r="D61">
-        <v>2500000</v>
+        <v>3</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -26226,17 +26223,17 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D62">
-        <v>11000000</v>
+        <v>2500000</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -26244,20 +26241,17 @@
         <v>4</v>
       </c>
       <c r="B63">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D63">
-        <v>5000000</v>
-      </c>
-      <c r="F63">
-        <v>5000000</v>
+        <v>11000000</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -26265,20 +26259,20 @@
         <v>4</v>
       </c>
       <c r="B64">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D64">
-        <v>17000000</v>
+        <v>5000000</v>
       </c>
       <c r="F64">
-        <v>17000000</v>
+        <v>5000000</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -26286,17 +26280,20 @@
         <v>4</v>
       </c>
       <c r="B65">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C65">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65">
-        <v>22500000</v>
+        <v>17000000</v>
+      </c>
+      <c r="F65">
+        <v>17000000</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -26304,23 +26301,17 @@
         <v>4</v>
       </c>
       <c r="B66">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C66">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D66">
-        <v>5000000</v>
-      </c>
-      <c r="F66">
-        <v>5500000</v>
-      </c>
-      <c r="G66" t="s">
-        <v>12</v>
+        <v>22500000</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -26328,23 +26319,23 @@
         <v>4</v>
       </c>
       <c r="B67">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C67">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D67">
-        <v>15000000</v>
+        <v>5000000</v>
       </c>
       <c r="F67">
-        <v>15000000</v>
-      </c>
-      <c r="H67">
-        <v>15000000</v>
+        <v>5500000</v>
+      </c>
+      <c r="G67" t="s">
+        <v>12</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -26352,23 +26343,23 @@
         <v>4</v>
       </c>
       <c r="B68">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="C68">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D68">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="F68">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="H68">
-        <v>19000000</v>
+        <v>15000000</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -26376,17 +26367,23 @@
         <v>4</v>
       </c>
       <c r="B69">
-        <v>287</v>
+        <v>157</v>
       </c>
       <c r="C69">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D69">
-        <v>10000000</v>
+        <v>19000000</v>
+      </c>
+      <c r="F69">
+        <v>19000000</v>
+      </c>
+      <c r="H69">
+        <v>19000000</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -26394,47 +26391,50 @@
         <v>4</v>
       </c>
       <c r="B70">
-        <v>422</v>
+        <v>287</v>
       </c>
       <c r="C70">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D70">
-        <v>4500000</v>
-      </c>
-      <c r="F70">
-        <v>5000000</v>
-      </c>
-      <c r="H70">
-        <v>5500000</v>
-      </c>
-      <c r="I70" t="s">
-        <v>12</v>
-      </c>
-      <c r="J70">
-        <v>6000000</v>
-      </c>
-      <c r="K70" t="s">
-        <v>12</v>
+        <v>10000000</v>
       </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Kingston Flemings</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B71">
-        <v>305</v>
+        <v>422</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D71">
+        <v>4500000</v>
+      </c>
+      <c r="F71">
+        <v>5000000</v>
+      </c>
+      <c r="H71">
+        <v>5500000</v>
+      </c>
+      <c r="I71" t="s">
+        <v>12</v>
+      </c>
+      <c r="J71">
+        <v>6000000</v>
+      </c>
+      <c r="K71" t="s">
+        <v>12</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>Kingston Flemings</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -26442,29 +26442,14 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="C72">
-        <v>2</v>
-      </c>
-      <c r="D72">
-        <v>3600000</v>
-      </c>
-      <c r="F72">
-        <v>3800000</v>
-      </c>
-      <c r="G72" t="s">
-        <v>12</v>
-      </c>
-      <c r="H72">
-        <v>4100000</v>
-      </c>
-      <c r="I72" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -26472,14 +26457,29 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D73">
+        <v>3600000</v>
+      </c>
+      <c r="F73">
+        <v>3800000</v>
+      </c>
+      <c r="G73" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73">
+        <v>4100000</v>
+      </c>
+      <c r="I73" t="s">
+        <v>12</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -26487,20 +26487,14 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="C74">
-        <v>4</v>
-      </c>
-      <c r="D74">
-        <v>21000000</v>
-      </c>
-      <c r="F74">
-        <v>21000000</v>
+        <v>3</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -26508,14 +26502,20 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D75">
+        <v>21000000</v>
+      </c>
+      <c r="F75">
+        <v>21000000</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -26523,29 +26523,14 @@
         <v>5</v>
       </c>
       <c r="B76">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C76">
-        <v>6</v>
-      </c>
-      <c r="D76">
-        <v>1000000</v>
-      </c>
-      <c r="F76">
-        <v>1000000</v>
-      </c>
-      <c r="G76" t="s">
-        <v>12</v>
-      </c>
-      <c r="H76">
-        <v>1000000</v>
-      </c>
-      <c r="I76" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Danny Wolf</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -26553,20 +26538,29 @@
         <v>5</v>
       </c>
       <c r="B77">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D77">
-        <v>17000000</v>
+        <v>1000000</v>
       </c>
       <c r="F77">
-        <v>17000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G77" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77">
+        <v>1000000</v>
+      </c>
+      <c r="I77" t="s">
+        <v>12</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>Danny Wolf</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -26574,23 +26568,20 @@
         <v>5</v>
       </c>
       <c r="B78">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C78">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D78">
-        <v>40000000</v>
+        <v>17000000</v>
       </c>
       <c r="F78">
-        <v>40000000</v>
-      </c>
-      <c r="H78">
-        <v>40000000</v>
+        <v>17000000</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -26598,20 +26589,23 @@
         <v>5</v>
       </c>
       <c r="B79">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="C79">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D79">
-        <v>3100000</v>
+        <v>40000000</v>
       </c>
       <c r="F79">
-        <v>3100000</v>
+        <v>40000000</v>
+      </c>
+      <c r="H79">
+        <v>40000000</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -26619,14 +26613,20 @@
         <v>5</v>
       </c>
       <c r="B80">
-        <v>227</v>
+        <v>72</v>
       </c>
       <c r="C80">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D80">
+        <v>3100000</v>
+      </c>
+      <c r="F80">
+        <v>3100000</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>Jerami Grant</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -26634,14 +26634,14 @@
         <v>5</v>
       </c>
       <c r="B81">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="C81">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -26649,14 +26649,14 @@
         <v>5</v>
       </c>
       <c r="B82">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="C82">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Royce O'Neale</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -26664,14 +26664,14 @@
         <v>5</v>
       </c>
       <c r="B83">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C83">
         <v>12</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Ryan Rollins</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -26679,32 +26679,14 @@
         <v>5</v>
       </c>
       <c r="B84">
-        <v>418</v>
+        <v>152</v>
       </c>
       <c r="C84">
-        <v>13</v>
-      </c>
-      <c r="D84">
-        <v>8000000</v>
-      </c>
-      <c r="F84">
-        <v>8500000</v>
-      </c>
-      <c r="H84">
-        <v>9250000</v>
-      </c>
-      <c r="I84" t="s">
-        <v>12</v>
-      </c>
-      <c r="J84">
-        <v>10000000</v>
-      </c>
-      <c r="K84" t="s">
         <v>12</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>Caleb Wilson</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -26712,53 +26694,65 @@
         <v>5</v>
       </c>
       <c r="B85">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D85">
-        <v>2800000</v>
+        <v>8000000</v>
       </c>
       <c r="F85">
-        <v>3000000</v>
+        <v>8500000</v>
       </c>
       <c r="H85">
-        <v>3200000</v>
+        <v>9250000</v>
       </c>
       <c r="I85" t="s">
         <v>12</v>
       </c>
       <c r="J85">
-        <v>3500000</v>
+        <v>10000000</v>
       </c>
       <c r="K85" t="s">
         <v>12</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Yaxel Lendeborg</v>
+        <v>Caleb Wilson</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B86">
-        <v>162</v>
+        <v>429</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D86">
-        <v>6000000</v>
+        <v>2800000</v>
       </c>
       <c r="F86">
-        <v>6000000</v>
+        <v>3000000</v>
+      </c>
+      <c r="H86">
+        <v>3200000</v>
+      </c>
+      <c r="I86" t="s">
+        <v>12</v>
+      </c>
+      <c r="J86">
+        <v>3500000</v>
+      </c>
+      <c r="K86" t="s">
+        <v>12</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Yaxel Lendeborg</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -26766,17 +26760,20 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>338</v>
+        <v>162</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>1000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="F87">
+        <v>6000000</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -26784,14 +26781,17 @@
         <v>6</v>
       </c>
       <c r="B88">
-        <v>45</v>
+        <v>338</v>
       </c>
       <c r="C88">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D88">
+        <v>1000000</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -26799,14 +26799,14 @@
         <v>6</v>
       </c>
       <c r="B89">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="C89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -26814,14 +26814,14 @@
         <v>6</v>
       </c>
       <c r="B90">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -26829,14 +26829,14 @@
         <v>6</v>
       </c>
       <c r="B91">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="C91">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -26844,17 +26844,14 @@
         <v>6</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C92">
-        <v>7</v>
-      </c>
-      <c r="D92">
-        <v>20000000</v>
+        <v>6</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -26862,14 +26859,17 @@
         <v>6</v>
       </c>
       <c r="B93">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D93">
+        <v>20000000</v>
       </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -26877,17 +26877,14 @@
         <v>6</v>
       </c>
       <c r="B94">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C94">
-        <v>9</v>
-      </c>
-      <c r="D94">
-        <v>7000000</v>
+        <v>8</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -26895,20 +26892,17 @@
         <v>6</v>
       </c>
       <c r="B95">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C95">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D95">
-        <v>35000000</v>
-      </c>
-      <c r="F95">
-        <v>35000000</v>
+        <v>7000000</v>
       </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -26916,20 +26910,20 @@
         <v>6</v>
       </c>
       <c r="B96">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="C96">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D96">
-        <v>3100000</v>
+        <v>35000000</v>
       </c>
       <c r="F96">
-        <v>3100000</v>
+        <v>35000000</v>
       </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -26937,17 +26931,20 @@
         <v>6</v>
       </c>
       <c r="B97">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="C97">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D97">
-        <v>1000000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F97">
+        <v>3100000</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -26955,14 +26952,17 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="C98">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="D98">
+        <v>1000000</v>
       </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>Damian Lillard</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -26970,20 +26970,14 @@
         <v>6</v>
       </c>
       <c r="B99">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="C99">
-        <v>14</v>
-      </c>
-      <c r="D99">
-        <v>6000000</v>
-      </c>
-      <c r="F99">
-        <v>6000000</v>
+        <v>13</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -26991,71 +26985,68 @@
         <v>6</v>
       </c>
       <c r="B100">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C100">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="D100">
+        <v>6000000</v>
+      </c>
+      <c r="F100">
+        <v>6000000</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Tari Eason</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B101">
-        <v>420</v>
+        <v>71</v>
       </c>
       <c r="C101">
-        <v>13</v>
-      </c>
-      <c r="D101">
-        <v>6000000</v>
-      </c>
-      <c r="F101">
-        <v>6500000</v>
-      </c>
-      <c r="H101">
-        <v>7000000</v>
-      </c>
-      <c r="I101" t="s">
-        <v>12</v>
-      </c>
-      <c r="J101">
-        <v>7500000</v>
-      </c>
-      <c r="K101" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Darryn Peterson</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B102">
-        <v>242</v>
+        <v>420</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D102">
-        <v>3800000</v>
+        <v>6000000</v>
       </c>
       <c r="F102">
-        <v>4100000</v>
-      </c>
-      <c r="G102" t="s">
+        <v>6500000</v>
+      </c>
+      <c r="H102">
+        <v>7000000</v>
+      </c>
+      <c r="I102" t="s">
+        <v>12</v>
+      </c>
+      <c r="J102">
+        <v>7500000</v>
+      </c>
+      <c r="K102" t="s">
         <v>12</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Darryn Peterson</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -27063,14 +27054,23 @@
         <v>8</v>
       </c>
       <c r="B103">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>3800000</v>
+      </c>
+      <c r="F103">
+        <v>4100000</v>
+      </c>
+      <c r="G103" t="s">
+        <v>12</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -27078,29 +27078,14 @@
         <v>8</v>
       </c>
       <c r="B104">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="C104">
-        <v>3</v>
-      </c>
-      <c r="D104">
-        <v>1000000</v>
-      </c>
-      <c r="F104">
-        <v>1000000</v>
-      </c>
-      <c r="G104" t="s">
-        <v>12</v>
-      </c>
-      <c r="H104">
-        <v>1000000</v>
-      </c>
-      <c r="I104" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -27108,17 +27093,29 @@
         <v>8</v>
       </c>
       <c r="B105">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D105">
-        <v>2000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F105">
+        <v>1000000</v>
+      </c>
+      <c r="G105" t="s">
+        <v>12</v>
+      </c>
+      <c r="H105">
+        <v>1000000</v>
+      </c>
+      <c r="I105" t="s">
+        <v>12</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -27126,23 +27123,17 @@
         <v>8</v>
       </c>
       <c r="B106">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="C106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D106">
-        <v>6000000</v>
-      </c>
-      <c r="F106">
-        <v>6000000</v>
-      </c>
-      <c r="H106">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -27150,23 +27141,23 @@
         <v>8</v>
       </c>
       <c r="B107">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="C107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
       <c r="F107">
-        <v>7500000</v>
-      </c>
-      <c r="G107" t="s">
-        <v>12</v>
+        <v>6000000</v>
+      </c>
+      <c r="H107">
+        <v>6000000</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -27174,20 +27165,23 @@
         <v>8</v>
       </c>
       <c r="B108">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D108">
-        <v>4000000</v>
+        <v>7000000</v>
       </c>
       <c r="F108">
-        <v>4000000</v>
+        <v>7500000</v>
+      </c>
+      <c r="G108" t="s">
+        <v>12</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -27195,23 +27189,20 @@
         <v>8</v>
       </c>
       <c r="B109">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C109">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D109">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="F109">
-        <v>16000000</v>
-      </c>
-      <c r="H109">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -27219,20 +27210,23 @@
         <v>8</v>
       </c>
       <c r="B110">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="C110">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D110">
-        <v>9000000</v>
+        <v>16000000</v>
       </c>
       <c r="F110">
-        <v>9000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="H110">
+        <v>16000000</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -27240,17 +27234,20 @@
         <v>8</v>
       </c>
       <c r="B111">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C111">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D111">
-        <v>16000000</v>
+        <v>9000000</v>
+      </c>
+      <c r="F111">
+        <v>9000000</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -27258,23 +27255,17 @@
         <v>8</v>
       </c>
       <c r="B112">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="C112">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D112">
-        <v>19000000</v>
-      </c>
-      <c r="F112">
-        <v>19000000</v>
-      </c>
-      <c r="H112">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -27282,14 +27273,23 @@
         <v>8</v>
       </c>
       <c r="B113">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C113">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D113">
+        <v>19000000</v>
+      </c>
+      <c r="F113">
+        <v>19000000</v>
+      </c>
+      <c r="H113">
+        <v>19000000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -27297,14 +27297,14 @@
         <v>8</v>
       </c>
       <c r="B114">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="C114">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -27312,14 +27312,14 @@
         <v>8</v>
       </c>
       <c r="B115">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="C115">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -27327,56 +27327,47 @@
         <v>8</v>
       </c>
       <c r="B116">
-        <v>428</v>
+        <v>336</v>
       </c>
       <c r="C116">
-        <v>15</v>
-      </c>
-      <c r="D116">
-        <v>3000000</v>
-      </c>
-      <c r="F116">
-        <v>3200000</v>
-      </c>
-      <c r="H116">
-        <v>3400000</v>
-      </c>
-      <c r="I116" t="s">
-        <v>12</v>
-      </c>
-      <c r="J116">
-        <v>3700000</v>
-      </c>
-      <c r="K116" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Aday Mara</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B117">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D117">
-        <v>3100000</v>
+        <v>3000000</v>
       </c>
       <c r="F117">
-        <v>3100000</v>
+        <v>3200000</v>
       </c>
       <c r="H117">
-        <v>3100000</v>
+        <v>3400000</v>
+      </c>
+      <c r="I117" t="s">
+        <v>12</v>
+      </c>
+      <c r="J117">
+        <v>3700000</v>
+      </c>
+      <c r="K117" t="s">
+        <v>12</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Aday Mara</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -27384,14 +27375,23 @@
         <v>9</v>
       </c>
       <c r="B118">
-        <v>240</v>
+        <v>384</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D118">
+        <v>3100000</v>
+      </c>
+      <c r="F118">
+        <v>3100000</v>
+      </c>
+      <c r="H118">
+        <v>3100000</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -27399,17 +27399,14 @@
         <v>9</v>
       </c>
       <c r="B119">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="C119">
-        <v>3</v>
-      </c>
-      <c r="D119">
-        <v>4500000</v>
+        <v>2</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -27417,14 +27414,17 @@
         <v>9</v>
       </c>
       <c r="B120">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D120">
+        <v>4500000</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -27432,14 +27432,14 @@
         <v>9</v>
       </c>
       <c r="B121">
-        <v>416</v>
+        <v>251</v>
       </c>
       <c r="C121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -27447,23 +27447,14 @@
         <v>9</v>
       </c>
       <c r="B122">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="C122">
-        <v>6</v>
-      </c>
-      <c r="D122">
-        <v>3100000</v>
-      </c>
-      <c r="F122">
-        <v>3100000</v>
-      </c>
-      <c r="H122">
-        <v>3100000</v>
+        <v>5</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -27471,23 +27462,23 @@
         <v>9</v>
       </c>
       <c r="B123">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D123">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="F123">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="H123">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -27495,23 +27486,23 @@
         <v>9</v>
       </c>
       <c r="B124">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C124">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D124">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="F124">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="H124">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -27519,17 +27510,23 @@
         <v>9</v>
       </c>
       <c r="B125">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="C125">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D125">
-        <v>11500000</v>
+        <v>12500000</v>
+      </c>
+      <c r="F125">
+        <v>12500000</v>
+      </c>
+      <c r="H125">
+        <v>12500000</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -27537,23 +27534,17 @@
         <v>9</v>
       </c>
       <c r="B126">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="C126">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D126">
-        <v>3100000</v>
-      </c>
-      <c r="F126">
-        <v>3100000</v>
-      </c>
-      <c r="H126">
-        <v>3100000</v>
+        <v>11500000</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -27561,17 +27552,23 @@
         <v>9</v>
       </c>
       <c r="B127">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="C127">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D127">
-        <v>25000000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F127">
+        <v>3100000</v>
+      </c>
+      <c r="H127">
+        <v>3100000</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -27579,23 +27576,17 @@
         <v>9</v>
       </c>
       <c r="B128">
-        <v>331</v>
+        <v>217</v>
       </c>
       <c r="C128">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D128">
-        <v>12000000</v>
-      </c>
-      <c r="F128">
-        <v>12000000</v>
-      </c>
-      <c r="H128">
-        <v>12000000</v>
+        <v>25000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -27603,47 +27594,56 @@
         <v>9</v>
       </c>
       <c r="B129">
-        <v>433</v>
+        <v>331</v>
       </c>
       <c r="C129">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D129">
-        <v>1000000</v>
+        <v>12000000</v>
       </c>
       <c r="F129">
-        <v>1000000</v>
+        <v>12000000</v>
       </c>
       <c r="H129">
-        <v>1000000</v>
-      </c>
-      <c r="I129" t="s">
-        <v>12</v>
-      </c>
-      <c r="J129">
-        <v>1000000</v>
-      </c>
-      <c r="K129" t="s">
-        <v>12</v>
+        <v>12000000</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Ebuka Okorie</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B130">
-        <v>9</v>
+        <v>433</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D130">
+        <v>1000000</v>
+      </c>
+      <c r="F130">
+        <v>1000000</v>
+      </c>
+      <c r="H130">
+        <v>1000000</v>
+      </c>
+      <c r="I130" t="s">
+        <v>12</v>
+      </c>
+      <c r="J130">
+        <v>1000000</v>
+      </c>
+      <c r="K130" t="s">
+        <v>12</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Walker Kessler</v>
+        <v>Ebuka Okorie</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -27651,14 +27651,14 @@
         <v>10</v>
       </c>
       <c r="B131">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="C131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -27666,14 +27666,14 @@
         <v>10</v>
       </c>
       <c r="B132">
-        <v>249</v>
+        <v>373</v>
       </c>
       <c r="C132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -27681,17 +27681,14 @@
         <v>10</v>
       </c>
       <c r="B133">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="C133">
-        <v>4</v>
-      </c>
-      <c r="D133">
-        <v>4100000</v>
+        <v>3</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -27699,20 +27696,17 @@
         <v>10</v>
       </c>
       <c r="B134">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="C134">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D134">
-        <v>6000000</v>
-      </c>
-      <c r="F134">
-        <v>6000000</v>
+        <v>4100000</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -27720,17 +27714,20 @@
         <v>10</v>
       </c>
       <c r="B135">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="C135">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D135">
-        <v>1000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="F135">
+        <v>6000000</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -27738,14 +27735,17 @@
         <v>10</v>
       </c>
       <c r="B136">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D136">
+        <v>1000000</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -27753,23 +27753,14 @@
         <v>10</v>
       </c>
       <c r="B137">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C137">
-        <v>8</v>
-      </c>
-      <c r="D137">
-        <v>9250000</v>
-      </c>
-      <c r="F137">
-        <v>10000000</v>
-      </c>
-      <c r="G137" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -27777,23 +27768,23 @@
         <v>10</v>
       </c>
       <c r="B138">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C138">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D138">
-        <v>15000000</v>
+        <v>9250000</v>
       </c>
       <c r="F138">
-        <v>15000000</v>
-      </c>
-      <c r="H138">
-        <v>15000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G138" t="s">
+        <v>12</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -27801,20 +27792,23 @@
         <v>10</v>
       </c>
       <c r="B139">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="C139">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D139">
-        <v>11000000</v>
+        <v>15000000</v>
       </c>
       <c r="F139">
-        <v>11000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="H139">
+        <v>15000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -27822,23 +27816,20 @@
         <v>10</v>
       </c>
       <c r="B140">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C140">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D140">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="F140">
-        <v>16000000</v>
-      </c>
-      <c r="H140">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -27846,32 +27837,41 @@
         <v>10</v>
       </c>
       <c r="B141">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="C141">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D141">
-        <v>24000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="F141">
+        <v>16000000</v>
+      </c>
+      <c r="H141">
+        <v>16000000</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B142">
-        <v>327</v>
+        <v>246</v>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D142">
+        <v>24000000</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -27879,14 +27879,14 @@
         <v>11</v>
       </c>
       <c r="B143">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -27894,17 +27894,14 @@
         <v>11</v>
       </c>
       <c r="B144">
-        <v>111</v>
+        <v>213</v>
       </c>
       <c r="C144">
-        <v>3</v>
-      </c>
-      <c r="D144">
-        <v>1000000</v>
+        <v>2</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -27912,14 +27909,17 @@
         <v>11</v>
       </c>
       <c r="B145">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C145">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D145">
+        <v>1000000</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -27927,17 +27927,14 @@
         <v>11</v>
       </c>
       <c r="B146">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C146">
-        <v>5</v>
-      </c>
-      <c r="D146">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -27945,14 +27942,17 @@
         <v>11</v>
       </c>
       <c r="B147">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C147">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D147">
+        <v>1000000</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -27960,17 +27960,14 @@
         <v>11</v>
       </c>
       <c r="B148">
+        <v>63</v>
+      </c>
+      <c r="C148">
         <v>6</v>
-      </c>
-      <c r="C148">
-        <v>7</v>
-      </c>
-      <c r="D148">
-        <v>26000000</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -27978,17 +27975,17 @@
         <v>11</v>
       </c>
       <c r="B149">
-        <v>177</v>
+        <v>6</v>
       </c>
       <c r="C149">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D149">
-        <v>15000000</v>
+        <v>26000000</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -27996,17 +27993,17 @@
         <v>11</v>
       </c>
       <c r="B150">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="C150">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D150">
-        <v>7500000</v>
+        <v>15000000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -28014,23 +28011,17 @@
         <v>11</v>
       </c>
       <c r="B151">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="C151">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D151">
-        <v>30000000</v>
-      </c>
-      <c r="F151">
-        <v>30000000</v>
-      </c>
-      <c r="H151">
-        <v>30000000</v>
+        <v>7500000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -28038,17 +28029,23 @@
         <v>11</v>
       </c>
       <c r="B152">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="C152">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D152">
-        <v>1000000</v>
+        <v>30000000</v>
+      </c>
+      <c r="F152">
+        <v>30000000</v>
+      </c>
+      <c r="H152">
+        <v>30000000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -28056,14 +28053,17 @@
         <v>11</v>
       </c>
       <c r="B153">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="C153">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D153">
+        <v>1000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -28071,14 +28071,14 @@
         <v>11</v>
       </c>
       <c r="B154">
-        <v>266</v>
+        <v>109</v>
       </c>
       <c r="C154">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -28086,14 +28086,14 @@
         <v>11</v>
       </c>
       <c r="B155">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="C155">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -28101,53 +28101,47 @@
         <v>11</v>
       </c>
       <c r="B156">
-        <v>436</v>
+        <v>195</v>
       </c>
       <c r="C156">
-        <v>15</v>
-      </c>
-      <c r="D156">
-        <v>1000000</v>
-      </c>
-      <c r="F156">
-        <v>1000000</v>
-      </c>
-      <c r="H156">
-        <v>1000000</v>
-      </c>
-      <c r="I156" t="s">
-        <v>12</v>
-      </c>
-      <c r="J156">
-        <v>1000000</v>
-      </c>
-      <c r="K156" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Meleek Thomas</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157">
+        <v>11</v>
+      </c>
+      <c r="B157">
+        <v>436</v>
+      </c>
+      <c r="C157">
+        <v>15</v>
+      </c>
+      <c r="D157">
+        <v>1000000</v>
+      </c>
+      <c r="F157">
+        <v>1000000</v>
+      </c>
+      <c r="H157">
+        <v>1000000</v>
+      </c>
+      <c r="I157" t="s">
         <v>12</v>
       </c>
-      <c r="B157">
-        <v>403</v>
-      </c>
-      <c r="C157">
-        <v>1</v>
-      </c>
-      <c r="D157">
-        <v>5000000</v>
-      </c>
-      <c r="F157">
-        <v>5000000</v>
+      <c r="J157">
+        <v>1000000</v>
+      </c>
+      <c r="K157" t="s">
+        <v>12</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Meleek Thomas</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -28155,20 +28149,20 @@
         <v>12</v>
       </c>
       <c r="B158">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C158">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="F158">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -28176,17 +28170,20 @@
         <v>12</v>
       </c>
       <c r="B159">
-        <v>120</v>
+        <v>345</v>
       </c>
       <c r="C159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D159">
-        <v>1000000</v>
+        <v>3500000</v>
+      </c>
+      <c r="F159">
+        <v>3500000</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -28194,14 +28191,17 @@
         <v>12</v>
       </c>
       <c r="B160">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="C160">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D160">
+        <v>1000000</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -28209,17 +28209,14 @@
         <v>12</v>
       </c>
       <c r="B161">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C161">
-        <v>5</v>
-      </c>
-      <c r="D161">
-        <v>11000000</v>
+        <v>4</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -28227,20 +28224,17 @@
         <v>12</v>
       </c>
       <c r="B162">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="C162">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D162">
-        <v>20000000</v>
-      </c>
-      <c r="F162">
-        <v>20000000</v>
+        <v>11000000</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -28248,23 +28242,20 @@
         <v>12</v>
       </c>
       <c r="B163">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="C163">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D163">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="F163">
-        <v>18000000</v>
-      </c>
-      <c r="H163">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -28272,17 +28263,23 @@
         <v>12</v>
       </c>
       <c r="B164">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="C164">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D164">
-        <v>2500000</v>
+        <v>18000000</v>
+      </c>
+      <c r="F164">
+        <v>18000000</v>
+      </c>
+      <c r="H164">
+        <v>18000000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -28290,32 +28287,17 @@
         <v>12</v>
       </c>
       <c r="B165">
-        <v>417</v>
+        <v>115</v>
       </c>
       <c r="C165">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D165">
-        <v>9000000</v>
-      </c>
-      <c r="F165">
-        <v>9500000</v>
-      </c>
-      <c r="H165">
-        <v>10500000</v>
-      </c>
-      <c r="I165" t="s">
-        <v>12</v>
-      </c>
-      <c r="J165">
-        <v>11500000</v>
-      </c>
-      <c r="K165" t="s">
-        <v>12</v>
+        <v>2500000</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>A.J. Dybantsa</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -28323,50 +28305,65 @@
         <v>12</v>
       </c>
       <c r="B166">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="C166">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D166">
-        <v>1000000</v>
+        <v>9000000</v>
       </c>
       <c r="F166">
-        <v>1000000</v>
+        <v>9500000</v>
       </c>
       <c r="H166">
-        <v>1000000</v>
+        <v>10500000</v>
       </c>
       <c r="I166" t="s">
         <v>12</v>
       </c>
       <c r="J166">
-        <v>1000000</v>
+        <v>11500000</v>
       </c>
       <c r="K166" t="s">
         <v>12</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Nate Ament</v>
+        <v>A.J. Dybantsa</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B167">
-        <v>307</v>
+        <v>431</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D167">
         <v>1000000</v>
       </c>
+      <c r="F167">
+        <v>1000000</v>
+      </c>
+      <c r="H167">
+        <v>1000000</v>
+      </c>
+      <c r="I167" t="s">
+        <v>12</v>
+      </c>
+      <c r="J167">
+        <v>1000000</v>
+      </c>
+      <c r="K167" t="s">
+        <v>12</v>
+      </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Nate Ament</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -28374,14 +28371,17 @@
         <v>13</v>
       </c>
       <c r="B168">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c r="C168">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D168">
+        <v>1000000</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -28389,17 +28389,14 @@
         <v>13</v>
       </c>
       <c r="B169">
-        <v>296</v>
+        <v>363</v>
       </c>
       <c r="C169">
-        <v>3</v>
-      </c>
-      <c r="D169">
-        <v>3000000</v>
+        <v>2</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -28407,17 +28404,17 @@
         <v>13</v>
       </c>
       <c r="B170">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="C170">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D170">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -28425,14 +28422,17 @@
         <v>13</v>
       </c>
       <c r="B171">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="C171">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D171">
+        <v>2000000</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -28440,14 +28440,14 @@
         <v>13</v>
       </c>
       <c r="B172">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C172">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -28455,17 +28455,14 @@
         <v>13</v>
       </c>
       <c r="B173">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C173">
-        <v>7</v>
-      </c>
-      <c r="D173">
-        <v>11500000</v>
+        <v>6</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -28473,23 +28470,17 @@
         <v>13</v>
       </c>
       <c r="B174">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C174">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D174">
-        <v>16000000</v>
-      </c>
-      <c r="F174">
-        <v>16000000</v>
-      </c>
-      <c r="H174">
-        <v>16000000</v>
+        <v>11500000</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -28497,23 +28488,23 @@
         <v>13</v>
       </c>
       <c r="B175">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C175">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D175">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="F175">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="H175">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="L175" t="str">
         <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -28521,17 +28512,23 @@
         <v>13</v>
       </c>
       <c r="B176">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C176">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D176">
-        <v>19000000</v>
+        <v>12000000</v>
+      </c>
+      <c r="F176">
+        <v>12000000</v>
+      </c>
+      <c r="H176">
+        <v>12000000</v>
       </c>
       <c r="L176" t="str">
         <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -28539,23 +28536,17 @@
         <v>13</v>
       </c>
       <c r="B177">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="C177">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D177">
-        <v>6000000</v>
-      </c>
-      <c r="F177">
-        <v>6000000</v>
-      </c>
-      <c r="H177">
-        <v>6000000</v>
+        <v>19000000</v>
       </c>
       <c r="L177" t="str">
         <f>VLOOKUP(B177,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -28563,47 +28554,56 @@
         <v>13</v>
       </c>
       <c r="B178">
-        <v>430</v>
+        <v>150</v>
       </c>
       <c r="C178">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D178">
-        <v>2600000</v>
+        <v>6000000</v>
       </c>
       <c r="F178">
-        <v>2800000</v>
+        <v>6000000</v>
       </c>
       <c r="H178">
-        <v>3000000</v>
-      </c>
-      <c r="I178" t="s">
-        <v>12</v>
-      </c>
-      <c r="J178">
-        <v>3300000</v>
-      </c>
-      <c r="K178" t="s">
-        <v>12</v>
+        <v>6000000</v>
       </c>
       <c r="L178" t="str">
         <f>VLOOKUP(B178,players!A:B,2)</f>
-        <v>Cameron Carr</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B179">
-        <v>317</v>
+        <v>430</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D179">
+        <v>2600000</v>
+      </c>
+      <c r="F179">
+        <v>2800000</v>
+      </c>
+      <c r="H179">
+        <v>3000000</v>
+      </c>
+      <c r="I179" t="s">
+        <v>12</v>
+      </c>
+      <c r="J179">
+        <v>3300000</v>
+      </c>
+      <c r="K179" t="s">
+        <v>12</v>
       </c>
       <c r="L179" t="str">
         <f>VLOOKUP(B179,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Cameron Carr</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -28611,14 +28611,14 @@
         <v>14</v>
       </c>
       <c r="B180">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L180" t="str">
         <f>VLOOKUP(B180,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -28626,14 +28626,14 @@
         <v>14</v>
       </c>
       <c r="B181">
-        <v>129</v>
+        <v>299</v>
       </c>
       <c r="C181">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L181" t="str">
         <f>VLOOKUP(B181,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -28641,14 +28641,14 @@
         <v>14</v>
       </c>
       <c r="B182">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="C182">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L182" t="str">
         <f>VLOOKUP(B182,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -28656,17 +28656,14 @@
         <v>14</v>
       </c>
       <c r="B183">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="C183">
-        <v>5</v>
-      </c>
-      <c r="D183">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L183" t="str">
         <f>VLOOKUP(B183,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -28674,17 +28671,17 @@
         <v>14</v>
       </c>
       <c r="B184">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="C184">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D184">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="L184" t="str">
         <f>VLOOKUP(B184,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -28692,23 +28689,17 @@
         <v>14</v>
       </c>
       <c r="B185">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="C185">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D185">
-        <v>20500000</v>
-      </c>
-      <c r="F185">
-        <v>20500000</v>
-      </c>
-      <c r="H185">
-        <v>20500000</v>
+        <v>3000000</v>
       </c>
       <c r="L185" t="str">
         <f>VLOOKUP(B185,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -28716,17 +28707,23 @@
         <v>14</v>
       </c>
       <c r="B186">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C186">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D186">
-        <v>19500000</v>
+        <v>20500000</v>
+      </c>
+      <c r="F186">
+        <v>20500000</v>
+      </c>
+      <c r="H186">
+        <v>20500000</v>
       </c>
       <c r="L186" t="str">
         <f>VLOOKUP(B186,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -28734,29 +28731,17 @@
         <v>14</v>
       </c>
       <c r="B187">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C187">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D187">
-        <v>9500000</v>
-      </c>
-      <c r="F187">
-        <v>10500000</v>
-      </c>
-      <c r="G187" t="s">
-        <v>12</v>
-      </c>
-      <c r="H187">
-        <v>11500000</v>
-      </c>
-      <c r="I187" t="s">
-        <v>12</v>
+        <v>19500000</v>
       </c>
       <c r="L187" t="str">
         <f>VLOOKUP(B187,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -28764,14 +28749,29 @@
         <v>14</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C188">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D188">
+        <v>9500000</v>
+      </c>
+      <c r="F188">
+        <v>10500000</v>
+      </c>
+      <c r="G188" t="s">
+        <v>12</v>
+      </c>
+      <c r="H188">
+        <v>11500000</v>
+      </c>
+      <c r="I188" t="s">
+        <v>12</v>
       </c>
       <c r="L188" t="str">
         <f>VLOOKUP(B188,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -28779,14 +28779,14 @@
         <v>14</v>
       </c>
       <c r="B189">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="C189">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L189" t="str">
         <f>VLOOKUP(B189,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -28794,23 +28794,14 @@
         <v>14</v>
       </c>
       <c r="B190">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C190">
-        <v>12</v>
-      </c>
-      <c r="D190">
-        <v>20000000</v>
-      </c>
-      <c r="F190">
-        <v>20000000</v>
-      </c>
-      <c r="H190">
-        <v>20000000</v>
+        <v>11</v>
       </c>
       <c r="L190" t="str">
         <f>VLOOKUP(B190,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Quentin Grimes</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -28818,52 +28809,76 @@
         <v>14</v>
       </c>
       <c r="B191">
-        <v>273</v>
+        <v>145</v>
       </c>
       <c r="C191">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D191">
-        <v>3200000</v>
+        <v>20000000</v>
       </c>
       <c r="F191">
-        <v>3500000</v>
+        <v>20000000</v>
+      </c>
+      <c r="H191">
+        <v>20000000</v>
       </c>
       <c r="L191" t="str">
         <f>VLOOKUP(B191,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>LaMelo Ball</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192">
+        <v>14</v>
+      </c>
+      <c r="B192">
+        <v>273</v>
+      </c>
+      <c r="C192">
         <v>13</v>
       </c>
-      <c r="B192">
-        <v>426</v>
-      </c>
-      <c r="C192">
-        <v>14</v>
-      </c>
       <c r="D192">
-        <v>3400000</v>
+        <v>3200000</v>
       </c>
       <c r="F192">
-        <v>3600000</v>
-      </c>
-      <c r="H192">
-        <v>3800000</v>
-      </c>
-      <c r="I192" t="s">
-        <v>12</v>
-      </c>
-      <c r="J192">
-        <v>4100000</v>
-      </c>
-      <c r="K192" t="s">
-        <v>12</v>
+        <v>3500000</v>
       </c>
       <c r="L192" t="str">
         <f>VLOOKUP(B192,players!A:B,2)</f>
+        <v>Cason Wallace</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>13</v>
+      </c>
+      <c r="B193">
+        <v>426</v>
+      </c>
+      <c r="C193">
+        <v>14</v>
+      </c>
+      <c r="D193">
+        <v>3400000</v>
+      </c>
+      <c r="F193">
+        <v>3600000</v>
+      </c>
+      <c r="H193">
+        <v>3800000</v>
+      </c>
+      <c r="I193" t="s">
+        <v>12</v>
+      </c>
+      <c r="J193">
+        <v>4100000</v>
+      </c>
+      <c r="K193" t="s">
+        <v>12</v>
+      </c>
+      <c r="L193" t="str">
+        <f>VLOOKUP(B193,players!A:B,2)</f>
         <v>Morez Johnson Jr.</v>
       </c>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="83" documentId="11_D6E5441B28627EDC4691F04D3F68059E5C7A7665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5903E1-1834-440B-81CB-D043C7CFBF43}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -2334,6 +2334,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/home/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="11_D6E5441B28627EDC4691F04D3F68059E5C7A7665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5903E1-1834-440B-81CB-D043C7CFBF43}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="11_D6E5441B28627EDC4691F04D3F68059E5C7A7665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8DF7B22-233D-4C85-A700-15BFF3BD9355}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="737">
   <si>
     <t>player_id</t>
   </si>
@@ -2254,6 +2254,9 @@
   </si>
   <si>
     <t>Karim López</t>
+  </si>
+  <si>
+    <t>Christian Anderson Jr.</t>
   </si>
 </sst>
 </file>
@@ -2653,7 +2656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M444"/>
+  <dimension ref="A1:M445"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -16923,6 +16926,38 @@
         <v>0</v>
       </c>
       <c r="K444" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>444</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="D445" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E445" s="1">
+        <v>0</v>
+      </c>
+      <c r="F445" s="1">
+        <v>0</v>
+      </c>
+      <c r="G445" s="1">
+        <v>0</v>
+      </c>
+      <c r="H445" s="1">
+        <v>0</v>
+      </c>
+      <c r="I445" s="1">
+        <v>0</v>
+      </c>
+      <c r="J445" s="1">
+        <v>0</v>
+      </c>
+      <c r="K445" s="1">
         <v>0</v>
       </c>
     </row>
@@ -25267,7 +25302,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -27410,59 +27445,68 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B103">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="C103">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D103">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="F103">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="H103">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="I103" t="s">
         <v>620</v>
       </c>
       <c r="J103">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="K103" t="s">
         <v>620</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Darryn Peterson</v>
+        <v>Christian Anderson Jr.</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B104">
-        <v>242</v>
+        <v>420</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D104">
-        <v>3800000</v>
+        <v>6000000</v>
       </c>
       <c r="F104">
-        <v>4100000</v>
-      </c>
-      <c r="G104" t="s">
+        <v>6500000</v>
+      </c>
+      <c r="H104">
+        <v>7000000</v>
+      </c>
+      <c r="I104" t="s">
+        <v>620</v>
+      </c>
+      <c r="J104">
+        <v>7500000</v>
+      </c>
+      <c r="K104" t="s">
         <v>620</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Darryn Peterson</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -27470,14 +27514,23 @@
         <v>8</v>
       </c>
       <c r="B105">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>3800000</v>
+      </c>
+      <c r="F105">
+        <v>4100000</v>
+      </c>
+      <c r="G105" t="s">
+        <v>620</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -27485,29 +27538,14 @@
         <v>8</v>
       </c>
       <c r="B106">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="C106">
-        <v>3</v>
-      </c>
-      <c r="D106">
-        <v>1000000</v>
-      </c>
-      <c r="F106">
-        <v>1000000</v>
-      </c>
-      <c r="G106" t="s">
-        <v>620</v>
-      </c>
-      <c r="H106">
-        <v>1000000</v>
-      </c>
-      <c r="I106" t="s">
-        <v>620</v>
+        <v>2</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -27515,17 +27553,29 @@
         <v>8</v>
       </c>
       <c r="B107">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107">
-        <v>2000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F107">
+        <v>1000000</v>
+      </c>
+      <c r="G107" t="s">
+        <v>620</v>
+      </c>
+      <c r="H107">
+        <v>1000000</v>
+      </c>
+      <c r="I107" t="s">
+        <v>620</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -27533,23 +27583,17 @@
         <v>8</v>
       </c>
       <c r="B108">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D108">
-        <v>6000000</v>
-      </c>
-      <c r="F108">
-        <v>6000000</v>
-      </c>
-      <c r="H108">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -27557,23 +27601,23 @@
         <v>8</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="C109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D109">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
       <c r="F109">
-        <v>7500000</v>
-      </c>
-      <c r="G109" t="s">
-        <v>620</v>
+        <v>6000000</v>
+      </c>
+      <c r="H109">
+        <v>6000000</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -27581,20 +27625,23 @@
         <v>8</v>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D110">
-        <v>4000000</v>
+        <v>7000000</v>
       </c>
       <c r="F110">
-        <v>4000000</v>
+        <v>7500000</v>
+      </c>
+      <c r="G110" t="s">
+        <v>620</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -27602,23 +27649,20 @@
         <v>8</v>
       </c>
       <c r="B111">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="F111">
-        <v>16000000</v>
-      </c>
-      <c r="H111">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -27626,20 +27670,23 @@
         <v>8</v>
       </c>
       <c r="B112">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="C112">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D112">
-        <v>9000000</v>
+        <v>16000000</v>
       </c>
       <c r="F112">
-        <v>9000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="H112">
+        <v>16000000</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -27647,17 +27694,20 @@
         <v>8</v>
       </c>
       <c r="B113">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C113">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D113">
-        <v>16000000</v>
+        <v>9000000</v>
+      </c>
+      <c r="F113">
+        <v>9000000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -27665,23 +27715,17 @@
         <v>8</v>
       </c>
       <c r="B114">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="C114">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D114">
-        <v>19000000</v>
-      </c>
-      <c r="F114">
-        <v>19000000</v>
-      </c>
-      <c r="H114">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -27689,14 +27733,23 @@
         <v>8</v>
       </c>
       <c r="B115">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C115">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D115">
+        <v>19000000</v>
+      </c>
+      <c r="F115">
+        <v>19000000</v>
+      </c>
+      <c r="H115">
+        <v>19000000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -27704,14 +27757,14 @@
         <v>8</v>
       </c>
       <c r="B116">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="C116">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -27719,14 +27772,14 @@
         <v>8</v>
       </c>
       <c r="B117">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="C117">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -27734,32 +27787,14 @@
         <v>8</v>
       </c>
       <c r="B118">
-        <v>428</v>
+        <v>336</v>
       </c>
       <c r="C118">
-        <v>15</v>
-      </c>
-      <c r="D118">
-        <v>3000000</v>
-      </c>
-      <c r="F118">
-        <v>3200000</v>
-      </c>
-      <c r="H118">
-        <v>3400000</v>
-      </c>
-      <c r="I118" t="s">
-        <v>620</v>
-      </c>
-      <c r="J118">
-        <v>3700000</v>
-      </c>
-      <c r="K118" t="s">
-        <v>620</v>
+        <v>14</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Aday Mara</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -27767,32 +27802,32 @@
         <v>8</v>
       </c>
       <c r="B119">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="C119">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D119">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="F119">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="H119">
-        <v>1000000</v>
+        <v>3400000</v>
       </c>
       <c r="I119" t="s">
         <v>620</v>
       </c>
       <c r="J119">
-        <v>1000000</v>
+        <v>3700000</v>
       </c>
       <c r="K119" t="s">
         <v>620</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Bennett Stirtz</v>
+        <v>Aday Mara</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -27800,10 +27835,10 @@
         <v>8</v>
       </c>
       <c r="B120">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C120">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D120">
         <v>1000000</v>
@@ -27825,31 +27860,40 @@
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Chris Cenac Jr.</v>
+        <v>Bennett Stirtz</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B121">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D121">
-        <v>3100000</v>
+        <v>1000000</v>
       </c>
       <c r="F121">
-        <v>3100000</v>
+        <v>1000000</v>
       </c>
       <c r="H121">
-        <v>3100000</v>
+        <v>1000000</v>
+      </c>
+      <c r="I121" t="s">
+        <v>620</v>
+      </c>
+      <c r="J121">
+        <v>1000000</v>
+      </c>
+      <c r="K121" t="s">
+        <v>620</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Chris Cenac Jr.</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -27857,14 +27901,23 @@
         <v>9</v>
       </c>
       <c r="B122">
-        <v>240</v>
+        <v>384</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>3100000</v>
+      </c>
+      <c r="F122">
+        <v>3100000</v>
+      </c>
+      <c r="H122">
+        <v>3100000</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -27872,17 +27925,14 @@
         <v>9</v>
       </c>
       <c r="B123">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="C123">
-        <v>3</v>
-      </c>
-      <c r="D123">
-        <v>4500000</v>
+        <v>2</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -27890,14 +27940,17 @@
         <v>9</v>
       </c>
       <c r="B124">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="C124">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D124">
+        <v>4500000</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -27905,14 +27958,14 @@
         <v>9</v>
       </c>
       <c r="B125">
-        <v>416</v>
+        <v>251</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -27920,23 +27973,14 @@
         <v>9</v>
       </c>
       <c r="B126">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="C126">
-        <v>6</v>
-      </c>
-      <c r="D126">
-        <v>3100000</v>
-      </c>
-      <c r="F126">
-        <v>3100000</v>
-      </c>
-      <c r="H126">
-        <v>3100000</v>
+        <v>5</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -27944,23 +27988,23 @@
         <v>9</v>
       </c>
       <c r="B127">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D127">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="F127">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="H127">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -27968,23 +28012,23 @@
         <v>9</v>
       </c>
       <c r="B128">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D128">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="F128">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="H128">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -27992,17 +28036,23 @@
         <v>9</v>
       </c>
       <c r="B129">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="C129">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D129">
-        <v>11500000</v>
+        <v>12500000</v>
+      </c>
+      <c r="F129">
+        <v>12500000</v>
+      </c>
+      <c r="H129">
+        <v>12500000</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -28010,23 +28060,17 @@
         <v>9</v>
       </c>
       <c r="B130">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="C130">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D130">
-        <v>3100000</v>
-      </c>
-      <c r="F130">
-        <v>3100000</v>
-      </c>
-      <c r="H130">
-        <v>3100000</v>
+        <v>11500000</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -28034,17 +28078,23 @@
         <v>9</v>
       </c>
       <c r="B131">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="C131">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D131">
-        <v>25000000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F131">
+        <v>3100000</v>
+      </c>
+      <c r="H131">
+        <v>3100000</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -28052,23 +28102,17 @@
         <v>9</v>
       </c>
       <c r="B132">
-        <v>331</v>
+        <v>217</v>
       </c>
       <c r="C132">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D132">
-        <v>12000000</v>
-      </c>
-      <c r="F132">
-        <v>12000000</v>
-      </c>
-      <c r="H132">
-        <v>12000000</v>
+        <v>25000000</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -28076,62 +28120,71 @@
         <v>9</v>
       </c>
       <c r="B133">
-        <v>433</v>
+        <v>331</v>
       </c>
       <c r="C133">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D133">
-        <v>1000000</v>
+        <v>12000000</v>
       </c>
       <c r="F133">
-        <v>1000000</v>
+        <v>12000000</v>
       </c>
       <c r="H133">
-        <v>1000000</v>
-      </c>
-      <c r="I133" t="s">
-        <v>620</v>
-      </c>
-      <c r="J133">
-        <v>1000000</v>
-      </c>
-      <c r="K133" t="s">
-        <v>620</v>
+        <v>12000000</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Ebuka Okorie</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Darius Garland</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B134">
-        <v>9</v>
+        <v>433</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D134">
+        <v>1000000</v>
+      </c>
+      <c r="F134">
+        <v>1000000</v>
+      </c>
+      <c r="H134">
+        <v>1000000</v>
+      </c>
+      <c r="I134" t="s">
+        <v>620</v>
+      </c>
+      <c r="J134">
+        <v>1000000</v>
+      </c>
+      <c r="K134" t="s">
+        <v>620</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Walker Kessler</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+        <v>Ebuka Okorie</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>10</v>
       </c>
       <c r="B135">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="C135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -28139,14 +28192,14 @@
         <v>10</v>
       </c>
       <c r="B136">
-        <v>249</v>
+        <v>373</v>
       </c>
       <c r="C136">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -28154,17 +28207,14 @@
         <v>10</v>
       </c>
       <c r="B137">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="C137">
-        <v>4</v>
-      </c>
-      <c r="D137">
-        <v>4100000</v>
+        <v>3</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -28172,20 +28222,17 @@
         <v>10</v>
       </c>
       <c r="B138">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D138">
-        <v>6000000</v>
-      </c>
-      <c r="F138">
-        <v>6000000</v>
+        <v>4100000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -28193,17 +28240,20 @@
         <v>10</v>
       </c>
       <c r="B139">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="C139">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D139">
-        <v>1000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="F139">
+        <v>6000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -28211,14 +28261,17 @@
         <v>10</v>
       </c>
       <c r="B140">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D140">
+        <v>1000000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -28226,23 +28279,14 @@
         <v>10</v>
       </c>
       <c r="B141">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C141">
-        <v>8</v>
-      </c>
-      <c r="D141">
-        <v>9250000</v>
-      </c>
-      <c r="F141">
-        <v>10000000</v>
-      </c>
-      <c r="G141" t="s">
-        <v>620</v>
+        <v>7</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -28250,23 +28294,23 @@
         <v>10</v>
       </c>
       <c r="B142">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C142">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D142">
-        <v>15000000</v>
+        <v>9250000</v>
       </c>
       <c r="F142">
-        <v>15000000</v>
-      </c>
-      <c r="H142">
-        <v>15000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G142" t="s">
+        <v>620</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -28274,20 +28318,23 @@
         <v>10</v>
       </c>
       <c r="B143">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="C143">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D143">
-        <v>11000000</v>
+        <v>15000000</v>
       </c>
       <c r="F143">
-        <v>11000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="H143">
+        <v>15000000</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -28295,23 +28342,20 @@
         <v>10</v>
       </c>
       <c r="B144">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C144">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D144">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="F144">
-        <v>16000000</v>
-      </c>
-      <c r="H144">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -28319,17 +28363,23 @@
         <v>10</v>
       </c>
       <c r="B145">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="C145">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D145">
-        <v>24000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="F145">
+        <v>16000000</v>
+      </c>
+      <c r="H145">
+        <v>16000000</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -28337,47 +28387,50 @@
         <v>10</v>
       </c>
       <c r="B146">
-        <v>443</v>
+        <v>246</v>
       </c>
       <c r="C146">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D146">
-        <v>1000000</v>
-      </c>
-      <c r="F146">
-        <v>1000000</v>
-      </c>
-      <c r="H146">
-        <v>1000000</v>
-      </c>
-      <c r="I146" t="s">
-        <v>620</v>
-      </c>
-      <c r="J146">
-        <v>1000000</v>
-      </c>
-      <c r="K146" t="s">
-        <v>620</v>
+        <v>24000000</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Zuby Ejiofor</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B147">
-        <v>327</v>
+        <v>443</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D147">
+        <v>1000000</v>
+      </c>
+      <c r="F147">
+        <v>1000000</v>
+      </c>
+      <c r="H147">
+        <v>1000000</v>
+      </c>
+      <c r="I147" t="s">
+        <v>620</v>
+      </c>
+      <c r="J147">
+        <v>1000000</v>
+      </c>
+      <c r="K147" t="s">
+        <v>620</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Zuby Ejiofor</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -28385,14 +28438,14 @@
         <v>11</v>
       </c>
       <c r="B148">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -28400,17 +28453,14 @@
         <v>11</v>
       </c>
       <c r="B149">
-        <v>111</v>
+        <v>213</v>
       </c>
       <c r="C149">
-        <v>3</v>
-      </c>
-      <c r="D149">
-        <v>1000000</v>
+        <v>2</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -28418,14 +28468,17 @@
         <v>11</v>
       </c>
       <c r="B150">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C150">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D150">
+        <v>1000000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -28433,17 +28486,14 @@
         <v>11</v>
       </c>
       <c r="B151">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C151">
-        <v>5</v>
-      </c>
-      <c r="D151">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -28451,14 +28501,17 @@
         <v>11</v>
       </c>
       <c r="B152">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C152">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D152">
+        <v>1000000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -28466,17 +28519,14 @@
         <v>11</v>
       </c>
       <c r="B153">
+        <v>63</v>
+      </c>
+      <c r="C153">
         <v>6</v>
-      </c>
-      <c r="C153">
-        <v>7</v>
-      </c>
-      <c r="D153">
-        <v>26000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -28484,17 +28534,17 @@
         <v>11</v>
       </c>
       <c r="B154">
-        <v>177</v>
+        <v>6</v>
       </c>
       <c r="C154">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D154">
-        <v>15000000</v>
+        <v>26000000</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -28502,17 +28552,17 @@
         <v>11</v>
       </c>
       <c r="B155">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="C155">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D155">
-        <v>7500000</v>
+        <v>15000000</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -28520,23 +28570,17 @@
         <v>11</v>
       </c>
       <c r="B156">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="C156">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D156">
-        <v>30000000</v>
-      </c>
-      <c r="F156">
-        <v>30000000</v>
-      </c>
-      <c r="H156">
-        <v>30000000</v>
+        <v>7500000</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -28544,17 +28588,23 @@
         <v>11</v>
       </c>
       <c r="B157">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="C157">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D157">
-        <v>1000000</v>
+        <v>30000000</v>
+      </c>
+      <c r="F157">
+        <v>30000000</v>
+      </c>
+      <c r="H157">
+        <v>30000000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -28562,14 +28612,17 @@
         <v>11</v>
       </c>
       <c r="B158">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="C158">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D158">
+        <v>1000000</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -28577,14 +28630,14 @@
         <v>11</v>
       </c>
       <c r="B159">
-        <v>266</v>
+        <v>109</v>
       </c>
       <c r="C159">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -28592,14 +28645,14 @@
         <v>11</v>
       </c>
       <c r="B160">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="C160">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -28607,53 +28660,47 @@
         <v>11</v>
       </c>
       <c r="B161">
-        <v>436</v>
+        <v>195</v>
       </c>
       <c r="C161">
-        <v>15</v>
-      </c>
-      <c r="D161">
-        <v>1000000</v>
-      </c>
-      <c r="F161">
-        <v>1000000</v>
-      </c>
-      <c r="H161">
-        <v>1000000</v>
-      </c>
-      <c r="I161" t="s">
-        <v>620</v>
-      </c>
-      <c r="J161">
-        <v>1000000</v>
-      </c>
-      <c r="K161" t="s">
-        <v>620</v>
+        <v>14</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Meleek Thomas</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B162">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D162">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="F162">
-        <v>5000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="H162">
+        <v>1000000</v>
+      </c>
+      <c r="I162" t="s">
+        <v>620</v>
+      </c>
+      <c r="J162">
+        <v>1000000</v>
+      </c>
+      <c r="K162" t="s">
+        <v>620</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Meleek Thomas</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -28661,20 +28708,20 @@
         <v>12</v>
       </c>
       <c r="B163">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="F163">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -28682,17 +28729,20 @@
         <v>12</v>
       </c>
       <c r="B164">
-        <v>120</v>
+        <v>345</v>
       </c>
       <c r="C164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D164">
-        <v>1000000</v>
+        <v>3500000</v>
+      </c>
+      <c r="F164">
+        <v>3500000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -28700,14 +28750,17 @@
         <v>12</v>
       </c>
       <c r="B165">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="C165">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D165">
+        <v>1000000</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -28715,17 +28768,14 @@
         <v>12</v>
       </c>
       <c r="B166">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C166">
-        <v>5</v>
-      </c>
-      <c r="D166">
-        <v>11000000</v>
+        <v>4</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -28733,20 +28783,17 @@
         <v>12</v>
       </c>
       <c r="B167">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="C167">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D167">
-        <v>20000000</v>
-      </c>
-      <c r="F167">
-        <v>20000000</v>
+        <v>11000000</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -28754,23 +28801,20 @@
         <v>12</v>
       </c>
       <c r="B168">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="C168">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D168">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="F168">
-        <v>18000000</v>
-      </c>
-      <c r="H168">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -28778,17 +28822,23 @@
         <v>12</v>
       </c>
       <c r="B169">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="C169">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D169">
-        <v>2500000</v>
+        <v>18000000</v>
+      </c>
+      <c r="F169">
+        <v>18000000</v>
+      </c>
+      <c r="H169">
+        <v>18000000</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -28796,32 +28846,17 @@
         <v>12</v>
       </c>
       <c r="B170">
-        <v>417</v>
+        <v>115</v>
       </c>
       <c r="C170">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D170">
-        <v>9000000</v>
-      </c>
-      <c r="F170">
-        <v>9500000</v>
-      </c>
-      <c r="H170">
-        <v>10500000</v>
-      </c>
-      <c r="I170" t="s">
-        <v>620</v>
-      </c>
-      <c r="J170">
-        <v>11500000</v>
-      </c>
-      <c r="K170" t="s">
-        <v>620</v>
+        <v>2500000</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>A.J. Dybantsa</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -28829,50 +28864,65 @@
         <v>12</v>
       </c>
       <c r="B171">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="C171">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D171">
-        <v>1000000</v>
+        <v>9000000</v>
       </c>
       <c r="F171">
-        <v>1000000</v>
+        <v>9500000</v>
       </c>
       <c r="H171">
-        <v>1000000</v>
+        <v>10500000</v>
       </c>
       <c r="I171" t="s">
         <v>620</v>
       </c>
       <c r="J171">
-        <v>1000000</v>
+        <v>11500000</v>
       </c>
       <c r="K171" t="s">
         <v>620</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Nate Ament</v>
+        <v>A.J. Dybantsa</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B172">
-        <v>307</v>
+        <v>431</v>
       </c>
       <c r="C172">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D172">
         <v>1000000</v>
       </c>
+      <c r="F172">
+        <v>1000000</v>
+      </c>
+      <c r="H172">
+        <v>1000000</v>
+      </c>
+      <c r="I172" t="s">
+        <v>620</v>
+      </c>
+      <c r="J172">
+        <v>1000000</v>
+      </c>
+      <c r="K172" t="s">
+        <v>620</v>
+      </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Nate Ament</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -28880,14 +28930,17 @@
         <v>13</v>
       </c>
       <c r="B173">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c r="C173">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D173">
+        <v>1000000</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -28895,17 +28948,14 @@
         <v>13</v>
       </c>
       <c r="B174">
-        <v>296</v>
+        <v>363</v>
       </c>
       <c r="C174">
-        <v>3</v>
-      </c>
-      <c r="D174">
-        <v>3000000</v>
+        <v>2</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -28913,17 +28963,17 @@
         <v>13</v>
       </c>
       <c r="B175">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="C175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D175">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="L175" t="str">
         <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -28931,14 +28981,17 @@
         <v>13</v>
       </c>
       <c r="B176">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="C176">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D176">
+        <v>2000000</v>
       </c>
       <c r="L176" t="str">
         <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -28946,14 +28999,14 @@
         <v>13</v>
       </c>
       <c r="B177">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C177">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L177" t="str">
         <f>VLOOKUP(B177,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -28961,17 +29014,14 @@
         <v>13</v>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C178">
-        <v>7</v>
-      </c>
-      <c r="D178">
-        <v>11500000</v>
+        <v>6</v>
       </c>
       <c r="L178" t="str">
         <f>VLOOKUP(B178,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -28979,23 +29029,17 @@
         <v>13</v>
       </c>
       <c r="B179">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C179">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D179">
-        <v>16000000</v>
-      </c>
-      <c r="F179">
-        <v>16000000</v>
-      </c>
-      <c r="H179">
-        <v>16000000</v>
+        <v>11500000</v>
       </c>
       <c r="L179" t="str">
         <f>VLOOKUP(B179,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -29003,23 +29047,23 @@
         <v>13</v>
       </c>
       <c r="B180">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C180">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D180">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="F180">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="H180">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="L180" t="str">
         <f>VLOOKUP(B180,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -29027,17 +29071,23 @@
         <v>13</v>
       </c>
       <c r="B181">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C181">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D181">
-        <v>19000000</v>
+        <v>12000000</v>
+      </c>
+      <c r="F181">
+        <v>12000000</v>
+      </c>
+      <c r="H181">
+        <v>12000000</v>
       </c>
       <c r="L181" t="str">
         <f>VLOOKUP(B181,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -29045,23 +29095,17 @@
         <v>13</v>
       </c>
       <c r="B182">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="C182">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D182">
-        <v>6000000</v>
-      </c>
-      <c r="F182">
-        <v>6000000</v>
-      </c>
-      <c r="H182">
-        <v>6000000</v>
+        <v>19000000</v>
       </c>
       <c r="L182" t="str">
         <f>VLOOKUP(B182,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -29069,32 +29113,23 @@
         <v>13</v>
       </c>
       <c r="B183">
-        <v>430</v>
+        <v>150</v>
       </c>
       <c r="C183">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D183">
-        <v>2600000</v>
+        <v>6000000</v>
       </c>
       <c r="F183">
-        <v>2800000</v>
+        <v>6000000</v>
       </c>
       <c r="H183">
-        <v>3000000</v>
-      </c>
-      <c r="I183" t="s">
-        <v>620</v>
-      </c>
-      <c r="J183">
-        <v>3300000</v>
-      </c>
-      <c r="K183" t="s">
-        <v>620</v>
+        <v>6000000</v>
       </c>
       <c r="L183" t="str">
         <f>VLOOKUP(B183,players!A:B,2)</f>
-        <v>Cameron Carr</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -29102,47 +29137,65 @@
         <v>13</v>
       </c>
       <c r="B184">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C184">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D184">
-        <v>1000000</v>
+        <v>2600000</v>
       </c>
       <c r="F184">
-        <v>1000000</v>
+        <v>2800000</v>
       </c>
       <c r="H184">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="I184" t="s">
         <v>620</v>
       </c>
       <c r="J184">
-        <v>1000000</v>
+        <v>3300000</v>
       </c>
       <c r="K184" t="s">
         <v>620</v>
       </c>
       <c r="L184" t="str">
         <f>VLOOKUP(B184,players!A:B,2)</f>
-        <v>Sergio de Larrea</v>
+        <v>Cameron Carr</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185">
+        <v>13</v>
+      </c>
+      <c r="B185">
+        <v>440</v>
+      </c>
+      <c r="C185">
         <v>14</v>
       </c>
-      <c r="B185">
-        <v>317</v>
-      </c>
-      <c r="C185">
-        <v>1</v>
+      <c r="D185">
+        <v>1000000</v>
+      </c>
+      <c r="F185">
+        <v>1000000</v>
+      </c>
+      <c r="H185">
+        <v>1000000</v>
+      </c>
+      <c r="I185" t="s">
+        <v>620</v>
+      </c>
+      <c r="J185">
+        <v>1000000</v>
+      </c>
+      <c r="K185" t="s">
+        <v>620</v>
       </c>
       <c r="L185" t="str">
         <f>VLOOKUP(B185,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Sergio de Larrea</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -29150,14 +29203,14 @@
         <v>14</v>
       </c>
       <c r="B186">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L186" t="str">
         <f>VLOOKUP(B186,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -29165,14 +29218,14 @@
         <v>14</v>
       </c>
       <c r="B187">
-        <v>129</v>
+        <v>299</v>
       </c>
       <c r="C187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L187" t="str">
         <f>VLOOKUP(B187,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -29180,14 +29233,14 @@
         <v>14</v>
       </c>
       <c r="B188">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="C188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L188" t="str">
         <f>VLOOKUP(B188,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -29195,17 +29248,14 @@
         <v>14</v>
       </c>
       <c r="B189">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="C189">
-        <v>5</v>
-      </c>
-      <c r="D189">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L189" t="str">
         <f>VLOOKUP(B189,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -29213,17 +29263,17 @@
         <v>14</v>
       </c>
       <c r="B190">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="C190">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D190">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="L190" t="str">
         <f>VLOOKUP(B190,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -29231,23 +29281,17 @@
         <v>14</v>
       </c>
       <c r="B191">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="C191">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D191">
-        <v>20500000</v>
-      </c>
-      <c r="F191">
-        <v>20500000</v>
-      </c>
-      <c r="H191">
-        <v>20500000</v>
+        <v>3000000</v>
       </c>
       <c r="L191" t="str">
         <f>VLOOKUP(B191,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -29255,17 +29299,23 @@
         <v>14</v>
       </c>
       <c r="B192">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C192">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D192">
-        <v>19500000</v>
+        <v>20500000</v>
+      </c>
+      <c r="F192">
+        <v>20500000</v>
+      </c>
+      <c r="H192">
+        <v>20500000</v>
       </c>
       <c r="L192" t="str">
         <f>VLOOKUP(B192,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -29273,29 +29323,17 @@
         <v>14</v>
       </c>
       <c r="B193">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C193">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D193">
-        <v>9500000</v>
-      </c>
-      <c r="F193">
-        <v>10500000</v>
-      </c>
-      <c r="G193" t="s">
-        <v>620</v>
-      </c>
-      <c r="H193">
-        <v>11500000</v>
-      </c>
-      <c r="I193" t="s">
-        <v>620</v>
+        <v>19500000</v>
       </c>
       <c r="L193" t="str">
         <f>VLOOKUP(B193,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -29303,14 +29341,29 @@
         <v>14</v>
       </c>
       <c r="B194">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C194">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D194">
+        <v>9500000</v>
+      </c>
+      <c r="F194">
+        <v>10500000</v>
+      </c>
+      <c r="G194" t="s">
+        <v>620</v>
+      </c>
+      <c r="H194">
+        <v>11500000</v>
+      </c>
+      <c r="I194" t="s">
+        <v>620</v>
       </c>
       <c r="L194" t="str">
         <f>VLOOKUP(B194,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
@@ -29318,14 +29371,14 @@
         <v>14</v>
       </c>
       <c r="B195">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="C195">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L195" t="str">
         <f>VLOOKUP(B195,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
@@ -29333,23 +29386,14 @@
         <v>14</v>
       </c>
       <c r="B196">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C196">
-        <v>12</v>
-      </c>
-      <c r="D196">
-        <v>20000000</v>
-      </c>
-      <c r="F196">
-        <v>20000000</v>
-      </c>
-      <c r="H196">
-        <v>20000000</v>
+        <v>11</v>
       </c>
       <c r="L196" t="str">
         <f>VLOOKUP(B196,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Quentin Grimes</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
@@ -29357,85 +29401,109 @@
         <v>14</v>
       </c>
       <c r="B197">
-        <v>273</v>
+        <v>145</v>
       </c>
       <c r="C197">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D197">
-        <v>3200000</v>
+        <v>20000000</v>
       </c>
       <c r="F197">
-        <v>3500000</v>
+        <v>20000000</v>
+      </c>
+      <c r="H197">
+        <v>20000000</v>
       </c>
       <c r="L197" t="str">
         <f>VLOOKUP(B197,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>LaMelo Ball</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198">
+        <v>14</v>
+      </c>
+      <c r="B198">
+        <v>273</v>
+      </c>
+      <c r="C198">
         <v>13</v>
       </c>
-      <c r="B198">
-        <v>426</v>
-      </c>
-      <c r="C198">
-        <v>14</v>
-      </c>
       <c r="D198">
-        <v>3400000</v>
+        <v>3200000</v>
       </c>
       <c r="F198">
-        <v>3600000</v>
-      </c>
-      <c r="H198">
-        <v>3800000</v>
-      </c>
-      <c r="I198" t="s">
-        <v>620</v>
-      </c>
-      <c r="J198">
-        <v>4100000</v>
-      </c>
-      <c r="K198" t="s">
-        <v>620</v>
+        <v>3500000</v>
       </c>
       <c r="L198" t="str">
         <f>VLOOKUP(B198,players!A:B,2)</f>
-        <v>Morez Johnson Jr.</v>
+        <v>Cason Wallace</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B199">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C199">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D199">
-        <v>1000000</v>
+        <v>3400000</v>
       </c>
       <c r="F199">
-        <v>1000000</v>
+        <v>3600000</v>
       </c>
       <c r="H199">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="I199" t="s">
         <v>620</v>
       </c>
       <c r="J199">
-        <v>1000000</v>
+        <v>4100000</v>
       </c>
       <c r="K199" t="s">
         <v>620</v>
       </c>
       <c r="L199" t="str">
         <f>VLOOKUP(B199,players!A:B,2)</f>
+        <v>Morez Johnson Jr.</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>7</v>
+      </c>
+      <c r="B200">
+        <v>434</v>
+      </c>
+      <c r="C200">
+        <v>15</v>
+      </c>
+      <c r="D200">
+        <v>1000000</v>
+      </c>
+      <c r="F200">
+        <v>1000000</v>
+      </c>
+      <c r="H200">
+        <v>1000000</v>
+      </c>
+      <c r="I200" t="s">
+        <v>620</v>
+      </c>
+      <c r="J200">
+        <v>1000000</v>
+      </c>
+      <c r="K200" t="s">
+        <v>620</v>
+      </c>
+      <c r="L200" t="str">
+        <f>VLOOKUP(B200,players!A:B,2)</f>
         <v>Allen Graves</v>
       </c>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/home/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="11_D6E5441B28627EDC4691F04D3F68059E5C7A7665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8DF7B22-233D-4C85-A700-15BFF3BD9355}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="11_D6E5441B28627EDC4691F04D3F68059E5C7A7665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7363FC2B-D0F1-44EC-AB61-1EFB31467497}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -21583,7 +21583,8 @@
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21668,8 +21669,12 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="B7" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1200000</v>
+      </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_99A569367B49D9CD84C3CDC2E5883E38D9AF0EAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97E2A5F0-73B0-4120-956A-FB98B4C49D6B}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_99A569367B49D9CD84C3CDC2E5883E38D9AF0EAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B945DE74-221E-47C5-BD71-3F141122B8D1}"/>
   <bookViews>
-    <workbookView xWindow="31530" yWindow="4365" windowWidth="21600" windowHeight="11835" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31530" yWindow="4365" windowWidth="21600" windowHeight="11835" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -2346,6 +2346,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21693,7 +21697,8 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>750000</v>
+        <f>750000+3000000</f>
+        <v>3750000</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_99A569367B49D9CD84C3CDC2E5883E38D9AF0EAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B945DE74-221E-47C5-BD71-3F141122B8D1}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_99A569367B49D9CD84C3CDC2E5883E38D9AF0EAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A04FAC3-BAEB-40B9-AE86-CFB5EA9624B8}"/>
   <bookViews>
-    <workbookView xWindow="31530" yWindow="4365" windowWidth="21600" windowHeight="11835" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11835" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -28125,6 +28125,9 @@
       <c r="C123">
         <v>4</v>
       </c>
+      <c r="D123">
+        <v>1000000</v>
+      </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
         <v>Jaden McDaniels</v>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Evolucoes/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3CA14E4-2249-4B98-A3E0-47247A6C8E58}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8CEADB7-D625-4CA9-8123-BD4FA2F3FDF8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="698">
   <si>
     <t>team_id</t>
   </si>
@@ -1684,48 +1684,6 @@
   </si>
   <si>
     <t>nome_time_2</t>
-  </si>
-  <si>
-    <t>J1R1S2526</t>
-  </si>
-  <si>
-    <t>J2R1S2526</t>
-  </si>
-  <si>
-    <t>J3R1S2526</t>
-  </si>
-  <si>
-    <t>J4R1S2526</t>
-  </si>
-  <si>
-    <t>J5R1S2526</t>
-  </si>
-  <si>
-    <t>J6R1S2526</t>
-  </si>
-  <si>
-    <t>J7R1S2526</t>
-  </si>
-  <si>
-    <t>J1R2S2526</t>
-  </si>
-  <si>
-    <t>J2R2S2526</t>
-  </si>
-  <si>
-    <t>J3R2S2526</t>
-  </si>
-  <si>
-    <t>J4R2S2526</t>
-  </si>
-  <si>
-    <t>J5R2S2526</t>
-  </si>
-  <si>
-    <t>J6R2S2526</t>
-  </si>
-  <si>
-    <t>J7R2S2526</t>
   </si>
   <si>
     <t>transactiondate</t>
@@ -17949,24 +17907,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="B1" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="C1" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="D1" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="E1" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="B2">
         <v>7</v>
@@ -17983,7 +17941,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="B3">
         <v>9</v>
@@ -18000,7 +17958,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -18017,7 +17975,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -18034,7 +17992,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -18051,7 +18009,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -18068,7 +18026,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -18085,7 +18043,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -18102,7 +18060,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="B10">
         <v>11</v>
@@ -18119,7 +18077,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -18136,7 +18094,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -18153,7 +18111,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -18170,7 +18128,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -18187,7 +18145,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -18204,7 +18162,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -18221,7 +18179,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -18238,7 +18196,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -18255,7 +18213,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -18272,7 +18230,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -18289,7 +18247,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -18306,7 +18264,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -18323,7 +18281,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -18340,7 +18298,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -18357,7 +18315,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -18374,7 +18332,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -18391,7 +18349,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -18408,7 +18366,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -18425,7 +18383,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -18442,7 +18400,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
       <c r="B30">
         <v>3</v>
@@ -18459,7 +18417,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="B31">
         <v>3</v>
@@ -18476,7 +18434,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -18493,7 +18451,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -18510,7 +18468,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -18527,7 +18485,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -18544,7 +18502,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -18561,7 +18519,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="B37">
         <v>4</v>
@@ -18578,7 +18536,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="B38">
         <v>4</v>
@@ -18595,7 +18553,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -18612,7 +18570,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -18629,7 +18587,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="B41">
         <v>4</v>
@@ -18646,7 +18604,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="B42">
         <v>4</v>
@@ -18663,7 +18621,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B43">
         <v>14</v>
@@ -18680,7 +18638,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -18697,7 +18655,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="B45">
         <v>14</v>
@@ -18714,7 +18672,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="B46">
         <v>10</v>
@@ -18731,7 +18689,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="B47">
         <v>5</v>
@@ -18748,7 +18706,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="B48">
         <v>7</v>
@@ -18765,7 +18723,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="B49">
         <v>5</v>
@@ -18782,7 +18740,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="B50">
         <v>5</v>
@@ -18799,7 +18757,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="B51">
         <v>5</v>
@@ -18816,7 +18774,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="B52">
         <v>6</v>
@@ -18833,7 +18791,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="B53">
         <v>5</v>
@@ -18850,7 +18808,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="B54">
         <v>6</v>
@@ -18867,7 +18825,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="B55">
         <v>6</v>
@@ -18884,7 +18842,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="B56">
         <v>6</v>
@@ -18901,7 +18859,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="B57">
         <v>5</v>
@@ -18918,7 +18876,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="B58">
         <v>6</v>
@@ -18935,7 +18893,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="B59">
         <v>6</v>
@@ -18952,7 +18910,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="B60">
         <v>8</v>
@@ -18969,7 +18927,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="B61">
         <v>8</v>
@@ -18986,7 +18944,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="B62">
         <v>3</v>
@@ -19003,7 +18961,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="B63">
         <v>8</v>
@@ -19020,7 +18978,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="B64">
         <v>8</v>
@@ -19037,7 +18995,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="B65">
         <v>8</v>
@@ -19054,7 +19012,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="B66">
         <v>8</v>
@@ -19071,7 +19029,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="B67">
         <v>6</v>
@@ -19088,7 +19046,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="B68">
         <v>8</v>
@@ -19105,7 +19063,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="B69">
         <v>8</v>
@@ -19122,7 +19080,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="B70">
         <v>9</v>
@@ -19139,7 +19097,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="B71">
         <v>9</v>
@@ -19156,7 +19114,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="B72">
         <v>9</v>
@@ -19173,7 +19131,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="B73">
         <v>9</v>
@@ -19190,7 +19148,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="B74">
         <v>9</v>
@@ -19207,7 +19165,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="B75">
         <v>9</v>
@@ -19224,7 +19182,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="B76">
         <v>9</v>
@@ -19241,7 +19199,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="B77">
         <v>13</v>
@@ -19258,7 +19216,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="B78">
         <v>7</v>
@@ -19275,7 +19233,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="B79">
         <v>10</v>
@@ -19292,7 +19250,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="B80">
         <v>10</v>
@@ -19309,7 +19267,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B81">
         <v>10</v>
@@ -19326,7 +19284,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="B82">
         <v>10</v>
@@ -19343,7 +19301,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B83">
         <v>10</v>
@@ -19360,7 +19318,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="B84">
         <v>10</v>
@@ -19377,7 +19335,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="B85">
         <v>11</v>
@@ -19394,7 +19352,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="B86">
         <v>11</v>
@@ -19411,7 +19369,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="B87">
         <v>11</v>
@@ -19428,7 +19386,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -19445,7 +19403,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="B89">
         <v>11</v>
@@ -19462,7 +19420,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="B90">
         <v>11</v>
@@ -19479,7 +19437,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="B91">
         <v>11</v>
@@ -19496,7 +19454,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="B92">
         <v>12</v>
@@ -19513,7 +19471,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="B93">
         <v>12</v>
@@ -19530,7 +19488,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="B94">
         <v>12</v>
@@ -19547,7 +19505,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="B95">
         <v>12</v>
@@ -19564,7 +19522,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="B96">
         <v>12</v>
@@ -19581,7 +19539,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="B97">
         <v>12</v>
@@ -19598,7 +19556,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="B98">
         <v>12</v>
@@ -19615,7 +19573,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="B99">
         <v>12</v>
@@ -19632,7 +19590,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="B100">
         <v>4</v>
@@ -19649,7 +19607,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="B101">
         <v>13</v>
@@ -19666,7 +19624,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="B102">
         <v>13</v>
@@ -19683,7 +19641,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="B103">
         <v>13</v>
@@ -19700,7 +19658,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="B104">
         <v>13</v>
@@ -19717,7 +19675,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="B105">
         <v>13</v>
@@ -19734,7 +19692,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="B106">
         <v>13</v>
@@ -19751,7 +19709,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="B107">
         <v>14</v>
@@ -19768,7 +19726,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="B108">
         <v>14</v>
@@ -19785,7 +19743,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="B109">
         <v>2</v>
@@ -19802,7 +19760,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="B110">
         <v>14</v>
@@ -19819,7 +19777,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="B111">
         <v>14</v>
@@ -19836,7 +19794,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="B112">
         <v>14</v>
@@ -19853,7 +19811,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="B113">
         <v>14</v>
@@ -21952,8 +21910,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>546</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2">
         <v>14</v>
@@ -21977,8 +21935,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>547</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -22002,8 +21960,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>548</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -22027,8 +21985,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>549</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5">
         <v>9</v>
@@ -22052,8 +22010,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>550</v>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -22077,8 +22035,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>551</v>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7">
         <v>13</v>
@@ -22102,8 +22060,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>552</v>
+      <c r="A8">
+        <v>7</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -22127,8 +22085,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>553</v>
+      <c r="A9">
+        <v>8</v>
       </c>
       <c r="B9">
         <v>14</v>
@@ -22152,8 +22110,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>554</v>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -22177,8 +22135,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>555</v>
+      <c r="A11">
+        <v>10</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -22202,8 +22160,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>556</v>
+      <c r="A12">
+        <v>11</v>
       </c>
       <c r="B12">
         <v>9</v>
@@ -22227,8 +22185,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>557</v>
+      <c r="A13">
+        <v>12</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -22252,8 +22210,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>558</v>
+      <c r="A14">
+        <v>13</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -22277,8 +22235,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>559</v>
+      <c r="A15">
+        <v>14</v>
       </c>
       <c r="B15">
         <v>7</v>
@@ -22322,19 +22280,19 @@
         <v>512</v>
       </c>
       <c r="C1" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="D1" t="s">
         <v>514</v>
       </c>
       <c r="E1" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="F1" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="G1" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="H1" t="s">
         <v>23</v>
@@ -22354,10 +22312,10 @@
         <v>520</v>
       </c>
       <c r="C2" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D2" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -22366,10 +22324,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H2" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -22380,10 +22338,10 @@
         <v>520</v>
       </c>
       <c r="C3" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D3" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -22392,10 +22350,10 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H3" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -22406,10 +22364,10 @@
         <v>518</v>
       </c>
       <c r="C4" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D4" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -22418,10 +22376,10 @@
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H4" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -22432,10 +22390,10 @@
         <v>518</v>
       </c>
       <c r="C5" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D5" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -22444,10 +22402,10 @@
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H5" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -22458,10 +22416,10 @@
         <v>518</v>
       </c>
       <c r="C6" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D6" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -22470,10 +22428,10 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H6" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -22484,10 +22442,10 @@
         <v>518</v>
       </c>
       <c r="C7" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D7" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E7">
         <v>14</v>
@@ -22496,10 +22454,10 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H7" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -22510,10 +22468,10 @@
         <v>518</v>
       </c>
       <c r="C8" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D8" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -22522,10 +22480,10 @@
         <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="H8" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -22536,10 +22494,10 @@
         <v>518</v>
       </c>
       <c r="C9" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D9" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -22548,10 +22506,10 @@
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="H9" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -22562,10 +22520,10 @@
         <v>518</v>
       </c>
       <c r="C10" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D10" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -22574,10 +22532,10 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H10" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -22588,10 +22546,10 @@
         <v>518</v>
       </c>
       <c r="C11" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D11" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E11">
         <v>14</v>
@@ -22600,10 +22558,10 @@
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H11" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -22614,10 +22572,10 @@
         <v>518</v>
       </c>
       <c r="C12" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D12" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E12">
         <v>14</v>
@@ -22626,10 +22584,10 @@
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H12" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -22640,10 +22598,10 @@
         <v>518</v>
       </c>
       <c r="C13" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D13" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E13">
         <v>13</v>
@@ -22652,10 +22610,10 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H13" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -22666,10 +22624,10 @@
         <v>518</v>
       </c>
       <c r="C14" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D14" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E14">
         <v>14</v>
@@ -22678,10 +22636,10 @@
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="H14" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -22692,10 +22650,10 @@
         <v>518</v>
       </c>
       <c r="C15" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D15" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E15">
         <v>11</v>
@@ -22704,10 +22662,10 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="H15" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -22718,10 +22676,10 @@
         <v>518</v>
       </c>
       <c r="C16" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D16" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E16">
         <v>14</v>
@@ -22730,10 +22688,10 @@
         <v>6</v>
       </c>
       <c r="G16" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="H16" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -22744,10 +22702,10 @@
         <v>518</v>
       </c>
       <c r="C17" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D17" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E17">
         <v>6</v>
@@ -22756,10 +22714,10 @@
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="H17" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -22770,10 +22728,10 @@
         <v>518</v>
       </c>
       <c r="C18" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D18" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E18">
         <v>13</v>
@@ -22782,10 +22740,10 @@
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H18" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -22796,10 +22754,10 @@
         <v>518</v>
       </c>
       <c r="C19" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D19" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -22808,10 +22766,10 @@
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H19" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -22822,10 +22780,10 @@
         <v>518</v>
       </c>
       <c r="C20" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D20" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E20">
         <v>14</v>
@@ -22834,10 +22792,10 @@
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H20" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -22848,10 +22806,10 @@
         <v>518</v>
       </c>
       <c r="C21" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D21" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -22860,10 +22818,10 @@
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H21" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -22874,10 +22832,10 @@
         <v>518</v>
       </c>
       <c r="C22" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D22" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -22886,10 +22844,10 @@
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H22" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -22900,10 +22858,10 @@
         <v>518</v>
       </c>
       <c r="C23" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D23" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -22912,10 +22870,10 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H23" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -22926,10 +22884,10 @@
         <v>522</v>
       </c>
       <c r="C24" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D24" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -22938,10 +22896,10 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H24" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -22952,10 +22910,10 @@
         <v>522</v>
       </c>
       <c r="C25" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D25" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E25">
         <v>13</v>
@@ -22964,10 +22922,10 @@
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="H25" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -22978,10 +22936,10 @@
         <v>522</v>
       </c>
       <c r="C26" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D26" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E26">
         <v>14</v>
@@ -22990,10 +22948,10 @@
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H26" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -23004,10 +22962,10 @@
         <v>522</v>
       </c>
       <c r="C27" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D27" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E27">
         <v>5</v>
@@ -23016,10 +22974,10 @@
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H27" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -23030,10 +22988,10 @@
         <v>521</v>
       </c>
       <c r="C28" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D28" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E28">
         <v>14</v>
@@ -23042,10 +23000,10 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H28" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -23056,10 +23014,10 @@
         <v>522</v>
       </c>
       <c r="C29" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D29" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -23068,10 +23026,10 @@
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="H29" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -23082,10 +23040,10 @@
         <v>523</v>
       </c>
       <c r="C30" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D30" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E30">
         <v>5</v>
@@ -23094,10 +23052,10 @@
         <v>538</v>
       </c>
       <c r="G30" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H30" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -23108,10 +23066,10 @@
         <v>523</v>
       </c>
       <c r="C31" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D31" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E31">
         <v>13</v>
@@ -23120,10 +23078,10 @@
         <v>538</v>
       </c>
       <c r="G31" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="H31" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -23131,13 +23089,13 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="C32" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D32" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -23146,10 +23104,10 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H32" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -23157,13 +23115,13 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="C33" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D33" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -23172,10 +23130,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H33" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -23186,10 +23144,10 @@
         <v>522</v>
       </c>
       <c r="C34" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D34" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -23198,10 +23156,10 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H34" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -23209,13 +23167,13 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="C35" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D35" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -23224,10 +23182,10 @@
         <v>5</v>
       </c>
       <c r="G35" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H35" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -23238,10 +23196,10 @@
         <v>522</v>
       </c>
       <c r="C36" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D36" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E36">
         <v>7</v>
@@ -23250,10 +23208,10 @@
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H36" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -23264,10 +23222,10 @@
         <v>521</v>
       </c>
       <c r="C37" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D37" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -23276,10 +23234,10 @@
         <v>2</v>
       </c>
       <c r="G37" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H37" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -23287,13 +23245,13 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="C38" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D38" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E38">
         <v>7</v>
@@ -23302,10 +23260,10 @@
         <v>7</v>
       </c>
       <c r="G38" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H38" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -23313,13 +23271,13 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="C39" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D39" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E39">
         <v>7</v>
@@ -23328,10 +23286,10 @@
         <v>7</v>
       </c>
       <c r="G39" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H39" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -23339,13 +23297,13 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="C40" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="D40" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -23354,10 +23312,10 @@
         <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H40" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -23365,22 +23323,22 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="C41" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="D41" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E41">
         <v>6</v>
       </c>
       <c r="G41" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H41" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -23391,22 +23349,22 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="C42" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="D42" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E42">
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H42" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="J42">
         <v>2</v>
@@ -23417,13 +23375,13 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="C43" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="D43" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -23432,10 +23390,10 @@
         <v>6</v>
       </c>
       <c r="G43" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H43" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="J43">
         <v>3</v>
@@ -23483,13 +23441,13 @@
         <v>532</v>
       </c>
       <c r="L1" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="M1" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="N1" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -23497,13 +23455,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="C2" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D2" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -23518,7 +23476,7 @@
         <v>538</v>
       </c>
       <c r="I2" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -23526,13 +23484,13 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="C3" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D3" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -23547,7 +23505,7 @@
         <v>538</v>
       </c>
       <c r="I3" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -23555,13 +23513,13 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="C4" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D4" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -23576,7 +23534,7 @@
         <v>538</v>
       </c>
       <c r="I4" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -23584,13 +23542,13 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="C5" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D5" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -23605,7 +23563,7 @@
         <v>538</v>
       </c>
       <c r="I5" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -23616,7 +23574,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D6">
         <v>9</v>
@@ -23628,13 +23586,13 @@
         <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H6" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I6" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -23645,7 +23603,7 @@
         <v>219</v>
       </c>
       <c r="C7" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D7">
         <v>219</v>
@@ -23657,13 +23615,13 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H7" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I7" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -23674,7 +23632,7 @@
         <v>220</v>
       </c>
       <c r="C8" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D8">
         <v>220</v>
@@ -23686,13 +23644,13 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H8" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I8" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -23703,7 +23661,7 @@
         <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D9">
         <v>194</v>
@@ -23715,13 +23673,13 @@
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H9" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I9" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -23732,7 +23690,7 @@
         <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D10">
         <v>158</v>
@@ -23744,13 +23702,13 @@
         <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H10" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I10" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -23761,7 +23719,7 @@
         <v>247</v>
       </c>
       <c r="C11" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D11">
         <v>247</v>
@@ -23773,13 +23731,13 @@
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H11" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I11" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -23790,7 +23748,7 @@
         <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D12">
         <v>88</v>
@@ -23802,13 +23760,13 @@
         <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H12" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I12" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -23819,7 +23777,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -23831,13 +23789,13 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H13" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I13" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -23848,7 +23806,7 @@
         <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D14">
         <v>152</v>
@@ -23860,13 +23818,13 @@
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H14" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I14" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -23874,13 +23832,13 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="C15" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D15" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -23895,7 +23853,7 @@
         <v>538</v>
       </c>
       <c r="I15" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -23903,13 +23861,13 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="C16" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D16" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="E16">
         <v>14</v>
@@ -23924,7 +23882,7 @@
         <v>538</v>
       </c>
       <c r="I16" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -23932,13 +23890,13 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="C17" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D17" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="E17">
         <v>14</v>
@@ -23953,7 +23911,7 @@
         <v>538</v>
       </c>
       <c r="I17" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -23961,13 +23919,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="C18" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D18" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="E18">
         <v>14</v>
@@ -23982,7 +23940,7 @@
         <v>538</v>
       </c>
       <c r="I18" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -23993,7 +23951,7 @@
         <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D19">
         <v>73</v>
@@ -24005,13 +23963,13 @@
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H19" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I19" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -24022,7 +23980,7 @@
         <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D20">
         <v>241</v>
@@ -24034,13 +23992,13 @@
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H20" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I20" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -24051,7 +24009,7 @@
         <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D21">
         <v>121</v>
@@ -24063,13 +24021,13 @@
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H21" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I21" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -24080,7 +24038,7 @@
         <v>177</v>
       </c>
       <c r="C22" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D22">
         <v>177</v>
@@ -24092,13 +24050,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H22" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I22" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -24109,7 +24067,7 @@
         <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D23">
         <v>66</v>
@@ -24121,13 +24079,13 @@
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H23" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I23" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -24138,7 +24096,7 @@
         <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D24">
         <v>145</v>
@@ -24150,13 +24108,13 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H24" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I24" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -24167,7 +24125,7 @@
         <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D25">
         <v>56</v>
@@ -24179,13 +24137,13 @@
         <v>6</v>
       </c>
       <c r="G25" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H25" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I25" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -24196,7 +24154,7 @@
         <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D26">
         <v>93</v>
@@ -24208,13 +24166,13 @@
         <v>6</v>
       </c>
       <c r="G26" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H26" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I26" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -24225,7 +24183,7 @@
         <v>161</v>
       </c>
       <c r="C27" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D27">
         <v>161</v>
@@ -24237,13 +24195,13 @@
         <v>6</v>
       </c>
       <c r="G27" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H27" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I27" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -24251,13 +24209,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="C28" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D28" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="E28">
         <v>14</v>
@@ -24272,7 +24230,7 @@
         <v>538</v>
       </c>
       <c r="I28" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -24280,13 +24238,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="C29" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D29" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="E29">
         <v>13</v>
@@ -24301,7 +24259,7 @@
         <v>538</v>
       </c>
       <c r="I29" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -24309,13 +24267,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="C30" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D30" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="E30">
         <v>13</v>
@@ -24330,7 +24288,7 @@
         <v>538</v>
       </c>
       <c r="I30" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -24338,13 +24296,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="C31" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D31" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="E31">
         <v>5</v>
@@ -24359,7 +24317,7 @@
         <v>538</v>
       </c>
       <c r="I31" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -24370,7 +24328,7 @@
         <v>409</v>
       </c>
       <c r="C32" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D32">
         <v>409</v>
@@ -24382,13 +24340,13 @@
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H32" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I32" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -24399,7 +24357,7 @@
         <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D33">
         <v>48</v>
@@ -24411,13 +24369,13 @@
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H33" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I33" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -24428,7 +24386,7 @@
         <v>414</v>
       </c>
       <c r="C34" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D34">
         <v>414</v>
@@ -24440,13 +24398,13 @@
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H34" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I34" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -24457,7 +24415,7 @@
         <v>238</v>
       </c>
       <c r="C35" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D35">
         <v>238</v>
@@ -24469,13 +24427,13 @@
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H35" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I35" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -24486,7 +24444,7 @@
         <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D36">
         <v>133</v>
@@ -24498,13 +24456,13 @@
         <v>5</v>
       </c>
       <c r="G36" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H36" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I36" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -24515,7 +24473,7 @@
         <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D37">
         <v>143</v>
@@ -24527,13 +24485,13 @@
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H37" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I37" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -24544,7 +24502,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D38">
         <v>72</v>
@@ -24556,13 +24514,13 @@
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H38" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I38" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -24573,7 +24531,7 @@
         <v>219</v>
       </c>
       <c r="C39" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D39">
         <v>219</v>
@@ -24585,13 +24543,13 @@
         <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H39" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I39" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -24602,7 +24560,7 @@
         <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D40">
         <v>49</v>
@@ -24614,13 +24572,13 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H40" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I40" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -24628,13 +24586,13 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="C41" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D41" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="E41">
         <v>5</v>
@@ -24649,7 +24607,7 @@
         <v>538</v>
       </c>
       <c r="I41" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -24660,7 +24618,7 @@
         <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D42">
         <v>92</v>
@@ -24672,13 +24630,13 @@
         <v>5</v>
       </c>
       <c r="G42" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H42" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I42" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -24689,7 +24647,7 @@
         <v>241</v>
       </c>
       <c r="C43" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D43">
         <v>241</v>
@@ -24701,13 +24659,13 @@
         <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H43" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I43" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -24718,7 +24676,7 @@
         <v>259</v>
       </c>
       <c r="C44" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D44">
         <v>259</v>
@@ -24730,13 +24688,13 @@
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H44" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I44" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -24747,7 +24705,7 @@
         <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D45">
         <v>133</v>
@@ -24759,13 +24717,13 @@
         <v>5</v>
       </c>
       <c r="G45" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H45" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I45" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -24776,7 +24734,7 @@
         <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D46">
         <v>139</v>
@@ -24788,13 +24746,13 @@
         <v>5</v>
       </c>
       <c r="G46" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="H46" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I46" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -24805,7 +24763,7 @@
         <v>273</v>
       </c>
       <c r="C47" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D47">
         <v>273</v>
@@ -24817,13 +24775,13 @@
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="H47" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I47" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -24834,7 +24792,7 @@
         <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D48">
         <v>49</v>
@@ -24846,13 +24804,13 @@
         <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H48" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I48" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -24863,7 +24821,7 @@
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D49">
         <v>8</v>
@@ -24875,13 +24833,13 @@
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H49" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I49" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -24892,7 +24850,7 @@
         <v>290</v>
       </c>
       <c r="C50" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D50">
         <v>290</v>
@@ -24904,13 +24862,13 @@
         <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H50" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I50" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -24921,7 +24879,7 @@
         <v>209</v>
       </c>
       <c r="C51" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D51">
         <v>209</v>
@@ -24933,16 +24891,16 @@
         <v>538</v>
       </c>
       <c r="G51" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H51" t="s">
         <v>538</v>
       </c>
       <c r="I51" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="J51" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -24953,7 +24911,7 @@
         <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D52">
         <v>94</v>
@@ -24965,16 +24923,16 @@
         <v>538</v>
       </c>
       <c r="G52" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H52" t="s">
         <v>538</v>
       </c>
       <c r="I52" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="J52" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -24985,7 +24943,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D53">
         <v>420</v>
@@ -25003,7 +24961,7 @@
         <v>534</v>
       </c>
       <c r="I53" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -25014,10 +24972,10 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D54" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="E54">
         <v>6</v>
@@ -25026,7 +24984,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -25037,7 +24995,7 @@
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D55">
         <v>419</v>
@@ -25055,7 +25013,7 @@
         <v>534</v>
       </c>
       <c r="I55" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -25066,10 +25024,10 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D56" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="E56">
         <v>6</v>
@@ -25078,7 +25036,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -25089,7 +25047,7 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D57">
         <v>421</v>
@@ -25107,7 +25065,7 @@
         <v>537</v>
       </c>
       <c r="I57" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -25118,7 +25076,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D58">
         <v>130</v>
@@ -25136,7 +25094,7 @@
         <v>534</v>
       </c>
       <c r="I58" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -25147,10 +25105,10 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D59" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="E59">
         <v>5</v>
@@ -25159,7 +25117,7 @@
         <v>7</v>
       </c>
       <c r="I59" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -25170,10 +25128,10 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D60" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="E60">
         <v>5</v>
@@ -25182,7 +25140,7 @@
         <v>7</v>
       </c>
       <c r="I60" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -25193,7 +25151,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D61">
         <v>49</v>
@@ -25205,13 +25163,13 @@
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="H61" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I61" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -25222,7 +25180,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D62">
         <v>423</v>
@@ -25240,7 +25198,7 @@
         <v>537</v>
       </c>
       <c r="I62" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -25251,7 +25209,7 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D63">
         <v>435</v>
@@ -25269,7 +25227,7 @@
         <v>537</v>
       </c>
       <c r="I63" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -25280,7 +25238,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D64">
         <v>437</v>
@@ -25298,7 +25256,7 @@
         <v>537</v>
       </c>
       <c r="I64" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -25309,7 +25267,7 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D65">
         <v>434</v>
@@ -25327,7 +25285,7 @@
         <v>537</v>
       </c>
       <c r="I65" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -25338,7 +25296,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D66">
         <v>437</v>
@@ -25356,7 +25314,7 @@
         <v>534</v>
       </c>
       <c r="I66" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -25367,7 +25325,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D67">
         <v>437</v>
@@ -25385,7 +25343,7 @@
         <v>537</v>
       </c>
       <c r="I67" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -25396,7 +25354,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D68">
         <v>434</v>
@@ -25414,7 +25372,7 @@
         <v>534</v>
       </c>
       <c r="I68" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -25425,10 +25383,10 @@
         <v>1</v>
       </c>
       <c r="C69" t="s">
+        <v>575</v>
+      </c>
+      <c r="D69" t="s">
         <v>589</v>
-      </c>
-      <c r="D69" t="s">
-        <v>603</v>
       </c>
       <c r="E69">
         <v>2</v>
@@ -25437,7 +25395,7 @@
         <v>13</v>
       </c>
       <c r="I69" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -25448,10 +25406,10 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D70" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="E70">
         <v>13</v>
@@ -25460,7 +25418,7 @@
         <v>2</v>
       </c>
       <c r="I70" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -25471,7 +25429,7 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D71">
         <v>93</v>
@@ -25483,7 +25441,7 @@
         <v>534</v>
       </c>
       <c r="I71" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -25494,7 +25452,7 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D72">
         <v>158</v>
@@ -25506,7 +25464,7 @@
         <v>534</v>
       </c>
       <c r="I72" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -25517,7 +25475,7 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D73">
         <v>419</v>
@@ -25543,7 +25501,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D74">
         <v>444</v>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Evolucoes/Fantasy unificado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8CEADB7-D625-4CA9-8123-BD4FA2F3FDF8}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C5E5BD-639C-424F-90AB-AB669A451335}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2218,10 +2218,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21875,7 +21871,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G274"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -21920,12 +21916,6 @@
         <f>VLOOKUP(B2,teams!$A$1:$B$15,2)</f>
         <v>Tchêltics da Peleia</v>
       </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
         <v>5</v>
       </c>
@@ -21945,12 +21935,6 @@
         <f>VLOOKUP(B3,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
         <v>1</v>
       </c>
@@ -21970,12 +21954,6 @@
         <f>VLOOKUP(B4,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="F4">
         <v>4</v>
       </c>
@@ -21995,12 +21973,6 @@
         <f>VLOOKUP(B5,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
       <c r="F5">
         <v>2</v>
       </c>
@@ -22020,12 +21992,6 @@
         <f>VLOOKUP(B6,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
       <c r="F6">
         <v>12</v>
       </c>
@@ -22045,12 +22011,6 @@
         <f>VLOOKUP(B7,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
       <c r="F7">
         <v>11</v>
       </c>
@@ -22070,12 +22030,6 @@
         <f>VLOOKUP(B8,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
       <c r="F8">
         <v>10</v>
       </c>
@@ -22095,12 +22049,6 @@
         <f>VLOOKUP(B9,teams!$A$1:$B$15,2)</f>
         <v>Tchêltics da Peleia</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
       <c r="F9">
         <v>6</v>
       </c>
@@ -22120,12 +22068,6 @@
         <f>VLOOKUP(B10,teams!$A$1:$B$15,2)</f>
         <v>Kaipiras da Gema</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>6</v>
-      </c>
       <c r="F10">
         <v>10</v>
       </c>
@@ -22145,12 +22087,6 @@
         <f>VLOOKUP(B11,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>3</v>
-      </c>
       <c r="F11">
         <v>1</v>
       </c>
@@ -22170,12 +22106,6 @@
         <f>VLOOKUP(B12,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>4</v>
-      </c>
       <c r="F12">
         <v>4</v>
       </c>
@@ -22195,12 +22125,6 @@
         <f>VLOOKUP(B13,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>3</v>
-      </c>
       <c r="F13">
         <v>2</v>
       </c>
@@ -22220,12 +22144,6 @@
         <f>VLOOKUP(B14,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-      <c r="D14">
-        <v>6</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
       <c r="F14">
         <v>12</v>
       </c>
@@ -22245,18 +22163,4933 @@
         <f>VLOOKUP(B15,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
       <c r="F15">
         <v>11</v>
       </c>
       <c r="G15" t="str">
         <f>VLOOKUP(F15,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" t="str">
+        <f>VLOOKUP(B16,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16" t="str">
+        <f>VLOOKUP(F16,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17" t="str">
+        <f>VLOOKUP(B17,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F17">
+        <v>8</v>
+      </c>
+      <c r="G17" t="str">
+        <f>VLOOKUP(F17,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" t="str">
+        <f>VLOOKUP(B18,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18" t="str">
+        <f>VLOOKUP(F18,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19" t="str">
+        <f>VLOOKUP(B19,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <f>VLOOKUP(F19,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>11</v>
+      </c>
+      <c r="C20" t="str">
+        <f>VLOOKUP(B20,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20" t="str">
+        <f>VLOOKUP(F20,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>13</v>
+      </c>
+      <c r="C21" t="str">
+        <f>VLOOKUP(B21,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="str">
+        <f>VLOOKUP(F21,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22" t="str">
+        <f>VLOOKUP(B22,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F22">
+        <v>12</v>
+      </c>
+      <c r="G22" t="str">
+        <f>VLOOKUP(F22,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23" t="str">
+        <f>VLOOKUP(B23,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F23">
+        <v>8</v>
+      </c>
+      <c r="G23" t="str">
+        <f>VLOOKUP(F23,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>14</v>
+      </c>
+      <c r="C24" t="str">
+        <f>VLOOKUP(B24,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24" t="str">
+        <f>VLOOKUP(F24,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="str">
+        <f>VLOOKUP(B25,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="str">
+        <f>VLOOKUP(F25,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>11</v>
+      </c>
+      <c r="C26" t="str">
+        <f>VLOOKUP(B26,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F26">
+        <v>12</v>
+      </c>
+      <c r="G26" t="str">
+        <f>VLOOKUP(F26,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" t="str">
+        <f>VLOOKUP(B27,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F27">
+        <v>10</v>
+      </c>
+      <c r="G27" t="str">
+        <f>VLOOKUP(F27,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28" t="str">
+        <f>VLOOKUP(B28,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F28">
+        <v>13</v>
+      </c>
+      <c r="G28" t="str">
+        <f>VLOOKUP(F28,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29" t="str">
+        <f>VLOOKUP(B29,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29" t="str">
+        <f>VLOOKUP(F29,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="str">
+        <f>VLOOKUP(B30,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F30">
+        <v>9</v>
+      </c>
+      <c r="G30" t="str">
+        <f>VLOOKUP(F30,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>14</v>
+      </c>
+      <c r="C31" t="str">
+        <f>VLOOKUP(B31,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" t="str">
+        <f>VLOOKUP(F31,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32" t="str">
+        <f>VLOOKUP(B32,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32" t="str">
+        <f>VLOOKUP(F32,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33" t="str">
+        <f>VLOOKUP(B33,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="str">
+        <f>VLOOKUP(F33,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>11</v>
+      </c>
+      <c r="C34" t="str">
+        <f>VLOOKUP(B34,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34" t="str">
+        <f>VLOOKUP(F34,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>13</v>
+      </c>
+      <c r="C35" t="str">
+        <f>VLOOKUP(B35,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="str">
+        <f>VLOOKUP(F35,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>10</v>
+      </c>
+      <c r="C36" t="str">
+        <f>VLOOKUP(B36,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F36">
+        <v>12</v>
+      </c>
+      <c r="G36" t="str">
+        <f>VLOOKUP(F36,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>5</v>
+      </c>
+      <c r="C37" t="str">
+        <f>VLOOKUP(B37,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" t="str">
+        <f>VLOOKUP(F37,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>14</v>
+      </c>
+      <c r="C38" t="str">
+        <f>VLOOKUP(B38,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F38">
+        <v>13</v>
+      </c>
+      <c r="G38" t="str">
+        <f>VLOOKUP(F38,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="str">
+        <f>VLOOKUP(B39,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39" t="str">
+        <f>VLOOKUP(F39,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="str">
+        <f>VLOOKUP(B40,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40" t="str">
+        <f>VLOOKUP(F40,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>12</v>
+      </c>
+      <c r="C41" t="str">
+        <f>VLOOKUP(B41,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="str">
+        <f>VLOOKUP(F41,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="str">
+        <f>VLOOKUP(B42,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42" t="str">
+        <f>VLOOKUP(F42,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43" t="str">
+        <f>VLOOKUP(B43,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="str">
+        <f>VLOOKUP(F43,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44" t="str">
+        <f>VLOOKUP(B44,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F44">
+        <v>13</v>
+      </c>
+      <c r="G44" t="str">
+        <f>VLOOKUP(F44,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="str">
+        <f>VLOOKUP(B45,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F45">
+        <v>7</v>
+      </c>
+      <c r="G45" t="str">
+        <f>VLOOKUP(F45,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>8</v>
+      </c>
+      <c r="C46" t="str">
+        <f>VLOOKUP(B46,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F46">
+        <v>9</v>
+      </c>
+      <c r="G46" t="str">
+        <f>VLOOKUP(F46,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47" t="str">
+        <f>VLOOKUP(B47,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47" t="str">
+        <f>VLOOKUP(F47,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48" t="str">
+        <f>VLOOKUP(B48,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F48">
+        <v>6</v>
+      </c>
+      <c r="G48" t="str">
+        <f>VLOOKUP(F48,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49" t="str">
+        <f>VLOOKUP(B49,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F49">
+        <v>12</v>
+      </c>
+      <c r="G49" t="str">
+        <f>VLOOKUP(F49,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="str">
+        <f>VLOOKUP(B50,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F50">
+        <v>11</v>
+      </c>
+      <c r="G50" t="str">
+        <f>VLOOKUP(F50,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="str">
+        <f>VLOOKUP(B51,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F51">
+        <v>7</v>
+      </c>
+      <c r="G51" t="str">
+        <f>VLOOKUP(F51,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>14</v>
+      </c>
+      <c r="C52" t="str">
+        <f>VLOOKUP(B52,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F52">
+        <v>11</v>
+      </c>
+      <c r="G52" t="str">
+        <f>VLOOKUP(F52,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>8</v>
+      </c>
+      <c r="C53" t="str">
+        <f>VLOOKUP(B53,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53" t="str">
+        <f>VLOOKUP(F53,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>9</v>
+      </c>
+      <c r="C54" t="str">
+        <f>VLOOKUP(B54,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F54">
+        <v>10</v>
+      </c>
+      <c r="G54" t="str">
+        <f>VLOOKUP(F54,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="str">
+        <f>VLOOKUP(B55,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="G55" t="str">
+        <f>VLOOKUP(F55,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="str">
+        <f>VLOOKUP(B56,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F56">
+        <v>12</v>
+      </c>
+      <c r="G56" t="str">
+        <f>VLOOKUP(F56,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>6</v>
+      </c>
+      <c r="C57" t="str">
+        <f>VLOOKUP(B57,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F57">
+        <v>13</v>
+      </c>
+      <c r="G57" t="str">
+        <f>VLOOKUP(F57,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+      <c r="C58" t="str">
+        <f>VLOOKUP(B58,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F58">
+        <v>11</v>
+      </c>
+      <c r="G58" t="str">
+        <f>VLOOKUP(F58,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>14</v>
+      </c>
+      <c r="C59" t="str">
+        <f>VLOOKUP(B59,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F59">
+        <v>12</v>
+      </c>
+      <c r="G59" t="str">
+        <f>VLOOKUP(F59,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60" t="str">
+        <f>VLOOKUP(B60,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F60">
+        <v>13</v>
+      </c>
+      <c r="G60" t="str">
+        <f>VLOOKUP(F60,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>9</v>
+      </c>
+      <c r="C61" t="str">
+        <f>VLOOKUP(B61,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61" t="str">
+        <f>VLOOKUP(F61,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="str">
+        <f>VLOOKUP(B62,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62" t="str">
+        <f>VLOOKUP(F62,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63" t="str">
+        <f>VLOOKUP(B63,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F63">
+        <v>10</v>
+      </c>
+      <c r="G63" t="str">
+        <f>VLOOKUP(F63,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>7</v>
+      </c>
+      <c r="C64" t="str">
+        <f>VLOOKUP(B64,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F64">
+        <v>6</v>
+      </c>
+      <c r="G64" t="str">
+        <f>VLOOKUP(F64,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+      <c r="C65" t="str">
+        <f>VLOOKUP(B65,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F65">
+        <v>12</v>
+      </c>
+      <c r="G65" t="str">
+        <f>VLOOKUP(F65,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>14</v>
+      </c>
+      <c r="C66" t="str">
+        <f>VLOOKUP(B66,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66" t="str">
+        <f>VLOOKUP(F66,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>8</v>
+      </c>
+      <c r="C67" t="str">
+        <f>VLOOKUP(B67,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F67">
+        <v>7</v>
+      </c>
+      <c r="G67" t="str">
+        <f>VLOOKUP(F67,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>9</v>
+      </c>
+      <c r="C68" t="str">
+        <f>VLOOKUP(B68,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F68">
+        <v>13</v>
+      </c>
+      <c r="G68" t="str">
+        <f>VLOOKUP(F68,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
+      </c>
+      <c r="C69" t="str">
+        <f>VLOOKUP(B69,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F69">
+        <v>10</v>
+      </c>
+      <c r="G69" t="str">
+        <f>VLOOKUP(F69,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>4</v>
+      </c>
+      <c r="C70" t="str">
+        <f>VLOOKUP(B70,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="str">
+        <f>VLOOKUP(F70,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>6</v>
+      </c>
+      <c r="C71" t="str">
+        <f>VLOOKUP(B71,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F71">
+        <v>11</v>
+      </c>
+      <c r="G71" t="str">
+        <f>VLOOKUP(F71,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>5</v>
+      </c>
+      <c r="C72" t="str">
+        <f>VLOOKUP(B72,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72" t="str">
+        <f>VLOOKUP(F72,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>14</v>
+      </c>
+      <c r="C73" t="str">
+        <f>VLOOKUP(B73,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F73">
+        <v>4</v>
+      </c>
+      <c r="G73" t="str">
+        <f>VLOOKUP(F73,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>8</v>
+      </c>
+      <c r="C74" t="str">
+        <f>VLOOKUP(B74,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F74">
+        <v>11</v>
+      </c>
+      <c r="G74" t="str">
+        <f>VLOOKUP(F74,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>9</v>
+      </c>
+      <c r="C75" t="str">
+        <f>VLOOKUP(B75,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F75">
+        <v>7</v>
+      </c>
+      <c r="G75" t="str">
+        <f>VLOOKUP(F75,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>3</v>
+      </c>
+      <c r="C76" t="str">
+        <f>VLOOKUP(B76,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F76">
+        <v>13</v>
+      </c>
+      <c r="G76" t="str">
+        <f>VLOOKUP(F76,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>6</v>
+      </c>
+      <c r="C77" t="str">
+        <f>VLOOKUP(B77,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F77">
+        <v>12</v>
+      </c>
+      <c r="G77" t="str">
+        <f>VLOOKUP(F77,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>10</v>
+      </c>
+      <c r="C78" t="str">
+        <f>VLOOKUP(B78,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" t="str">
+        <f>VLOOKUP(F78,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>5</v>
+      </c>
+      <c r="C79" t="str">
+        <f>VLOOKUP(B79,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F79">
+        <v>4</v>
+      </c>
+      <c r="G79" t="str">
+        <f>VLOOKUP(F79,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>14</v>
+      </c>
+      <c r="C80" t="str">
+        <f>VLOOKUP(B80,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" t="str">
+        <f>VLOOKUP(F80,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>8</v>
+      </c>
+      <c r="C81" t="str">
+        <f>VLOOKUP(B81,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F81">
+        <v>12</v>
+      </c>
+      <c r="G81" t="str">
+        <f>VLOOKUP(F81,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>9</v>
+      </c>
+      <c r="C82" t="str">
+        <f>VLOOKUP(B82,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F82">
+        <v>11</v>
+      </c>
+      <c r="G82" t="str">
+        <f>VLOOKUP(F82,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>6</v>
+      </c>
+      <c r="C83" t="str">
+        <f>VLOOKUP(B83,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83" t="str">
+        <f>VLOOKUP(F83,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>13</v>
+      </c>
+      <c r="C84" t="str">
+        <f>VLOOKUP(B84,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84" t="str">
+        <f>VLOOKUP(F84,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7</v>
+      </c>
+      <c r="C85" t="str">
+        <f>VLOOKUP(B85,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="G85" t="str">
+        <f>VLOOKUP(F85,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>5</v>
+      </c>
+      <c r="C86" t="str">
+        <f>VLOOKUP(B86,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86" t="str">
+        <f>VLOOKUP(F86,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>14</v>
+      </c>
+      <c r="C87" t="str">
+        <f>VLOOKUP(B87,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F87">
+        <v>10</v>
+      </c>
+      <c r="G87" t="str">
+        <f>VLOOKUP(F87,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>8</v>
+      </c>
+      <c r="C88" t="str">
+        <f>VLOOKUP(B88,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88" t="str">
+        <f>VLOOKUP(F88,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>9</v>
+      </c>
+      <c r="C89" t="str">
+        <f>VLOOKUP(B89,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F89">
+        <v>12</v>
+      </c>
+      <c r="G89" t="str">
+        <f>VLOOKUP(F89,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>3</v>
+      </c>
+      <c r="C90" t="str">
+        <f>VLOOKUP(B90,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F90">
+        <v>11</v>
+      </c>
+      <c r="G90" t="str">
+        <f>VLOOKUP(F90,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>13</v>
+      </c>
+      <c r="C91" t="str">
+        <f>VLOOKUP(B91,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F91">
+        <v>7</v>
+      </c>
+      <c r="G91" t="str">
+        <f>VLOOKUP(F91,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>6</v>
+      </c>
+      <c r="C92" t="str">
+        <f>VLOOKUP(B92,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F92">
+        <v>4</v>
+      </c>
+      <c r="G92" t="str">
+        <f>VLOOKUP(F92,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>14</v>
+      </c>
+      <c r="C93" t="str">
+        <f>VLOOKUP(B93,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F93">
+        <v>5</v>
+      </c>
+      <c r="G93" t="str">
+        <f>VLOOKUP(F93,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>6</v>
+      </c>
+      <c r="C94" t="str">
+        <f>VLOOKUP(B94,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94" t="str">
+        <f>VLOOKUP(F94,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95" t="str">
+        <f>VLOOKUP(B95,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F95">
+        <v>4</v>
+      </c>
+      <c r="G95" t="str">
+        <f>VLOOKUP(F95,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>9</v>
+      </c>
+      <c r="C96" t="str">
+        <f>VLOOKUP(B96,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F96">
+        <v>2</v>
+      </c>
+      <c r="G96" t="str">
+        <f>VLOOKUP(F96,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>3</v>
+      </c>
+      <c r="C97" t="str">
+        <f>VLOOKUP(B97,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F97">
+        <v>12</v>
+      </c>
+      <c r="G97" t="str">
+        <f>VLOOKUP(F97,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>13</v>
+      </c>
+      <c r="C98" t="str">
+        <f>VLOOKUP(B98,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F98">
+        <v>11</v>
+      </c>
+      <c r="G98" t="str">
+        <f>VLOOKUP(F98,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7</v>
+      </c>
+      <c r="C99" t="str">
+        <f>VLOOKUP(B99,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F99">
+        <v>10</v>
+      </c>
+      <c r="G99" t="str">
+        <f>VLOOKUP(F99,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>14</v>
+      </c>
+      <c r="C100" t="str">
+        <f>VLOOKUP(B100,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F100">
+        <v>6</v>
+      </c>
+      <c r="G100" t="str">
+        <f>VLOOKUP(F100,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>5</v>
+      </c>
+      <c r="C101" t="str">
+        <f>VLOOKUP(B101,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F101">
+        <v>10</v>
+      </c>
+      <c r="G101" t="str">
+        <f>VLOOKUP(F101,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>8</v>
+      </c>
+      <c r="C102" t="str">
+        <f>VLOOKUP(B102,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102" t="str">
+        <f>VLOOKUP(F102,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>9</v>
+      </c>
+      <c r="C103" t="str">
+        <f>VLOOKUP(B103,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F103">
+        <v>4</v>
+      </c>
+      <c r="G103" t="str">
+        <f>VLOOKUP(F103,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>3</v>
+      </c>
+      <c r="C104" t="str">
+        <f>VLOOKUP(B104,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="G104" t="str">
+        <f>VLOOKUP(F104,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>13</v>
+      </c>
+      <c r="C105" t="str">
+        <f>VLOOKUP(B105,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F105">
+        <v>12</v>
+      </c>
+      <c r="G105" t="str">
+        <f>VLOOKUP(F105,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7</v>
+      </c>
+      <c r="C106" t="str">
+        <f>VLOOKUP(B106,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F106">
+        <v>11</v>
+      </c>
+      <c r="G106" t="str">
+        <f>VLOOKUP(F106,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>5</v>
+      </c>
+      <c r="C107" t="str">
+        <f>VLOOKUP(B107,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F107">
+        <v>6</v>
+      </c>
+      <c r="G107" t="str">
+        <f>VLOOKUP(F107,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>14</v>
+      </c>
+      <c r="C108" t="str">
+        <f>VLOOKUP(B108,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F108">
+        <v>8</v>
+      </c>
+      <c r="G108" t="str">
+        <f>VLOOKUP(F108,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>3</v>
+      </c>
+      <c r="C109" t="str">
+        <f>VLOOKUP(B109,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F109">
+        <v>4</v>
+      </c>
+      <c r="G109" t="str">
+        <f>VLOOKUP(F109,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>9</v>
+      </c>
+      <c r="C110" t="str">
+        <f>VLOOKUP(B110,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110" t="str">
+        <f>VLOOKUP(F110,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>11</v>
+      </c>
+      <c r="C111" t="str">
+        <f>VLOOKUP(B111,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F111">
+        <v>10</v>
+      </c>
+      <c r="G111" t="str">
+        <f>VLOOKUP(F111,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>13</v>
+      </c>
+      <c r="C112" t="str">
+        <f>VLOOKUP(B112,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F112">
+        <v>2</v>
+      </c>
+      <c r="G112" t="str">
+        <f>VLOOKUP(F112,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7</v>
+      </c>
+      <c r="C113" t="str">
+        <f>VLOOKUP(B113,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F113">
+        <v>12</v>
+      </c>
+      <c r="G113" t="str">
+        <f>VLOOKUP(F113,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>5</v>
+      </c>
+      <c r="C114" t="str">
+        <f>VLOOKUP(B114,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F114">
+        <v>8</v>
+      </c>
+      <c r="G114" t="str">
+        <f>VLOOKUP(F114,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>14</v>
+      </c>
+      <c r="C115" t="str">
+        <f>VLOOKUP(B115,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F115">
+        <v>9</v>
+      </c>
+      <c r="G115" t="str">
+        <f>VLOOKUP(F115,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="C116" t="str">
+        <f>VLOOKUP(B116,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116" t="str">
+        <f>VLOOKUP(F116,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>11</v>
+      </c>
+      <c r="C117" t="str">
+        <f>VLOOKUP(B117,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F117">
+        <v>12</v>
+      </c>
+      <c r="G117" t="str">
+        <f>VLOOKUP(F117,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>6</v>
+      </c>
+      <c r="C118" t="str">
+        <f>VLOOKUP(B118,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F118">
+        <v>10</v>
+      </c>
+      <c r="G118" t="str">
+        <f>VLOOKUP(F118,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>4</v>
+      </c>
+      <c r="C119" t="str">
+        <f>VLOOKUP(B119,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F119">
+        <v>13</v>
+      </c>
+      <c r="G119" t="str">
+        <f>VLOOKUP(F119,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7</v>
+      </c>
+      <c r="C120" t="str">
+        <f>VLOOKUP(B120,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+      <c r="G120" t="str">
+        <f>VLOOKUP(F120,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>5</v>
+      </c>
+      <c r="C121" t="str">
+        <f>VLOOKUP(B121,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F121">
+        <v>9</v>
+      </c>
+      <c r="G121" t="str">
+        <f>VLOOKUP(F121,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>14</v>
+      </c>
+      <c r="C122" t="str">
+        <f>VLOOKUP(B122,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F122">
+        <v>3</v>
+      </c>
+      <c r="G122" t="str">
+        <f>VLOOKUP(F122,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>8</v>
+      </c>
+      <c r="C123" t="str">
+        <f>VLOOKUP(B123,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F123">
+        <v>6</v>
+      </c>
+      <c r="G123" t="str">
+        <f>VLOOKUP(F123,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7</v>
+      </c>
+      <c r="C124" t="str">
+        <f>VLOOKUP(B124,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F124">
+        <v>4</v>
+      </c>
+      <c r="G124" t="str">
+        <f>VLOOKUP(F124,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>11</v>
+      </c>
+      <c r="C125" t="str">
+        <f>VLOOKUP(B125,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F125">
+        <v>2</v>
+      </c>
+      <c r="G125" t="str">
+        <f>VLOOKUP(F125,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>13</v>
+      </c>
+      <c r="C126" t="str">
+        <f>VLOOKUP(B126,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126" t="str">
+        <f>VLOOKUP(F126,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>10</v>
+      </c>
+      <c r="C127" t="str">
+        <f>VLOOKUP(B127,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F127">
+        <v>12</v>
+      </c>
+      <c r="G127" t="str">
+        <f>VLOOKUP(F127,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>5</v>
+      </c>
+      <c r="C128" t="str">
+        <f>VLOOKUP(B128,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F128">
+        <v>3</v>
+      </c>
+      <c r="G128" t="str">
+        <f>VLOOKUP(F128,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>14</v>
+      </c>
+      <c r="C129" t="str">
+        <f>VLOOKUP(B129,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F129">
+        <v>13</v>
+      </c>
+      <c r="G129" t="str">
+        <f>VLOOKUP(F129,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>8</v>
+      </c>
+      <c r="C130" t="str">
+        <f>VLOOKUP(B130,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F130">
+        <v>10</v>
+      </c>
+      <c r="G130" t="str">
+        <f>VLOOKUP(F130,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>9</v>
+      </c>
+      <c r="C131" t="str">
+        <f>VLOOKUP(B131,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F131">
+        <v>6</v>
+      </c>
+      <c r="G131" t="str">
+        <f>VLOOKUP(F131,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>12</v>
+      </c>
+      <c r="C132" t="str">
+        <f>VLOOKUP(B132,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+      <c r="G132" t="str">
+        <f>VLOOKUP(F132,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>11</v>
+      </c>
+      <c r="C133" t="str">
+        <f>VLOOKUP(B133,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F133">
+        <v>4</v>
+      </c>
+      <c r="G133" t="str">
+        <f>VLOOKUP(F133,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7</v>
+      </c>
+      <c r="C134" t="str">
+        <f>VLOOKUP(B134,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="str">
+        <f>VLOOKUP(F134,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>5</v>
+      </c>
+      <c r="C135" t="str">
+        <f>VLOOKUP(B135,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F135">
+        <v>13</v>
+      </c>
+      <c r="G135" t="str">
+        <f>VLOOKUP(F135,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>14</v>
+      </c>
+      <c r="C136" t="str">
+        <f>VLOOKUP(B136,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F136">
+        <v>7</v>
+      </c>
+      <c r="G136" t="str">
+        <f>VLOOKUP(F136,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>8</v>
+      </c>
+      <c r="C137" t="str">
+        <f>VLOOKUP(B137,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F137">
+        <v>9</v>
+      </c>
+      <c r="G137" t="str">
+        <f>VLOOKUP(F137,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>10</v>
+      </c>
+      <c r="C138" t="str">
+        <f>VLOOKUP(B138,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F138">
+        <v>2</v>
+      </c>
+      <c r="G138" t="str">
+        <f>VLOOKUP(F138,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>3</v>
+      </c>
+      <c r="C139" t="str">
+        <f>VLOOKUP(B139,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F139">
+        <v>6</v>
+      </c>
+      <c r="G139" t="str">
+        <f>VLOOKUP(F139,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>4</v>
+      </c>
+      <c r="C140" t="str">
+        <f>VLOOKUP(B140,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F140">
+        <v>12</v>
+      </c>
+      <c r="G140" t="str">
+        <f>VLOOKUP(F140,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141" t="str">
+        <f>VLOOKUP(B141,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F141">
+        <v>11</v>
+      </c>
+      <c r="G141" t="str">
+        <f>VLOOKUP(F141,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>5</v>
+      </c>
+      <c r="C142" t="str">
+        <f>VLOOKUP(B142,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F142">
+        <v>7</v>
+      </c>
+      <c r="G142" t="str">
+        <f>VLOOKUP(F142,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>14</v>
+      </c>
+      <c r="C143" t="str">
+        <f>VLOOKUP(B143,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F143">
+        <v>11</v>
+      </c>
+      <c r="G143" t="str">
+        <f>VLOOKUP(F143,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>8</v>
+      </c>
+      <c r="C144" t="str">
+        <f>VLOOKUP(B144,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F144">
+        <v>3</v>
+      </c>
+      <c r="G144" t="str">
+        <f>VLOOKUP(F144,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>9</v>
+      </c>
+      <c r="C145" t="str">
+        <f>VLOOKUP(B145,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F145">
+        <v>10</v>
+      </c>
+      <c r="G145" t="str">
+        <f>VLOOKUP(F145,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>4</v>
+      </c>
+      <c r="C146" t="str">
+        <f>VLOOKUP(B146,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F146">
+        <v>2</v>
+      </c>
+      <c r="G146" t="str">
+        <f>VLOOKUP(F146,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147" t="str">
+        <f>VLOOKUP(B147,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F147">
+        <v>12</v>
+      </c>
+      <c r="G147" t="str">
+        <f>VLOOKUP(F147,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>6</v>
+      </c>
+      <c r="C148" t="str">
+        <f>VLOOKUP(B148,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F148">
+        <v>13</v>
+      </c>
+      <c r="G148" t="str">
+        <f>VLOOKUP(F148,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>5</v>
+      </c>
+      <c r="C149" t="str">
+        <f>VLOOKUP(B149,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F149">
+        <v>11</v>
+      </c>
+      <c r="G149" t="str">
+        <f>VLOOKUP(F149,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>14</v>
+      </c>
+      <c r="C150" t="str">
+        <f>VLOOKUP(B150,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F150">
+        <v>12</v>
+      </c>
+      <c r="G150" t="str">
+        <f>VLOOKUP(F150,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>8</v>
+      </c>
+      <c r="C151" t="str">
+        <f>VLOOKUP(B151,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F151">
+        <v>13</v>
+      </c>
+      <c r="G151" t="str">
+        <f>VLOOKUP(F151,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>9</v>
+      </c>
+      <c r="C152" t="str">
+        <f>VLOOKUP(B152,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F152">
+        <v>3</v>
+      </c>
+      <c r="G152" t="str">
+        <f>VLOOKUP(F152,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153" t="str">
+        <f>VLOOKUP(B153,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+      <c r="G153" t="str">
+        <f>VLOOKUP(F153,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="C154" t="str">
+        <f>VLOOKUP(B154,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F154">
+        <v>10</v>
+      </c>
+      <c r="G154" t="str">
+        <f>VLOOKUP(F154,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7</v>
+      </c>
+      <c r="C155" t="str">
+        <f>VLOOKUP(B155,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F155">
+        <v>6</v>
+      </c>
+      <c r="G155" t="str">
+        <f>VLOOKUP(F155,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>5</v>
+      </c>
+      <c r="C156" t="str">
+        <f>VLOOKUP(B156,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F156">
+        <v>12</v>
+      </c>
+      <c r="G156" t="str">
+        <f>VLOOKUP(F156,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>14</v>
+      </c>
+      <c r="C157" t="str">
+        <f>VLOOKUP(B157,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F157">
+        <v>2</v>
+      </c>
+      <c r="G157" t="str">
+        <f>VLOOKUP(F157,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>8</v>
+      </c>
+      <c r="C158" t="str">
+        <f>VLOOKUP(B158,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F158">
+        <v>7</v>
+      </c>
+      <c r="G158" t="str">
+        <f>VLOOKUP(F158,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>9</v>
+      </c>
+      <c r="C159" t="str">
+        <f>VLOOKUP(B159,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F159">
+        <v>13</v>
+      </c>
+      <c r="G159" t="str">
+        <f>VLOOKUP(F159,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>3</v>
+      </c>
+      <c r="C160" t="str">
+        <f>VLOOKUP(B160,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F160">
+        <v>10</v>
+      </c>
+      <c r="G160" t="str">
+        <f>VLOOKUP(F160,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161" t="str">
+        <f>VLOOKUP(B161,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161" t="str">
+        <f>VLOOKUP(F161,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>6</v>
+      </c>
+      <c r="C162" t="str">
+        <f>VLOOKUP(B162,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F162">
+        <v>11</v>
+      </c>
+      <c r="G162" t="str">
+        <f>VLOOKUP(F162,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>5</v>
+      </c>
+      <c r="C163" t="str">
+        <f>VLOOKUP(B163,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F163">
+        <v>2</v>
+      </c>
+      <c r="G163" t="str">
+        <f>VLOOKUP(F163,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>14</v>
+      </c>
+      <c r="C164" t="str">
+        <f>VLOOKUP(B164,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F164">
+        <v>4</v>
+      </c>
+      <c r="G164" t="str">
+        <f>VLOOKUP(F164,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>8</v>
+      </c>
+      <c r="C165" t="str">
+        <f>VLOOKUP(B165,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F165">
+        <v>11</v>
+      </c>
+      <c r="G165" t="str">
+        <f>VLOOKUP(F165,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>9</v>
+      </c>
+      <c r="C166" t="str">
+        <f>VLOOKUP(B166,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F166">
+        <v>7</v>
+      </c>
+      <c r="G166" t="str">
+        <f>VLOOKUP(F166,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>3</v>
+      </c>
+      <c r="C167" t="str">
+        <f>VLOOKUP(B167,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F167">
+        <v>13</v>
+      </c>
+      <c r="G167" t="str">
+        <f>VLOOKUP(F167,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>6</v>
+      </c>
+      <c r="C168" t="str">
+        <f>VLOOKUP(B168,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F168">
+        <v>12</v>
+      </c>
+      <c r="G168" t="str">
+        <f>VLOOKUP(F168,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>10</v>
+      </c>
+      <c r="C169" t="str">
+        <f>VLOOKUP(B169,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169" t="str">
+        <f>VLOOKUP(F169,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>5</v>
+      </c>
+      <c r="C170" t="str">
+        <f>VLOOKUP(B170,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F170">
+        <v>4</v>
+      </c>
+      <c r="G170" t="str">
+        <f>VLOOKUP(F170,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>14</v>
+      </c>
+      <c r="C171" t="str">
+        <f>VLOOKUP(B171,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171" t="str">
+        <f>VLOOKUP(F171,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>8</v>
+      </c>
+      <c r="C172" t="str">
+        <f>VLOOKUP(B172,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F172">
+        <v>12</v>
+      </c>
+      <c r="G172" t="str">
+        <f>VLOOKUP(F172,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>9</v>
+      </c>
+      <c r="C173" t="str">
+        <f>VLOOKUP(B173,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F173">
+        <v>11</v>
+      </c>
+      <c r="G173" t="str">
+        <f>VLOOKUP(F173,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>6</v>
+      </c>
+      <c r="C174" t="str">
+        <f>VLOOKUP(B174,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F174">
+        <v>2</v>
+      </c>
+      <c r="G174" t="str">
+        <f>VLOOKUP(F174,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>13</v>
+      </c>
+      <c r="C175" t="str">
+        <f>VLOOKUP(B175,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F175">
+        <v>10</v>
+      </c>
+      <c r="G175" t="str">
+        <f>VLOOKUP(F175,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7</v>
+      </c>
+      <c r="C176" t="str">
+        <f>VLOOKUP(B176,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F176">
+        <v>3</v>
+      </c>
+      <c r="G176" t="str">
+        <f>VLOOKUP(F176,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>5</v>
+      </c>
+      <c r="C177" t="str">
+        <f>VLOOKUP(B177,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177" t="str">
+        <f>VLOOKUP(F177,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>14</v>
+      </c>
+      <c r="C178" t="str">
+        <f>VLOOKUP(B178,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F178">
+        <v>10</v>
+      </c>
+      <c r="G178" t="str">
+        <f>VLOOKUP(F178,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>8</v>
+      </c>
+      <c r="C179" t="str">
+        <f>VLOOKUP(B179,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F179">
+        <v>2</v>
+      </c>
+      <c r="G179" t="str">
+        <f>VLOOKUP(F179,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>9</v>
+      </c>
+      <c r="C180" t="str">
+        <f>VLOOKUP(B180,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F180">
+        <v>12</v>
+      </c>
+      <c r="G180" t="str">
+        <f>VLOOKUP(F180,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>3</v>
+      </c>
+      <c r="C181" t="str">
+        <f>VLOOKUP(B181,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F181">
+        <v>11</v>
+      </c>
+      <c r="G181" t="str">
+        <f>VLOOKUP(F181,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>13</v>
+      </c>
+      <c r="C182" t="str">
+        <f>VLOOKUP(B182,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F182">
+        <v>7</v>
+      </c>
+      <c r="G182" t="str">
+        <f>VLOOKUP(F182,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>6</v>
+      </c>
+      <c r="C183" t="str">
+        <f>VLOOKUP(B183,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F183">
+        <v>4</v>
+      </c>
+      <c r="G183" t="str">
+        <f>VLOOKUP(F183,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>14</v>
+      </c>
+      <c r="C184" t="str">
+        <f>VLOOKUP(B184,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F184">
+        <v>5</v>
+      </c>
+      <c r="G184" t="str">
+        <f>VLOOKUP(F184,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>6</v>
+      </c>
+      <c r="C185" t="str">
+        <f>VLOOKUP(B185,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185" t="str">
+        <f>VLOOKUP(F185,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>8</v>
+      </c>
+      <c r="C186" t="str">
+        <f>VLOOKUP(B186,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F186">
+        <v>4</v>
+      </c>
+      <c r="G186" t="str">
+        <f>VLOOKUP(F186,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>9</v>
+      </c>
+      <c r="C187" t="str">
+        <f>VLOOKUP(B187,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F187">
+        <v>2</v>
+      </c>
+      <c r="G187" t="str">
+        <f>VLOOKUP(F187,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>3</v>
+      </c>
+      <c r="C188" t="str">
+        <f>VLOOKUP(B188,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F188">
+        <v>12</v>
+      </c>
+      <c r="G188" t="str">
+        <f>VLOOKUP(F188,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>13</v>
+      </c>
+      <c r="C189" t="str">
+        <f>VLOOKUP(B189,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F189">
+        <v>11</v>
+      </c>
+      <c r="G189" t="str">
+        <f>VLOOKUP(F189,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7</v>
+      </c>
+      <c r="C190" t="str">
+        <f>VLOOKUP(B190,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F190">
+        <v>10</v>
+      </c>
+      <c r="G190" t="str">
+        <f>VLOOKUP(F190,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>14</v>
+      </c>
+      <c r="C191" t="str">
+        <f>VLOOKUP(B191,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F191">
+        <v>6</v>
+      </c>
+      <c r="G191" t="str">
+        <f>VLOOKUP(F191,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>5</v>
+      </c>
+      <c r="C192" t="str">
+        <f>VLOOKUP(B192,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F192">
+        <v>10</v>
+      </c>
+      <c r="G192" t="str">
+        <f>VLOOKUP(F192,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>8</v>
+      </c>
+      <c r="C193" t="str">
+        <f>VLOOKUP(B193,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193" t="str">
+        <f>VLOOKUP(F193,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>9</v>
+      </c>
+      <c r="C194" t="str">
+        <f>VLOOKUP(B194,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F194">
+        <v>4</v>
+      </c>
+      <c r="G194" t="str">
+        <f>VLOOKUP(F194,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>3</v>
+      </c>
+      <c r="C195" t="str">
+        <f>VLOOKUP(B195,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+      <c r="G195" t="str">
+        <f>VLOOKUP(F195,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>13</v>
+      </c>
+      <c r="C196" t="str">
+        <f>VLOOKUP(B196,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F196">
+        <v>12</v>
+      </c>
+      <c r="G196" t="str">
+        <f>VLOOKUP(F196,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7</v>
+      </c>
+      <c r="C197" t="str">
+        <f>VLOOKUP(B197,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F197">
+        <v>11</v>
+      </c>
+      <c r="G197" t="str">
+        <f>VLOOKUP(F197,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>5</v>
+      </c>
+      <c r="C198" t="str">
+        <f>VLOOKUP(B198,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F198">
+        <v>6</v>
+      </c>
+      <c r="G198" t="str">
+        <f>VLOOKUP(F198,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>14</v>
+      </c>
+      <c r="C199" t="str">
+        <f>VLOOKUP(B199,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F199">
+        <v>8</v>
+      </c>
+      <c r="G199" t="str">
+        <f>VLOOKUP(F199,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>3</v>
+      </c>
+      <c r="C200" t="str">
+        <f>VLOOKUP(B200,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F200">
+        <v>4</v>
+      </c>
+      <c r="G200" t="str">
+        <f>VLOOKUP(F200,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>9</v>
+      </c>
+      <c r="C201" t="str">
+        <f>VLOOKUP(B201,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201" t="str">
+        <f>VLOOKUP(F201,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>11</v>
+      </c>
+      <c r="C202" t="str">
+        <f>VLOOKUP(B202,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F202">
+        <v>10</v>
+      </c>
+      <c r="G202" t="str">
+        <f>VLOOKUP(F202,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>13</v>
+      </c>
+      <c r="C203" t="str">
+        <f>VLOOKUP(B203,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F203">
+        <v>2</v>
+      </c>
+      <c r="G203" t="str">
+        <f>VLOOKUP(F203,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7</v>
+      </c>
+      <c r="C204" t="str">
+        <f>VLOOKUP(B204,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F204">
+        <v>12</v>
+      </c>
+      <c r="G204" t="str">
+        <f>VLOOKUP(F204,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>5</v>
+      </c>
+      <c r="C205" t="str">
+        <f>VLOOKUP(B205,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F205">
+        <v>8</v>
+      </c>
+      <c r="G205" t="str">
+        <f>VLOOKUP(F205,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>14</v>
+      </c>
+      <c r="C206" t="str">
+        <f>VLOOKUP(B206,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F206">
+        <v>9</v>
+      </c>
+      <c r="G206" t="str">
+        <f>VLOOKUP(F206,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>3</v>
+      </c>
+      <c r="C207" t="str">
+        <f>VLOOKUP(B207,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207" t="str">
+        <f>VLOOKUP(F207,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>11</v>
+      </c>
+      <c r="C208" t="str">
+        <f>VLOOKUP(B208,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F208">
+        <v>12</v>
+      </c>
+      <c r="G208" t="str">
+        <f>VLOOKUP(F208,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>6</v>
+      </c>
+      <c r="C209" t="str">
+        <f>VLOOKUP(B209,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F209">
+        <v>10</v>
+      </c>
+      <c r="G209" t="str">
+        <f>VLOOKUP(F209,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>4</v>
+      </c>
+      <c r="C210" t="str">
+        <f>VLOOKUP(B210,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F210">
+        <v>13</v>
+      </c>
+      <c r="G210" t="str">
+        <f>VLOOKUP(F210,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7</v>
+      </c>
+      <c r="C211" t="str">
+        <f>VLOOKUP(B211,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F211">
+        <v>2</v>
+      </c>
+      <c r="G211" t="str">
+        <f>VLOOKUP(F211,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>5</v>
+      </c>
+      <c r="C212" t="str">
+        <f>VLOOKUP(B212,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F212">
+        <v>9</v>
+      </c>
+      <c r="G212" t="str">
+        <f>VLOOKUP(F212,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>14</v>
+      </c>
+      <c r="C213" t="str">
+        <f>VLOOKUP(B213,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F213">
+        <v>3</v>
+      </c>
+      <c r="G213" t="str">
+        <f>VLOOKUP(F213,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>8</v>
+      </c>
+      <c r="C214" t="str">
+        <f>VLOOKUP(B214,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F214">
+        <v>6</v>
+      </c>
+      <c r="G214" t="str">
+        <f>VLOOKUP(F214,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7</v>
+      </c>
+      <c r="C215" t="str">
+        <f>VLOOKUP(B215,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F215">
+        <v>4</v>
+      </c>
+      <c r="G215" t="str">
+        <f>VLOOKUP(F215,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>11</v>
+      </c>
+      <c r="C216" t="str">
+        <f>VLOOKUP(B216,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F216">
+        <v>2</v>
+      </c>
+      <c r="G216" t="str">
+        <f>VLOOKUP(F216,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>13</v>
+      </c>
+      <c r="C217" t="str">
+        <f>VLOOKUP(B217,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217" t="str">
+        <f>VLOOKUP(F217,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>10</v>
+      </c>
+      <c r="C218" t="str">
+        <f>VLOOKUP(B218,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F218">
+        <v>12</v>
+      </c>
+      <c r="G218" t="str">
+        <f>VLOOKUP(F218,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>5</v>
+      </c>
+      <c r="C219" t="str">
+        <f>VLOOKUP(B219,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F219">
+        <v>3</v>
+      </c>
+      <c r="G219" t="str">
+        <f>VLOOKUP(F219,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>14</v>
+      </c>
+      <c r="C220" t="str">
+        <f>VLOOKUP(B220,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F220">
+        <v>13</v>
+      </c>
+      <c r="G220" t="str">
+        <f>VLOOKUP(F220,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>8</v>
+      </c>
+      <c r="C221" t="str">
+        <f>VLOOKUP(B221,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F221">
+        <v>10</v>
+      </c>
+      <c r="G221" t="str">
+        <f>VLOOKUP(F221,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>9</v>
+      </c>
+      <c r="C222" t="str">
+        <f>VLOOKUP(B222,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F222">
+        <v>6</v>
+      </c>
+      <c r="G222" t="str">
+        <f>VLOOKUP(F222,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>12</v>
+      </c>
+      <c r="C223" t="str">
+        <f>VLOOKUP(B223,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="F223">
+        <v>2</v>
+      </c>
+      <c r="G223" t="str">
+        <f>VLOOKUP(F223,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>11</v>
+      </c>
+      <c r="C224" t="str">
+        <f>VLOOKUP(B224,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F224">
+        <v>4</v>
+      </c>
+      <c r="G224" t="str">
+        <f>VLOOKUP(F224,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7</v>
+      </c>
+      <c r="C225" t="str">
+        <f>VLOOKUP(B225,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+      <c r="G225" t="str">
+        <f>VLOOKUP(F225,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>5</v>
+      </c>
+      <c r="C226" t="str">
+        <f>VLOOKUP(B226,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F226">
+        <v>13</v>
+      </c>
+      <c r="G226" t="str">
+        <f>VLOOKUP(F226,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>14</v>
+      </c>
+      <c r="C227" t="str">
+        <f>VLOOKUP(B227,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F227">
+        <v>7</v>
+      </c>
+      <c r="G227" t="str">
+        <f>VLOOKUP(F227,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>8</v>
+      </c>
+      <c r="C228" t="str">
+        <f>VLOOKUP(B228,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F228">
+        <v>9</v>
+      </c>
+      <c r="G228" t="str">
+        <f>VLOOKUP(F228,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>10</v>
+      </c>
+      <c r="C229" t="str">
+        <f>VLOOKUP(B229,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F229">
+        <v>2</v>
+      </c>
+      <c r="G229" t="str">
+        <f>VLOOKUP(F229,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>3</v>
+      </c>
+      <c r="C230" t="str">
+        <f>VLOOKUP(B230,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F230">
+        <v>6</v>
+      </c>
+      <c r="G230" t="str">
+        <f>VLOOKUP(F230,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>4</v>
+      </c>
+      <c r="C231" t="str">
+        <f>VLOOKUP(B231,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F231">
+        <v>12</v>
+      </c>
+      <c r="G231" t="str">
+        <f>VLOOKUP(F231,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+      <c r="C232" t="str">
+        <f>VLOOKUP(B232,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F232">
+        <v>11</v>
+      </c>
+      <c r="G232" t="str">
+        <f>VLOOKUP(F232,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>5</v>
+      </c>
+      <c r="C233" t="str">
+        <f>VLOOKUP(B233,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F233">
+        <v>7</v>
+      </c>
+      <c r="G233" t="str">
+        <f>VLOOKUP(F233,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>14</v>
+      </c>
+      <c r="C234" t="str">
+        <f>VLOOKUP(B234,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F234">
+        <v>11</v>
+      </c>
+      <c r="G234" t="str">
+        <f>VLOOKUP(F234,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>8</v>
+      </c>
+      <c r="C235" t="str">
+        <f>VLOOKUP(B235,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F235">
+        <v>3</v>
+      </c>
+      <c r="G235" t="str">
+        <f>VLOOKUP(F235,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>9</v>
+      </c>
+      <c r="C236" t="str">
+        <f>VLOOKUP(B236,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F236">
+        <v>10</v>
+      </c>
+      <c r="G236" t="str">
+        <f>VLOOKUP(F236,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>4</v>
+      </c>
+      <c r="C237" t="str">
+        <f>VLOOKUP(B237,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F237">
+        <v>2</v>
+      </c>
+      <c r="G237" t="str">
+        <f>VLOOKUP(F237,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>1</v>
+      </c>
+      <c r="C238" t="str">
+        <f>VLOOKUP(B238,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F238">
+        <v>12</v>
+      </c>
+      <c r="G238" t="str">
+        <f>VLOOKUP(F238,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>6</v>
+      </c>
+      <c r="C239" t="str">
+        <f>VLOOKUP(B239,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F239">
+        <v>13</v>
+      </c>
+      <c r="G239" t="str">
+        <f>VLOOKUP(F239,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>5</v>
+      </c>
+      <c r="C240" t="str">
+        <f>VLOOKUP(B240,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F240">
+        <v>11</v>
+      </c>
+      <c r="G240" t="str">
+        <f>VLOOKUP(F240,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>14</v>
+      </c>
+      <c r="C241" t="str">
+        <f>VLOOKUP(B241,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F241">
+        <v>12</v>
+      </c>
+      <c r="G241" t="str">
+        <f>VLOOKUP(F241,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>8</v>
+      </c>
+      <c r="C242" t="str">
+        <f>VLOOKUP(B242,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F242">
+        <v>13</v>
+      </c>
+      <c r="G242" t="str">
+        <f>VLOOKUP(F242,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>9</v>
+      </c>
+      <c r="C243" t="str">
+        <f>VLOOKUP(B243,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F243">
+        <v>3</v>
+      </c>
+      <c r="G243" t="str">
+        <f>VLOOKUP(F243,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>1</v>
+      </c>
+      <c r="C244" t="str">
+        <f>VLOOKUP(B244,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F244">
+        <v>2</v>
+      </c>
+      <c r="G244" t="str">
+        <f>VLOOKUP(F244,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>4</v>
+      </c>
+      <c r="C245" t="str">
+        <f>VLOOKUP(B245,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F245">
+        <v>10</v>
+      </c>
+      <c r="G245" t="str">
+        <f>VLOOKUP(F245,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7</v>
+      </c>
+      <c r="C246" t="str">
+        <f>VLOOKUP(B246,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F246">
+        <v>6</v>
+      </c>
+      <c r="G246" t="str">
+        <f>VLOOKUP(F246,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>5</v>
+      </c>
+      <c r="C247" t="str">
+        <f>VLOOKUP(B247,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F247">
+        <v>12</v>
+      </c>
+      <c r="G247" t="str">
+        <f>VLOOKUP(F247,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>14</v>
+      </c>
+      <c r="C248" t="str">
+        <f>VLOOKUP(B248,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F248">
+        <v>2</v>
+      </c>
+      <c r="G248" t="str">
+        <f>VLOOKUP(F248,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>8</v>
+      </c>
+      <c r="C249" t="str">
+        <f>VLOOKUP(B249,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F249">
+        <v>7</v>
+      </c>
+      <c r="G249" t="str">
+        <f>VLOOKUP(F249,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>9</v>
+      </c>
+      <c r="C250" t="str">
+        <f>VLOOKUP(B250,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F250">
+        <v>13</v>
+      </c>
+      <c r="G250" t="str">
+        <f>VLOOKUP(F250,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>3</v>
+      </c>
+      <c r="C251" t="str">
+        <f>VLOOKUP(B251,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F251">
+        <v>10</v>
+      </c>
+      <c r="G251" t="str">
+        <f>VLOOKUP(F251,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>4</v>
+      </c>
+      <c r="C252" t="str">
+        <f>VLOOKUP(B252,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F252">
+        <v>1</v>
+      </c>
+      <c r="G252" t="str">
+        <f>VLOOKUP(F252,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>6</v>
+      </c>
+      <c r="C253" t="str">
+        <f>VLOOKUP(B253,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F253">
+        <v>11</v>
+      </c>
+      <c r="G253" t="str">
+        <f>VLOOKUP(F253,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>5</v>
+      </c>
+      <c r="C254" t="str">
+        <f>VLOOKUP(B254,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F254">
+        <v>2</v>
+      </c>
+      <c r="G254" t="str">
+        <f>VLOOKUP(F254,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>14</v>
+      </c>
+      <c r="C255" t="str">
+        <f>VLOOKUP(B255,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F255">
+        <v>4</v>
+      </c>
+      <c r="G255" t="str">
+        <f>VLOOKUP(F255,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>8</v>
+      </c>
+      <c r="C256" t="str">
+        <f>VLOOKUP(B256,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F256">
+        <v>11</v>
+      </c>
+      <c r="G256" t="str">
+        <f>VLOOKUP(F256,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>9</v>
+      </c>
+      <c r="C257" t="str">
+        <f>VLOOKUP(B257,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F257">
+        <v>7</v>
+      </c>
+      <c r="G257" t="str">
+        <f>VLOOKUP(F257,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>3</v>
+      </c>
+      <c r="C258" t="str">
+        <f>VLOOKUP(B258,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F258">
+        <v>13</v>
+      </c>
+      <c r="G258" t="str">
+        <f>VLOOKUP(F258,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>6</v>
+      </c>
+      <c r="C259" t="str">
+        <f>VLOOKUP(B259,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F259">
+        <v>12</v>
+      </c>
+      <c r="G259" t="str">
+        <f>VLOOKUP(F259,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>10</v>
+      </c>
+      <c r="C260" t="str">
+        <f>VLOOKUP(B260,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F260">
+        <v>1</v>
+      </c>
+      <c r="G260" t="str">
+        <f>VLOOKUP(F260,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>5</v>
+      </c>
+      <c r="C261" t="str">
+        <f>VLOOKUP(B261,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F261">
+        <v>4</v>
+      </c>
+      <c r="G261" t="str">
+        <f>VLOOKUP(F261,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>14</v>
+      </c>
+      <c r="C262" t="str">
+        <f>VLOOKUP(B262,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F262">
+        <v>1</v>
+      </c>
+      <c r="G262" t="str">
+        <f>VLOOKUP(F262,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>8</v>
+      </c>
+      <c r="C263" t="str">
+        <f>VLOOKUP(B263,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F263">
+        <v>12</v>
+      </c>
+      <c r="G263" t="str">
+        <f>VLOOKUP(F263,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>9</v>
+      </c>
+      <c r="C264" t="str">
+        <f>VLOOKUP(B264,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F264">
+        <v>11</v>
+      </c>
+      <c r="G264" t="str">
+        <f>VLOOKUP(F264,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>6</v>
+      </c>
+      <c r="C265" t="str">
+        <f>VLOOKUP(B265,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F265">
+        <v>2</v>
+      </c>
+      <c r="G265" t="str">
+        <f>VLOOKUP(F265,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>13</v>
+      </c>
+      <c r="C266" t="str">
+        <f>VLOOKUP(B266,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F266">
+        <v>10</v>
+      </c>
+      <c r="G266" t="str">
+        <f>VLOOKUP(F266,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7</v>
+      </c>
+      <c r="C267" t="str">
+        <f>VLOOKUP(B267,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F267">
+        <v>3</v>
+      </c>
+      <c r="G267" t="str">
+        <f>VLOOKUP(F267,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>5</v>
+      </c>
+      <c r="C268" t="str">
+        <f>VLOOKUP(B268,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F268">
+        <v>1</v>
+      </c>
+      <c r="G268" t="str">
+        <f>VLOOKUP(F268,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>14</v>
+      </c>
+      <c r="C269" t="str">
+        <f>VLOOKUP(B269,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F269">
+        <v>10</v>
+      </c>
+      <c r="G269" t="str">
+        <f>VLOOKUP(F269,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>8</v>
+      </c>
+      <c r="C270" t="str">
+        <f>VLOOKUP(B270,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F270">
+        <v>2</v>
+      </c>
+      <c r="G270" t="str">
+        <f>VLOOKUP(F270,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>9</v>
+      </c>
+      <c r="C271" t="str">
+        <f>VLOOKUP(B271,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F271">
+        <v>12</v>
+      </c>
+      <c r="G271" t="str">
+        <f>VLOOKUP(F271,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>3</v>
+      </c>
+      <c r="C272" t="str">
+        <f>VLOOKUP(B272,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F272">
+        <v>11</v>
+      </c>
+      <c r="G272" t="str">
+        <f>VLOOKUP(F272,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>13</v>
+      </c>
+      <c r="C273" t="str">
+        <f>VLOOKUP(B273,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F273">
+        <v>7</v>
+      </c>
+      <c r="G273" t="str">
+        <f>VLOOKUP(F273,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>6</v>
+      </c>
+      <c r="C274" t="str">
+        <f>VLOOKUP(B274,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F274">
+        <v>4</v>
+      </c>
+      <c r="G274" t="str">
+        <f>VLOOKUP(F274,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
       </c>
     </row>
   </sheetData>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C5E5BD-639C-424F-90AB-AB669A451335}"/>
+  <xr:revisionPtr revIDLastSave="350" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3EA1D77-A540-40BF-A4A6-6F1074C29FD7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="699">
   <si>
     <t>team_id</t>
   </si>
@@ -2140,6 +2140,9 @@
   </si>
   <si>
     <t>P2029_R2_T14</t>
+  </si>
+  <si>
+    <t>rodada</t>
   </si>
 </sst>
 </file>
@@ -2218,6 +2221,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21871,7 +21878,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G274"/>
+  <dimension ref="A1:H274"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -21882,7 +21889,7 @@
     <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>539</v>
       </c>
@@ -21904,8 +21911,11 @@
       <c r="G1" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -21923,8 +21933,11 @@
         <f>VLOOKUP(F2,teams!$A$1:$B$15,2)</f>
         <v>Kaipiras da Gema</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -21942,8 +21955,11 @@
         <f>VLOOKUP(F3,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -21961,8 +21977,11 @@
         <f>VLOOKUP(F4,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -21980,8 +21999,11 @@
         <f>VLOOKUP(F5,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -21999,8 +22021,11 @@
         <f>VLOOKUP(F6,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -22018,8 +22043,11 @@
         <f>VLOOKUP(F7,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -22037,8 +22065,11 @@
         <f>VLOOKUP(F8,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -22056,8 +22087,12 @@
         <f>VLOOKUP(F9,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <f t="shared" ref="H9:H29" si="0">H2+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -22075,8 +22110,12 @@
         <f>VLOOKUP(F10,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -22094,8 +22133,12 @@
         <f>VLOOKUP(F11,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -22113,8 +22156,12 @@
         <f>VLOOKUP(F12,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -22132,8 +22179,12 @@
         <f>VLOOKUP(F13,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -22151,8 +22202,12 @@
         <f>VLOOKUP(F14,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -22170,8 +22225,12 @@
         <f>VLOOKUP(F15,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -22189,8 +22248,12 @@
         <f>VLOOKUP(F16,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -22208,8 +22271,12 @@
         <f>VLOOKUP(F17,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -22227,8 +22294,12 @@
         <f>VLOOKUP(F18,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -22246,8 +22317,12 @@
         <f>VLOOKUP(F19,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -22265,8 +22340,12 @@
         <f>VLOOKUP(F20,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -22284,8 +22363,12 @@
         <f>VLOOKUP(F21,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -22303,8 +22386,12 @@
         <f>VLOOKUP(F22,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -22322,8 +22409,12 @@
         <f>VLOOKUP(F23,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -22341,8 +22432,12 @@
         <f>VLOOKUP(F24,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -22360,8 +22455,12 @@
         <f>VLOOKUP(F25,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -22379,8 +22478,12 @@
         <f>VLOOKUP(F26,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -22398,8 +22501,12 @@
         <f>VLOOKUP(F27,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -22417,8 +22524,12 @@
         <f>VLOOKUP(F28,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -22436,8 +22547,12 @@
         <f>VLOOKUP(F29,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -22455,8 +22570,12 @@
         <f>VLOOKUP(F30,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30">
+        <f>H23+1</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -22474,8 +22593,12 @@
         <f>VLOOKUP(F31,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31">
+        <f t="shared" ref="H31:H94" si="1">H24+1</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -22493,8 +22616,12 @@
         <f>VLOOKUP(F32,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -22512,8 +22639,12 @@
         <f>VLOOKUP(F33,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -22531,8 +22662,12 @@
         <f>VLOOKUP(F34,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -22550,8 +22685,12 @@
         <f>VLOOKUP(F35,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -22569,8 +22708,12 @@
         <f>VLOOKUP(F36,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -22588,8 +22731,12 @@
         <f>VLOOKUP(F37,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -22607,8 +22754,12 @@
         <f>VLOOKUP(F38,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -22626,8 +22777,12 @@
         <f>VLOOKUP(F39,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -22645,8 +22800,12 @@
         <f>VLOOKUP(F40,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -22664,8 +22823,12 @@
         <f>VLOOKUP(F41,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -22683,8 +22846,12 @@
         <f>VLOOKUP(F42,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -22702,8 +22869,12 @@
         <f>VLOOKUP(F43,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -22721,8 +22892,12 @@
         <f>VLOOKUP(F44,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -22740,8 +22915,12 @@
         <f>VLOOKUP(F45,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -22759,8 +22938,12 @@
         <f>VLOOKUP(F46,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -22778,8 +22961,12 @@
         <f>VLOOKUP(F47,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -22797,8 +22984,12 @@
         <f>VLOOKUP(F48,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -22816,8 +23007,12 @@
         <f>VLOOKUP(F49,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -22835,8 +23030,12 @@
         <f>VLOOKUP(F50,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -22854,8 +23053,12 @@
         <f>VLOOKUP(F51,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -22873,8 +23076,12 @@
         <f>VLOOKUP(F52,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -22892,8 +23099,12 @@
         <f>VLOOKUP(F53,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -22911,8 +23122,12 @@
         <f>VLOOKUP(F54,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -22930,8 +23145,12 @@
         <f>VLOOKUP(F55,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -22949,8 +23168,12 @@
         <f>VLOOKUP(F56,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -22968,8 +23191,12 @@
         <f>VLOOKUP(F57,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -22987,8 +23214,12 @@
         <f>VLOOKUP(F58,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -23006,8 +23237,12 @@
         <f>VLOOKUP(F59,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -23025,8 +23260,12 @@
         <f>VLOOKUP(F60,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -23044,8 +23283,12 @@
         <f>VLOOKUP(F61,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -23063,8 +23306,12 @@
         <f>VLOOKUP(F62,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -23082,8 +23329,12 @@
         <f>VLOOKUP(F63,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -23101,8 +23352,12 @@
         <f>VLOOKUP(F64,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -23120,8 +23375,12 @@
         <f>VLOOKUP(F65,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -23139,8 +23398,12 @@
         <f>VLOOKUP(F66,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -23158,8 +23421,12 @@
         <f>VLOOKUP(F67,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -23177,8 +23444,12 @@
         <f>VLOOKUP(F68,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -23196,8 +23467,12 @@
         <f>VLOOKUP(F69,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -23215,8 +23490,12 @@
         <f>VLOOKUP(F70,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -23234,8 +23513,12 @@
         <f>VLOOKUP(F71,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -23253,8 +23536,12 @@
         <f>VLOOKUP(F72,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -23272,8 +23559,12 @@
         <f>VLOOKUP(F73,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H73">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -23291,8 +23582,12 @@
         <f>VLOOKUP(F74,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H74">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -23310,8 +23605,12 @@
         <f>VLOOKUP(F75,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H75">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -23329,8 +23628,12 @@
         <f>VLOOKUP(F76,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -23348,8 +23651,12 @@
         <f>VLOOKUP(F77,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H77">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -23367,8 +23674,12 @@
         <f>VLOOKUP(F78,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H78">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -23386,8 +23697,12 @@
         <f>VLOOKUP(F79,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H79">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -23405,8 +23720,12 @@
         <f>VLOOKUP(F80,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H80">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -23424,8 +23743,12 @@
         <f>VLOOKUP(F81,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H81">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -23443,8 +23766,12 @@
         <f>VLOOKUP(F82,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H82">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -23462,8 +23789,12 @@
         <f>VLOOKUP(F83,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H83">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -23481,8 +23812,12 @@
         <f>VLOOKUP(F84,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H84">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -23500,8 +23835,12 @@
         <f>VLOOKUP(F85,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H85">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -23519,8 +23858,12 @@
         <f>VLOOKUP(F86,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H86">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -23538,8 +23881,12 @@
         <f>VLOOKUP(F87,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H87">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -23557,8 +23904,12 @@
         <f>VLOOKUP(F88,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -23576,8 +23927,12 @@
         <f>VLOOKUP(F89,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H89">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -23595,8 +23950,12 @@
         <f>VLOOKUP(F90,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H90">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -23614,8 +23973,12 @@
         <f>VLOOKUP(F91,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H91">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -23633,8 +23996,12 @@
         <f>VLOOKUP(F92,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H92">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -23652,8 +24019,12 @@
         <f>VLOOKUP(F93,teams!$A$1:$B$15,2)</f>
         <v>Kaipiras da Gema</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H93">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -23671,8 +24042,12 @@
         <f>VLOOKUP(F94,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H94">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -23690,8 +24065,12 @@
         <f>VLOOKUP(F95,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H95">
+        <f t="shared" ref="H95:H158" si="2">H88+1</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -23709,8 +24088,12 @@
         <f>VLOOKUP(F96,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H96">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -23728,8 +24111,12 @@
         <f>VLOOKUP(F97,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H97">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -23747,8 +24134,12 @@
         <f>VLOOKUP(F98,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H98">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -23766,8 +24157,12 @@
         <f>VLOOKUP(F99,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H99">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -23785,8 +24180,12 @@
         <f>VLOOKUP(F100,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H100">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -23804,8 +24203,12 @@
         <f>VLOOKUP(F101,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H101">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -23823,8 +24226,12 @@
         <f>VLOOKUP(F102,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H102">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -23842,8 +24249,12 @@
         <f>VLOOKUP(F103,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H103">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -23861,8 +24272,12 @@
         <f>VLOOKUP(F104,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H104">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -23880,8 +24295,12 @@
         <f>VLOOKUP(F105,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H105">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -23899,8 +24318,12 @@
         <f>VLOOKUP(F106,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H106">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -23918,8 +24341,12 @@
         <f>VLOOKUP(F107,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H107">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -23937,8 +24364,12 @@
         <f>VLOOKUP(F108,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H108">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -23956,8 +24387,12 @@
         <f>VLOOKUP(F109,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H109">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -23975,8 +24410,12 @@
         <f>VLOOKUP(F110,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H110">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -23994,8 +24433,12 @@
         <f>VLOOKUP(F111,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H111">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -24013,8 +24456,12 @@
         <f>VLOOKUP(F112,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H112">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -24032,8 +24479,12 @@
         <f>VLOOKUP(F113,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H113">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -24051,8 +24502,12 @@
         <f>VLOOKUP(F114,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H114">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -24070,8 +24525,12 @@
         <f>VLOOKUP(F115,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H115">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -24089,8 +24548,12 @@
         <f>VLOOKUP(F116,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H116">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -24108,8 +24571,12 @@
         <f>VLOOKUP(F117,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H117">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -24127,8 +24594,12 @@
         <f>VLOOKUP(F118,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H118">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -24146,8 +24617,12 @@
         <f>VLOOKUP(F119,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H119">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -24165,8 +24640,12 @@
         <f>VLOOKUP(F120,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -24184,8 +24663,12 @@
         <f>VLOOKUP(F121,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H121">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -24203,8 +24686,12 @@
         <f>VLOOKUP(F122,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H122">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -24222,8 +24709,12 @@
         <f>VLOOKUP(F123,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H123">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -24241,8 +24732,12 @@
         <f>VLOOKUP(F124,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H124">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -24260,8 +24755,12 @@
         <f>VLOOKUP(F125,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H125">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -24279,8 +24778,12 @@
         <f>VLOOKUP(F126,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H126">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -24298,8 +24801,12 @@
         <f>VLOOKUP(F127,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H127">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -24317,8 +24824,12 @@
         <f>VLOOKUP(F128,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H128">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -24336,8 +24847,12 @@
         <f>VLOOKUP(F129,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H129">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -24355,8 +24870,12 @@
         <f>VLOOKUP(F130,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H130">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -24374,8 +24893,12 @@
         <f>VLOOKUP(F131,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H131">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -24393,8 +24916,12 @@
         <f>VLOOKUP(F132,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H132">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -24412,8 +24939,12 @@
         <f>VLOOKUP(F133,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H133">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -24431,8 +24962,12 @@
         <f>VLOOKUP(F134,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H134">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -24450,8 +24985,12 @@
         <f>VLOOKUP(F135,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H135">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -24469,8 +25008,12 @@
         <f>VLOOKUP(F136,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H136">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -24488,8 +25031,12 @@
         <f>VLOOKUP(F137,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H137">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -24507,8 +25054,12 @@
         <f>VLOOKUP(F138,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H138">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -24526,8 +25077,12 @@
         <f>VLOOKUP(F139,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H139">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -24545,8 +25100,12 @@
         <f>VLOOKUP(F140,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H140">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -24564,8 +25123,12 @@
         <f>VLOOKUP(F141,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H141">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -24583,8 +25146,12 @@
         <f>VLOOKUP(F142,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H142">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -24602,8 +25169,12 @@
         <f>VLOOKUP(F143,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H143">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -24621,8 +25192,12 @@
         <f>VLOOKUP(F144,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H144">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -24640,8 +25215,12 @@
         <f>VLOOKUP(F145,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H145">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -24659,8 +25238,12 @@
         <f>VLOOKUP(F146,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H146">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -24678,8 +25261,12 @@
         <f>VLOOKUP(F147,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H147">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -24697,8 +25284,12 @@
         <f>VLOOKUP(F148,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H148">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -24716,8 +25307,12 @@
         <f>VLOOKUP(F149,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H149">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -24735,8 +25330,12 @@
         <f>VLOOKUP(F150,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H150">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -24754,8 +25353,12 @@
         <f>VLOOKUP(F151,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H151">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -24773,8 +25376,12 @@
         <f>VLOOKUP(F152,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H152">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -24792,8 +25399,12 @@
         <f>VLOOKUP(F153,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H153">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -24811,8 +25422,12 @@
         <f>VLOOKUP(F154,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H154">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -24830,8 +25445,12 @@
         <f>VLOOKUP(F155,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H155">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -24849,8 +25468,12 @@
         <f>VLOOKUP(F156,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H156">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -24868,8 +25491,12 @@
         <f>VLOOKUP(F157,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H157">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -24887,8 +25514,12 @@
         <f>VLOOKUP(F158,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H158">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -24906,8 +25537,12 @@
         <f>VLOOKUP(F159,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H159">
+        <f t="shared" ref="H159:H222" si="3">H152+1</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -24925,8 +25560,12 @@
         <f>VLOOKUP(F160,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H160">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -24944,8 +25583,12 @@
         <f>VLOOKUP(F161,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H161">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -24963,8 +25606,12 @@
         <f>VLOOKUP(F162,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H162">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -24982,8 +25629,12 @@
         <f>VLOOKUP(F163,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H163">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -25001,8 +25652,12 @@
         <f>VLOOKUP(F164,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H164">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -25020,8 +25675,12 @@
         <f>VLOOKUP(F165,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H165">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -25039,8 +25698,12 @@
         <f>VLOOKUP(F166,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H166">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -25058,8 +25721,12 @@
         <f>VLOOKUP(F167,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H167">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -25077,8 +25744,12 @@
         <f>VLOOKUP(F168,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H168">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -25096,8 +25767,12 @@
         <f>VLOOKUP(F169,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H169">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -25115,8 +25790,12 @@
         <f>VLOOKUP(F170,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H170">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -25134,8 +25813,12 @@
         <f>VLOOKUP(F171,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H171">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -25153,8 +25836,12 @@
         <f>VLOOKUP(F172,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H172">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -25172,8 +25859,12 @@
         <f>VLOOKUP(F173,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H173">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -25191,8 +25882,12 @@
         <f>VLOOKUP(F174,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H174">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -25210,8 +25905,12 @@
         <f>VLOOKUP(F175,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H175">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -25229,8 +25928,12 @@
         <f>VLOOKUP(F176,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H176">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -25248,8 +25951,12 @@
         <f>VLOOKUP(F177,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H177">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -25267,8 +25974,12 @@
         <f>VLOOKUP(F178,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H178">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -25286,8 +25997,12 @@
         <f>VLOOKUP(F179,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H179">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -25305,8 +26020,12 @@
         <f>VLOOKUP(F180,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H180">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -25324,8 +26043,12 @@
         <f>VLOOKUP(F181,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H181">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -25343,8 +26066,12 @@
         <f>VLOOKUP(F182,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H182">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -25362,8 +26089,12 @@
         <f>VLOOKUP(F183,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H183">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -25381,8 +26112,12 @@
         <f>VLOOKUP(F184,teams!$A$1:$B$15,2)</f>
         <v>Kaipiras da Gema</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H184">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -25400,8 +26135,12 @@
         <f>VLOOKUP(F185,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H185">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -25419,8 +26158,12 @@
         <f>VLOOKUP(F186,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H186">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -25438,8 +26181,12 @@
         <f>VLOOKUP(F187,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H187">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -25457,8 +26204,12 @@
         <f>VLOOKUP(F188,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H188">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -25476,8 +26227,12 @@
         <f>VLOOKUP(F189,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H189">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -25495,8 +26250,12 @@
         <f>VLOOKUP(F190,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H190">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -25514,8 +26273,12 @@
         <f>VLOOKUP(F191,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H191">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -25533,8 +26296,12 @@
         <f>VLOOKUP(F192,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H192">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -25552,8 +26319,12 @@
         <f>VLOOKUP(F193,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H193">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -25571,8 +26342,12 @@
         <f>VLOOKUP(F194,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H194">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -25590,8 +26365,12 @@
         <f>VLOOKUP(F195,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H195">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -25609,8 +26388,12 @@
         <f>VLOOKUP(F196,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H196">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -25628,8 +26411,12 @@
         <f>VLOOKUP(F197,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H197">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -25647,8 +26434,12 @@
         <f>VLOOKUP(F198,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H198">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -25666,8 +26457,12 @@
         <f>VLOOKUP(F199,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H199">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -25685,8 +26480,12 @@
         <f>VLOOKUP(F200,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H200">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -25704,8 +26503,12 @@
         <f>VLOOKUP(F201,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H201">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -25723,8 +26526,12 @@
         <f>VLOOKUP(F202,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H202">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -25742,8 +26549,12 @@
         <f>VLOOKUP(F203,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H203">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -25761,8 +26572,12 @@
         <f>VLOOKUP(F204,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H204">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -25780,8 +26595,12 @@
         <f>VLOOKUP(F205,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H205">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -25799,8 +26618,12 @@
         <f>VLOOKUP(F206,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H206">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -25818,8 +26641,12 @@
         <f>VLOOKUP(F207,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H207">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -25837,8 +26664,12 @@
         <f>VLOOKUP(F208,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H208">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -25856,8 +26687,12 @@
         <f>VLOOKUP(F209,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H209">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -25875,8 +26710,12 @@
         <f>VLOOKUP(F210,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H210">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -25894,8 +26733,12 @@
         <f>VLOOKUP(F211,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H211">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -25913,8 +26756,12 @@
         <f>VLOOKUP(F212,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H212">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -25932,8 +26779,12 @@
         <f>VLOOKUP(F213,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H213">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -25951,8 +26802,12 @@
         <f>VLOOKUP(F214,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H214">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -25970,8 +26825,12 @@
         <f>VLOOKUP(F215,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H215">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -25989,8 +26848,12 @@
         <f>VLOOKUP(F216,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H216">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -26008,8 +26871,12 @@
         <f>VLOOKUP(F217,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H217">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -26027,8 +26894,12 @@
         <f>VLOOKUP(F218,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H218">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -26046,8 +26917,12 @@
         <f>VLOOKUP(F219,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H219">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -26065,8 +26940,12 @@
         <f>VLOOKUP(F220,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H220">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -26084,8 +26963,12 @@
         <f>VLOOKUP(F221,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H221">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -26103,8 +26986,12 @@
         <f>VLOOKUP(F222,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H222">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -26122,8 +27009,12 @@
         <f>VLOOKUP(F223,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H223">
+        <f t="shared" ref="H223:H274" si="4">H216+1</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -26141,8 +27032,12 @@
         <f>VLOOKUP(F224,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H224">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -26160,8 +27055,12 @@
         <f>VLOOKUP(F225,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H225">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -26179,8 +27078,12 @@
         <f>VLOOKUP(F226,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H226">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -26198,8 +27101,12 @@
         <f>VLOOKUP(F227,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H227">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -26217,8 +27124,12 @@
         <f>VLOOKUP(F228,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H228">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -26236,8 +27147,12 @@
         <f>VLOOKUP(F229,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H229">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -26255,8 +27170,12 @@
         <f>VLOOKUP(F230,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H230">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -26274,8 +27193,12 @@
         <f>VLOOKUP(F231,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H231">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -26293,8 +27216,12 @@
         <f>VLOOKUP(F232,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H232">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -26312,8 +27239,12 @@
         <f>VLOOKUP(F233,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H233">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -26331,8 +27262,12 @@
         <f>VLOOKUP(F234,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H234">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -26350,8 +27285,12 @@
         <f>VLOOKUP(F235,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H235">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -26369,8 +27308,12 @@
         <f>VLOOKUP(F236,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H236">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -26388,8 +27331,12 @@
         <f>VLOOKUP(F237,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H237">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -26407,8 +27354,12 @@
         <f>VLOOKUP(F238,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H238">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -26426,8 +27377,12 @@
         <f>VLOOKUP(F239,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H239">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -26445,8 +27400,12 @@
         <f>VLOOKUP(F240,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H240">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -26464,8 +27423,12 @@
         <f>VLOOKUP(F241,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H241">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -26483,8 +27446,12 @@
         <f>VLOOKUP(F242,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H242">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -26502,8 +27469,12 @@
         <f>VLOOKUP(F243,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H243">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -26521,8 +27492,12 @@
         <f>VLOOKUP(F244,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H244">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -26540,8 +27515,12 @@
         <f>VLOOKUP(F245,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H245">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -26559,8 +27538,12 @@
         <f>VLOOKUP(F246,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H246">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -26578,8 +27561,12 @@
         <f>VLOOKUP(F247,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H247">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -26597,8 +27584,12 @@
         <f>VLOOKUP(F248,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H248">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -26616,8 +27607,12 @@
         <f>VLOOKUP(F249,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H249">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -26635,8 +27630,12 @@
         <f>VLOOKUP(F250,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H250">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -26654,8 +27653,12 @@
         <f>VLOOKUP(F251,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H251">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -26673,8 +27676,12 @@
         <f>VLOOKUP(F252,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H252">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -26692,8 +27699,12 @@
         <f>VLOOKUP(F253,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H253">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -26711,8 +27722,12 @@
         <f>VLOOKUP(F254,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H254">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -26730,8 +27745,12 @@
         <f>VLOOKUP(F255,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H255">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -26749,8 +27768,12 @@
         <f>VLOOKUP(F256,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H256">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -26768,8 +27791,12 @@
         <f>VLOOKUP(F257,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H257">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -26787,8 +27814,12 @@
         <f>VLOOKUP(F258,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H258">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -26806,8 +27837,12 @@
         <f>VLOOKUP(F259,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H259">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -26825,8 +27860,12 @@
         <f>VLOOKUP(F260,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H260">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -26844,8 +27883,12 @@
         <f>VLOOKUP(F261,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H261">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -26863,8 +27906,12 @@
         <f>VLOOKUP(F262,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H262">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -26882,8 +27929,12 @@
         <f>VLOOKUP(F263,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H263">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -26901,8 +27952,12 @@
         <f>VLOOKUP(F264,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H264">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -26920,8 +27975,12 @@
         <f>VLOOKUP(F265,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H265">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -26939,8 +27998,12 @@
         <f>VLOOKUP(F266,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H266">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -26958,8 +28021,12 @@
         <f>VLOOKUP(F267,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H267">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -26977,8 +28044,12 @@
         <f>VLOOKUP(F268,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H268">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -26996,8 +28067,12 @@
         <f>VLOOKUP(F269,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H269">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -27015,8 +28090,12 @@
         <f>VLOOKUP(F270,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H270">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -27034,8 +28113,12 @@
         <f>VLOOKUP(F271,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H271">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -27053,8 +28136,12 @@
         <f>VLOOKUP(F272,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H272">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -27072,8 +28159,12 @@
         <f>VLOOKUP(F273,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H273">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -27090,6 +28181,10 @@
       <c r="G274" t="str">
         <f>VLOOKUP(F274,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H274">
+        <f t="shared" si="4"/>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -16611,7 +16611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17505,35 +17505,19 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="F31" t="n">
-        <v>9250000</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+        <v>1000000</v>
       </c>
       <c r="L31">
-        <f>VLOOKUP(B31,players!A:B,2)</f>
+        <f>VLOOKUP(B32,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -17542,50 +17526,69 @@
         <v>14</v>
       </c>
       <c r="B32" t="n">
-        <v>259</v>
+        <v>415</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>1000000</v>
+        <v>3800000</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="L32">
-        <f>VLOOKUP(B32,players!A:B,2)</f>
+        <f>VLOOKUP(B33,players!A:B,2)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>3800000</v>
+        <v>5000000</v>
       </c>
       <c r="F33" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="G33" t="inlineStr">
+        <v>5500000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="L33">
-        <f>VLOOKUP(B33,players!A:B,2)</f>
+        <f>VLOOKUP(B34,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -17594,19 +17597,19 @@
         <v>7</v>
       </c>
       <c r="B34" t="n">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="F34" t="n">
-        <v>5500000</v>
+        <v>1000000</v>
       </c>
       <c r="H34" t="n">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -17614,7 +17617,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -17622,7 +17625,7 @@
         </is>
       </c>
       <c r="L34">
-        <f>VLOOKUP(B34,players!A:B,2)</f>
+        <f>VLOOKUP(B35,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -17631,10 +17634,10 @@
         <v>7</v>
       </c>
       <c r="B35" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
         <v>1000000</v>
@@ -17659,28 +17662,28 @@
         </is>
       </c>
       <c r="L35">
-        <f>VLOOKUP(B35,players!A:B,2)</f>
+        <f>VLOOKUP(B36,players!A:B,2)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" t="n">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D36" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="F36" t="n">
-        <v>1000000</v>
+        <v>7500000</v>
       </c>
       <c r="H36" t="n">
-        <v>1000000</v>
+        <v>8250000</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -17688,7 +17691,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1000000</v>
+        <v>9000000</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -17696,7 +17699,7 @@
         </is>
       </c>
       <c r="L36">
-        <f>VLOOKUP(B36,players!A:B,2)</f>
+        <f>VLOOKUP(B37,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -17705,19 +17708,19 @@
         <v>6</v>
       </c>
       <c r="B37" t="n">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="C37" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D37" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="F37" t="n">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="H37" t="n">
-        <v>8250000</v>
+        <v>1000000</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -17725,7 +17728,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>9000000</v>
+        <v>1000000</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -17733,44 +17736,118 @@
         </is>
       </c>
       <c r="L37">
-        <f>VLOOKUP(B37,players!A:B,2)</f>
+        <f>VLOOKUP(B38,players!A:B,2)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B38" t="n">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="C38" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D38" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L38">
+        <f>VLOOKUP(B195,players!A:B,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>13</v>
+      </c>
+      <c r="B39" t="n">
+        <v>440</v>
+      </c>
+      <c r="C39" t="n">
+        <v>14</v>
+      </c>
+      <c r="D39" t="n">
         <v>1000000</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F39" t="n">
         <v>1000000</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H39" t="n">
         <v>1000000</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>1000000</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="L38">
-        <f>VLOOKUP(B38,players!A:B,2)</f>
+      <c r="L39">
+        <f>VLOOKUP(B181,players!A:B,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" t="n">
+        <v>430</v>
+      </c>
+      <c r="C40" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L40">
+        <f>VLOOKUP(B180,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -28658,7 +28735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30458,6 +30535,42 @@
       </c>
       <c r="J46" t="n">
         <v>44</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MOVE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>26_27</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>13</v>
+      </c>
+      <c r="F47" t="n">
+        <v>13</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>admin@auction.local</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -30471,7 +30584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33607,6 +33720,134 @@
         </is>
       </c>
       <c r="H86" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>45</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>426</v>
+      </c>
+      <c r="E87" t="n">
+        <v>13</v>
+      </c>
+      <c r="F87" t="n">
+        <v>13</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>45</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>440</v>
+      </c>
+      <c r="E88" t="n">
+        <v>13</v>
+      </c>
+      <c r="F88" t="n">
+        <v>13</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>45</v>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>430</v>
+      </c>
+      <c r="E89" t="n">
+        <v>13</v>
+      </c>
+      <c r="F89" t="n">
+        <v>13</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>45</v>
+      </c>
+      <c r="B90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>241</v>
+      </c>
+      <c r="E90" t="n">
+        <v>13</v>
+      </c>
+      <c r="F90" t="n">
+        <v>13</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t>MAIN</t>
         </is>
@@ -33623,7 +33864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37493,75 +37734,31 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B180" t="n">
-        <v>430</v>
+        <v>317</v>
       </c>
       <c r="C180" t="n">
-        <v>13</v>
-      </c>
-      <c r="D180" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="F180" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="H180" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J180" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L180">
-        <f>VLOOKUP(B180,players!A:B,2)</f>
+        <f>VLOOKUP(B182,players!A:B,2)</f>
         <v/>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B181" t="n">
-        <v>440</v>
+        <v>299</v>
       </c>
       <c r="C181" t="n">
-        <v>14</v>
-      </c>
-      <c r="D181" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F181" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="H181" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J181" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="L181">
-        <f>VLOOKUP(B181,players!A:B,2)</f>
+        <f>VLOOKUP(B183,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37570,13 +37767,13 @@
         <v>14</v>
       </c>
       <c r="B182" t="n">
-        <v>317</v>
+        <v>129</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L182">
-        <f>VLOOKUP(B182,players!A:B,2)</f>
+        <f>VLOOKUP(B184,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37585,13 +37782,13 @@
         <v>14</v>
       </c>
       <c r="B183" t="n">
-        <v>299</v>
+        <v>90</v>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L183">
-        <f>VLOOKUP(B183,players!A:B,2)</f>
+        <f>VLOOKUP(B185,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37600,13 +37797,16 @@
         <v>14</v>
       </c>
       <c r="B184" t="n">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1000000</v>
       </c>
       <c r="L184">
-        <f>VLOOKUP(B184,players!A:B,2)</f>
+        <f>VLOOKUP(B186,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37615,13 +37815,16 @@
         <v>14</v>
       </c>
       <c r="B185" t="n">
-        <v>90</v>
+        <v>238</v>
       </c>
       <c r="C185" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="D185" t="n">
+        <v>3000000</v>
       </c>
       <c r="L185">
-        <f>VLOOKUP(B185,players!A:B,2)</f>
+        <f>VLOOKUP(B187,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37630,16 +37833,22 @@
         <v>14</v>
       </c>
       <c r="B186" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C186" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D186" t="n">
-        <v>1000000</v>
+        <v>20500000</v>
+      </c>
+      <c r="F186" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="H186" t="n">
+        <v>20500000</v>
       </c>
       <c r="L186">
-        <f>VLOOKUP(B186,players!A:B,2)</f>
+        <f>VLOOKUP(B188,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37648,16 +37857,16 @@
         <v>14</v>
       </c>
       <c r="B187" t="n">
-        <v>238</v>
+        <v>73</v>
       </c>
       <c r="C187" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D187" t="n">
-        <v>3000000</v>
+        <v>19500000</v>
       </c>
       <c r="L187">
-        <f>VLOOKUP(B187,players!A:B,2)</f>
+        <f>VLOOKUP(B189,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37666,22 +37875,32 @@
         <v>14</v>
       </c>
       <c r="B188" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="C188" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D188" t="n">
-        <v>20500000</v>
+        <v>9500000</v>
       </c>
       <c r="F188" t="n">
-        <v>20500000</v>
+        <v>10500000</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="H188" t="n">
-        <v>20500000</v>
+        <v>11500000</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="L188">
-        <f>VLOOKUP(B188,players!A:B,2)</f>
+        <f>VLOOKUP(B190,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37690,16 +37909,13 @@
         <v>14</v>
       </c>
       <c r="B189" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="C189" t="n">
-        <v>8</v>
-      </c>
-      <c r="D189" t="n">
-        <v>19500000</v>
+        <v>10</v>
       </c>
       <c r="L189">
-        <f>VLOOKUP(B189,players!A:B,2)</f>
+        <f>VLOOKUP(B191,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37708,32 +37924,13 @@
         <v>14</v>
       </c>
       <c r="B190" t="n">
-        <v>61</v>
+        <v>220</v>
       </c>
       <c r="C190" t="n">
-        <v>9</v>
-      </c>
-      <c r="D190" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="F190" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H190" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="L190">
-        <f>VLOOKUP(B190,players!A:B,2)</f>
+        <f>VLOOKUP(B192,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37742,13 +37939,22 @@
         <v>14</v>
       </c>
       <c r="B191" t="n">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="C191" t="n">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D191" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="F191" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="H191" t="n">
+        <v>20000000</v>
       </c>
       <c r="L191">
-        <f>VLOOKUP(B191,players!A:B,2)</f>
+        <f>VLOOKUP(B193,players!A:B,2)</f>
         <v/>
       </c>
     </row>
@@ -37757,132 +37963,90 @@
         <v>14</v>
       </c>
       <c r="B192" t="n">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="C192" t="n">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="D192" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="F192" t="n">
+        <v>3500000</v>
       </c>
       <c r="L192">
-        <f>VLOOKUP(B192,players!A:B,2)</f>
+        <f>VLOOKUP(B194,players!A:B,2)</f>
         <v/>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B193" t="n">
-        <v>145</v>
+        <v>434</v>
       </c>
       <c r="C193" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D193" t="n">
-        <v>20000000</v>
+        <v>1000000</v>
       </c>
       <c r="F193" t="n">
-        <v>20000000</v>
+        <v>1000000</v>
       </c>
       <c r="H193" t="n">
-        <v>20000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="L193">
-        <f>VLOOKUP(B193,players!A:B,2)</f>
+        <f>VLOOKUP(B196,players!A:B,2)</f>
         <v/>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B194" t="n">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="C194" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>3200000</v>
+        <v>8500000</v>
       </c>
       <c r="F194" t="n">
-        <v>3500000</v>
+        <v>9250000</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="L194">
-        <f>VLOOKUP(B194,players!A:B,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>13</v>
-      </c>
-      <c r="B195" t="n">
-        <v>426</v>
-      </c>
-      <c r="C195" t="n">
-        <v>14</v>
-      </c>
-      <c r="D195" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="F195" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="H195" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J195" t="n">
-        <v>4100000</v>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="L195">
-        <f>VLOOKUP(B195,players!A:B,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>7</v>
-      </c>
-      <c r="B196" t="n">
-        <v>434</v>
-      </c>
-      <c r="C196" t="n">
-        <v>15</v>
-      </c>
-      <c r="D196" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F196" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="H196" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J196" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="L196">
-        <f>VLOOKUP(B196,players!A:B,2)</f>
+        <f>VLOOKUP(B31,players!A:B,2)</f>
         <v/>
       </c>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_74BB96416BE38E46CF7F0B9A45DA4DD825CFB4FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECF8EF0F-9966-474E-AC19-C93A4AA0B3CB}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_74BB96416BE38E46CF7F0B9A45DA4DD825CFB4FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C32F924B-9827-488C-9ECD-C1DD6163C37A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -2245,6 +2245,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -28071,7 +28075,7 @@
         <v>Franca Celtics</v>
       </c>
       <c r="H265">
-        <f t="shared" ref="H265:H328" si="4">H258+1</f>
+        <f t="shared" ref="H265:H274" si="4">H258+1</f>
         <v>38</v>
       </c>
     </row>
@@ -32168,7 +32172,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -35907,8 +35911,8 @@
         <v>1</v>
       </c>
       <c r="L180" t="str">
-        <f>VLOOKUP(B182,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <f>VLOOKUP(B180,players!A:B,2)</f>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -35922,8 +35926,8 @@
         <v>2</v>
       </c>
       <c r="L181" t="str">
-        <f>VLOOKUP(B183,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <f>VLOOKUP(B181,players!A:B,2)</f>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -35937,8 +35941,8 @@
         <v>3</v>
       </c>
       <c r="L182" t="str">
-        <f>VLOOKUP(B184,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <f>VLOOKUP(B182,players!A:B,2)</f>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -35952,8 +35956,8 @@
         <v>4</v>
       </c>
       <c r="L183" t="str">
-        <f>VLOOKUP(B185,players!A:B,2)</f>
-        <v>Coby White</v>
+        <f>VLOOKUP(B183,players!A:B,2)</f>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -35970,8 +35974,8 @@
         <v>1000000</v>
       </c>
       <c r="L184" t="str">
-        <f>VLOOKUP(B186,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <f>VLOOKUP(B184,players!A:B,2)</f>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -35988,8 +35992,8 @@
         <v>3000000</v>
       </c>
       <c r="L185" t="str">
-        <f>VLOOKUP(B187,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <f>VLOOKUP(B185,players!A:B,2)</f>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -36012,8 +36016,8 @@
         <v>20500000</v>
       </c>
       <c r="L186" t="str">
-        <f>VLOOKUP(B188,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <f>VLOOKUP(B186,players!A:B,2)</f>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -36030,8 +36034,8 @@
         <v>19500000</v>
       </c>
       <c r="L187" t="str">
-        <f>VLOOKUP(B189,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <f>VLOOKUP(B187,players!A:B,2)</f>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -36060,8 +36064,8 @@
         <v>599</v>
       </c>
       <c r="L188" t="str">
-        <f>VLOOKUP(B190,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <f>VLOOKUP(B188,players!A:B,2)</f>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -36075,8 +36079,8 @@
         <v>10</v>
       </c>
       <c r="L189" t="str">
-        <f>VLOOKUP(B191,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <f>VLOOKUP(B189,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -36090,8 +36094,8 @@
         <v>11</v>
       </c>
       <c r="L190" t="str">
-        <f>VLOOKUP(B192,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <f>VLOOKUP(B190,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -36114,8 +36118,8 @@
         <v>20000000</v>
       </c>
       <c r="L191" t="str">
-        <f>VLOOKUP(B193,players!A:B,2)</f>
-        <v>Allen Graves</v>
+        <f>VLOOKUP(B191,players!A:B,2)</f>
+        <v>LaMelo Ball</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -36135,8 +36139,8 @@
         <v>3500000</v>
       </c>
       <c r="L192" t="str">
-        <f>VLOOKUP(B194,players!A:B,2)</f>
-        <v>Dylan Harper</v>
+        <f>VLOOKUP(B192,players!A:B,2)</f>
+        <v>Cason Wallace</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -36167,9 +36171,9 @@
       <c r="K193" t="s">
         <v>599</v>
       </c>
-      <c r="L193" t="e">
-        <f>VLOOKUP(B196,players!A:B,2)</f>
-        <v>#N/A</v>
+      <c r="L193" t="str">
+        <f>VLOOKUP(B193,players!A:B,2)</f>
+        <v>Allen Graves</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -36198,8 +36202,32 @@
         <v>599</v>
       </c>
       <c r="L194" t="str">
-        <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Hannes Steinbach</v>
+        <f>VLOOKUP(B194,players!A:B,2)</f>
+        <v>Dylan Harper</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>13</v>
+      </c>
+      <c r="B195">
+        <v>121</v>
+      </c>
+      <c r="C195">
+        <v>14</v>
+      </c>
+      <c r="D195">
+        <v>3100000</v>
+      </c>
+      <c r="F195">
+        <v>3100000</v>
+      </c>
+      <c r="H195">
+        <v>3100000</v>
+      </c>
+      <c r="L195" t="str">
+        <f>VLOOKUP(B195,players!A:B,2)</f>
+        <v>Toumani Camara</v>
       </c>
     </row>
   </sheetData>
